--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0252533B-725D-43C8-850A-4FC45D9F3A2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E2A71-F740-46E2-9725-BC23427B07BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="324">
   <si>
     <t>Status</t>
   </si>
@@ -48,295 +48,961 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>834695235</t>
+    <t>817723418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>735814703</t>
+  </si>
+  <si>
+    <t>705577264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>840108991</t>
+  </si>
+  <si>
+    <t>655586398</t>
+  </si>
+  <si>
+    <t>736733662</t>
+  </si>
+  <si>
+    <t>682018175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>673446799</t>
+  </si>
+  <si>
+    <t>883934212</t>
+  </si>
+  <si>
+    <t>852501349</t>
+  </si>
+  <si>
+    <t>842762316</t>
+  </si>
+  <si>
+    <t>807424472</t>
+  </si>
+  <si>
+    <t>805465196</t>
+  </si>
+  <si>
+    <t>839879511</t>
+  </si>
+  <si>
+    <t>824725406</t>
+  </si>
+  <si>
+    <t>806806141</t>
+  </si>
+  <si>
+    <t>816003184</t>
+  </si>
+  <si>
+    <t>714295957</t>
+  </si>
+  <si>
+    <t>783710985</t>
+  </si>
+  <si>
+    <t>783061173</t>
+  </si>
+  <si>
+    <t>742310562</t>
+  </si>
+  <si>
+    <t>756551093</t>
+  </si>
+  <si>
+    <t>755622010</t>
+  </si>
+  <si>
+    <t>740841493</t>
+  </si>
+  <si>
+    <t>715883033</t>
+  </si>
+  <si>
+    <t>883849469</t>
+  </si>
+  <si>
+    <t>671928384</t>
+  </si>
+  <si>
+    <t>885079099</t>
+  </si>
+  <si>
+    <t>884946660</t>
+  </si>
+  <si>
+    <t>884361522</t>
+  </si>
+  <si>
+    <t>884108907</t>
+  </si>
+  <si>
+    <t>884093943</t>
+  </si>
+  <si>
+    <t>883648473</t>
+  </si>
+  <si>
+    <t>883087102</t>
+  </si>
+  <si>
+    <t>882801974</t>
+  </si>
+  <si>
+    <t>881345304</t>
+  </si>
+  <si>
+    <t>881345296</t>
+  </si>
+  <si>
+    <t>851688576</t>
+  </si>
+  <si>
+    <t>880677582</t>
+  </si>
+  <si>
+    <t>880566066</t>
+  </si>
+  <si>
+    <t>878674211</t>
+  </si>
+  <si>
+    <t>873258184</t>
+  </si>
+  <si>
+    <t>868791108</t>
+  </si>
+  <si>
+    <t>870995531</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>837918873</t>
-  </si>
-  <si>
-    <t>848045245</t>
-  </si>
-  <si>
-    <t>797451774</t>
-  </si>
-  <si>
-    <t>751707534</t>
-  </si>
-  <si>
-    <t>779949969</t>
-  </si>
-  <si>
-    <t>782164853</t>
-  </si>
-  <si>
-    <t>751698311</t>
-  </si>
-  <si>
-    <t>681509224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>688336605</t>
-  </si>
-  <si>
-    <t>644764858</t>
-  </si>
-  <si>
-    <t>855051094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>700928488</t>
-  </si>
-  <si>
-    <t>740194943</t>
-  </si>
-  <si>
-    <t>749808659</t>
-  </si>
-  <si>
-    <t>725484665</t>
-  </si>
-  <si>
-    <t>818026522</t>
-  </si>
-  <si>
-    <t>815876457</t>
-  </si>
-  <si>
-    <t>732119791</t>
-  </si>
-  <si>
-    <t>738735129</t>
-  </si>
-  <si>
-    <t>774557551</t>
-  </si>
-  <si>
-    <t>691673887</t>
-  </si>
-  <si>
-    <t>806333427</t>
-  </si>
-  <si>
-    <t>808416402</t>
-  </si>
-  <si>
-    <t>857538999</t>
-  </si>
-  <si>
-    <t>856119239</t>
-  </si>
-  <si>
-    <t>824294403</t>
-  </si>
-  <si>
-    <t>840240786</t>
-  </si>
-  <si>
-    <t>791818853</t>
-  </si>
-  <si>
-    <t>797790932</t>
-  </si>
-  <si>
-    <t>788571606</t>
-  </si>
-  <si>
-    <t>673564005</t>
-  </si>
-  <si>
-    <t>814206094</t>
-  </si>
-  <si>
-    <t>861919151</t>
-  </si>
-  <si>
-    <t>841965746</t>
-  </si>
-  <si>
-    <t>826897401</t>
-  </si>
-  <si>
-    <t>823850783</t>
-  </si>
-  <si>
-    <t>855083642</t>
-  </si>
-  <si>
-    <t>854046152</t>
-  </si>
-  <si>
-    <t>851751234</t>
-  </si>
-  <si>
-    <t>851137608</t>
-  </si>
-  <si>
-    <t>848210575</t>
-  </si>
-  <si>
-    <t>795738735</t>
-  </si>
-  <si>
-    <t>854080623</t>
-  </si>
-  <si>
-    <t>743983920</t>
-  </si>
-  <si>
-    <t>774025302</t>
-  </si>
-  <si>
-    <t>819946868</t>
-  </si>
-  <si>
-    <t>172084893</t>
-  </si>
-  <si>
-    <t>805805987</t>
-  </si>
-  <si>
-    <t>805882028</t>
-  </si>
-  <si>
-    <t>818009213</t>
-  </si>
-  <si>
-    <t>809156502</t>
-  </si>
-  <si>
-    <t>807085398</t>
-  </si>
-  <si>
-    <t>780166561</t>
-  </si>
-  <si>
-    <t>679010664</t>
-  </si>
-  <si>
-    <t>667172369</t>
-  </si>
-  <si>
-    <t>670149479</t>
-  </si>
-  <si>
-    <t>772511436</t>
-  </si>
-  <si>
-    <t>768607677</t>
-  </si>
-  <si>
-    <t>810968655</t>
-  </si>
-  <si>
-    <t>783639838</t>
-  </si>
-  <si>
-    <t>666798719</t>
-  </si>
-  <si>
-    <t>694884895</t>
-  </si>
-  <si>
-    <t>698224965</t>
-  </si>
-  <si>
-    <t>775110491</t>
-  </si>
-  <si>
-    <t>807393107</t>
-  </si>
-  <si>
-    <t>864571348</t>
-  </si>
-  <si>
-    <t>854009093</t>
-  </si>
-  <si>
-    <t>820568636</t>
-  </si>
-  <si>
-    <t>833357522</t>
-  </si>
-  <si>
-    <t>803750813</t>
-  </si>
-  <si>
-    <t>800435079</t>
-  </si>
-  <si>
-    <t>764401968</t>
-  </si>
-  <si>
-    <t>843168257</t>
-  </si>
-  <si>
-    <t>821416108</t>
-  </si>
-  <si>
-    <t>822966069</t>
-  </si>
-  <si>
-    <t>798315044</t>
-  </si>
-  <si>
-    <t>802943047</t>
-  </si>
-  <si>
-    <t>763493594</t>
-  </si>
-  <si>
-    <t>780260000</t>
-  </si>
-  <si>
-    <t>747742512</t>
-  </si>
-  <si>
-    <t>729532170</t>
-  </si>
-  <si>
-    <t>747391708</t>
-  </si>
-  <si>
-    <t>798895839</t>
-  </si>
-  <si>
-    <t>812684318</t>
-  </si>
-  <si>
-    <t>818296471</t>
-  </si>
-  <si>
-    <t>818071429</t>
-  </si>
-  <si>
-    <t>815554872</t>
-  </si>
-  <si>
-    <t>858620325</t>
-  </si>
-  <si>
-    <t>776703526</t>
-  </si>
-  <si>
-    <t>876233820</t>
-  </si>
-  <si>
-    <t>769824883</t>
-  </si>
-  <si>
-    <t>856003672</t>
-  </si>
-  <si>
-    <t>719596565</t>
+    <t>766140978</t>
+  </si>
+  <si>
+    <t>699073031</t>
+  </si>
+  <si>
+    <t>867179909</t>
+  </si>
+  <si>
+    <t>848988683</t>
+  </si>
+  <si>
+    <t>830972984</t>
+  </si>
+  <si>
+    <t>867203329</t>
+  </si>
+  <si>
+    <t>762728990</t>
+  </si>
+  <si>
+    <t>875609020</t>
+  </si>
+  <si>
+    <t>875156840</t>
+  </si>
+  <si>
+    <t>794658223</t>
+  </si>
+  <si>
+    <t>855051318</t>
+  </si>
+  <si>
+    <t>845558778</t>
+  </si>
+  <si>
+    <t>787068232</t>
+  </si>
+  <si>
+    <t>725869154</t>
+  </si>
+  <si>
+    <t>723772830</t>
+  </si>
+  <si>
+    <t>688720667</t>
+  </si>
+  <si>
+    <t>844955041</t>
+  </si>
+  <si>
+    <t>849233246</t>
+  </si>
+  <si>
+    <t>802896948</t>
+  </si>
+  <si>
+    <t>817637352</t>
+  </si>
+  <si>
+    <t>785468517</t>
+  </si>
+  <si>
+    <t>773929389</t>
+  </si>
+  <si>
+    <t>875639829</t>
+  </si>
+  <si>
+    <t>739823361</t>
+  </si>
+  <si>
+    <t>848889246</t>
+  </si>
+  <si>
+    <t>810987770</t>
+  </si>
+  <si>
+    <t>804569485</t>
+  </si>
+  <si>
+    <t>867959375</t>
+  </si>
+  <si>
+    <t>171859972</t>
+  </si>
+  <si>
+    <t>657825489</t>
+  </si>
+  <si>
+    <t>650853009</t>
+  </si>
+  <si>
+    <t>621943558</t>
+  </si>
+  <si>
+    <t>175714009</t>
+  </si>
+  <si>
+    <t>174948277</t>
+  </si>
+  <si>
+    <t>174765861</t>
+  </si>
+  <si>
+    <t>174650535</t>
+  </si>
+  <si>
+    <t>863769315</t>
+  </si>
+  <si>
+    <t>863489583</t>
+  </si>
+  <si>
+    <t>863489468</t>
+  </si>
+  <si>
+    <t>862506668</t>
+  </si>
+  <si>
+    <t>862503012</t>
+  </si>
+  <si>
+    <t>861238172</t>
+  </si>
+  <si>
+    <t>859358610</t>
+  </si>
+  <si>
+    <t>857953362</t>
+  </si>
+  <si>
+    <t>855900571</t>
+  </si>
+  <si>
+    <t>844685119</t>
+  </si>
+  <si>
+    <t>845633506</t>
+  </si>
+  <si>
+    <t>848173351</t>
+  </si>
+  <si>
+    <t>846602880</t>
+  </si>
+  <si>
+    <t>842337531</t>
+  </si>
+  <si>
+    <t>840938470</t>
+  </si>
+  <si>
+    <t>836900989</t>
+  </si>
+  <si>
+    <t>835406160</t>
+  </si>
+  <si>
+    <t>832045409</t>
+  </si>
+  <si>
+    <t>830871756</t>
+  </si>
+  <si>
+    <t>826219036</t>
+  </si>
+  <si>
+    <t>825839685</t>
+  </si>
+  <si>
+    <t>825024296</t>
+  </si>
+  <si>
+    <t>823193655</t>
+  </si>
+  <si>
+    <t>820622219</t>
+  </si>
+  <si>
+    <t>803496557</t>
+  </si>
+  <si>
+    <t>804567836</t>
+  </si>
+  <si>
+    <t>802129704</t>
+  </si>
+  <si>
+    <t>795481245</t>
+  </si>
+  <si>
+    <t>794300735</t>
+  </si>
+  <si>
+    <t>787551476</t>
+  </si>
+  <si>
+    <t>740048594</t>
+  </si>
+  <si>
+    <t>685930111</t>
+  </si>
+  <si>
+    <t>693158838</t>
+  </si>
+  <si>
+    <t>692457694</t>
+  </si>
+  <si>
+    <t>691157899</t>
+  </si>
+  <si>
+    <t>690229004</t>
+  </si>
+  <si>
+    <t>688823768</t>
+  </si>
+  <si>
+    <t>682452416</t>
+  </si>
+  <si>
+    <t>680105222</t>
+  </si>
+  <si>
+    <t>773016534</t>
+  </si>
+  <si>
+    <t>786945760</t>
+  </si>
+  <si>
+    <t>786909485</t>
+  </si>
+  <si>
+    <t>786766133</t>
+  </si>
+  <si>
+    <t>774891679</t>
+  </si>
+  <si>
+    <t>738933377</t>
+  </si>
+  <si>
+    <t>735230991</t>
+  </si>
+  <si>
+    <t>734227857</t>
+  </si>
+  <si>
+    <t>714167487</t>
+  </si>
+  <si>
+    <t>710907647</t>
+  </si>
+  <si>
+    <t>710550306</t>
+  </si>
+  <si>
+    <t>705697492</t>
+  </si>
+  <si>
+    <t>705490344</t>
+  </si>
+  <si>
+    <t>704406457</t>
+  </si>
+  <si>
+    <t>699803452</t>
+  </si>
+  <si>
+    <t>695124614</t>
+  </si>
+  <si>
+    <t>697050122</t>
+  </si>
+  <si>
+    <t>668649720</t>
+  </si>
+  <si>
+    <t>685108098</t>
+  </si>
+  <si>
+    <t>685609244</t>
+  </si>
+  <si>
+    <t>685377727</t>
+  </si>
+  <si>
+    <t>663487654</t>
+  </si>
+  <si>
+    <t>792405452</t>
+  </si>
+  <si>
+    <t>823316397</t>
+  </si>
+  <si>
+    <t>829591647</t>
+  </si>
+  <si>
+    <t>838804239</t>
+  </si>
+  <si>
+    <t>835207568</t>
+  </si>
+  <si>
+    <t>827253752</t>
+  </si>
+  <si>
+    <t>818804613</t>
+  </si>
+  <si>
+    <t>814251546</t>
+  </si>
+  <si>
+    <t>813347584</t>
+  </si>
+  <si>
+    <t>812775355</t>
+  </si>
+  <si>
+    <t>861854903</t>
+  </si>
+  <si>
+    <t>637988332</t>
+  </si>
+  <si>
+    <t>866744711</t>
+  </si>
+  <si>
+    <t>874438009</t>
+  </si>
+  <si>
+    <t>874013935</t>
+  </si>
+  <si>
+    <t>862168287</t>
+  </si>
+  <si>
+    <t>855902338</t>
+  </si>
+  <si>
+    <t>802903413</t>
+  </si>
+  <si>
+    <t>886152564</t>
+  </si>
+  <si>
+    <t>886128978</t>
+  </si>
+  <si>
+    <t>885854145</t>
+  </si>
+  <si>
+    <t>885145791</t>
+  </si>
+  <si>
+    <t>884705181</t>
+  </si>
+  <si>
+    <t>884287792</t>
+  </si>
+  <si>
+    <t>883861290</t>
+  </si>
+  <si>
+    <t>883848214</t>
+  </si>
+  <si>
+    <t>883750519</t>
+  </si>
+  <si>
+    <t>883740437</t>
+  </si>
+  <si>
+    <t>882987344</t>
+  </si>
+  <si>
+    <t>882765823</t>
+  </si>
+  <si>
+    <t>882556206</t>
+  </si>
+  <si>
+    <t>881459790</t>
+  </si>
+  <si>
+    <t>879768582</t>
+  </si>
+  <si>
+    <t>878737471</t>
+  </si>
+  <si>
+    <t>878679558</t>
+  </si>
+  <si>
+    <t>878651532</t>
+  </si>
+  <si>
+    <t>878185374</t>
+  </si>
+  <si>
+    <t>877956023</t>
+  </si>
+  <si>
+    <t>877033245</t>
+  </si>
+  <si>
+    <t>876515119</t>
+  </si>
+  <si>
+    <t>876366687</t>
+  </si>
+  <si>
+    <t>876332804</t>
+  </si>
+  <si>
+    <t>875983268</t>
+  </si>
+  <si>
+    <t>875788931</t>
+  </si>
+  <si>
+    <t>875713566</t>
+  </si>
+  <si>
+    <t>875286803</t>
+  </si>
+  <si>
+    <t>767978467</t>
+  </si>
+  <si>
+    <t>775386646</t>
+  </si>
+  <si>
+    <t>784918389</t>
+  </si>
+  <si>
+    <t>782292647</t>
+  </si>
+  <si>
+    <t>777924600</t>
+  </si>
+  <si>
+    <t>775350097</t>
+  </si>
+  <si>
+    <t>763707191</t>
+  </si>
+  <si>
+    <t>762420614</t>
+  </si>
+  <si>
+    <t>733583680</t>
+  </si>
+  <si>
+    <t>732707884</t>
+  </si>
+  <si>
+    <t>698545542</t>
+  </si>
+  <si>
+    <t>697200917</t>
+  </si>
+  <si>
+    <t>681966333</t>
+  </si>
+  <si>
+    <t>686394572</t>
+  </si>
+  <si>
+    <t>677552477</t>
+  </si>
+  <si>
+    <t>675763761</t>
+  </si>
+  <si>
+    <t>875603726</t>
+  </si>
+  <si>
+    <t>659931046</t>
+  </si>
+  <si>
+    <t>177306531</t>
+  </si>
+  <si>
+    <t>866051083</t>
+  </si>
+  <si>
+    <t>859605960</t>
+  </si>
+  <si>
+    <t>858854015</t>
+  </si>
+  <si>
+    <t>797668237</t>
+  </si>
+  <si>
+    <t>853626731</t>
+  </si>
+  <si>
+    <t>724033869</t>
+  </si>
+  <si>
+    <t>690405034</t>
+  </si>
+  <si>
+    <t>669644027</t>
+  </si>
+  <si>
+    <t>668196243</t>
+  </si>
+  <si>
+    <t>653366496</t>
+  </si>
+  <si>
+    <t>659498798</t>
+  </si>
+  <si>
+    <t>663151169</t>
+  </si>
+  <si>
+    <t>661952717</t>
+  </si>
+  <si>
+    <t>815099951</t>
+  </si>
+  <si>
+    <t>826735064</t>
+  </si>
+  <si>
+    <t>836801948</t>
+  </si>
+  <si>
+    <t>813859661</t>
+  </si>
+  <si>
+    <t>807790658</t>
+  </si>
+  <si>
+    <t>844316392</t>
+  </si>
+  <si>
+    <t>850095229</t>
+  </si>
+  <si>
+    <t>848432856</t>
+  </si>
+  <si>
+    <t>804023996</t>
+  </si>
+  <si>
+    <t>796584542</t>
+  </si>
+  <si>
+    <t>772761395</t>
+  </si>
+  <si>
+    <t>776136669</t>
+  </si>
+  <si>
+    <t>773287895</t>
+  </si>
+  <si>
+    <t>752712749</t>
+  </si>
+  <si>
+    <t>750470951</t>
+  </si>
+  <si>
+    <t>730831587</t>
+  </si>
+  <si>
+    <t>716452440</t>
+  </si>
+  <si>
+    <t>741123917</t>
+  </si>
+  <si>
+    <t>840035988</t>
+  </si>
+  <si>
+    <t>785286810</t>
+  </si>
+  <si>
+    <t>739685414</t>
+  </si>
+  <si>
+    <t>767665205</t>
+  </si>
+  <si>
+    <t>836000095</t>
+  </si>
+  <si>
+    <t>887761371</t>
+  </si>
+  <si>
+    <t>876251673</t>
+  </si>
+  <si>
+    <t>872907898</t>
+  </si>
+  <si>
+    <t>848343517</t>
+  </si>
+  <si>
+    <t>837398357</t>
+  </si>
+  <si>
+    <t>836758676</t>
+  </si>
+  <si>
+    <t>829632045</t>
+  </si>
+  <si>
+    <t>825431251</t>
+  </si>
+  <si>
+    <t>810815096</t>
+  </si>
+  <si>
+    <t>783106341</t>
+  </si>
+  <si>
+    <t>767072188</t>
+  </si>
+  <si>
+    <t>752080717</t>
+  </si>
+  <si>
+    <t>739568271</t>
+  </si>
+  <si>
+    <t>721121980</t>
+  </si>
+  <si>
+    <t>673086710</t>
+  </si>
+  <si>
+    <t>658921394</t>
+  </si>
+  <si>
+    <t>700612280</t>
+  </si>
+  <si>
+    <t>772468298</t>
+  </si>
+  <si>
+    <t>815364355</t>
+  </si>
+  <si>
+    <t>888111717</t>
+  </si>
+  <si>
+    <t>888003682</t>
+  </si>
+  <si>
+    <t>814659821</t>
+  </si>
+  <si>
+    <t>690176916</t>
+  </si>
+  <si>
+    <t>862944471</t>
+  </si>
+  <si>
+    <t>175180813</t>
+  </si>
+  <si>
+    <t>886909096</t>
+  </si>
+  <si>
+    <t>871503946</t>
+  </si>
+  <si>
+    <t>861234023</t>
+  </si>
+  <si>
+    <t>848045138</t>
+  </si>
+  <si>
+    <t>847826074</t>
+  </si>
+  <si>
+    <t>837696388</t>
+  </si>
+  <si>
+    <t>816638716</t>
+  </si>
+  <si>
+    <t>782070969</t>
+  </si>
+  <si>
+    <t>764401463</t>
+  </si>
+  <si>
+    <t>763385162</t>
+  </si>
+  <si>
+    <t>763385154</t>
+  </si>
+  <si>
+    <t>763107707</t>
+  </si>
+  <si>
+    <t>751754759</t>
+  </si>
+  <si>
+    <t>735416186</t>
+  </si>
+  <si>
+    <t>716284488</t>
+  </si>
+  <si>
+    <t>698729690</t>
+  </si>
+  <si>
+    <t>698256686</t>
+  </si>
+  <si>
+    <t>686227483</t>
+  </si>
+  <si>
+    <t>679367643</t>
+  </si>
+  <si>
+    <t>669989315</t>
+  </si>
+  <si>
+    <t>662514045</t>
+  </si>
+  <si>
+    <t>176168841</t>
+  </si>
+  <si>
+    <t>176168833</t>
+  </si>
+  <si>
+    <t>641418094</t>
+  </si>
+  <si>
+    <t>815738368</t>
+  </si>
+  <si>
+    <t>887430183</t>
+  </si>
+  <si>
+    <t>887577272</t>
+  </si>
+  <si>
+    <t>886072408</t>
+  </si>
+  <si>
+    <t>886037450</t>
+  </si>
+  <si>
+    <t>885829295</t>
+  </si>
+  <si>
+    <t>882361144</t>
+  </si>
+  <si>
+    <t>881734374</t>
+  </si>
+  <si>
+    <t>878523046</t>
+  </si>
+  <si>
+    <t>878113244</t>
+  </si>
+  <si>
+    <t>877803464</t>
+  </si>
+  <si>
+    <t>877345615</t>
+  </si>
+  <si>
+    <t>877221709</t>
+  </si>
+  <si>
+    <t>876997929</t>
+  </si>
+  <si>
+    <t>876856372</t>
+  </si>
+  <si>
+    <t>876839675</t>
+  </si>
+  <si>
+    <t>875802690</t>
+  </si>
+  <si>
+    <t>875488821</t>
+  </si>
+  <si>
+    <t>873295202</t>
+  </si>
+  <si>
+    <t>847800202</t>
+  </si>
+  <si>
+    <t>853560344</t>
+  </si>
+  <si>
+    <t>804851966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>625944453</t>
   </si>
 </sst>
 </file>
@@ -796,7 +1462,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D315"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -849,7 +1515,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -858,7 +1524,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -870,7 +1536,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>6</v>
@@ -882,7 +1548,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>6</v>
@@ -894,10 +1560,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -906,10 +1572,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -918,10 +1584,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -930,10 +1596,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -942,10 +1608,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -954,10 +1620,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -969,7 +1635,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -981,7 +1647,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -993,7 +1659,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1005,7 +1671,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1017,7 +1683,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1029,7 +1695,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1041,7 +1707,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1053,7 +1719,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1065,7 +1731,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1077,7 +1743,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1089,7 +1755,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1101,7 +1767,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1113,7 +1779,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1125,7 +1791,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1137,7 +1803,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1149,7 +1815,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1161,7 +1827,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1173,7 +1839,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1185,7 +1851,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1197,7 +1863,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1209,7 +1875,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1221,7 +1887,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1233,7 +1899,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1245,7 +1911,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1257,7 +1923,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1269,7 +1935,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1281,7 +1947,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1293,7 +1959,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1305,7 +1971,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1317,7 +1983,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1329,7 +1995,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1341,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1350,10 +2016,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1362,10 +2028,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1374,10 +2040,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1386,10 +2052,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>15</v>
+        <v>52</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1398,10 +2064,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1410,10 +2076,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1422,10 +2088,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1434,10 +2100,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1446,10 +2112,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1458,10 +2124,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1470,10 +2136,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1482,10 +2148,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1494,10 +2160,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1506,10 +2172,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1518,10 +2184,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1530,10 +2196,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1542,10 +2208,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1554,10 +2220,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1566,10 +2232,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1578,10 +2244,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1590,10 +2256,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1602,10 +2268,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1613,10 +2279,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1624,10 +2290,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1635,10 +2301,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1646,10 +2312,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1657,10 +2323,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1668,10 +2334,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1679,10 +2345,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1690,10 +2356,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1701,10 +2367,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1712,10 +2378,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1723,10 +2389,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1734,10 +2400,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1745,10 +2411,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1756,10 +2422,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1767,10 +2433,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1778,10 +2444,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1789,10 +2455,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1800,10 +2466,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1811,10 +2477,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -1822,10 +2488,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -1833,10 +2499,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -1844,10 +2510,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -1855,10 +2521,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -1866,10 +2532,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -1877,10 +2543,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -1888,10 +2554,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -1899,10 +2565,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -1910,12 +2576,2432 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>322</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C315" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C4D798B-A26B-47F0-B551-77B3D2C50FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4647C380-C860-4326-8BFD-4257EC4D379B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="111">
   <si>
     <t>Status</t>
   </si>
@@ -48,259 +48,322 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>875166971</t>
+    <t>859469961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>759085263</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>812283707</t>
-  </si>
-  <si>
-    <t>810854590</t>
-  </si>
-  <si>
-    <t>786755888</t>
-  </si>
-  <si>
-    <t>785783857</t>
-  </si>
-  <si>
-    <t>731280461</t>
-  </si>
-  <si>
-    <t>764046169</t>
-  </si>
-  <si>
-    <t>783546769</t>
-  </si>
-  <si>
-    <t>775936176</t>
-  </si>
-  <si>
-    <t>766258119</t>
-  </si>
-  <si>
-    <t>764560383</t>
-  </si>
-  <si>
-    <t>741103489</t>
-  </si>
-  <si>
-    <t>685070959</t>
-  </si>
-  <si>
-    <t>697859605</t>
-  </si>
-  <si>
-    <t>728966437</t>
+    <t>788188997</t>
+  </si>
+  <si>
+    <t>787118532</t>
+  </si>
+  <si>
+    <t>785246988</t>
+  </si>
+  <si>
+    <t>751645395</t>
+  </si>
+  <si>
+    <t>883778932</t>
+  </si>
+  <si>
+    <t>653653984</t>
+  </si>
+  <si>
+    <t>718779105</t>
+  </si>
+  <si>
+    <t>696697329</t>
+  </si>
+  <si>
+    <t>690716299</t>
+  </si>
+  <si>
+    <t>680815580</t>
+  </si>
+  <si>
+    <t>887767352</t>
+  </si>
+  <si>
+    <t>889037796</t>
+  </si>
+  <si>
+    <t>888585175</t>
+  </si>
+  <si>
+    <t>887607954</t>
+  </si>
+  <si>
+    <t>886146426</t>
+  </si>
+  <si>
+    <t>884101613</t>
+  </si>
+  <si>
+    <t>883454286</t>
+  </si>
+  <si>
+    <t>882745916</t>
+  </si>
+  <si>
+    <t>878092885</t>
+  </si>
+  <si>
+    <t>879817421</t>
+  </si>
+  <si>
+    <t>882685492</t>
+  </si>
+  <si>
+    <t>880914068</t>
+  </si>
+  <si>
+    <t>879321572</t>
+  </si>
+  <si>
+    <t>878690456</t>
+  </si>
+  <si>
+    <t>878170962</t>
+  </si>
+  <si>
+    <t>878142466</t>
+  </si>
+  <si>
+    <t>877104418</t>
+  </si>
+  <si>
+    <t>875752382</t>
+  </si>
+  <si>
+    <t>874548153</t>
+  </si>
+  <si>
+    <t>862057589</t>
+  </si>
+  <si>
+    <t>870744897</t>
+  </si>
+  <si>
+    <t>870298647</t>
+  </si>
+  <si>
+    <t>862460361</t>
+  </si>
+  <si>
+    <t>859649448</t>
+  </si>
+  <si>
+    <t>811342686</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>877087068</t>
-  </si>
-  <si>
-    <t>877387237</t>
-  </si>
-  <si>
-    <t>855546630</t>
+    <t>726558491</t>
+  </si>
+  <si>
+    <t>724084961</t>
+  </si>
+  <si>
+    <t>787446966</t>
+  </si>
+  <si>
+    <t>806946202</t>
+  </si>
+  <si>
+    <t>791060423</t>
+  </si>
+  <si>
+    <t>888133802</t>
+  </si>
+  <si>
+    <t>675904563</t>
+  </si>
+  <si>
+    <t>701040432</t>
+  </si>
+  <si>
+    <t>702631148</t>
+  </si>
+  <si>
+    <t>678244660</t>
+  </si>
+  <si>
+    <t>659245868</t>
+  </si>
+  <si>
+    <t>874414786</t>
+  </si>
+  <si>
+    <t>879936692</t>
+  </si>
+  <si>
+    <t>881263192</t>
+  </si>
+  <si>
+    <t>878326358</t>
+  </si>
+  <si>
+    <t>867135299</t>
+  </si>
+  <si>
+    <t>837050891</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>851161996</t>
-  </si>
-  <si>
-    <t>877495303</t>
-  </si>
-  <si>
-    <t>875121489</t>
-  </si>
-  <si>
-    <t>858540861</t>
-  </si>
-  <si>
-    <t>723129650</t>
-  </si>
-  <si>
-    <t>774052942</t>
-  </si>
-  <si>
-    <t>719708780</t>
-  </si>
-  <si>
-    <t>847022740</t>
-  </si>
-  <si>
-    <t>877708135</t>
-  </si>
-  <si>
-    <t>805315045</t>
-  </si>
-  <si>
-    <t>178873521</t>
-  </si>
-  <si>
-    <t>881324986</t>
-  </si>
-  <si>
-    <t>826861035</t>
-  </si>
-  <si>
-    <t>808441855</t>
-  </si>
-  <si>
-    <t>830071936</t>
-  </si>
-  <si>
-    <t>879028961</t>
-  </si>
-  <si>
-    <t>720276553</t>
-  </si>
-  <si>
-    <t>720276546</t>
-  </si>
-  <si>
-    <t>710696968</t>
-  </si>
-  <si>
-    <t>705184053</t>
-  </si>
-  <si>
-    <t>704677990</t>
-  </si>
-  <si>
-    <t>679744577</t>
-  </si>
-  <si>
-    <t>678651187</t>
-  </si>
-  <si>
-    <t>675350171</t>
-  </si>
-  <si>
-    <t>649293564</t>
-  </si>
-  <si>
-    <t>634535557</t>
-  </si>
-  <si>
-    <t>171844735</t>
-  </si>
-  <si>
-    <t>625947506</t>
-  </si>
-  <si>
-    <t>625944008</t>
-  </si>
-  <si>
-    <t>625941244</t>
-  </si>
-  <si>
-    <t>625938430</t>
-  </si>
-  <si>
-    <t>625937978</t>
-  </si>
-  <si>
-    <t>625937721</t>
-  </si>
-  <si>
-    <t>625937432</t>
-  </si>
-  <si>
-    <t>625936905</t>
-  </si>
-  <si>
-    <t>625936384</t>
-  </si>
-  <si>
-    <t>176223901</t>
-  </si>
-  <si>
-    <t>172434445</t>
-  </si>
-  <si>
-    <t>749109363</t>
-  </si>
-  <si>
-    <t>807856491</t>
-  </si>
-  <si>
-    <t>778071567</t>
-  </si>
-  <si>
-    <t>771541194</t>
-  </si>
-  <si>
-    <t>768194346</t>
-  </si>
-  <si>
-    <t>761372105</t>
-  </si>
-  <si>
-    <t>748369034</t>
-  </si>
-  <si>
-    <t>736569835</t>
-  </si>
-  <si>
-    <t>725904506</t>
-  </si>
-  <si>
-    <t>888829102</t>
-  </si>
-  <si>
-    <t>888460551</t>
-  </si>
-  <si>
-    <t>886244205</t>
-  </si>
-  <si>
-    <t>883619714</t>
-  </si>
-  <si>
-    <t>880006642</t>
-  </si>
-  <si>
-    <t>823211184</t>
-  </si>
-  <si>
-    <t>814383257</t>
-  </si>
-  <si>
-    <t>877914543</t>
-  </si>
-  <si>
-    <t>872292234</t>
-  </si>
-  <si>
-    <t>864528371</t>
-  </si>
-  <si>
-    <t>860097744</t>
-  </si>
-  <si>
-    <t>858877958</t>
-  </si>
-  <si>
-    <t>849798800</t>
-  </si>
-  <si>
-    <t>857176741</t>
-  </si>
-  <si>
-    <t>726197217</t>
-  </si>
-  <si>
-    <t>819514781</t>
-  </si>
-  <si>
-    <t>854301755</t>
+    <t>878144280</t>
+  </si>
+  <si>
+    <t>810285159</t>
+  </si>
+  <si>
+    <t>863841866</t>
+  </si>
+  <si>
+    <t>863264978</t>
+  </si>
+  <si>
+    <t>877220388</t>
+  </si>
+  <si>
+    <t>878704497</t>
+  </si>
+  <si>
+    <t>178561126</t>
+  </si>
+  <si>
+    <t>661875884</t>
+  </si>
+  <si>
+    <t>778510622</t>
+  </si>
+  <si>
+    <t>693442299</t>
+  </si>
+  <si>
+    <t>732218924</t>
+  </si>
+  <si>
+    <t>878432388</t>
+  </si>
+  <si>
+    <t>880512607</t>
+  </si>
+  <si>
+    <t>879121303</t>
+  </si>
+  <si>
+    <t>879029837</t>
+  </si>
+  <si>
+    <t>878300809</t>
+  </si>
+  <si>
+    <t>674717479</t>
+  </si>
+  <si>
+    <t>873804862</t>
+  </si>
+  <si>
+    <t>873962264</t>
+  </si>
+  <si>
+    <t>811453624</t>
+  </si>
+  <si>
+    <t>771299157</t>
+  </si>
+  <si>
+    <t>879762544</t>
+  </si>
+  <si>
+    <t>880757624</t>
+  </si>
+  <si>
+    <t>885219323</t>
+  </si>
+  <si>
+    <t>852658925</t>
+  </si>
+  <si>
+    <t>810321830</t>
+  </si>
+  <si>
+    <t>812392490</t>
+  </si>
+  <si>
+    <t>767136157</t>
+  </si>
+  <si>
+    <t>766982718</t>
+  </si>
+  <si>
+    <t>756306779</t>
+  </si>
+  <si>
+    <t>736541438</t>
+  </si>
+  <si>
+    <t>733029981</t>
+  </si>
+  <si>
+    <t>730349978</t>
+  </si>
+  <si>
+    <t>725937134</t>
+  </si>
+  <si>
+    <t>725186955</t>
+  </si>
+  <si>
+    <t>724383249</t>
+  </si>
+  <si>
+    <t>717402576</t>
+  </si>
+  <si>
+    <t>715449553</t>
+  </si>
+  <si>
+    <t>706878760</t>
+  </si>
+  <si>
+    <t>697689226</t>
+  </si>
+  <si>
+    <t>853397879</t>
+  </si>
+  <si>
+    <t>890389236</t>
+  </si>
+  <si>
+    <t>887568842</t>
+  </si>
+  <si>
+    <t>673462259</t>
+  </si>
+  <si>
+    <t>175765720</t>
+  </si>
+  <si>
+    <t>175242449</t>
+  </si>
+  <si>
+    <t>172089397</t>
+  </si>
+  <si>
+    <t>171994720</t>
   </si>
 </sst>
 </file>
@@ -760,7 +823,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -801,7 +864,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -810,10 +873,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -822,10 +885,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -834,10 +897,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -846,10 +909,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -858,10 +921,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -870,10 +933,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -882,10 +945,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -894,10 +957,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -906,10 +969,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -918,10 +981,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -930,10 +993,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -942,10 +1005,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -954,10 +1017,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -969,7 +1032,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -981,7 +1044,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -993,7 +1056,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1002,10 +1065,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1014,10 +1077,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1026,10 +1089,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1038,10 +1101,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1050,10 +1113,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1125,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1137,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1086,10 +1149,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1098,10 +1161,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1110,10 +1173,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1122,10 +1185,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1134,10 +1197,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1146,10 +1209,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1158,10 +1221,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1170,10 +1233,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1182,10 +1245,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1194,10 +1257,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1206,10 +1269,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1218,10 +1281,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1233,7 +1296,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1245,7 +1308,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1257,7 +1320,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1269,7 +1332,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1281,7 +1344,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1293,7 +1356,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1305,7 +1368,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1317,7 +1380,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1329,7 +1392,7 @@
         <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1341,7 +1404,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1353,7 +1416,7 @@
         <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1365,7 +1428,7 @@
         <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1377,7 +1440,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1389,7 +1452,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1401,7 +1464,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1413,7 +1476,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1425,7 +1488,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1497,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1509,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1521,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1470,10 +1533,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1482,10 +1545,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1557,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1506,10 +1569,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1518,10 +1581,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1593,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1542,10 +1605,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1554,10 +1617,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1566,10 +1629,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1577,10 +1640,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1588,10 +1651,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1599,10 +1662,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1610,10 +1673,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1621,10 +1684,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1632,10 +1695,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1643,10 +1706,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1654,10 +1717,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1665,10 +1728,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1676,10 +1739,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1687,10 +1750,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1698,10 +1761,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1709,10 +1772,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1720,10 +1783,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1731,10 +1794,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1742,10 +1805,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1753,12 +1816,221 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C103" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F2AAD6-78E2-473F-B91E-FFB5D5EB766D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA15D0B-635C-4980-8E80-B3952664AF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="81">
   <si>
     <t>Status</t>
   </si>
@@ -48,253 +48,232 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>878739170</t>
+    <t>840156537</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>870958356</t>
-  </si>
-  <si>
-    <t>832214864</t>
-  </si>
-  <si>
-    <t>832051381</t>
-  </si>
-  <si>
-    <t>818175279</t>
-  </si>
-  <si>
-    <t>809058559</t>
-  </si>
-  <si>
-    <t>801932413</t>
-  </si>
-  <si>
-    <t>780771592</t>
-  </si>
-  <si>
-    <t>770329138</t>
-  </si>
-  <si>
-    <t>742777430</t>
-  </si>
-  <si>
-    <t>742633211</t>
-  </si>
-  <si>
-    <t>739633315</t>
-  </si>
-  <si>
-    <t>732308048</t>
-  </si>
-  <si>
-    <t>719562930</t>
-  </si>
-  <si>
-    <t>714429754</t>
-  </si>
-  <si>
-    <t>705239238</t>
-  </si>
-  <si>
-    <t>701093928</t>
-  </si>
-  <si>
-    <t>694029418</t>
-  </si>
-  <si>
-    <t>670972599</t>
-  </si>
-  <si>
-    <t>602894861</t>
-  </si>
-  <si>
-    <t>171894425</t>
-  </si>
-  <si>
-    <t>887771297</t>
-  </si>
-  <si>
-    <t>887607566</t>
+    <t>837340540</t>
+  </si>
+  <si>
+    <t>824646065</t>
+  </si>
+  <si>
+    <t>823889567</t>
+  </si>
+  <si>
+    <t>809373784</t>
+  </si>
+  <si>
+    <t>815470046</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>814160895</t>
-  </si>
-  <si>
-    <t>867717930</t>
-  </si>
-  <si>
-    <t>878853906</t>
-  </si>
-  <si>
-    <t>866746807</t>
-  </si>
-  <si>
-    <t>854721432</t>
-  </si>
-  <si>
-    <t>844546220</t>
-  </si>
-  <si>
-    <t>843566260</t>
-  </si>
-  <si>
-    <t>841683893</t>
-  </si>
-  <si>
-    <t>840917276</t>
-  </si>
-  <si>
-    <t>829367329</t>
-  </si>
-  <si>
-    <t>817098662</t>
-  </si>
-  <si>
-    <t>895940579</t>
-  </si>
-  <si>
-    <t>895689432</t>
-  </si>
-  <si>
-    <t>895514267</t>
-  </si>
-  <si>
-    <t>895267817</t>
-  </si>
-  <si>
-    <t>894566805</t>
-  </si>
-  <si>
-    <t>893892574</t>
-  </si>
-  <si>
-    <t>893709778</t>
-  </si>
-  <si>
-    <t>893302624</t>
-  </si>
-  <si>
-    <t>892947726</t>
-  </si>
-  <si>
-    <t>892695804</t>
-  </si>
-  <si>
-    <t>892673843</t>
-  </si>
-  <si>
-    <t>892513940</t>
-  </si>
-  <si>
-    <t>890095270</t>
-  </si>
-  <si>
-    <t>889979856</t>
-  </si>
-  <si>
-    <t>887894289</t>
-  </si>
-  <si>
-    <t>887812463</t>
-  </si>
-  <si>
-    <t>887147795</t>
-  </si>
-  <si>
-    <t>886505571</t>
-  </si>
-  <si>
-    <t>886163900</t>
-  </si>
-  <si>
-    <t>885949101</t>
-  </si>
-  <si>
-    <t>884094230</t>
-  </si>
-  <si>
-    <t>669936589</t>
-  </si>
-  <si>
-    <t>753270408</t>
-  </si>
-  <si>
-    <t>782864015</t>
-  </si>
-  <si>
-    <t>804643991</t>
-  </si>
-  <si>
-    <t>791406287</t>
-  </si>
-  <si>
-    <t>781553049</t>
-  </si>
-  <si>
-    <t>778899728</t>
-  </si>
-  <si>
-    <t>775999554</t>
-  </si>
-  <si>
-    <t>710187539</t>
-  </si>
-  <si>
-    <t>736975214</t>
-  </si>
-  <si>
-    <t>730439605</t>
-  </si>
-  <si>
-    <t>724022854</t>
-  </si>
-  <si>
-    <t>704740947</t>
-  </si>
-  <si>
-    <t>648258642</t>
-  </si>
-  <si>
-    <t>890622248</t>
+    <t>728808407</t>
+  </si>
+  <si>
+    <t>784520441</t>
+  </si>
+  <si>
+    <t>797936527</t>
+  </si>
+  <si>
+    <t>793344692</t>
+  </si>
+  <si>
+    <t>776822094</t>
+  </si>
+  <si>
+    <t>775357175</t>
+  </si>
+  <si>
+    <t>750936597</t>
+  </si>
+  <si>
+    <t>739800351</t>
+  </si>
+  <si>
+    <t>729885321</t>
+  </si>
+  <si>
+    <t>722661257</t>
+  </si>
+  <si>
+    <t>677860623</t>
+  </si>
+  <si>
+    <t>706157470</t>
+  </si>
+  <si>
+    <t>681665570</t>
+  </si>
+  <si>
+    <t>680521139</t>
+  </si>
+  <si>
+    <t>176643991</t>
+  </si>
+  <si>
+    <t>896709908</t>
+  </si>
+  <si>
+    <t>897029355</t>
+  </si>
+  <si>
+    <t>887519688</t>
+  </si>
+  <si>
+    <t>886658040</t>
+  </si>
+  <si>
+    <t>886456163</t>
+  </si>
+  <si>
+    <t>886275951</t>
+  </si>
+  <si>
+    <t>886180326</t>
+  </si>
+  <si>
+    <t>881786374</t>
+  </si>
+  <si>
+    <t>879827750</t>
+  </si>
+  <si>
+    <t>842931077</t>
+  </si>
+  <si>
+    <t>870338880</t>
+  </si>
+  <si>
+    <t>868123450</t>
+  </si>
+  <si>
+    <t>860557036</t>
+  </si>
+  <si>
+    <t>856851955</t>
+  </si>
+  <si>
+    <t>856748995</t>
+  </si>
+  <si>
+    <t>851732234</t>
+  </si>
+  <si>
+    <t>845987431</t>
+  </si>
+  <si>
+    <t>845687023</t>
+  </si>
+  <si>
+    <t>844683510</t>
+  </si>
+  <si>
+    <t>834897104</t>
+  </si>
+  <si>
+    <t>839209065</t>
+  </si>
+  <si>
+    <t>834728580</t>
+  </si>
+  <si>
+    <t>830903880</t>
+  </si>
+  <si>
+    <t>818231791</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>890622230</t>
-  </si>
-  <si>
-    <t>885173256</t>
-  </si>
-  <si>
-    <t>866370103</t>
-  </si>
-  <si>
-    <t>818589354</t>
-  </si>
-  <si>
-    <t>840504017</t>
-  </si>
-  <si>
-    <t>845821663</t>
-  </si>
-  <si>
-    <t>812369837</t>
-  </si>
-  <si>
-    <t>680280215</t>
-  </si>
-  <si>
-    <t>869403026</t>
-  </si>
-  <si>
-    <t>874736709</t>
+    <t>703241285</t>
+  </si>
+  <si>
+    <t>774820777</t>
+  </si>
+  <si>
+    <t>773803246</t>
+  </si>
+  <si>
+    <t>698976671</t>
+  </si>
+  <si>
+    <t>878990666</t>
+  </si>
+  <si>
+    <t>885579932</t>
+  </si>
+  <si>
+    <t>845178270</t>
+  </si>
+  <si>
+    <t>839289174</t>
+  </si>
+  <si>
+    <t>887613622</t>
+  </si>
+  <si>
+    <t>887769945</t>
+  </si>
+  <si>
+    <t>887717837</t>
+  </si>
+  <si>
+    <t>887664492</t>
+  </si>
+  <si>
+    <t>836409932</t>
+  </si>
+  <si>
+    <t>888593757</t>
+  </si>
+  <si>
+    <t>875191045</t>
+  </si>
+  <si>
+    <t>888245481</t>
+  </si>
+  <si>
+    <t>728804299</t>
+  </si>
+  <si>
+    <t>745441216</t>
+  </si>
+  <si>
+    <t>886976103</t>
+  </si>
+  <si>
+    <t>888721424</t>
+  </si>
+  <si>
+    <t>887616153</t>
+  </si>
+  <si>
+    <t>824986644</t>
+  </si>
+  <si>
+    <t>821268574</t>
+  </si>
+  <si>
+    <t>817517133</t>
+  </si>
+  <si>
+    <t>796728933</t>
+  </si>
+  <si>
+    <t>796584229</t>
+  </si>
+  <si>
+    <t>796187445</t>
+  </si>
+  <si>
+    <t>775090743</t>
   </si>
 </sst>
 </file>
@@ -754,7 +733,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D81"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -843,7 +822,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -852,10 +831,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -864,10 +843,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -876,10 +855,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -888,10 +867,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -900,10 +879,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -912,10 +891,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -924,10 +903,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -936,10 +915,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -948,10 +927,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -960,10 +939,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -972,10 +951,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -984,10 +963,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -996,10 +975,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1008,10 +987,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1020,10 +999,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1032,10 +1011,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1044,10 +1023,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1059,7 +1038,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1071,7 +1050,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1083,7 +1062,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1095,7 +1074,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1107,7 +1086,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1119,7 +1098,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1131,7 +1110,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1143,7 +1122,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1155,7 +1134,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1167,7 +1146,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1179,7 +1158,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1191,7 +1170,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1203,7 +1182,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1215,7 +1194,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1227,7 +1206,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1239,7 +1218,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1251,7 +1230,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1263,7 +1242,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1275,7 +1254,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1287,7 +1266,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1299,7 +1278,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1311,7 +1290,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1320,10 +1299,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1332,10 +1311,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1344,10 +1323,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1356,10 +1335,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1368,10 +1347,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1380,10 +1359,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1392,10 +1371,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1404,10 +1383,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1416,10 +1395,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1428,10 +1407,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1440,10 +1419,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1452,10 +1431,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1464,10 +1443,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1476,10 +1455,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1488,10 +1467,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1500,10 +1479,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1512,10 +1491,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1524,10 +1503,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1536,10 +1515,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1548,10 +1527,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1560,10 +1539,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1571,10 +1550,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1582,10 +1561,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1593,10 +1572,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1604,10 +1583,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1618,7 +1597,7 @@
         <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1629,7 +1608,7 @@
         <v>79</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1640,86 +1619,9 @@
         <v>80</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C81" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDA15D0B-635C-4980-8E80-B3952664AF8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{430B50FA-4AF6-4017-8672-FD1C776AF508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="187">
   <si>
     <t>Status</t>
   </si>
@@ -48,12 +48,15 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>724224906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
     <t>840156537</t>
   </si>
   <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
     <t>837340540</t>
   </si>
   <si>
@@ -274,6 +277,321 @@
   </si>
   <si>
     <t>775090743</t>
+  </si>
+  <si>
+    <t>752647457</t>
+  </si>
+  <si>
+    <t>742116373</t>
+  </si>
+  <si>
+    <t>682535624</t>
+  </si>
+  <si>
+    <t>731176107</t>
+  </si>
+  <si>
+    <t>719679866</t>
+  </si>
+  <si>
+    <t>697716086</t>
+  </si>
+  <si>
+    <t>693585873</t>
+  </si>
+  <si>
+    <t>686352471</t>
+  </si>
+  <si>
+    <t>657915074</t>
+  </si>
+  <si>
+    <t>874486305</t>
+  </si>
+  <si>
+    <t>874474335</t>
+  </si>
+  <si>
+    <t>858913399</t>
+  </si>
+  <si>
+    <t>866762879</t>
+  </si>
+  <si>
+    <t>830673368</t>
+  </si>
+  <si>
+    <t>822016824</t>
+  </si>
+  <si>
+    <t>744227889</t>
+  </si>
+  <si>
+    <t>804464174</t>
+  </si>
+  <si>
+    <t>814809087</t>
+  </si>
+  <si>
+    <t>820936577</t>
+  </si>
+  <si>
+    <t>777031737</t>
+  </si>
+  <si>
+    <t>898255587</t>
+  </si>
+  <si>
+    <t>686650239</t>
+  </si>
+  <si>
+    <t>708717180</t>
+  </si>
+  <si>
+    <t>725464055</t>
+  </si>
+  <si>
+    <t>687057145</t>
+  </si>
+  <si>
+    <t>708410661</t>
+  </si>
+  <si>
+    <t>897804963</t>
+  </si>
+  <si>
+    <t>897766501</t>
+  </si>
+  <si>
+    <t>897697045</t>
+  </si>
+  <si>
+    <t>897160580</t>
+  </si>
+  <si>
+    <t>897126607</t>
+  </si>
+  <si>
+    <t>896962010</t>
+  </si>
+  <si>
+    <t>895626970</t>
+  </si>
+  <si>
+    <t>893972095</t>
+  </si>
+  <si>
+    <t>893972087</t>
+  </si>
+  <si>
+    <t>892840152</t>
+  </si>
+  <si>
+    <t>892738752</t>
+  </si>
+  <si>
+    <t>854838913</t>
+  </si>
+  <si>
+    <t>837054745</t>
+  </si>
+  <si>
+    <t>836837090</t>
+  </si>
+  <si>
+    <t>836485288</t>
+  </si>
+  <si>
+    <t>777495270</t>
+  </si>
+  <si>
+    <t>751283775</t>
+  </si>
+  <si>
+    <t>750199113</t>
+  </si>
+  <si>
+    <t>870230376</t>
+  </si>
+  <si>
+    <t>856470152</t>
+  </si>
+  <si>
+    <t>843710942</t>
+  </si>
+  <si>
+    <t>847485459</t>
+  </si>
+  <si>
+    <t>832324200</t>
+  </si>
+  <si>
+    <t>835767090</t>
+  </si>
+  <si>
+    <t>883806279</t>
+  </si>
+  <si>
+    <t>863204313</t>
+  </si>
+  <si>
+    <t>729856082</t>
+  </si>
+  <si>
+    <t>863582304</t>
+  </si>
+  <si>
+    <t>866734449</t>
+  </si>
+  <si>
+    <t>790023786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>801076211</t>
+  </si>
+  <si>
+    <t>865908309</t>
+  </si>
+  <si>
+    <t>834434742</t>
+  </si>
+  <si>
+    <t>807587773</t>
+  </si>
+  <si>
+    <t>736325790</t>
+  </si>
+  <si>
+    <t>734322948</t>
+  </si>
+  <si>
+    <t>686584446</t>
+  </si>
+  <si>
+    <t>666984871</t>
+  </si>
+  <si>
+    <t>888734997</t>
+  </si>
+  <si>
+    <t>859334512</t>
+  </si>
+  <si>
+    <t>856734391</t>
+  </si>
+  <si>
+    <t>773262732</t>
+  </si>
+  <si>
+    <t>822060384</t>
+  </si>
+  <si>
+    <t>853537631</t>
+  </si>
+  <si>
+    <t>817100435</t>
+  </si>
+  <si>
+    <t>772944991</t>
+  </si>
+  <si>
+    <t>685718805</t>
+  </si>
+  <si>
+    <t>732604438</t>
+  </si>
+  <si>
+    <t>729004634</t>
+  </si>
+  <si>
+    <t>722600297</t>
+  </si>
+  <si>
+    <t>899074458</t>
+  </si>
+  <si>
+    <t>177351966</t>
+  </si>
+  <si>
+    <t>177351792</t>
+  </si>
+  <si>
+    <t>898668847</t>
+  </si>
+  <si>
+    <t>897920561</t>
+  </si>
+  <si>
+    <t>897246074</t>
+  </si>
+  <si>
+    <t>897226951</t>
+  </si>
+  <si>
+    <t>897206078</t>
+  </si>
+  <si>
+    <t>897201764</t>
+  </si>
+  <si>
+    <t>897197681</t>
+  </si>
+  <si>
+    <t>897175828</t>
+  </si>
+  <si>
+    <t>897152033</t>
+  </si>
+  <si>
+    <t>897124446</t>
+  </si>
+  <si>
+    <t>897112128</t>
+  </si>
+  <si>
+    <t>896652686</t>
+  </si>
+  <si>
+    <t>896514944</t>
+  </si>
+  <si>
+    <t>888758574</t>
+  </si>
+  <si>
+    <t>893069629</t>
+  </si>
+  <si>
+    <t>892541909</t>
+  </si>
+  <si>
+    <t>891956538</t>
+  </si>
+  <si>
+    <t>889426346</t>
+  </si>
+  <si>
+    <t>888996984</t>
+  </si>
+  <si>
+    <t>888914193</t>
+  </si>
+  <si>
+    <t>885775472</t>
+  </si>
+  <si>
+    <t>878114390</t>
+  </si>
+  <si>
+    <t>877510580</t>
+  </si>
+  <si>
+    <t>889370981</t>
+  </si>
+  <si>
+    <t>741002244</t>
   </si>
 </sst>
 </file>
@@ -733,7 +1051,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D74"/>
+  <dimension ref="A1:D179"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -822,7 +1140,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -831,10 +1149,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -846,7 +1164,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -858,7 +1176,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -870,7 +1188,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -882,7 +1200,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -894,7 +1212,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -906,7 +1224,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -918,7 +1236,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -930,7 +1248,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -942,7 +1260,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -954,7 +1272,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -966,7 +1284,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -978,7 +1296,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -990,7 +1308,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1002,7 +1320,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1014,7 +1332,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1026,7 +1344,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1038,7 +1356,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1050,7 +1368,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1062,7 +1380,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1074,7 +1392,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1086,7 +1404,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1098,7 +1416,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1110,7 +1428,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1122,7 +1440,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1134,7 +1452,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1146,7 +1464,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1158,7 +1476,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1170,7 +1488,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1182,7 +1500,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1194,7 +1512,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1206,7 +1524,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1218,7 +1536,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1230,7 +1548,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1242,7 +1560,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1254,7 +1572,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1266,7 +1584,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1278,7 +1596,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1290,7 +1608,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1617,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B47" s="5" t="s">
         <v>53</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>52</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1314,7 +1632,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1326,7 +1644,7 @@
         <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1338,7 +1656,7 @@
         <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1350,7 +1668,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1362,7 +1680,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1374,7 +1692,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1386,7 +1704,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1398,7 +1716,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>12</v>
+        <v>53</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1410,7 +1728,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1422,7 +1740,7 @@
         <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1434,7 +1752,7 @@
         <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1446,7 +1764,7 @@
         <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1458,7 +1776,7 @@
         <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1470,7 +1788,7 @@
         <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1482,7 +1800,7 @@
         <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1494,7 +1812,7 @@
         <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1506,7 +1824,7 @@
         <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1518,7 +1836,7 @@
         <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1622,6 +1940,1161 @@
         <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C179" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7C01BDE-B091-4BAB-85AC-C190E843CF63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF603A5E-12CC-4861-8DAF-FB09D1088E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DescarteIncidencia" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="82">
   <si>
     <t>Status</t>
   </si>
@@ -48,202 +48,235 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>884008875</t>
+    <t>877258719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>894866312</t>
+  </si>
+  <si>
+    <t>887364176</t>
+  </si>
+  <si>
+    <t>883504577</t>
+  </si>
+  <si>
+    <t>882952074</t>
+  </si>
+  <si>
+    <t>837472459</t>
+  </si>
+  <si>
+    <t>850478615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>692085123</t>
+  </si>
+  <si>
+    <t>736516919</t>
+  </si>
+  <si>
+    <t>705628364</t>
+  </si>
+  <si>
+    <t>697908279</t>
+  </si>
+  <si>
+    <t>691504025</t>
+  </si>
+  <si>
+    <t>823603810</t>
+  </si>
+  <si>
+    <t>821123332</t>
+  </si>
+  <si>
+    <t>809108495</t>
+  </si>
+  <si>
+    <t>806607036</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>875050332</t>
-  </si>
-  <si>
-    <t>849382928</t>
-  </si>
-  <si>
-    <t>869993208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>799975366</t>
-  </si>
-  <si>
-    <t>794843890</t>
-  </si>
-  <si>
-    <t>825985074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>832168177</t>
-  </si>
-  <si>
-    <t>833251303</t>
-  </si>
-  <si>
-    <t>790356483</t>
-  </si>
-  <si>
-    <t>786812309</t>
-  </si>
-  <si>
-    <t>786812291</t>
-  </si>
-  <si>
-    <t>781497494</t>
-  </si>
-  <si>
-    <t>776952040</t>
-  </si>
-  <si>
-    <t>775091097</t>
-  </si>
-  <si>
-    <t>736688320</t>
-  </si>
-  <si>
-    <t>725232197</t>
-  </si>
-  <si>
-    <t>724467034</t>
-  </si>
-  <si>
-    <t>723340760</t>
-  </si>
-  <si>
-    <t>694684550</t>
-  </si>
-  <si>
-    <t>679734552</t>
-  </si>
-  <si>
-    <t>673725119</t>
-  </si>
-  <si>
-    <t>174608541</t>
-  </si>
-  <si>
-    <t>566865733</t>
-  </si>
-  <si>
-    <t>899210755</t>
-  </si>
-  <si>
-    <t>893582290</t>
-  </si>
-  <si>
-    <t>878052848</t>
-  </si>
-  <si>
-    <t>861321101</t>
-  </si>
-  <si>
-    <t>844394993</t>
-  </si>
-  <si>
-    <t>832463636</t>
-  </si>
-  <si>
-    <t>828998421</t>
-  </si>
-  <si>
-    <t>641419530</t>
-  </si>
-  <si>
-    <t>760680649</t>
-  </si>
-  <si>
-    <t>800402566</t>
-  </si>
-  <si>
-    <t>795145295</t>
-  </si>
-  <si>
-    <t>791471232</t>
-  </si>
-  <si>
-    <t>758748770</t>
-  </si>
-  <si>
-    <t>758310472</t>
-  </si>
-  <si>
-    <t>756609651</t>
-  </si>
-  <si>
-    <t>756457705</t>
-  </si>
-  <si>
-    <t>754268153</t>
-  </si>
-  <si>
-    <t>723680074</t>
-  </si>
-  <si>
-    <t>749964270</t>
-  </si>
-  <si>
-    <t>749003384</t>
-  </si>
-  <si>
-    <t>741260453</t>
-  </si>
-  <si>
-    <t>694650569</t>
-  </si>
-  <si>
-    <t>708550276</t>
-  </si>
-  <si>
-    <t>690915768</t>
-  </si>
-  <si>
-    <t>899576304</t>
-  </si>
-  <si>
-    <t>179022375</t>
-  </si>
-  <si>
-    <t>178566125</t>
-  </si>
-  <si>
-    <t>904648734</t>
-  </si>
-  <si>
-    <t>904270851</t>
-  </si>
-  <si>
-    <t>904049271</t>
-  </si>
-  <si>
-    <t>903116576</t>
-  </si>
-  <si>
-    <t>901849194</t>
-  </si>
-  <si>
-    <t>900639471</t>
-  </si>
-  <si>
-    <t>900637509</t>
-  </si>
-  <si>
-    <t>900636808</t>
-  </si>
-  <si>
-    <t>896036518</t>
-  </si>
-  <si>
-    <t>895119083</t>
-  </si>
-  <si>
-    <t>891799862</t>
-  </si>
-  <si>
-    <t>889040758</t>
+    <t>773174218</t>
+  </si>
+  <si>
+    <t>734888161</t>
+  </si>
+  <si>
+    <t>748840869</t>
+  </si>
+  <si>
+    <t>848461285</t>
+  </si>
+  <si>
+    <t>808431906</t>
+  </si>
+  <si>
+    <t>806695726</t>
+  </si>
+  <si>
+    <t>727645883</t>
+  </si>
+  <si>
+    <t>822459248</t>
+  </si>
+  <si>
+    <t>848320952</t>
+  </si>
+  <si>
+    <t>816929552</t>
+  </si>
+  <si>
+    <t>798104174</t>
+  </si>
+  <si>
+    <t>798104166</t>
+  </si>
+  <si>
+    <t>781876788</t>
+  </si>
+  <si>
+    <t>766964799</t>
+  </si>
+  <si>
+    <t>742676376</t>
+  </si>
+  <si>
+    <t>724003722</t>
+  </si>
+  <si>
+    <t>700211166</t>
+  </si>
+  <si>
+    <t>680733759</t>
+  </si>
+  <si>
+    <t>675398550</t>
+  </si>
+  <si>
+    <t>786660393</t>
+  </si>
+  <si>
+    <t>853129678</t>
+  </si>
+  <si>
+    <t>848291492</t>
+  </si>
+  <si>
+    <t>844233506</t>
+  </si>
+  <si>
+    <t>843741954</t>
+  </si>
+  <si>
+    <t>819390000</t>
+  </si>
+  <si>
+    <t>836728778</t>
+  </si>
+  <si>
+    <t>813283656</t>
+  </si>
+  <si>
+    <t>758309953</t>
+  </si>
+  <si>
+    <t>697690174</t>
+  </si>
+  <si>
+    <t>691537611</t>
+  </si>
+  <si>
+    <t>178794834</t>
+  </si>
+  <si>
+    <t>905321794</t>
+  </si>
+  <si>
+    <t>904321068</t>
+  </si>
+  <si>
+    <t>904177064</t>
+  </si>
+  <si>
+    <t>904037821</t>
+  </si>
+  <si>
+    <t>902105448</t>
+  </si>
+  <si>
+    <t>895776890</t>
+  </si>
+  <si>
+    <t>895752131</t>
+  </si>
+  <si>
+    <t>895727075</t>
+  </si>
+  <si>
+    <t>895548638</t>
+  </si>
+  <si>
+    <t>895474231</t>
+  </si>
+  <si>
+    <t>893898076</t>
+  </si>
+  <si>
+    <t>893792089</t>
+  </si>
+  <si>
+    <t>881743201</t>
+  </si>
+  <si>
+    <t>806237586</t>
+  </si>
+  <si>
+    <t>798230631</t>
+  </si>
+  <si>
+    <t>742997467</t>
+  </si>
+  <si>
+    <t>903040438</t>
+  </si>
+  <si>
+    <t>905907352</t>
+  </si>
+  <si>
+    <t>895553463</t>
+  </si>
+  <si>
+    <t>895537706</t>
+  </si>
+  <si>
+    <t>895509820</t>
+  </si>
+  <si>
+    <t>889812677</t>
+  </si>
+  <si>
+    <t>895507121</t>
+  </si>
+  <si>
+    <t>895650848</t>
+  </si>
+  <si>
+    <t>891677324</t>
+  </si>
+  <si>
+    <t>805940677</t>
+  </si>
+  <si>
+    <t>892640875</t>
   </si>
 </sst>
 </file>
@@ -703,7 +736,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -768,7 +801,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -777,10 +810,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -789,10 +822,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -801,10 +834,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>13</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>14</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -813,10 +846,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -825,10 +858,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -837,10 +870,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -849,10 +882,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -861,10 +894,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -873,10 +906,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -885,10 +918,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -897,10 +930,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -909,10 +942,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -936,7 +969,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -948,7 +981,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -960,7 +993,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -996,7 +1029,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1008,7 +1041,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1020,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1032,7 +1065,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1044,7 +1077,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1056,7 +1089,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1068,7 +1101,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1080,7 +1113,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1092,7 +1125,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1104,7 +1137,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1116,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1128,7 +1161,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1140,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1152,7 +1185,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1164,7 +1197,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1176,7 +1209,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1188,7 +1221,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1200,7 +1233,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1212,7 +1245,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1224,7 +1257,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1236,7 +1269,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1248,7 +1281,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1260,7 +1293,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1272,7 +1305,7 @@
         <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1284,7 +1317,7 @@
         <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1296,7 +1329,7 @@
         <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1308,7 +1341,7 @@
         <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1320,7 +1353,7 @@
         <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1332,7 +1365,7 @@
         <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1344,7 +1377,7 @@
         <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1356,7 +1389,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1368,7 +1401,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1380,7 +1413,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1392,7 +1425,7 @@
         <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1404,7 +1437,7 @@
         <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1416,7 +1449,7 @@
         <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1428,7 +1461,7 @@
         <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1440,7 +1473,7 @@
         <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1452,7 +1485,7 @@
         <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1464,7 +1497,7 @@
         <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1476,20 +1509,135 @@
         <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D64"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="6"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D65"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="6"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF603A5E-12CC-4861-8DAF-FB09D1088E4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4A13BE-7B39-413A-82B3-0A96A69163B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="111">
   <si>
     <t>Status</t>
   </si>
@@ -48,235 +48,322 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>877258719</t>
+    <t>812237604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>801377460</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>903377947</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>894866312</t>
-  </si>
-  <si>
-    <t>887364176</t>
-  </si>
-  <si>
-    <t>883504577</t>
-  </si>
-  <si>
-    <t>882952074</t>
-  </si>
-  <si>
-    <t>837472459</t>
-  </si>
-  <si>
-    <t>850478615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>692085123</t>
-  </si>
-  <si>
-    <t>736516919</t>
-  </si>
-  <si>
-    <t>705628364</t>
-  </si>
-  <si>
-    <t>697908279</t>
-  </si>
-  <si>
-    <t>691504025</t>
-  </si>
-  <si>
-    <t>823603810</t>
-  </si>
-  <si>
-    <t>821123332</t>
-  </si>
-  <si>
-    <t>809108495</t>
-  </si>
-  <si>
-    <t>806607036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>773174218</t>
-  </si>
-  <si>
-    <t>734888161</t>
-  </si>
-  <si>
-    <t>748840869</t>
-  </si>
-  <si>
-    <t>848461285</t>
-  </si>
-  <si>
-    <t>808431906</t>
-  </si>
-  <si>
-    <t>806695726</t>
-  </si>
-  <si>
-    <t>727645883</t>
-  </si>
-  <si>
-    <t>822459248</t>
-  </si>
-  <si>
-    <t>848320952</t>
-  </si>
-  <si>
-    <t>816929552</t>
-  </si>
-  <si>
-    <t>798104174</t>
-  </si>
-  <si>
-    <t>798104166</t>
-  </si>
-  <si>
-    <t>781876788</t>
-  </si>
-  <si>
-    <t>766964799</t>
-  </si>
-  <si>
-    <t>742676376</t>
-  </si>
-  <si>
-    <t>724003722</t>
-  </si>
-  <si>
-    <t>700211166</t>
-  </si>
-  <si>
-    <t>680733759</t>
-  </si>
-  <si>
-    <t>675398550</t>
-  </si>
-  <si>
-    <t>786660393</t>
-  </si>
-  <si>
-    <t>853129678</t>
-  </si>
-  <si>
-    <t>848291492</t>
-  </si>
-  <si>
-    <t>844233506</t>
-  </si>
-  <si>
-    <t>843741954</t>
-  </si>
-  <si>
-    <t>819390000</t>
-  </si>
-  <si>
-    <t>836728778</t>
-  </si>
-  <si>
-    <t>813283656</t>
-  </si>
-  <si>
-    <t>758309953</t>
-  </si>
-  <si>
-    <t>697690174</t>
-  </si>
-  <si>
-    <t>691537611</t>
-  </si>
-  <si>
-    <t>178794834</t>
-  </si>
-  <si>
-    <t>905321794</t>
-  </si>
-  <si>
-    <t>904321068</t>
-  </si>
-  <si>
-    <t>904177064</t>
-  </si>
-  <si>
-    <t>904037821</t>
-  </si>
-  <si>
-    <t>902105448</t>
-  </si>
-  <si>
-    <t>895776890</t>
-  </si>
-  <si>
-    <t>895752131</t>
-  </si>
-  <si>
-    <t>895727075</t>
-  </si>
-  <si>
-    <t>895548638</t>
-  </si>
-  <si>
-    <t>895474231</t>
-  </si>
-  <si>
-    <t>893898076</t>
-  </si>
-  <si>
-    <t>893792089</t>
-  </si>
-  <si>
-    <t>881743201</t>
-  </si>
-  <si>
-    <t>806237586</t>
-  </si>
-  <si>
-    <t>798230631</t>
-  </si>
-  <si>
-    <t>742997467</t>
-  </si>
-  <si>
-    <t>903040438</t>
-  </si>
-  <si>
-    <t>905907352</t>
-  </si>
-  <si>
-    <t>895553463</t>
-  </si>
-  <si>
-    <t>895537706</t>
-  </si>
-  <si>
-    <t>895509820</t>
-  </si>
-  <si>
-    <t>889812677</t>
-  </si>
-  <si>
-    <t>895507121</t>
-  </si>
-  <si>
-    <t>895650848</t>
-  </si>
-  <si>
-    <t>891677324</t>
-  </si>
-  <si>
-    <t>805940677</t>
-  </si>
-  <si>
-    <t>892640875</t>
+    <t>902857196</t>
+  </si>
+  <si>
+    <t>904680604</t>
+  </si>
+  <si>
+    <t>688972086</t>
+  </si>
+  <si>
+    <t>905062588</t>
+  </si>
+  <si>
+    <t>905512160</t>
+  </si>
+  <si>
+    <t>902728546</t>
+  </si>
+  <si>
+    <t>755793126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>804545055</t>
+  </si>
+  <si>
+    <t>905373993</t>
+  </si>
+  <si>
+    <t>896579780</t>
+  </si>
+  <si>
+    <t>896159427</t>
+  </si>
+  <si>
+    <t>896087206</t>
+  </si>
+  <si>
+    <t>895728131</t>
+  </si>
+  <si>
+    <t>758636348</t>
+  </si>
+  <si>
+    <t>758293116</t>
+  </si>
+  <si>
+    <t>693253183</t>
+  </si>
+  <si>
+    <t>689409120</t>
+  </si>
+  <si>
+    <t>878302946</t>
+  </si>
+  <si>
+    <t>829987340</t>
+  </si>
+  <si>
+    <t>807213677</t>
+  </si>
+  <si>
+    <t>737885065</t>
+  </si>
+  <si>
+    <t>802061204</t>
+  </si>
+  <si>
+    <t>745908677</t>
+  </si>
+  <si>
+    <t>896904038</t>
+  </si>
+  <si>
+    <t>845715857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>822449140</t>
+  </si>
+  <si>
+    <t>880744887</t>
+  </si>
+  <si>
+    <t>875835757</t>
+  </si>
+  <si>
+    <t>865784692</t>
+  </si>
+  <si>
+    <t>865710341</t>
+  </si>
+  <si>
+    <t>859983938</t>
+  </si>
+  <si>
+    <t>789524364</t>
+  </si>
+  <si>
+    <t>786602544</t>
+  </si>
+  <si>
+    <t>178877696</t>
+  </si>
+  <si>
+    <t>758985984</t>
+  </si>
+  <si>
+    <t>736472220</t>
+  </si>
+  <si>
+    <t>727616892</t>
+  </si>
+  <si>
+    <t>715573451</t>
+  </si>
+  <si>
+    <t>707624528</t>
+  </si>
+  <si>
+    <t>700249869</t>
+  </si>
+  <si>
+    <t>674237205</t>
+  </si>
+  <si>
+    <t>636345567</t>
+  </si>
+  <si>
+    <t>672300047</t>
+  </si>
+  <si>
+    <t>906455948</t>
+  </si>
+  <si>
+    <t>897156059</t>
+  </si>
+  <si>
+    <t>897070979</t>
+  </si>
+  <si>
+    <t>896959685</t>
+  </si>
+  <si>
+    <t>896941402</t>
+  </si>
+  <si>
+    <t>906405299</t>
+  </si>
+  <si>
+    <t>904319807</t>
+  </si>
+  <si>
+    <t>904000548</t>
+  </si>
+  <si>
+    <t>900246046</t>
+  </si>
+  <si>
+    <t>897492108</t>
+  </si>
+  <si>
+    <t>897271650</t>
+  </si>
+  <si>
+    <t>798626010</t>
+  </si>
+  <si>
+    <t>870141441</t>
+  </si>
+  <si>
+    <t>886900087</t>
+  </si>
+  <si>
+    <t>896710815</t>
+  </si>
+  <si>
+    <t>894310816</t>
+  </si>
+  <si>
+    <t>891748380</t>
+  </si>
+  <si>
+    <t>889015289</t>
+  </si>
+  <si>
+    <t>854673716</t>
+  </si>
+  <si>
+    <t>851535215</t>
+  </si>
+  <si>
+    <t>848575746</t>
+  </si>
+  <si>
+    <t>830624577</t>
+  </si>
+  <si>
+    <t>811354343</t>
+  </si>
+  <si>
+    <t>736228192</t>
+  </si>
+  <si>
+    <t>751425129</t>
+  </si>
+  <si>
+    <t>749993949</t>
+  </si>
+  <si>
+    <t>749293241</t>
+  </si>
+  <si>
+    <t>700264066</t>
+  </si>
+  <si>
+    <t>712693245</t>
+  </si>
+  <si>
+    <t>873103133</t>
+  </si>
+  <si>
+    <t>874845344</t>
+  </si>
+  <si>
+    <t>876584800</t>
+  </si>
+  <si>
+    <t>876310511</t>
+  </si>
+  <si>
+    <t>688485535</t>
+  </si>
+  <si>
+    <t>846400269</t>
+  </si>
+  <si>
+    <t>853240970</t>
+  </si>
+  <si>
+    <t>825992492</t>
+  </si>
+  <si>
+    <t>794392336</t>
+  </si>
+  <si>
+    <t>801895701</t>
+  </si>
+  <si>
+    <t>800208203</t>
+  </si>
+  <si>
+    <t>800129516</t>
+  </si>
+  <si>
+    <t>797921933</t>
+  </si>
+  <si>
+    <t>769363726</t>
+  </si>
+  <si>
+    <t>774746949</t>
+  </si>
+  <si>
+    <t>773578988</t>
+  </si>
+  <si>
+    <t>785945548</t>
+  </si>
+  <si>
+    <t>894116239</t>
+  </si>
+  <si>
+    <t>818924973</t>
+  </si>
+  <si>
+    <t>799828557</t>
+  </si>
+  <si>
+    <t>806651257</t>
+  </si>
+  <si>
+    <t>897249656</t>
+  </si>
+  <si>
+    <t>896865429</t>
+  </si>
+  <si>
+    <t>674542299</t>
+  </si>
+  <si>
+    <t>896903931</t>
+  </si>
+  <si>
+    <t>767043502</t>
   </si>
 </sst>
 </file>
@@ -736,7 +823,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -777,7 +864,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -786,10 +873,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -798,10 +885,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -810,10 +897,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -822,10 +909,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -834,10 +921,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -846,10 +933,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -858,10 +945,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -870,10 +957,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -882,10 +969,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -894,10 +981,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -906,10 +993,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -918,10 +1005,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -930,10 +1017,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -942,10 +1029,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -954,10 +1041,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -966,10 +1053,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -978,10 +1065,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -990,10 +1077,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1002,7 +1089,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>6</v>
@@ -1014,7 +1101,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>6</v>
@@ -1026,10 +1113,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1038,10 +1125,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1050,10 +1137,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1149,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1161,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1086,10 +1173,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1098,10 +1185,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1110,10 +1197,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1122,10 +1209,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1134,10 +1221,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1146,10 +1233,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1158,10 +1245,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1170,10 +1257,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1182,10 +1269,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1194,10 +1281,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1206,10 +1293,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1218,10 +1305,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1230,10 +1317,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1242,10 +1329,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1254,10 +1341,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1266,10 +1353,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1278,10 +1365,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1377,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1389,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1401,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1326,10 +1413,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1425,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1437,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1449,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1461,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1473,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1485,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1497,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1509,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1521,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1533,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1545,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1470,10 +1557,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1482,10 +1569,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1581,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1506,10 +1593,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1518,10 +1605,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1617,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1542,10 +1629,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1553,10 +1640,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1564,10 +1651,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1575,10 +1662,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1586,10 +1673,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1597,10 +1684,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1608,10 +1695,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1619,10 +1706,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1630,12 +1717,309 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C75" s="6" t="s">
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C102" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A4A13BE-7B39-413A-82B3-0A96A69163B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14424F34-66BA-43B6-9656-6FC7208F032A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DescarteIncidencia" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="158">
   <si>
     <t>Status</t>
   </si>
@@ -48,322 +48,463 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>812237604</t>
+    <t>660544473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>901837199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>896716655</t>
+  </si>
+  <si>
+    <t>879517435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>904501511</t>
+  </si>
+  <si>
+    <t>904147893</t>
+  </si>
+  <si>
+    <t>879525354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>738059249</t>
+  </si>
+  <si>
+    <t>883953485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>871386136</t>
+  </si>
+  <si>
+    <t>839950643</t>
+  </si>
+  <si>
+    <t>816063261</t>
+  </si>
+  <si>
+    <t>840758977</t>
+  </si>
+  <si>
+    <t>858435385</t>
+  </si>
+  <si>
+    <t>760025811</t>
+  </si>
+  <si>
+    <t>844219406</t>
+  </si>
+  <si>
+    <t>896765330</t>
+  </si>
+  <si>
+    <t>844672695</t>
+  </si>
+  <si>
+    <t>846851271</t>
+  </si>
+  <si>
+    <t>896759036</t>
+  </si>
+  <si>
+    <t>893871396</t>
+  </si>
+  <si>
+    <t>799864685</t>
+  </si>
+  <si>
+    <t>898200971</t>
+  </si>
+  <si>
+    <t>754334138</t>
+  </si>
+  <si>
+    <t>750987160</t>
+  </si>
+  <si>
+    <t>764041046</t>
+  </si>
+  <si>
+    <t>819997416</t>
+  </si>
+  <si>
+    <t>819733605</t>
+  </si>
+  <si>
+    <t>804869638</t>
+  </si>
+  <si>
+    <t>783044088</t>
+  </si>
+  <si>
+    <t>769979638</t>
+  </si>
+  <si>
+    <t>767630431</t>
+  </si>
+  <si>
+    <t>766766921</t>
+  </si>
+  <si>
+    <t>900579974</t>
+  </si>
+  <si>
+    <t>743089777</t>
+  </si>
+  <si>
+    <t>737545651</t>
+  </si>
+  <si>
+    <t>712884521</t>
+  </si>
+  <si>
+    <t>693877213</t>
+  </si>
+  <si>
+    <t>637424783</t>
+  </si>
+  <si>
+    <t>174606792</t>
+  </si>
+  <si>
+    <t>174456438</t>
+  </si>
+  <si>
+    <t>884298526</t>
+  </si>
+  <si>
+    <t>883230454</t>
+  </si>
+  <si>
+    <t>883212411</t>
+  </si>
+  <si>
+    <t>864848001</t>
+  </si>
+  <si>
+    <t>842865572</t>
+  </si>
+  <si>
+    <t>861207649</t>
+  </si>
+  <si>
+    <t>865337426</t>
+  </si>
+  <si>
+    <t>797944661</t>
+  </si>
+  <si>
+    <t>761624000</t>
+  </si>
+  <si>
+    <t>759722196</t>
+  </si>
+  <si>
+    <t>804435927</t>
+  </si>
+  <si>
+    <t>816677086</t>
+  </si>
+  <si>
+    <t>828982482</t>
+  </si>
+  <si>
+    <t>827471800</t>
+  </si>
+  <si>
+    <t>807605971</t>
+  </si>
+  <si>
+    <t>807149665</t>
+  </si>
+  <si>
+    <t>802545768</t>
+  </si>
+  <si>
+    <t>789952961</t>
+  </si>
+  <si>
+    <t>902058142</t>
+  </si>
+  <si>
+    <t>681151183</t>
+  </si>
+  <si>
+    <t>715387779</t>
+  </si>
+  <si>
+    <t>737398606</t>
+  </si>
+  <si>
+    <t>735486585</t>
+  </si>
+  <si>
+    <t>709176220</t>
+  </si>
+  <si>
+    <t>694024518</t>
+  </si>
+  <si>
+    <t>685052767</t>
+  </si>
+  <si>
+    <t>908581238</t>
+  </si>
+  <si>
+    <t>908383809</t>
+  </si>
+  <si>
+    <t>907114825</t>
+  </si>
+  <si>
+    <t>906982917</t>
+  </si>
+  <si>
+    <t>906970359</t>
+  </si>
+  <si>
+    <t>906873520</t>
+  </si>
+  <si>
+    <t>906531326</t>
+  </si>
+  <si>
+    <t>904938697</t>
+  </si>
+  <si>
+    <t>903340259</t>
+  </si>
+  <si>
+    <t>902129018</t>
+  </si>
+  <si>
+    <t>900283536</t>
+  </si>
+  <si>
+    <t>900242920</t>
+  </si>
+  <si>
+    <t>900116058</t>
+  </si>
+  <si>
+    <t>899665271</t>
+  </si>
+  <si>
+    <t>899417244</t>
+  </si>
+  <si>
+    <t>899333045</t>
+  </si>
+  <si>
+    <t>882967213</t>
+  </si>
+  <si>
+    <t>898126606</t>
+  </si>
+  <si>
+    <t>899331536</t>
+  </si>
+  <si>
+    <t>899244721</t>
+  </si>
+  <si>
+    <t>898960616</t>
+  </si>
+  <si>
+    <t>898450428</t>
+  </si>
+  <si>
+    <t>897926279</t>
+  </si>
+  <si>
+    <t>896082447</t>
+  </si>
+  <si>
+    <t>895514317</t>
+  </si>
+  <si>
+    <t>879473472</t>
+  </si>
+  <si>
+    <t>872878123</t>
+  </si>
+  <si>
+    <t>855720227</t>
+  </si>
+  <si>
+    <t>846244790</t>
+  </si>
+  <si>
+    <t>836961585</t>
+  </si>
+  <si>
+    <t>834854329</t>
+  </si>
+  <si>
+    <t>829657554</t>
+  </si>
+  <si>
+    <t>830100982</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>801377460</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>903377947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>902857196</t>
-  </si>
-  <si>
-    <t>904680604</t>
-  </si>
-  <si>
-    <t>688972086</t>
-  </si>
-  <si>
-    <t>905062588</t>
-  </si>
-  <si>
-    <t>905512160</t>
-  </si>
-  <si>
-    <t>902728546</t>
-  </si>
-  <si>
-    <t>755793126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>804545055</t>
-  </si>
-  <si>
-    <t>905373993</t>
-  </si>
-  <si>
-    <t>896579780</t>
-  </si>
-  <si>
-    <t>896159427</t>
-  </si>
-  <si>
-    <t>896087206</t>
-  </si>
-  <si>
-    <t>895728131</t>
-  </si>
-  <si>
-    <t>758636348</t>
-  </si>
-  <si>
-    <t>758293116</t>
-  </si>
-  <si>
-    <t>693253183</t>
-  </si>
-  <si>
-    <t>689409120</t>
-  </si>
-  <si>
-    <t>878302946</t>
-  </si>
-  <si>
-    <t>829987340</t>
-  </si>
-  <si>
-    <t>807213677</t>
-  </si>
-  <si>
-    <t>737885065</t>
-  </si>
-  <si>
-    <t>802061204</t>
-  </si>
-  <si>
-    <t>745908677</t>
-  </si>
-  <si>
-    <t>896904038</t>
-  </si>
-  <si>
-    <t>845715857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>822449140</t>
-  </si>
-  <si>
-    <t>880744887</t>
-  </si>
-  <si>
-    <t>875835757</t>
-  </si>
-  <si>
-    <t>865784692</t>
-  </si>
-  <si>
-    <t>865710341</t>
-  </si>
-  <si>
-    <t>859983938</t>
-  </si>
-  <si>
-    <t>789524364</t>
-  </si>
-  <si>
-    <t>786602544</t>
-  </si>
-  <si>
-    <t>178877696</t>
-  </si>
-  <si>
-    <t>758985984</t>
-  </si>
-  <si>
-    <t>736472220</t>
-  </si>
-  <si>
-    <t>727616892</t>
-  </si>
-  <si>
-    <t>715573451</t>
-  </si>
-  <si>
-    <t>707624528</t>
-  </si>
-  <si>
-    <t>700249869</t>
-  </si>
-  <si>
-    <t>674237205</t>
-  </si>
-  <si>
-    <t>636345567</t>
-  </si>
-  <si>
-    <t>672300047</t>
-  </si>
-  <si>
-    <t>906455948</t>
-  </si>
-  <si>
-    <t>897156059</t>
-  </si>
-  <si>
-    <t>897070979</t>
-  </si>
-  <si>
-    <t>896959685</t>
-  </si>
-  <si>
-    <t>896941402</t>
-  </si>
-  <si>
-    <t>906405299</t>
-  </si>
-  <si>
-    <t>904319807</t>
-  </si>
-  <si>
-    <t>904000548</t>
-  </si>
-  <si>
-    <t>900246046</t>
-  </si>
-  <si>
-    <t>897492108</t>
-  </si>
-  <si>
-    <t>897271650</t>
-  </si>
-  <si>
-    <t>798626010</t>
-  </si>
-  <si>
-    <t>870141441</t>
-  </si>
-  <si>
-    <t>886900087</t>
-  </si>
-  <si>
-    <t>896710815</t>
-  </si>
-  <si>
-    <t>894310816</t>
-  </si>
-  <si>
-    <t>891748380</t>
-  </si>
-  <si>
-    <t>889015289</t>
-  </si>
-  <si>
-    <t>854673716</t>
-  </si>
-  <si>
-    <t>851535215</t>
-  </si>
-  <si>
-    <t>848575746</t>
-  </si>
-  <si>
-    <t>830624577</t>
-  </si>
-  <si>
-    <t>811354343</t>
-  </si>
-  <si>
-    <t>736228192</t>
-  </si>
-  <si>
-    <t>751425129</t>
-  </si>
-  <si>
-    <t>749993949</t>
-  </si>
-  <si>
-    <t>749293241</t>
-  </si>
-  <si>
-    <t>700264066</t>
-  </si>
-  <si>
-    <t>712693245</t>
-  </si>
-  <si>
-    <t>873103133</t>
-  </si>
-  <si>
-    <t>874845344</t>
-  </si>
-  <si>
-    <t>876584800</t>
-  </si>
-  <si>
-    <t>876310511</t>
-  </si>
-  <si>
-    <t>688485535</t>
-  </si>
-  <si>
-    <t>846400269</t>
-  </si>
-  <si>
-    <t>853240970</t>
-  </si>
-  <si>
-    <t>825992492</t>
-  </si>
-  <si>
-    <t>794392336</t>
-  </si>
-  <si>
-    <t>801895701</t>
-  </si>
-  <si>
-    <t>800208203</t>
-  </si>
-  <si>
-    <t>800129516</t>
-  </si>
-  <si>
-    <t>797921933</t>
-  </si>
-  <si>
-    <t>769363726</t>
-  </si>
-  <si>
-    <t>774746949</t>
-  </si>
-  <si>
-    <t>773578988</t>
-  </si>
-  <si>
-    <t>785945548</t>
-  </si>
-  <si>
-    <t>894116239</t>
-  </si>
-  <si>
-    <t>818924973</t>
-  </si>
-  <si>
-    <t>799828557</t>
-  </si>
-  <si>
-    <t>806651257</t>
-  </si>
-  <si>
-    <t>897249656</t>
-  </si>
-  <si>
-    <t>896865429</t>
-  </si>
-  <si>
-    <t>674542299</t>
-  </si>
-  <si>
-    <t>896903931</t>
-  </si>
-  <si>
-    <t>767043502</t>
+    <t>659285047</t>
+  </si>
+  <si>
+    <t>723820688</t>
+  </si>
+  <si>
+    <t>721323925</t>
+  </si>
+  <si>
+    <t>712086028</t>
+  </si>
+  <si>
+    <t>780585141</t>
+  </si>
+  <si>
+    <t>757134303</t>
+  </si>
+  <si>
+    <t>760459341</t>
+  </si>
+  <si>
+    <t>800743506</t>
+  </si>
+  <si>
+    <t>827191069</t>
+  </si>
+  <si>
+    <t>826206116</t>
+  </si>
+  <si>
+    <t>814074757</t>
+  </si>
+  <si>
+    <t>897294884</t>
+  </si>
+  <si>
+    <t>897806638</t>
+  </si>
+  <si>
+    <t>899284941</t>
+  </si>
+  <si>
+    <t>882109675</t>
+  </si>
+  <si>
+    <t>884429089</t>
+  </si>
+  <si>
+    <t>860745953</t>
+  </si>
+  <si>
+    <t>874870979</t>
+  </si>
+  <si>
+    <t>855532580</t>
+  </si>
+  <si>
+    <t>853874737</t>
+  </si>
+  <si>
+    <t>879547028</t>
+  </si>
+  <si>
+    <t>819435334</t>
+  </si>
+  <si>
+    <t>880596675</t>
+  </si>
+  <si>
+    <t>740580042</t>
+  </si>
+  <si>
+    <t>898956903</t>
+  </si>
+  <si>
+    <t>822193383</t>
+  </si>
+  <si>
+    <t>897895805</t>
+  </si>
+  <si>
+    <t>898142892</t>
+  </si>
+  <si>
+    <t>841169679</t>
+  </si>
+  <si>
+    <t>899907855</t>
+  </si>
+  <si>
+    <t>899138352</t>
+  </si>
+  <si>
+    <t>837347669</t>
+  </si>
+  <si>
+    <t>833052602</t>
+  </si>
+  <si>
+    <t>899625119</t>
+  </si>
+  <si>
+    <t>772506733</t>
+  </si>
+  <si>
+    <t>889065979</t>
+  </si>
+  <si>
+    <t>897589572</t>
+  </si>
+  <si>
+    <t>819184676</t>
+  </si>
+  <si>
+    <t>900047451</t>
+  </si>
+  <si>
+    <t>686886452</t>
+  </si>
+  <si>
+    <t>900532726</t>
+  </si>
+  <si>
+    <t>898755479</t>
+  </si>
+  <si>
+    <t>897809426</t>
+  </si>
+  <si>
+    <t>893646160</t>
+  </si>
+  <si>
+    <t>898322445</t>
+  </si>
+  <si>
+    <t>900327002</t>
+  </si>
+  <si>
+    <t>876373543</t>
   </si>
 </sst>
 </file>
@@ -823,7 +964,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D148"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -876,7 +1017,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -885,10 +1026,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -912,7 +1053,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -924,7 +1065,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -933,10 +1074,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -945,10 +1086,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -957,10 +1098,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -969,7 +1110,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>8</v>
@@ -981,10 +1122,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -993,10 +1134,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1005,10 +1146,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1017,10 +1158,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1029,10 +1170,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1041,10 +1182,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1053,10 +1194,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1065,10 +1206,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1077,10 +1218,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1089,10 +1230,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1101,10 +1242,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1113,10 +1254,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1125,10 +1266,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1137,7 +1278,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1149,10 +1290,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1302,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1173,10 +1314,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1188,7 +1329,7 @@
         <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1200,7 +1341,7 @@
         <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1212,7 +1353,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1224,7 +1365,7 @@
         <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1236,7 +1377,7 @@
         <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1248,7 +1389,7 @@
         <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1260,7 +1401,7 @@
         <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1272,7 +1413,7 @@
         <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1284,7 +1425,7 @@
         <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1296,7 +1437,7 @@
         <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1308,7 +1449,7 @@
         <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1320,7 +1461,7 @@
         <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1332,7 +1473,7 @@
         <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1344,7 +1485,7 @@
         <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1356,7 +1497,7 @@
         <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1368,7 +1509,7 @@
         <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1380,7 +1521,7 @@
         <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1392,7 +1533,7 @@
         <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1404,7 +1545,7 @@
         <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1416,7 +1557,7 @@
         <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1428,7 +1569,7 @@
         <v>58</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1440,7 +1581,7 @@
         <v>59</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1452,7 +1593,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1464,7 +1605,7 @@
         <v>61</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1476,7 +1617,7 @@
         <v>62</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1488,7 +1629,7 @@
         <v>63</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1500,7 +1641,7 @@
         <v>64</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1512,7 +1653,7 @@
         <v>65</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1524,7 +1665,7 @@
         <v>66</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1536,7 +1677,7 @@
         <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1548,7 +1689,7 @@
         <v>68</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1560,7 +1701,7 @@
         <v>69</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1572,7 +1713,7 @@
         <v>70</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1584,7 +1725,7 @@
         <v>71</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1596,7 +1737,7 @@
         <v>72</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1608,7 +1749,7 @@
         <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1620,7 +1761,7 @@
         <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1632,7 +1773,7 @@
         <v>75</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1643,7 +1784,7 @@
         <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1654,7 +1795,7 @@
         <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1665,7 +1806,7 @@
         <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1676,7 +1817,7 @@
         <v>79</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1687,7 +1828,7 @@
         <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1698,7 +1839,7 @@
         <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1709,7 +1850,7 @@
         <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1720,7 +1861,7 @@
         <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1731,7 +1872,7 @@
         <v>84</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1742,7 +1883,7 @@
         <v>85</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1753,7 +1894,7 @@
         <v>86</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1764,7 +1905,7 @@
         <v>87</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1775,7 +1916,7 @@
         <v>88</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1962,7 +2103,7 @@
         <v>105</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -1973,7 +2114,7 @@
         <v>106</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -1984,7 +2125,7 @@
         <v>107</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2006,7 +2147,7 @@
         <v>109</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>8</v>
+        <v>110</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2014,12 +2155,518 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>8</v>
-      </c>
       <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B8969-E133-482F-825A-F0A751327385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36D398CD-01E6-47EB-8C5E-05E4281F80E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,208 +48,208 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>935217384</t>
+    <t>843420054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>854860347</t>
+  </si>
+  <si>
+    <t>863785741</t>
+  </si>
+  <si>
+    <t>845319346</t>
+  </si>
+  <si>
+    <t>829749377</t>
+  </si>
+  <si>
+    <t>927945612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>935116958</t>
+  </si>
+  <si>
+    <t>864353846</t>
+  </si>
+  <si>
+    <t>831438308</t>
+  </si>
+  <si>
+    <t>927350110</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>808704310</t>
-  </si>
-  <si>
-    <t>757547058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>806482026</t>
-  </si>
-  <si>
-    <t>179897693</t>
-  </si>
-  <si>
-    <t>813119389</t>
-  </si>
-  <si>
-    <t>804892077</t>
-  </si>
-  <si>
-    <t>782076578</t>
-  </si>
-  <si>
-    <t>770021057</t>
-  </si>
-  <si>
-    <t>732959147</t>
-  </si>
-  <si>
-    <t>728952536</t>
-  </si>
-  <si>
-    <t>695811210</t>
-  </si>
-  <si>
-    <t>689206401</t>
-  </si>
-  <si>
-    <t>684598596</t>
-  </si>
-  <si>
-    <t>663308306</t>
-  </si>
-  <si>
-    <t>657897983</t>
-  </si>
-  <si>
-    <t>919541783</t>
-  </si>
-  <si>
-    <t>884635461</t>
-  </si>
-  <si>
-    <t>865006005</t>
-  </si>
-  <si>
-    <t>858403607</t>
-  </si>
-  <si>
-    <t>843942289</t>
-  </si>
-  <si>
-    <t>831737642</t>
-  </si>
-  <si>
-    <t>829510621</t>
-  </si>
-  <si>
-    <t>820500324</t>
-  </si>
-  <si>
-    <t>892648845</t>
-  </si>
-  <si>
-    <t>919603153</t>
-  </si>
-  <si>
-    <t>924355344</t>
-  </si>
-  <si>
-    <t>918718358</t>
-  </si>
-  <si>
-    <t>918296876</t>
-  </si>
-  <si>
-    <t>853202897</t>
-  </si>
-  <si>
-    <t>875214474</t>
-  </si>
-  <si>
-    <t>875040804</t>
-  </si>
-  <si>
-    <t>866220217</t>
-  </si>
-  <si>
-    <t>936698657</t>
-  </si>
-  <si>
-    <t>770018426</t>
-  </si>
-  <si>
-    <t>800743514</t>
-  </si>
-  <si>
-    <t>813416843</t>
-  </si>
-  <si>
-    <t>791857554</t>
-  </si>
-  <si>
-    <t>936471923</t>
-  </si>
-  <si>
-    <t>936140601</t>
-  </si>
-  <si>
-    <t>931780062</t>
-  </si>
-  <si>
-    <t>930943638</t>
-  </si>
-  <si>
-    <t>930003292</t>
-  </si>
-  <si>
-    <t>930003284</t>
-  </si>
-  <si>
-    <t>929899932</t>
-  </si>
-  <si>
-    <t>927894398</t>
-  </si>
-  <si>
-    <t>935777304</t>
-  </si>
-  <si>
-    <t>935077663</t>
-  </si>
-  <si>
-    <t>933668646</t>
-  </si>
-  <si>
-    <t>933533881</t>
-  </si>
-  <si>
-    <t>932493822</t>
-  </si>
-  <si>
-    <t>723673194</t>
+    <t>927497408</t>
+  </si>
+  <si>
+    <t>914989797</t>
+  </si>
+  <si>
+    <t>911250615</t>
+  </si>
+  <si>
+    <t>902831076</t>
+  </si>
+  <si>
+    <t>868389820</t>
+  </si>
+  <si>
+    <t>723311803</t>
+  </si>
+  <si>
+    <t>937117293</t>
+  </si>
+  <si>
+    <t>937115925</t>
+  </si>
+  <si>
+    <t>936394703</t>
+  </si>
+  <si>
+    <t>934845474</t>
+  </si>
+  <si>
+    <t>933544490</t>
+  </si>
+  <si>
+    <t>931021863</t>
+  </si>
+  <si>
+    <t>929094039</t>
+  </si>
+  <si>
+    <t>870708603</t>
+  </si>
+  <si>
+    <t>911320491</t>
+  </si>
+  <si>
+    <t>927249320</t>
+  </si>
+  <si>
+    <t>926974761</t>
+  </si>
+  <si>
+    <t>925895652</t>
+  </si>
+  <si>
+    <t>925172979</t>
+  </si>
+  <si>
+    <t>855309351</t>
+  </si>
+  <si>
+    <t>809464633</t>
+  </si>
+  <si>
+    <t>829864291</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>761624018</t>
-  </si>
-  <si>
-    <t>915577252</t>
-  </si>
-  <si>
-    <t>908561198</t>
-  </si>
-  <si>
-    <t>912560442</t>
-  </si>
-  <si>
-    <t>926134572</t>
-  </si>
-  <si>
-    <t>925949277</t>
-  </si>
-  <si>
-    <t>925947461</t>
-  </si>
-  <si>
-    <t>866311636</t>
-  </si>
-  <si>
-    <t>920784471</t>
-  </si>
-  <si>
-    <t>925172979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>936607559</t>
-  </si>
-  <si>
-    <t>935899330</t>
+    <t>716018399</t>
+  </si>
+  <si>
+    <t>928632359</t>
+  </si>
+  <si>
+    <t>927630404</t>
+  </si>
+  <si>
+    <t>926898515</t>
+  </si>
+  <si>
+    <t>927050546</t>
+  </si>
+  <si>
+    <t>927514277</t>
+  </si>
+  <si>
+    <t>926836861</t>
+  </si>
+  <si>
+    <t>926742614</t>
+  </si>
+  <si>
+    <t>927352181</t>
+  </si>
+  <si>
+    <t>176795783</t>
+  </si>
+  <si>
+    <t>927396618</t>
+  </si>
+  <si>
+    <t>926705652</t>
+  </si>
+  <si>
+    <t>852397896</t>
+  </si>
+  <si>
+    <t>930667492</t>
+  </si>
+  <si>
+    <t>929171118</t>
+  </si>
+  <si>
+    <t>923110153</t>
+  </si>
+  <si>
+    <t>912763046</t>
+  </si>
+  <si>
+    <t>897262592</t>
+  </si>
+  <si>
+    <t>885084099</t>
+  </si>
+  <si>
+    <t>880852359</t>
+  </si>
+  <si>
+    <t>851218168</t>
+  </si>
+  <si>
+    <t>795340649</t>
+  </si>
+  <si>
+    <t>760738686</t>
+  </si>
+  <si>
+    <t>760044556</t>
+  </si>
+  <si>
+    <t>762803504</t>
+  </si>
+  <si>
+    <t>910988140</t>
+  </si>
+  <si>
+    <t>939341636</t>
+  </si>
+  <si>
+    <t>857974954</t>
+  </si>
+  <si>
+    <t>782587756</t>
+  </si>
+  <si>
+    <t>719181954</t>
+  </si>
+  <si>
+    <t>901748297</t>
+  </si>
+  <si>
+    <t>882073822</t>
   </si>
 </sst>
 </file>
@@ -762,7 +762,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -771,10 +771,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -783,7 +783,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>6</v>
@@ -795,10 +795,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -810,7 +810,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -846,7 +846,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -855,10 +855,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -867,10 +867,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -903,10 +903,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -915,10 +915,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -927,10 +927,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -939,10 +939,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -951,10 +951,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -963,10 +963,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -975,10 +975,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -987,10 +987,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1023,10 +1023,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1047,10 +1047,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1059,10 +1059,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1107,10 +1107,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1143,10 +1143,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1155,10 +1155,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1167,10 +1167,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1179,10 +1179,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1191,10 +1191,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1203,10 +1203,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1227,10 +1227,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1239,10 +1239,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1251,10 +1251,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1263,10 +1263,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1275,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1299,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1311,10 +1311,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1323,10 +1323,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1335,10 +1335,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1371,10 +1371,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1383,10 +1383,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1407,10 +1407,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1419,10 +1419,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1431,10 +1431,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1443,10 +1443,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1455,10 +1455,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1482,7 +1482,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>70</v>
+        <v>12</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1494,7 +1494,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB3D5E72-6EE4-4DB3-8668-773DF6ADA92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5F38445-77FB-4F8F-8A24-26C84CC0BFB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="269">
   <si>
     <t>Status</t>
   </si>
@@ -48,667 +48,796 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>790505071</t>
-  </si>
-  <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>791711637</t>
-  </si>
-  <si>
-    <t>792875688</t>
-  </si>
-  <si>
-    <t>792443305</t>
-  </si>
-  <si>
-    <t>793385372</t>
-  </si>
-  <si>
-    <t>796600645</t>
-  </si>
-  <si>
-    <t>797200940</t>
-  </si>
-  <si>
-    <t>799306554</t>
-  </si>
-  <si>
-    <t>800798344</t>
-  </si>
-  <si>
-    <t>802107403</t>
-  </si>
-  <si>
-    <t>801844113</t>
-  </si>
-  <si>
-    <t>802999346</t>
-  </si>
-  <si>
-    <t>803953599</t>
-  </si>
-  <si>
-    <t>804319485</t>
-  </si>
-  <si>
-    <t>804464877</t>
-  </si>
-  <si>
-    <t>804646846</t>
-  </si>
-  <si>
-    <t>805379744</t>
-  </si>
-  <si>
-    <t>806642538</t>
-  </si>
-  <si>
-    <t>806637264</t>
-  </si>
-  <si>
-    <t>807214972</t>
-  </si>
-  <si>
-    <t>808624690</t>
-  </si>
-  <si>
-    <t>810548994</t>
-  </si>
-  <si>
-    <t>812124638</t>
-  </si>
-  <si>
-    <t>814984583</t>
-  </si>
-  <si>
-    <t>815435031</t>
-  </si>
-  <si>
-    <t>816830503</t>
-  </si>
-  <si>
-    <t>816161859</t>
-  </si>
-  <si>
-    <t>818322780</t>
-  </si>
-  <si>
-    <t>819826151</t>
-  </si>
-  <si>
-    <t>818312518</t>
-  </si>
-  <si>
-    <t>818719258</t>
-  </si>
-  <si>
-    <t>818936043</t>
-  </si>
-  <si>
-    <t>820237216</t>
-  </si>
-  <si>
-    <t>821362146</t>
-  </si>
-  <si>
-    <t>822867168</t>
-  </si>
-  <si>
-    <t>827109616</t>
-  </si>
-  <si>
-    <t>831845999</t>
-  </si>
-  <si>
-    <t>832929453</t>
-  </si>
-  <si>
-    <t>836177166</t>
-  </si>
-  <si>
-    <t>840927242</t>
-  </si>
-  <si>
-    <t>840842656</t>
-  </si>
-  <si>
-    <t>841072303</t>
-  </si>
-  <si>
-    <t>841582293</t>
-  </si>
-  <si>
-    <t>841570991</t>
-  </si>
-  <si>
-    <t>842988929</t>
-  </si>
-  <si>
-    <t>843569033</t>
-  </si>
-  <si>
-    <t>847235383</t>
-  </si>
-  <si>
-    <t>848186007</t>
-  </si>
-  <si>
-    <t>707716027</t>
-  </si>
-  <si>
-    <t>724447887</t>
-  </si>
-  <si>
-    <t>840956506</t>
-  </si>
-  <si>
-    <t>667077915</t>
-  </si>
-  <si>
-    <t>667077402</t>
-  </si>
-  <si>
-    <t>667076370</t>
-  </si>
-  <si>
-    <t>671724585</t>
-  </si>
-  <si>
-    <t>671630063</t>
-  </si>
-  <si>
-    <t>672021122</t>
-  </si>
-  <si>
-    <t>674545870</t>
-  </si>
-  <si>
-    <t>677469318</t>
-  </si>
-  <si>
-    <t>676952520</t>
-  </si>
-  <si>
-    <t>678513882</t>
-  </si>
-  <si>
-    <t>679675946</t>
-  </si>
-  <si>
-    <t>678295118</t>
-  </si>
-  <si>
-    <t>681028688</t>
-  </si>
-  <si>
-    <t>834776431</t>
-  </si>
-  <si>
-    <t>681960930</t>
-  </si>
-  <si>
-    <t>683241842</t>
-  </si>
-  <si>
-    <t>688514409</t>
-  </si>
-  <si>
-    <t>688909815</t>
-  </si>
-  <si>
-    <t>688902778</t>
-  </si>
-  <si>
-    <t>690649482</t>
-  </si>
-  <si>
-    <t>689951394</t>
-  </si>
-  <si>
-    <t>693798161</t>
-  </si>
-  <si>
-    <t>694105200</t>
-  </si>
-  <si>
-    <t>695367205</t>
-  </si>
-  <si>
-    <t>694386206</t>
-  </si>
-  <si>
-    <t>695757322</t>
-  </si>
-  <si>
-    <t>695881882</t>
-  </si>
-  <si>
-    <t>698232414</t>
-  </si>
-  <si>
-    <t>698796046</t>
-  </si>
-  <si>
-    <t>701575833</t>
-  </si>
-  <si>
-    <t>704960735</t>
-  </si>
-  <si>
-    <t>708738921</t>
-  </si>
-  <si>
-    <t>708881374</t>
-  </si>
-  <si>
-    <t>709802122</t>
-  </si>
-  <si>
-    <t>710417225</t>
-  </si>
-  <si>
-    <t>714475104</t>
-  </si>
-  <si>
-    <t>714344805</t>
-  </si>
-  <si>
-    <t>715836700</t>
-  </si>
-  <si>
-    <t>717830263</t>
-  </si>
-  <si>
-    <t>723912915</t>
-  </si>
-  <si>
-    <t>724160985</t>
-  </si>
-  <si>
-    <t>729389654</t>
-  </si>
-  <si>
-    <t>729759393</t>
-  </si>
-  <si>
-    <t>730447574</t>
-  </si>
-  <si>
-    <t>732401389</t>
-  </si>
-  <si>
-    <t>731716332</t>
-  </si>
-  <si>
-    <t>732467810</t>
-  </si>
-  <si>
-    <t>736821012</t>
-  </si>
-  <si>
-    <t>929358368</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>775270998</t>
-  </si>
-  <si>
-    <t>799245588</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>938259623</t>
-  </si>
-  <si>
-    <t>847602509</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
     <t>937260077</t>
   </si>
   <si>
-    <t>936902133</t>
-  </si>
-  <si>
-    <t>768290409</t>
-  </si>
-  <si>
-    <t>760518625</t>
-  </si>
-  <si>
-    <t>826161360</t>
-  </si>
-  <si>
-    <t>876665328</t>
-  </si>
-  <si>
-    <t>901789721</t>
-  </si>
-  <si>
-    <t>914014638</t>
-  </si>
-  <si>
-    <t>899577997</t>
-  </si>
-  <si>
-    <t>879957433</t>
-  </si>
-  <si>
-    <t>824292324</t>
-  </si>
-  <si>
-    <t>865902435</t>
-  </si>
-  <si>
-    <t>821906108</t>
-  </si>
-  <si>
-    <t>816267383</t>
-  </si>
-  <si>
-    <t>768418984</t>
-  </si>
-  <si>
-    <t>712207558</t>
-  </si>
-  <si>
-    <t>750793865</t>
-  </si>
-  <si>
-    <t>735697512</t>
-  </si>
-  <si>
-    <t>724681485</t>
-  </si>
-  <si>
-    <t>709294056</t>
-  </si>
-  <si>
-    <t>694147715</t>
-  </si>
-  <si>
-    <t>691078830</t>
-  </si>
-  <si>
-    <t>680148750</t>
-  </si>
-  <si>
-    <t>664433392</t>
-  </si>
-  <si>
-    <t>644380267</t>
-  </si>
-  <si>
-    <t>709628998</t>
-  </si>
-  <si>
-    <t>785471297</t>
-  </si>
-  <si>
-    <t>880209337</t>
-  </si>
-  <si>
-    <t>938291246</t>
-  </si>
-  <si>
-    <t>936607559</t>
-  </si>
-  <si>
-    <t>936536485</t>
-  </si>
-  <si>
-    <t>935964407</t>
-  </si>
-  <si>
-    <t>935825491</t>
-  </si>
-  <si>
-    <t>934982517</t>
-  </si>
-  <si>
-    <t>934597828</t>
-  </si>
-  <si>
-    <t>932561412</t>
-  </si>
-  <si>
-    <t>932010998</t>
-  </si>
-  <si>
-    <t>931689107</t>
-  </si>
-  <si>
-    <t>931141489</t>
-  </si>
-  <si>
-    <t>929932543</t>
-  </si>
-  <si>
-    <t>929356925</t>
-  </si>
-  <si>
-    <t>928242878</t>
-  </si>
-  <si>
-    <t>927916092</t>
-  </si>
-  <si>
-    <t>927757355</t>
-  </si>
-  <si>
-    <t>926360615</t>
-  </si>
-  <si>
-    <t>925345104</t>
-  </si>
-  <si>
-    <t>921418699</t>
-  </si>
-  <si>
-    <t>921324400</t>
-  </si>
-  <si>
-    <t>921242610</t>
-  </si>
-  <si>
-    <t>920804097</t>
-  </si>
-  <si>
-    <t>918557392</t>
-  </si>
-  <si>
-    <t>918158464</t>
-  </si>
-  <si>
-    <t>895703811</t>
-  </si>
-  <si>
-    <t>907744696</t>
-  </si>
-  <si>
-    <t>903521601</t>
-  </si>
-  <si>
-    <t>882987377</t>
-  </si>
-  <si>
-    <t>878673643</t>
-  </si>
-  <si>
-    <t>878629017</t>
-  </si>
-  <si>
-    <t>870978917</t>
-  </si>
-  <si>
-    <t>854907726</t>
-  </si>
-  <si>
-    <t>826206124</t>
-  </si>
-  <si>
-    <t>838805475</t>
-  </si>
-  <si>
-    <t>838805442</t>
-  </si>
-  <si>
-    <t>829516503</t>
-  </si>
-  <si>
-    <t>824041994</t>
-  </si>
-  <si>
-    <t>805911546</t>
-  </si>
-  <si>
-    <t>780955310</t>
-  </si>
-  <si>
-    <t>939049338</t>
-  </si>
-  <si>
-    <t>938756990</t>
-  </si>
-  <si>
-    <t>938684317</t>
-  </si>
-  <si>
-    <t>729827109</t>
-  </si>
-  <si>
-    <t>758200178</t>
-  </si>
-  <si>
-    <t>762597254</t>
-  </si>
-  <si>
-    <t>760869481</t>
-  </si>
-  <si>
-    <t>758030948</t>
-  </si>
-  <si>
-    <t>754157810</t>
-  </si>
-  <si>
-    <t>731406637</t>
-  </si>
-  <si>
-    <t>729764542</t>
-  </si>
-  <si>
-    <t>728879762</t>
-  </si>
-  <si>
-    <t>720201643</t>
-  </si>
-  <si>
-    <t>714965419</t>
-  </si>
-  <si>
-    <t>753602287</t>
-  </si>
-  <si>
-    <t>840465748</t>
-  </si>
-  <si>
-    <t>857779254</t>
-  </si>
-  <si>
-    <t>827848825</t>
-  </si>
-  <si>
-    <t>914058924</t>
-  </si>
-  <si>
-    <t>174603161</t>
-  </si>
-  <si>
-    <t>725879666</t>
-  </si>
-  <si>
-    <t>709119246</t>
-  </si>
-  <si>
-    <t>903753675</t>
-  </si>
-  <si>
-    <t>882763844</t>
-  </si>
-  <si>
-    <t>883536686</t>
-  </si>
-  <si>
-    <t>789110891</t>
-  </si>
-  <si>
-    <t>864545565</t>
-  </si>
-  <si>
-    <t>872245430</t>
-  </si>
-  <si>
-    <t>921424911</t>
-  </si>
-  <si>
-    <t>896451428</t>
-  </si>
-  <si>
-    <t>174742308</t>
-  </si>
-  <si>
-    <t>889325068</t>
-  </si>
-  <si>
-    <t>928526114</t>
-  </si>
-  <si>
-    <t>849674514</t>
-  </si>
-  <si>
-    <t>825215571</t>
-  </si>
-  <si>
-    <t>825235082</t>
-  </si>
-  <si>
-    <t>928609787</t>
-  </si>
-  <si>
-    <t>176843351</t>
-  </si>
-  <si>
-    <t>706740655</t>
-  </si>
-  <si>
-    <t>761129596</t>
-  </si>
-  <si>
-    <t>771250200</t>
-  </si>
-  <si>
-    <t>924924958</t>
-  </si>
-  <si>
-    <t>759508207</t>
-  </si>
-  <si>
-    <t>743507612</t>
-  </si>
-  <si>
-    <t>940049913</t>
-  </si>
-  <si>
-    <t>939056556</t>
+    <t>688909823</t>
+  </si>
+  <si>
+    <t>692846540</t>
+  </si>
+  <si>
+    <t>692776440</t>
+  </si>
+  <si>
+    <t>692044096</t>
+  </si>
+  <si>
+    <t>694418348</t>
+  </si>
+  <si>
+    <t>693798179</t>
+  </si>
+  <si>
+    <t>695367213</t>
+  </si>
+  <si>
+    <t>694260211</t>
+  </si>
+  <si>
+    <t>695757330</t>
+  </si>
+  <si>
+    <t>698796053</t>
+  </si>
+  <si>
+    <t>701109757</t>
+  </si>
+  <si>
+    <t>701223871</t>
+  </si>
+  <si>
+    <t>702582523</t>
+  </si>
+  <si>
+    <t>702141965</t>
+  </si>
+  <si>
+    <t>702751714</t>
+  </si>
+  <si>
+    <t>703216550</t>
+  </si>
+  <si>
+    <t>705011983</t>
+  </si>
+  <si>
+    <t>708064146</t>
+  </si>
+  <si>
+    <t>708738939</t>
+  </si>
+  <si>
+    <t>710236765</t>
+  </si>
+  <si>
+    <t>714523069</t>
+  </si>
+  <si>
+    <t>710224241</t>
+  </si>
+  <si>
+    <t>738459258</t>
+  </si>
+  <si>
+    <t>738515323</t>
+  </si>
+  <si>
+    <t>744454624</t>
+  </si>
+  <si>
+    <t>740198936</t>
+  </si>
+  <si>
+    <t>742842358</t>
+  </si>
+  <si>
+    <t>745346159</t>
+  </si>
+  <si>
+    <t>746988686</t>
+  </si>
+  <si>
+    <t>751250865</t>
+  </si>
+  <si>
+    <t>754064263</t>
+  </si>
+  <si>
+    <t>758803724</t>
+  </si>
+  <si>
+    <t>759015740</t>
+  </si>
+  <si>
+    <t>761352222</t>
+  </si>
+  <si>
+    <t>762562993</t>
+  </si>
+  <si>
+    <t>765368471</t>
+  </si>
+  <si>
+    <t>768934220</t>
+  </si>
+  <si>
+    <t>771400490</t>
+  </si>
+  <si>
+    <t>770533127</t>
+  </si>
+  <si>
+    <t>771788985</t>
+  </si>
+  <si>
+    <t>774464428</t>
+  </si>
+  <si>
+    <t>782983096</t>
+  </si>
+  <si>
+    <t>784135760</t>
+  </si>
+  <si>
+    <t>788454068</t>
+  </si>
+  <si>
+    <t>788736621</t>
+  </si>
+  <si>
+    <t>794439319</t>
+  </si>
+  <si>
+    <t>796070989</t>
+  </si>
+  <si>
+    <t>801656277</t>
+  </si>
+  <si>
+    <t>801618178</t>
+  </si>
+  <si>
+    <t>802045876</t>
+  </si>
+  <si>
+    <t>803955842</t>
+  </si>
+  <si>
+    <t>803562838</t>
+  </si>
+  <si>
+    <t>805379751</t>
+  </si>
+  <si>
+    <t>806637272</t>
+  </si>
+  <si>
+    <t>807214980</t>
+  </si>
+  <si>
+    <t>809721727</t>
+  </si>
+  <si>
+    <t>810656193</t>
+  </si>
+  <si>
+    <t>812124646</t>
+  </si>
+  <si>
+    <t>811863566</t>
+  </si>
+  <si>
+    <t>815713429</t>
+  </si>
+  <si>
+    <t>815435049</t>
+  </si>
+  <si>
+    <t>821033317</t>
+  </si>
+  <si>
+    <t>822864363</t>
+  </si>
+  <si>
+    <t>825048295</t>
+  </si>
+  <si>
+    <t>822295980</t>
+  </si>
+  <si>
+    <t>823074517</t>
+  </si>
+  <si>
+    <t>823298603</t>
+  </si>
+  <si>
+    <t>826795845</t>
+  </si>
+  <si>
+    <t>826134417</t>
+  </si>
+  <si>
+    <t>828047559</t>
+  </si>
+  <si>
+    <t>828500144</t>
+  </si>
+  <si>
+    <t>830848390</t>
+  </si>
+  <si>
+    <t>830880864</t>
+  </si>
+  <si>
+    <t>833184363</t>
+  </si>
+  <si>
+    <t>834178802</t>
+  </si>
+  <si>
+    <t>833639085</t>
+  </si>
+  <si>
+    <t>836519912</t>
+  </si>
+  <si>
+    <t>842399705</t>
+  </si>
+  <si>
+    <t>846628414</t>
+  </si>
+  <si>
+    <t>847520487</t>
+  </si>
+  <si>
+    <t>848982892</t>
+  </si>
+  <si>
+    <t>849516830</t>
+  </si>
+  <si>
+    <t>855372029</t>
+  </si>
+  <si>
+    <t>853420390</t>
+  </si>
+  <si>
+    <t>853950933</t>
+  </si>
+  <si>
+    <t>854447319</t>
+  </si>
+  <si>
+    <t>860459449</t>
+  </si>
+  <si>
+    <t>861115750</t>
+  </si>
+  <si>
+    <t>863113993</t>
+  </si>
+  <si>
+    <t>862205394</t>
+  </si>
+  <si>
+    <t>862343047</t>
+  </si>
+  <si>
+    <t>864196757</t>
+  </si>
+  <si>
+    <t>865541894</t>
+  </si>
+  <si>
+    <t>868261813</t>
+  </si>
+  <si>
+    <t>870477258</t>
+  </si>
+  <si>
+    <t>870136953</t>
+  </si>
+  <si>
+    <t>873038008</t>
+  </si>
+  <si>
+    <t>872543875</t>
+  </si>
+  <si>
+    <t>874218476</t>
+  </si>
+  <si>
+    <t>876562731</t>
+  </si>
+  <si>
+    <t>895545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>741752244</t>
+  </si>
+  <si>
+    <t>935314744</t>
+  </si>
+  <si>
+    <t>837385784</t>
+  </si>
+  <si>
+    <t>785219688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>915209070</t>
+  </si>
+  <si>
+    <t>775814415</t>
+  </si>
+  <si>
+    <t>846064065</t>
+  </si>
+  <si>
+    <t>928336977</t>
+  </si>
+  <si>
+    <t>871428375</t>
+  </si>
+  <si>
+    <t>915509115</t>
+  </si>
+  <si>
+    <t>891836912</t>
+  </si>
+  <si>
+    <t>902556947</t>
+  </si>
+  <si>
+    <t>743949384</t>
+  </si>
+  <si>
+    <t>939165290</t>
+  </si>
+  <si>
+    <t>929053100</t>
+  </si>
+  <si>
+    <t>929730657</t>
+  </si>
+  <si>
+    <t>847886375</t>
+  </si>
+  <si>
+    <t>923836963</t>
+  </si>
+  <si>
+    <t>925092052</t>
+  </si>
+  <si>
+    <t>927982102</t>
+  </si>
+  <si>
+    <t>174756324</t>
+  </si>
+  <si>
+    <t>179500826</t>
+  </si>
+  <si>
+    <t>883206066</t>
+  </si>
+  <si>
+    <t>916573060</t>
+  </si>
+  <si>
+    <t>916216462</t>
+  </si>
+  <si>
+    <t>915476026</t>
+  </si>
+  <si>
+    <t>915096477</t>
+  </si>
+  <si>
+    <t>914333418</t>
+  </si>
+  <si>
+    <t>914196237</t>
+  </si>
+  <si>
+    <t>912376641</t>
+  </si>
+  <si>
+    <t>881998037</t>
+  </si>
+  <si>
+    <t>881970093</t>
+  </si>
+  <si>
+    <t>878464431</t>
+  </si>
+  <si>
+    <t>862297375</t>
+  </si>
+  <si>
+    <t>821555277</t>
+  </si>
+  <si>
+    <t>764662338</t>
+  </si>
+  <si>
+    <t>754782153</t>
+  </si>
+  <si>
+    <t>739794141</t>
+  </si>
+  <si>
+    <t>704406473</t>
+  </si>
+  <si>
+    <t>703192173</t>
+  </si>
+  <si>
+    <t>675787794</t>
+  </si>
+  <si>
+    <t>667997120</t>
+  </si>
+  <si>
+    <t>640970129</t>
+  </si>
+  <si>
+    <t>622755670</t>
+  </si>
+  <si>
+    <t>816854941</t>
+  </si>
+  <si>
+    <t>940536794</t>
+  </si>
+  <si>
+    <t>936061781</t>
+  </si>
+  <si>
+    <t>932402203</t>
+  </si>
+  <si>
+    <t>930978469</t>
+  </si>
+  <si>
+    <t>931012417</t>
+  </si>
+  <si>
+    <t>930302447</t>
+  </si>
+  <si>
+    <t>930128768</t>
+  </si>
+  <si>
+    <t>928053978</t>
+  </si>
+  <si>
+    <t>929717191</t>
+  </si>
+  <si>
+    <t>930026350</t>
+  </si>
+  <si>
+    <t>929785321</t>
+  </si>
+  <si>
+    <t>929766073</t>
+  </si>
+  <si>
+    <t>928438369</t>
+  </si>
+  <si>
+    <t>929514358</t>
+  </si>
+  <si>
+    <t>929276362</t>
+  </si>
+  <si>
+    <t>929275893</t>
+  </si>
+  <si>
+    <t>929223315</t>
+  </si>
+  <si>
+    <t>926679246</t>
+  </si>
+  <si>
+    <t>925405221</t>
+  </si>
+  <si>
+    <t>921973131</t>
+  </si>
+  <si>
+    <t>919797625</t>
+  </si>
+  <si>
+    <t>919797435</t>
+  </si>
+  <si>
+    <t>825104684</t>
+  </si>
+  <si>
+    <t>720215775</t>
+  </si>
+  <si>
+    <t>734333911</t>
+  </si>
+  <si>
+    <t>780526079</t>
+  </si>
+  <si>
+    <t>765514298</t>
+  </si>
+  <si>
+    <t>761530207</t>
+  </si>
+  <si>
+    <t>878471360</t>
+  </si>
+  <si>
+    <t>912825514</t>
+  </si>
+  <si>
+    <t>916540853</t>
+  </si>
+  <si>
+    <t>917038733</t>
+  </si>
+  <si>
+    <t>914010974</t>
+  </si>
+  <si>
+    <t>905998039</t>
+  </si>
+  <si>
+    <t>902296569</t>
+  </si>
+  <si>
+    <t>882394715</t>
+  </si>
+  <si>
+    <t>883996856</t>
+  </si>
+  <si>
+    <t>848851543</t>
+  </si>
+  <si>
+    <t>835142948</t>
+  </si>
+  <si>
+    <t>826251724</t>
+  </si>
+  <si>
+    <t>822360495</t>
+  </si>
+  <si>
+    <t>812488678</t>
+  </si>
+  <si>
+    <t>811360241</t>
+  </si>
+  <si>
+    <t>802948947</t>
+  </si>
+  <si>
+    <t>793842331</t>
+  </si>
+  <si>
+    <t>789811555</t>
+  </si>
+  <si>
+    <t>788884694</t>
+  </si>
+  <si>
+    <t>939993238</t>
+  </si>
+  <si>
+    <t>940190477</t>
+  </si>
+  <si>
+    <t>940686649</t>
+  </si>
+  <si>
+    <t>940113313</t>
+  </si>
+  <si>
+    <t>940084555</t>
+  </si>
+  <si>
+    <t>940025079</t>
+  </si>
+  <si>
+    <t>938875592</t>
+  </si>
+  <si>
+    <t>932285657</t>
+  </si>
+  <si>
+    <t>935165930</t>
+  </si>
+  <si>
+    <t>938260068</t>
+  </si>
+  <si>
+    <t>936212038</t>
+  </si>
+  <si>
+    <t>933681763</t>
+  </si>
+  <si>
+    <t>933681755</t>
+  </si>
+  <si>
+    <t>932209632</t>
+  </si>
+  <si>
+    <t>931199412</t>
+  </si>
+  <si>
+    <t>931166460</t>
+  </si>
+  <si>
+    <t>931018844</t>
+  </si>
+  <si>
+    <t>930769389</t>
+  </si>
+  <si>
+    <t>932551348</t>
+  </si>
+  <si>
+    <t>919793616</t>
+  </si>
+  <si>
+    <t>924990470</t>
+  </si>
+  <si>
+    <t>784597175</t>
+  </si>
+  <si>
+    <t>717762680</t>
+  </si>
+  <si>
+    <t>849698885</t>
+  </si>
+  <si>
+    <t>908345147</t>
+  </si>
+  <si>
+    <t>913400119</t>
+  </si>
+  <si>
+    <t>912148917</t>
+  </si>
+  <si>
+    <t>850664057</t>
+  </si>
+  <si>
+    <t>842818357</t>
+  </si>
+  <si>
+    <t>841621653</t>
+  </si>
+  <si>
+    <t>826827473</t>
+  </si>
+  <si>
+    <t>801711213</t>
+  </si>
+  <si>
+    <t>939898965</t>
+  </si>
+  <si>
+    <t>175702780</t>
+  </si>
+  <si>
+    <t>917665469</t>
+  </si>
+  <si>
+    <t>931649069</t>
+  </si>
+  <si>
+    <t>725061364</t>
+  </si>
+  <si>
+    <t>931262582</t>
+  </si>
+  <si>
+    <t>931434736</t>
+  </si>
+  <si>
+    <t>930164888</t>
+  </si>
+  <si>
+    <t>930759299</t>
+  </si>
+  <si>
+    <t>929354516</t>
+  </si>
+  <si>
+    <t>929784720</t>
+  </si>
+  <si>
+    <t>929537441</t>
+  </si>
+  <si>
+    <t>929748956</t>
+  </si>
+  <si>
+    <t>766499507</t>
+  </si>
+  <si>
+    <t>840243228</t>
+  </si>
+  <si>
+    <t>897549121</t>
+  </si>
+  <si>
+    <t>912693714</t>
+  </si>
+  <si>
+    <t>931018208</t>
+  </si>
+  <si>
+    <t>916755709</t>
+  </si>
+  <si>
+    <t>886315690</t>
+  </si>
+  <si>
+    <t>898443217</t>
+  </si>
+  <si>
+    <t>870448267</t>
+  </si>
+  <si>
+    <t>786601439</t>
+  </si>
+  <si>
+    <t>826594073</t>
+  </si>
+  <si>
+    <t>931174027</t>
+  </si>
+  <si>
+    <t>932443090</t>
+  </si>
+  <si>
+    <t>932616141</t>
+  </si>
+  <si>
+    <t>932559077</t>
+  </si>
+  <si>
+    <t>847462375</t>
+  </si>
+  <si>
+    <t>844786024</t>
+  </si>
+  <si>
+    <t>178897199</t>
+  </si>
+  <si>
+    <t>940112562</t>
   </si>
 </sst>
 </file>
@@ -1168,7 +1297,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D219"/>
+  <dimension ref="A1:D259"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -1194,10 +1323,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -1206,10 +1335,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -1218,10 +1347,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -1230,10 +1359,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -1242,10 +1371,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -1254,10 +1383,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1266,10 +1395,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -1278,10 +1407,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1419,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1431,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1443,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1326,10 +1455,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1467,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1479,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1491,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1503,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1515,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1527,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1539,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1551,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1563,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1575,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1587,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1470,10 +1599,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1482,10 +1611,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1623,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1506,10 +1635,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1518,10 +1647,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1659,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1542,10 +1671,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1554,10 +1683,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1566,10 +1695,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1578,10 +1707,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1590,10 +1719,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1602,10 +1731,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1614,10 +1743,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1626,10 +1755,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1638,10 +1767,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1650,10 +1779,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1662,10 +1791,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1674,10 +1803,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1686,10 +1815,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1698,10 +1827,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1710,10 +1839,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1722,10 +1851,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1734,10 +1863,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1746,10 +1875,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1758,10 +1887,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1770,10 +1899,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1782,10 +1911,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1794,10 +1923,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1806,10 +1935,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1818,10 +1947,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1830,10 +1959,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1842,10 +1971,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1854,10 +1983,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1866,10 +1995,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1878,10 +2007,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1890,10 +2019,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1902,10 +2031,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1914,10 +2043,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1926,10 +2055,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1938,10 +2067,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1950,10 +2079,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1962,10 +2091,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1974,10 +2103,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1985,10 +2114,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1996,10 +2125,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -2007,10 +2136,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -2018,10 +2147,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -2029,10 +2158,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -2040,10 +2169,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -2051,10 +2180,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -2062,10 +2191,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -2073,10 +2202,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -2084,10 +2213,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -2095,10 +2224,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -2106,10 +2235,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -2117,10 +2246,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -2128,10 +2257,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -2139,10 +2268,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -2150,10 +2279,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -2161,10 +2290,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -2172,10 +2301,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -2183,10 +2312,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -2194,10 +2323,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -2205,10 +2334,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -2216,10 +2345,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -2227,10 +2356,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -2238,10 +2367,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -2249,10 +2378,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -2260,10 +2389,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -2271,10 +2400,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -2282,10 +2411,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2293,10 +2422,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2304,10 +2433,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2315,10 +2444,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2326,10 +2455,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2337,10 +2466,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>4</v>
@@ -2348,10 +2477,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>106</v>
+        <v>5</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2359,10 +2488,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>4</v>
@@ -2370,10 +2499,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>4</v>
@@ -2381,10 +2510,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>4</v>
@@ -2392,10 +2521,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>4</v>
@@ -2403,10 +2532,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>4</v>
@@ -2414,10 +2543,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>4</v>
@@ -2425,10 +2554,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>4</v>
@@ -2436,10 +2565,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>4</v>
@@ -2447,10 +2576,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>4</v>
@@ -2458,10 +2587,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>4</v>
@@ -2469,10 +2598,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>4</v>
@@ -2480,10 +2609,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>4</v>
@@ -2491,10 +2620,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>4</v>
@@ -2502,10 +2631,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>4</v>
@@ -2513,10 +2642,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>4</v>
@@ -2524,10 +2653,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>4</v>
@@ -2535,10 +2664,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>4</v>
@@ -2546,10 +2675,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>4</v>
@@ -2557,10 +2686,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>4</v>
@@ -2568,10 +2697,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>4</v>
@@ -2579,10 +2708,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>4</v>
@@ -2590,10 +2719,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>4</v>
@@ -2601,10 +2730,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>4</v>
@@ -2612,10 +2741,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>4</v>
@@ -2623,10 +2752,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>4</v>
@@ -2634,10 +2763,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>4</v>
@@ -2645,10 +2774,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>4</v>
@@ -2656,10 +2785,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>4</v>
@@ -2667,10 +2796,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>4</v>
@@ -2678,10 +2807,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>4</v>
@@ -2689,10 +2818,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>4</v>
@@ -2700,10 +2829,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>4</v>
@@ -2711,10 +2840,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>4</v>
@@ -2722,10 +2851,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>4</v>
@@ -2733,10 +2862,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>4</v>
@@ -2744,10 +2873,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>4</v>
@@ -2755,10 +2884,10 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>4</v>
@@ -2766,10 +2895,10 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>4</v>
@@ -2777,10 +2906,10 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>4</v>
@@ -2788,10 +2917,10 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>4</v>
@@ -2799,10 +2928,10 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>4</v>
@@ -2810,10 +2939,10 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>4</v>
@@ -2821,10 +2950,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>4</v>
@@ -2832,10 +2961,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>4</v>
@@ -2843,10 +2972,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>4</v>
@@ -2854,10 +2983,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>4</v>
@@ -2865,10 +2994,10 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>4</v>
@@ -2876,10 +3005,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>4</v>
@@ -2887,10 +3016,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>4</v>
@@ -2898,10 +3027,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>4</v>
@@ -2909,10 +3038,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>4</v>
@@ -2920,10 +3049,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>4</v>
@@ -2931,10 +3060,10 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>4</v>
@@ -2942,10 +3071,10 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>4</v>
@@ -2953,10 +3082,10 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>4</v>
@@ -2964,10 +3093,10 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>4</v>
@@ -2975,10 +3104,10 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>4</v>
@@ -2986,10 +3115,10 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>4</v>
@@ -2997,10 +3126,10 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>4</v>
@@ -3008,10 +3137,10 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>4</v>
@@ -3019,10 +3148,10 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>4</v>
@@ -3030,10 +3159,10 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>4</v>
@@ -3041,10 +3170,10 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>4</v>
@@ -3052,10 +3181,10 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>111</v>
+        <v>175</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>4</v>
@@ -3063,10 +3192,10 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="4" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>4</v>
@@ -3074,10 +3203,10 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>4</v>
@@ -3085,10 +3214,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="4" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>4</v>
@@ -3096,10 +3225,10 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>4</v>
@@ -3107,10 +3236,10 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="4" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>4</v>
@@ -3118,10 +3247,10 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>4</v>
@@ -3129,10 +3258,10 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>4</v>
@@ -3140,10 +3269,10 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>4</v>
@@ -3151,10 +3280,10 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="4" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>4</v>
@@ -3162,10 +3291,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>4</v>
@@ -3173,10 +3302,10 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="4" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>4</v>
@@ -3184,10 +3313,10 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>4</v>
@@ -3195,10 +3324,10 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="4" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>4</v>
@@ -3206,10 +3335,10 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>4</v>
@@ -3217,10 +3346,10 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>4</v>
@@ -3228,10 +3357,10 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>4</v>
@@ -3239,10 +3368,10 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>4</v>
@@ -3250,10 +3379,10 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>4</v>
@@ -3261,10 +3390,10 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="4" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>4</v>
@@ -3272,10 +3401,10 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>4</v>
@@ -3283,10 +3412,10 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>4</v>
@@ -3294,10 +3423,10 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>4</v>
@@ -3305,10 +3434,10 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>4</v>
@@ -3316,10 +3445,10 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>4</v>
@@ -3327,10 +3456,10 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="4" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>4</v>
@@ -3338,10 +3467,10 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>4</v>
@@ -3349,10 +3478,10 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="4" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>4</v>
@@ -3360,10 +3489,10 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>4</v>
@@ -3371,10 +3500,10 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="4" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>4</v>
@@ -3382,10 +3511,10 @@
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>4</v>
@@ -3393,10 +3522,10 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>4</v>
@@ -3404,10 +3533,10 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>4</v>
@@ -3415,10 +3544,10 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="4" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>4</v>
@@ -3426,10 +3555,10 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>4</v>
@@ -3437,10 +3566,10 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="4" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>4</v>
@@ -3448,10 +3577,10 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>4</v>
@@ -3459,10 +3588,10 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="4" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>4</v>
@@ -3470,10 +3599,10 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>4</v>
@@ -3481,10 +3610,10 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="4" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>4</v>
@@ -3492,10 +3621,10 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>211</v>
+        <v>9</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>4</v>
@@ -3503,10 +3632,10 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="4" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>4</v>
@@ -3514,10 +3643,10 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>4</v>
@@ -3525,10 +3654,10 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="4" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>4</v>
@@ -3536,10 +3665,10 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>4</v>
@@ -3547,10 +3676,10 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="4" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>4</v>
@@ -3558,10 +3687,10 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>4</v>
@@ -3569,10 +3698,10 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="4" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>4</v>
@@ -3580,10 +3709,10 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>112</v>
+        <v>8</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>4</v>
@@ -3591,10 +3720,10 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>4</v>
@@ -3602,10 +3731,10 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>4</v>
@@ -3613,10 +3742,10 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="4" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>4</v>
@@ -3624,10 +3753,10 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>4</v>
@@ -3635,10 +3764,10 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>106</v>
+        <v>7</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>4</v>
@@ -3646,12 +3775,452 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>112</v>
+        <v>7</v>
       </c>
       <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C259" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -3678,31 +4247,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\WWG00M.ROOTDOM.NET\BFS-HOME\BE56740-R0562683\ICM\Desktop\PROJETOS\GIT.VICTOR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77BC1E91-24DA-4FA3-9A5F-9DC9B94C5BBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3C829D9-D189-4133-B1FF-C92527E813EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="838" uniqueCount="287">
   <si>
     <t>Status</t>
   </si>
@@ -48,295 +48,850 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>711435036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>712547060</t>
+  </si>
+  <si>
+    <t>713550998</t>
+  </si>
+  <si>
+    <t>713903361</t>
+  </si>
+  <si>
+    <t>718659521</t>
+  </si>
+  <si>
+    <t>719201737</t>
+  </si>
+  <si>
+    <t>722809401</t>
+  </si>
+  <si>
+    <t>724116375</t>
+  </si>
+  <si>
+    <t>728187380</t>
+  </si>
+  <si>
+    <t>726700119</t>
+  </si>
+  <si>
+    <t>861221764</t>
+  </si>
+  <si>
+    <t>732293927</t>
+  </si>
+  <si>
+    <t>738459050</t>
+  </si>
+  <si>
+    <t>738902091</t>
+  </si>
+  <si>
+    <t>760789119</t>
+  </si>
+  <si>
+    <t>740567726</t>
+  </si>
+  <si>
+    <t>739984254</t>
+  </si>
+  <si>
+    <t>740455369</t>
+  </si>
+  <si>
+    <t>740087352</t>
+  </si>
+  <si>
+    <t>742898251</t>
+  </si>
+  <si>
+    <t>748712373</t>
+  </si>
+  <si>
+    <t>751071378</t>
+  </si>
+  <si>
+    <t>753377955</t>
+  </si>
+  <si>
+    <t>754952434</t>
+  </si>
+  <si>
+    <t>760695563</t>
+  </si>
+  <si>
+    <t>757071455</t>
+  </si>
+  <si>
+    <t>756958660</t>
+  </si>
+  <si>
+    <t>756956318</t>
+  </si>
+  <si>
+    <t>757059435</t>
+  </si>
+  <si>
+    <t>759015757</t>
+  </si>
+  <si>
+    <t>759485414</t>
+  </si>
+  <si>
+    <t>759564424</t>
+  </si>
+  <si>
+    <t>762203333</t>
+  </si>
+  <si>
+    <t>761911191</t>
+  </si>
+  <si>
+    <t>764477869</t>
+  </si>
+  <si>
+    <t>767145257</t>
+  </si>
+  <si>
+    <t>767582020</t>
+  </si>
+  <si>
+    <t>768935789</t>
+  </si>
+  <si>
+    <t>771384900</t>
+  </si>
+  <si>
+    <t>773758507</t>
+  </si>
+  <si>
+    <t>773449016</t>
+  </si>
+  <si>
+    <t>774621316</t>
+  </si>
+  <si>
+    <t>775071966</t>
+  </si>
+  <si>
+    <t>781343896</t>
+  </si>
+  <si>
+    <t>780632794</t>
+  </si>
+  <si>
+    <t>782403483</t>
+  </si>
+  <si>
+    <t>784085999</t>
+  </si>
+  <si>
+    <t>787434699</t>
+  </si>
+  <si>
+    <t>788347866</t>
+  </si>
+  <si>
+    <t>789341314</t>
+  </si>
+  <si>
+    <t>789356890</t>
+  </si>
+  <si>
+    <t>790490837</t>
+  </si>
+  <si>
+    <t>790033710</t>
+  </si>
+  <si>
+    <t>790367753</t>
+  </si>
+  <si>
+    <t>791955630</t>
+  </si>
+  <si>
+    <t>792144382</t>
+  </si>
+  <si>
+    <t>792221321</t>
+  </si>
+  <si>
+    <t>792209474</t>
+  </si>
+  <si>
+    <t>795622608</t>
+  </si>
+  <si>
+    <t>796074601</t>
+  </si>
+  <si>
+    <t>797609017</t>
+  </si>
+  <si>
+    <t>800216024</t>
+  </si>
+  <si>
+    <t>801009634</t>
+  </si>
+  <si>
+    <t>902051568</t>
+  </si>
+  <si>
+    <t>801923883</t>
+  </si>
+  <si>
+    <t>803436447</t>
+  </si>
+  <si>
+    <t>804612038</t>
+  </si>
+  <si>
+    <t>805486119</t>
+  </si>
+  <si>
+    <t>809800620</t>
+  </si>
+  <si>
+    <t>809721735</t>
+  </si>
+  <si>
+    <t>809705621</t>
+  </si>
+  <si>
+    <t>811863574</t>
+  </si>
+  <si>
+    <t>813612730</t>
+  </si>
+  <si>
+    <t>814071860</t>
+  </si>
+  <si>
+    <t>820703787</t>
+  </si>
+  <si>
+    <t>823049162</t>
+  </si>
+  <si>
+    <t>822693010</t>
+  </si>
+  <si>
+    <t>825978939</t>
+  </si>
+  <si>
+    <t>828843114</t>
+  </si>
+  <si>
+    <t>828828446</t>
+  </si>
+  <si>
+    <t>830734426</t>
+  </si>
+  <si>
+    <t>830231050</t>
+  </si>
+  <si>
+    <t>829727993</t>
+  </si>
+  <si>
+    <t>830880872</t>
+  </si>
+  <si>
+    <t>831170513</t>
+  </si>
+  <si>
+    <t>831331941</t>
+  </si>
+  <si>
+    <t>836739981</t>
+  </si>
+  <si>
+    <t>833185782</t>
+  </si>
+  <si>
+    <t>832183564</t>
+  </si>
+  <si>
+    <t>835444062</t>
+  </si>
+  <si>
+    <t>836238281</t>
+  </si>
+  <si>
+    <t>835959234</t>
+  </si>
+  <si>
+    <t>836547384</t>
+  </si>
+  <si>
+    <t>842096368</t>
+  </si>
+  <si>
+    <t>841262979</t>
+  </si>
+  <si>
+    <t>843408166</t>
+  </si>
+  <si>
+    <t>845454259</t>
+  </si>
+  <si>
+    <t>846899734</t>
+  </si>
+  <si>
+    <t>845026370</t>
+  </si>
+  <si>
+    <t>847181959</t>
+  </si>
+  <si>
+    <t>740855303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>844934194</t>
+  </si>
+  <si>
+    <t>926331459</t>
+  </si>
+  <si>
+    <t>855532598</t>
+  </si>
+  <si>
+    <t>875103263</t>
+  </si>
+  <si>
+    <t>820668469</t>
+  </si>
+  <si>
+    <t>932524444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>932648474</t>
+  </si>
+  <si>
+    <t>932634243</t>
+  </si>
+  <si>
+    <t>932211232</t>
+  </si>
+  <si>
+    <t>727942397</t>
+  </si>
+  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>939939553</t>
-  </si>
-  <si>
-    <t>929269912</t>
-  </si>
-  <si>
-    <t>764515833</t>
-  </si>
-  <si>
-    <t>931110633</t>
-  </si>
-  <si>
-    <t>844469464</t>
-  </si>
-  <si>
-    <t>793932934</t>
-  </si>
-  <si>
-    <t>914202787</t>
-  </si>
-  <si>
-    <t>823316413</t>
-  </si>
-  <si>
-    <t>833605714</t>
-  </si>
-  <si>
-    <t>919257000</t>
-  </si>
-  <si>
-    <t>918742572</t>
-  </si>
-  <si>
-    <t>710550322</t>
-  </si>
-  <si>
-    <t>932502523</t>
-  </si>
-  <si>
-    <t>665600627</t>
-  </si>
-  <si>
-    <t>659036762</t>
-  </si>
-  <si>
-    <t>909118360</t>
-  </si>
-  <si>
-    <t>892131388</t>
-  </si>
-  <si>
-    <t>887321630</t>
-  </si>
-  <si>
-    <t>880727510</t>
-  </si>
-  <si>
-    <t>869829824</t>
-  </si>
-  <si>
-    <t>855027136</t>
-  </si>
-  <si>
-    <t>847028655</t>
-  </si>
-  <si>
-    <t>843243548</t>
-  </si>
-  <si>
-    <t>841754389</t>
-  </si>
-  <si>
-    <t>819817820</t>
-  </si>
-  <si>
-    <t>793367305</t>
-  </si>
-  <si>
-    <t>791713633</t>
-  </si>
-  <si>
-    <t>784084331</t>
-  </si>
-  <si>
-    <t>781905546</t>
-  </si>
-  <si>
-    <t>778006753</t>
-  </si>
-  <si>
-    <t>765498922</t>
-  </si>
-  <si>
-    <t>760720890</t>
-  </si>
-  <si>
-    <t>754005308</t>
-  </si>
-  <si>
-    <t>748003104</t>
-  </si>
-  <si>
-    <t>743513438</t>
-  </si>
-  <si>
-    <t>738621287</t>
-  </si>
-  <si>
-    <t>730519588</t>
-  </si>
-  <si>
-    <t>724405133</t>
-  </si>
-  <si>
-    <t>724405125</t>
-  </si>
-  <si>
-    <t>807363720</t>
-  </si>
-  <si>
-    <t>804559890</t>
-  </si>
-  <si>
-    <t>780993253</t>
-  </si>
-  <si>
-    <t>796010191</t>
-  </si>
-  <si>
-    <t>724243419</t>
-  </si>
-  <si>
-    <t>757894310</t>
-  </si>
-  <si>
-    <t>736013859</t>
-  </si>
-  <si>
-    <t>741102754</t>
-  </si>
-  <si>
-    <t>718257359</t>
-  </si>
-  <si>
-    <t>836203566</t>
-  </si>
-  <si>
-    <t>716104918</t>
-  </si>
-  <si>
-    <t>932048543</t>
-  </si>
-  <si>
-    <t>941454880</t>
-  </si>
-  <si>
-    <t>940688330</t>
-  </si>
-  <si>
-    <t>940622172</t>
-  </si>
-  <si>
-    <t>940482346</t>
-  </si>
-  <si>
-    <t>940035532</t>
-  </si>
-  <si>
-    <t>939908657</t>
-  </si>
-  <si>
-    <t>938404666</t>
-  </si>
-  <si>
-    <t>937827107</t>
-  </si>
-  <si>
-    <t>937706988</t>
-  </si>
-  <si>
-    <t>937551822</t>
-  </si>
-  <si>
-    <t>937111718</t>
-  </si>
-  <si>
-    <t>935285225</t>
-  </si>
-  <si>
-    <t>933338463</t>
-  </si>
-  <si>
-    <t>933324984</t>
-  </si>
-  <si>
-    <t>933306122</t>
-  </si>
-  <si>
-    <t>712203623</t>
-  </si>
-  <si>
-    <t>884489273</t>
-  </si>
-  <si>
-    <t>920799065</t>
-  </si>
-  <si>
-    <t>928432396</t>
-  </si>
-  <si>
-    <t>914176809</t>
-  </si>
-  <si>
-    <t>912279910</t>
-  </si>
-  <si>
-    <t>905183665</t>
-  </si>
-  <si>
-    <t>898069590</t>
-  </si>
-  <si>
-    <t>895754319</t>
-  </si>
-  <si>
-    <t>892383963</t>
-  </si>
-  <si>
-    <t>894203334</t>
-  </si>
-  <si>
-    <t>857293256</t>
-  </si>
-  <si>
-    <t>859037545</t>
-  </si>
-  <si>
-    <t>871267039</t>
-  </si>
-  <si>
-    <t>851220347</t>
-  </si>
-  <si>
-    <t>851001606</t>
-  </si>
-  <si>
-    <t>834892030</t>
-  </si>
-  <si>
-    <t>811681646</t>
-  </si>
-  <si>
-    <t>808811776</t>
-  </si>
-  <si>
-    <t>803238017</t>
-  </si>
-  <si>
-    <t>784648424</t>
-  </si>
-  <si>
-    <t>779175441</t>
-  </si>
-  <si>
-    <t>720386469</t>
-  </si>
-  <si>
-    <t>760054464</t>
-  </si>
-  <si>
-    <t>763393471</t>
-  </si>
-  <si>
-    <t>766003069</t>
-  </si>
-  <si>
-    <t>931919660</t>
+    <t>932553534</t>
+  </si>
+  <si>
+    <t>694158431</t>
+  </si>
+  <si>
+    <t>932590965</t>
+  </si>
+  <si>
+    <t>733828937</t>
+  </si>
+  <si>
+    <t>751377239</t>
+  </si>
+  <si>
+    <t>932101698</t>
+  </si>
+  <si>
+    <t>180002267</t>
+  </si>
+  <si>
+    <t>174340665</t>
+  </si>
+  <si>
+    <t>824940492</t>
+  </si>
+  <si>
+    <t>174340780</t>
+  </si>
+  <si>
+    <t>173942131</t>
+  </si>
+  <si>
+    <t>802588255</t>
+  </si>
+  <si>
+    <t>800901898</t>
+  </si>
+  <si>
+    <t>850017769</t>
+  </si>
+  <si>
+    <t>900671680</t>
+  </si>
+  <si>
+    <t>849233261</t>
+  </si>
+  <si>
+    <t>831113042</t>
+  </si>
+  <si>
+    <t>899607109</t>
+  </si>
+  <si>
+    <t>746648017</t>
+  </si>
+  <si>
+    <t>746634462</t>
+  </si>
+  <si>
+    <t>746348709</t>
+  </si>
+  <si>
+    <t>746148588</t>
+  </si>
+  <si>
+    <t>740048610</t>
+  </si>
+  <si>
+    <t>735231015</t>
+  </si>
+  <si>
+    <t>734975372</t>
+  </si>
+  <si>
+    <t>734902814</t>
+  </si>
+  <si>
+    <t>729849137</t>
+  </si>
+  <si>
+    <t>931948107</t>
+  </si>
+  <si>
+    <t>916252806</t>
+  </si>
+  <si>
+    <t>908420403</t>
+  </si>
+  <si>
+    <t>907385912</t>
+  </si>
+  <si>
+    <t>906094580</t>
+  </si>
+  <si>
+    <t>896060286</t>
+  </si>
+  <si>
+    <t>895367146</t>
+  </si>
+  <si>
+    <t>894876071</t>
+  </si>
+  <si>
+    <t>893541627</t>
+  </si>
+  <si>
+    <t>892919667</t>
+  </si>
+  <si>
+    <t>892884556</t>
+  </si>
+  <si>
+    <t>878398811</t>
+  </si>
+  <si>
+    <t>876525506</t>
+  </si>
+  <si>
+    <t>875680724</t>
+  </si>
+  <si>
+    <t>875120739</t>
+  </si>
+  <si>
+    <t>874414547</t>
+  </si>
+  <si>
+    <t>871347658</t>
+  </si>
+  <si>
+    <t>867418927</t>
+  </si>
+  <si>
+    <t>865913374</t>
+  </si>
+  <si>
+    <t>865078038</t>
+  </si>
+  <si>
+    <t>863533968</t>
+  </si>
+  <si>
+    <t>862386947</t>
+  </si>
+  <si>
+    <t>862324674</t>
+  </si>
+  <si>
+    <t>862119355</t>
+  </si>
+  <si>
+    <t>888817289</t>
+  </si>
+  <si>
+    <t>885971303</t>
+  </si>
+  <si>
+    <t>883883567</t>
+  </si>
+  <si>
+    <t>883883518</t>
+  </si>
+  <si>
+    <t>882520079</t>
+  </si>
+  <si>
+    <t>882410214</t>
+  </si>
+  <si>
+    <t>881973337</t>
+  </si>
+  <si>
+    <t>881124865</t>
+  </si>
+  <si>
+    <t>880316835</t>
+  </si>
+  <si>
+    <t>880162775</t>
+  </si>
+  <si>
+    <t>879487274</t>
+  </si>
+  <si>
+    <t>878574262</t>
+  </si>
+  <si>
+    <t>850005830</t>
+  </si>
+  <si>
+    <t>861179939</t>
+  </si>
+  <si>
+    <t>860049372</t>
+  </si>
+  <si>
+    <t>858383395</t>
+  </si>
+  <si>
+    <t>857976157</t>
+  </si>
+  <si>
+    <t>857440352</t>
+  </si>
+  <si>
+    <t>856447515</t>
+  </si>
+  <si>
+    <t>856239946</t>
+  </si>
+  <si>
+    <t>855652529</t>
+  </si>
+  <si>
+    <t>854549197</t>
+  </si>
+  <si>
+    <t>854140799</t>
+  </si>
+  <si>
+    <t>853864639</t>
+  </si>
+  <si>
+    <t>853826851</t>
+  </si>
+  <si>
+    <t>853363616</t>
+  </si>
+  <si>
+    <t>852262942</t>
+  </si>
+  <si>
+    <t>851987424</t>
+  </si>
+  <si>
+    <t>851362420</t>
+  </si>
+  <si>
+    <t>848266122</t>
+  </si>
+  <si>
+    <t>842488037</t>
+  </si>
+  <si>
+    <t>840681377</t>
+  </si>
+  <si>
+    <t>840681369</t>
+  </si>
+  <si>
+    <t>835394887</t>
+  </si>
+  <si>
+    <t>834376265</t>
+  </si>
+  <si>
+    <t>834371852</t>
+  </si>
+  <si>
+    <t>833604675</t>
+  </si>
+  <si>
+    <t>833252939</t>
+  </si>
+  <si>
+    <t>831316702</t>
+  </si>
+  <si>
+    <t>826083705</t>
+  </si>
+  <si>
+    <t>822638510</t>
+  </si>
+  <si>
+    <t>822425793</t>
+  </si>
+  <si>
+    <t>723423699</t>
+  </si>
+  <si>
+    <t>720703887</t>
+  </si>
+  <si>
+    <t>713595548</t>
+  </si>
+  <si>
+    <t>707499400</t>
+  </si>
+  <si>
+    <t>702618152</t>
+  </si>
+  <si>
+    <t>699494997</t>
+  </si>
+  <si>
+    <t>695175459</t>
+  </si>
+  <si>
+    <t>686646989</t>
+  </si>
+  <si>
+    <t>680573155</t>
+  </si>
+  <si>
+    <t>655956286</t>
+  </si>
+  <si>
+    <t>179913029</t>
+  </si>
+  <si>
+    <t>178783423</t>
+  </si>
+  <si>
+    <t>178338194</t>
+  </si>
+  <si>
+    <t>173057369</t>
+  </si>
+  <si>
+    <t>174364749</t>
+  </si>
+  <si>
+    <t>177554171</t>
+  </si>
+  <si>
+    <t>177116088</t>
+  </si>
+  <si>
+    <t>177111527</t>
+  </si>
+  <si>
+    <t>177107608</t>
+  </si>
+  <si>
+    <t>175553001</t>
+  </si>
+  <si>
+    <t>821237421</t>
+  </si>
+  <si>
+    <t>821227307</t>
+  </si>
+  <si>
+    <t>816995660</t>
+  </si>
+  <si>
+    <t>816092856</t>
+  </si>
+  <si>
+    <t>814800086</t>
+  </si>
+  <si>
+    <t>814494682</t>
+  </si>
+  <si>
+    <t>810260731</t>
+  </si>
+  <si>
+    <t>791847092</t>
+  </si>
+  <si>
+    <t>774213254</t>
+  </si>
+  <si>
+    <t>773817857</t>
+  </si>
+  <si>
+    <t>769097332</t>
+  </si>
+  <si>
+    <t>769019658</t>
+  </si>
+  <si>
+    <t>766391738</t>
+  </si>
+  <si>
+    <t>762824898</t>
+  </si>
+  <si>
+    <t>759336427</t>
+  </si>
+  <si>
+    <t>750535761</t>
+  </si>
+  <si>
+    <t>750441143</t>
+  </si>
+  <si>
+    <t>749842955</t>
+  </si>
+  <si>
+    <t>790995249</t>
+  </si>
+  <si>
+    <t>790612455</t>
+  </si>
+  <si>
+    <t>788665853</t>
+  </si>
+  <si>
+    <t>782043966</t>
+  </si>
+  <si>
+    <t>775572682</t>
+  </si>
+  <si>
+    <t>774716181</t>
+  </si>
+  <si>
+    <t>774681476</t>
+  </si>
+  <si>
+    <t>785053400</t>
+  </si>
+  <si>
+    <t>785138003</t>
+  </si>
+  <si>
+    <t>750979498</t>
+  </si>
+  <si>
+    <t>767588456</t>
+  </si>
+  <si>
+    <t>763646910</t>
+  </si>
+  <si>
+    <t>942418447</t>
+  </si>
+  <si>
+    <t>941583126</t>
+  </si>
+  <si>
+    <t>940307378</t>
+  </si>
+  <si>
+    <t>940304540</t>
+  </si>
+  <si>
+    <t>937580375</t>
+  </si>
+  <si>
+    <t>937245912</t>
+  </si>
+  <si>
+    <t>936745250</t>
+  </si>
+  <si>
+    <t>936431505</t>
+  </si>
+  <si>
+    <t>934117874</t>
+  </si>
+  <si>
+    <t>933528733</t>
+  </si>
+  <si>
+    <t>908149440</t>
+  </si>
+  <si>
+    <t>927395164</t>
+  </si>
+  <si>
+    <t>910588924</t>
+  </si>
+  <si>
+    <t>898061365</t>
+  </si>
+  <si>
+    <t>903081317</t>
+  </si>
+  <si>
+    <t>890752664</t>
+  </si>
+  <si>
+    <t>839475641</t>
+  </si>
+  <si>
+    <t>856595966</t>
+  </si>
+  <si>
+    <t>859555710</t>
+  </si>
+  <si>
+    <t>861524233</t>
+  </si>
+  <si>
+    <t>879985780</t>
+  </si>
+  <si>
+    <t>877033427</t>
+  </si>
+  <si>
+    <t>873304293</t>
+  </si>
+  <si>
+    <t>738464456</t>
   </si>
 </sst>
 </file>
@@ -796,7 +1351,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D259"/>
+  <dimension ref="A1:D279"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -822,10 +1377,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -834,10 +1389,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -846,10 +1401,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -858,10 +1413,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -870,10 +1425,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -882,10 +1437,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -894,10 +1449,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -906,10 +1461,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -918,10 +1473,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -930,10 +1485,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -942,10 +1497,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -954,10 +1509,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -966,10 +1521,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -978,10 +1533,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -990,10 +1545,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1002,10 +1557,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1014,10 +1569,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1026,10 +1581,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1038,10 +1593,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1050,10 +1605,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1617,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1629,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1086,10 +1641,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1098,10 +1653,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1110,10 +1665,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1122,10 +1677,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1134,10 +1689,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1146,10 +1701,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1158,10 +1713,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1170,10 +1725,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1182,10 +1737,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1194,10 +1749,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1206,10 +1761,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1218,10 +1773,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1230,10 +1785,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1242,10 +1797,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1254,10 +1809,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1266,10 +1821,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1278,10 +1833,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1845,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1857,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1869,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1326,10 +1881,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1893,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1905,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1917,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1929,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1941,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1953,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1965,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1977,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1989,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1446,10 +2001,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1458,10 +2013,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1470,10 +2025,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1482,10 +2037,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1494,10 +2049,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1506,10 +2061,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1518,10 +2073,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1530,10 +2085,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1542,10 +2097,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1554,10 +2109,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1566,10 +2121,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1578,10 +2133,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1590,10 +2145,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1602,10 +2157,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1613,10 +2168,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1624,10 +2179,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1635,10 +2190,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1646,10 +2201,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1657,10 +2212,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1668,10 +2223,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1679,10 +2234,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1690,10 +2245,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1701,10 +2256,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1712,10 +2267,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1723,10 +2278,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1734,10 +2289,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1745,10 +2300,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1756,10 +2311,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1767,10 +2322,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1778,10 +2333,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1789,10 +2344,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1800,10 +2355,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1811,7 +2366,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>6</v>
@@ -1822,7 +2377,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>6</v>
@@ -1833,7 +2388,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>6</v>
@@ -1844,7 +2399,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>6</v>
@@ -1855,7 +2410,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>6</v>
@@ -1866,7 +2421,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>6</v>
@@ -1877,7 +2432,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>6</v>
@@ -1888,7 +2443,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>6</v>
@@ -1899,509 +2454,2049 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="6"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="6"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="6"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="6"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="6"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="6"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="6"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="6"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="6"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="6"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="6"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="6"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="6"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="6"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="6"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="6"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="6"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="6"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="6"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="6"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="6"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="6"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="6"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="6"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="6"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="6"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="6"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="6"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="6"/>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="6"/>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="6"/>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="6"/>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="6"/>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="6"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="6"/>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="6"/>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="6"/>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C132" s="6"/>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="6"/>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="6"/>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C135" s="6"/>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C136" s="6"/>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C137" s="6"/>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C138" s="6"/>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C139" s="6"/>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C140" s="6"/>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C141" s="6"/>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C142" s="6"/>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C143" s="6"/>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C144" s="6"/>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C145" s="6"/>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C146" s="6"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="6"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="6"/>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="6"/>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="6"/>
-    </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="6"/>
-    </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="6"/>
-    </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="6"/>
-    </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="6"/>
-    </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="6"/>
-    </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="6"/>
-    </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="6"/>
-    </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="6"/>
-    </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="6"/>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="6"/>
-    </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="6"/>
-    </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="6"/>
-    </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C163" s="6"/>
-    </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="6"/>
-    </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="6"/>
-    </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="6"/>
-    </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="6"/>
-    </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="6"/>
-    </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="6"/>
-    </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="6"/>
-    </row>
-    <row r="171" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C171" s="6"/>
-    </row>
-    <row r="172" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C172" s="6"/>
-    </row>
-    <row r="173" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C173" s="6"/>
-    </row>
-    <row r="174" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C174" s="6"/>
-    </row>
-    <row r="175" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C175" s="6"/>
-    </row>
-    <row r="176" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C176" s="6"/>
-    </row>
-    <row r="177" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C177" s="6"/>
-    </row>
-    <row r="178" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C178" s="6"/>
-    </row>
-    <row r="179" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C179" s="6"/>
-    </row>
-    <row r="180" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C180" s="6"/>
-    </row>
-    <row r="181" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C181" s="6"/>
-    </row>
-    <row r="182" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C182" s="6"/>
-    </row>
-    <row r="183" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C183" s="6"/>
-    </row>
-    <row r="184" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C184" s="6"/>
-    </row>
-    <row r="185" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C185" s="6"/>
-    </row>
-    <row r="186" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C186" s="6"/>
-    </row>
-    <row r="187" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C187" s="6"/>
-    </row>
-    <row r="188" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C188" s="6"/>
-    </row>
-    <row r="189" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C189" s="6"/>
-    </row>
-    <row r="190" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C190" s="6"/>
-    </row>
-    <row r="191" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C191" s="6"/>
-    </row>
-    <row r="192" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C192" s="6"/>
-    </row>
-    <row r="193" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C193" s="6"/>
-    </row>
-    <row r="194" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C194" s="6"/>
-    </row>
-    <row r="195" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C195" s="6"/>
-    </row>
-    <row r="196" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C196" s="6"/>
-    </row>
-    <row r="197" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C197" s="6"/>
-    </row>
-    <row r="198" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C198" s="6"/>
-    </row>
-    <row r="199" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C199" s="6"/>
-    </row>
-    <row r="200" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C200" s="6"/>
-    </row>
-    <row r="201" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C201" s="6"/>
-    </row>
-    <row r="202" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C202" s="6"/>
-    </row>
-    <row r="203" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C203" s="6"/>
-    </row>
-    <row r="204" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C204" s="6"/>
-    </row>
-    <row r="205" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C205" s="6"/>
-    </row>
-    <row r="206" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C206" s="6"/>
-    </row>
-    <row r="207" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C207" s="6"/>
-    </row>
-    <row r="208" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C208" s="6"/>
-    </row>
-    <row r="209" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C209" s="6"/>
-    </row>
-    <row r="210" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C210" s="6"/>
-    </row>
-    <row r="211" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C211" s="6"/>
-    </row>
-    <row r="212" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C212" s="6"/>
-    </row>
-    <row r="213" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C213" s="6"/>
-    </row>
-    <row r="214" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C214" s="6"/>
-    </row>
-    <row r="215" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C215" s="6"/>
-    </row>
-    <row r="216" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C216" s="6"/>
-    </row>
-    <row r="217" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C217" s="6"/>
-    </row>
-    <row r="218" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C218" s="6"/>
-    </row>
-    <row r="219" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C219" s="6"/>
-    </row>
-    <row r="220" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C220" s="6"/>
-    </row>
-    <row r="221" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C221" s="6"/>
-    </row>
-    <row r="222" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C222" s="6"/>
-    </row>
-    <row r="223" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C223" s="6"/>
-    </row>
-    <row r="224" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C224" s="6"/>
-    </row>
-    <row r="225" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C225" s="6"/>
-    </row>
-    <row r="226" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C226" s="6"/>
-    </row>
-    <row r="227" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C227" s="6"/>
-    </row>
-    <row r="228" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C228" s="6"/>
-    </row>
-    <row r="229" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C229" s="6"/>
-    </row>
-    <row r="230" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C230" s="6"/>
-    </row>
-    <row r="231" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C231" s="6"/>
-    </row>
-    <row r="232" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C232" s="6"/>
-    </row>
-    <row r="233" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C233" s="6"/>
-    </row>
-    <row r="234" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C234" s="6"/>
-    </row>
-    <row r="235" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C235" s="6"/>
-    </row>
-    <row r="236" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C236" s="6"/>
-    </row>
-    <row r="237" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C237" s="6"/>
-    </row>
-    <row r="238" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C238" s="6"/>
-    </row>
-    <row r="239" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C239" s="6"/>
-    </row>
-    <row r="240" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C240" s="6"/>
-    </row>
-    <row r="241" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C241" s="6"/>
-    </row>
-    <row r="242" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C242" s="6"/>
-    </row>
-    <row r="243" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C243" s="6"/>
-    </row>
-    <row r="244" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C244" s="6"/>
-    </row>
-    <row r="245" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C245" s="6"/>
-    </row>
-    <row r="246" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C246" s="6"/>
-    </row>
-    <row r="247" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C247" s="6"/>
-    </row>
-    <row r="248" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C248" s="6"/>
-    </row>
-    <row r="249" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C249" s="6"/>
-    </row>
-    <row r="250" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C250" s="6"/>
-    </row>
-    <row r="251" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C251" s="6"/>
-    </row>
-    <row r="252" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C252" s="6"/>
-    </row>
-    <row r="253" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C253" s="6"/>
-    </row>
-    <row r="254" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C254" s="6"/>
-    </row>
-    <row r="255" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C255" s="6"/>
-    </row>
-    <row r="256" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C256" s="6"/>
-    </row>
-    <row r="257" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C257" s="6"/>
-    </row>
-    <row r="258" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C258" s="6"/>
-    </row>
-    <row r="259" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C259" s="6"/>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BF0078-D098-4C30-BC5B-D4D03E022FC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C7D4E1-249A-491B-BC84-1425B45C9D4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="174">
   <si>
     <t>Status</t>
   </si>
@@ -48,154 +48,511 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>175406044</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>940394483</t>
-  </si>
-  <si>
-    <t>925527701</t>
-  </si>
-  <si>
-    <t>847391509</t>
-  </si>
-  <si>
-    <t>803954969</t>
-  </si>
-  <si>
-    <t>803954951</t>
-  </si>
-  <si>
-    <t>801093166</t>
-  </si>
-  <si>
-    <t>750827184</t>
-  </si>
-  <si>
-    <t>750490751</t>
-  </si>
-  <si>
-    <t>731547703</t>
-  </si>
-  <si>
-    <t>714529686</t>
-  </si>
-  <si>
-    <t>738541642</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>952692832</t>
-  </si>
-  <si>
-    <t>952333908</t>
-  </si>
-  <si>
-    <t>952109712</t>
-  </si>
-  <si>
-    <t>937454100</t>
-  </si>
-  <si>
-    <t>951305253</t>
-  </si>
-  <si>
-    <t>951219736</t>
-  </si>
-  <si>
-    <t>949344752</t>
-  </si>
-  <si>
-    <t>948673805</t>
-  </si>
-  <si>
-    <t>943918502</t>
-  </si>
-  <si>
-    <t>942656533</t>
-  </si>
-  <si>
-    <t>941055323</t>
-  </si>
-  <si>
-    <t>940932662</t>
-  </si>
-  <si>
-    <t>940901626</t>
-  </si>
-  <si>
-    <t>913809376</t>
-  </si>
-  <si>
-    <t>910867203</t>
-  </si>
-  <si>
-    <t>893359988</t>
-  </si>
-  <si>
-    <t>796314809</t>
-  </si>
-  <si>
-    <t>806387860</t>
-  </si>
-  <si>
-    <t>794393615</t>
-  </si>
-  <si>
-    <t>948763572</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>948763580</t>
-  </si>
-  <si>
-    <t>921477794</t>
-  </si>
-  <si>
-    <t>928044522</t>
-  </si>
-  <si>
-    <t>941820353</t>
-  </si>
-  <si>
-    <t>941454385</t>
-  </si>
-  <si>
-    <t>941248860</t>
-  </si>
-  <si>
-    <t>940853504</t>
-  </si>
-  <si>
-    <t>802932602</t>
-  </si>
-  <si>
-    <t>941052387</t>
-  </si>
-  <si>
-    <t>941068946</t>
-  </si>
-  <si>
-    <t>941693305</t>
-  </si>
-  <si>
-    <t>941064044</t>
-  </si>
-  <si>
-    <t>856058437</t>
-  </si>
-  <si>
-    <t>879783573</t>
-  </si>
-  <si>
-    <t>952668576</t>
+    <t>884964440</t>
+  </si>
+  <si>
+    <t>848558833</t>
+  </si>
+  <si>
+    <t>936616360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>936428030</t>
+  </si>
+  <si>
+    <t>937807745</t>
+  </si>
+  <si>
+    <t>776643334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>898150267</t>
+  </si>
+  <si>
+    <t>797563081</t>
+  </si>
+  <si>
+    <t>752481436</t>
+  </si>
+  <si>
+    <t>926502638</t>
+  </si>
+  <si>
+    <t>837798408</t>
+  </si>
+  <si>
+    <t>861108771</t>
+  </si>
+  <si>
+    <t>846548661</t>
+  </si>
+  <si>
+    <t>954623173</t>
+  </si>
+  <si>
+    <t>179020049</t>
+  </si>
+  <si>
+    <t>933254348</t>
+  </si>
+  <si>
+    <t>899245504</t>
+  </si>
+  <si>
+    <t>845226590</t>
+  </si>
+  <si>
+    <t>871613513</t>
+  </si>
+  <si>
+    <t>884630934</t>
+  </si>
+  <si>
+    <t>638587885</t>
+  </si>
+  <si>
+    <t>782807303</t>
+  </si>
+  <si>
+    <t>782073088</t>
+  </si>
+  <si>
+    <t>746361355</t>
+  </si>
+  <si>
+    <t>742362605</t>
+  </si>
+  <si>
+    <t>725967602</t>
+  </si>
+  <si>
+    <t>723182444</t>
+  </si>
+  <si>
+    <t>719562955</t>
+  </si>
+  <si>
+    <t>714429770</t>
+  </si>
+  <si>
+    <t>667919199</t>
+  </si>
+  <si>
+    <t>924686169</t>
+  </si>
+  <si>
+    <t>929096943</t>
+  </si>
+  <si>
+    <t>939924357</t>
+  </si>
+  <si>
+    <t>928635253</t>
+  </si>
+  <si>
+    <t>928022163</t>
+  </si>
+  <si>
+    <t>916811619</t>
+  </si>
+  <si>
+    <t>865690402</t>
+  </si>
+  <si>
+    <t>859334736</t>
+  </si>
+  <si>
+    <t>844897698</t>
+  </si>
+  <si>
+    <t>838335150</t>
+  </si>
+  <si>
+    <t>829179450</t>
+  </si>
+  <si>
+    <t>827407713</t>
+  </si>
+  <si>
+    <t>821295742</t>
+  </si>
+  <si>
+    <t>829367345</t>
+  </si>
+  <si>
+    <t>918147749</t>
+  </si>
+  <si>
+    <t>936850589</t>
+  </si>
+  <si>
+    <t>944236730</t>
+  </si>
+  <si>
+    <t>943659684</t>
+  </si>
+  <si>
+    <t>943587042</t>
+  </si>
+  <si>
+    <t>943322838</t>
+  </si>
+  <si>
+    <t>943266423</t>
+  </si>
+  <si>
+    <t>942866306</t>
+  </si>
+  <si>
+    <t>942695895</t>
+  </si>
+  <si>
+    <t>923723856</t>
+  </si>
+  <si>
+    <t>953290172</t>
+  </si>
+  <si>
+    <t>752187710</t>
+  </si>
+  <si>
+    <t>769832290</t>
+  </si>
+  <si>
+    <t>763794116</t>
+  </si>
+  <si>
+    <t>951895642</t>
+  </si>
+  <si>
+    <t>951606254</t>
+  </si>
+  <si>
+    <t>951342090</t>
+  </si>
+  <si>
+    <t>951310139</t>
+  </si>
+  <si>
+    <t>946371410</t>
+  </si>
+  <si>
+    <t>945338386</t>
+  </si>
+  <si>
+    <t>945002115</t>
+  </si>
+  <si>
+    <t>950749923</t>
+  </si>
+  <si>
+    <t>949962355</t>
+  </si>
+  <si>
+    <t>949081339</t>
+  </si>
+  <si>
+    <t>949057339</t>
+  </si>
+  <si>
+    <t>948850965</t>
+  </si>
+  <si>
+    <t>948597103</t>
+  </si>
+  <si>
+    <t>947794644</t>
+  </si>
+  <si>
+    <t>897972596</t>
+  </si>
+  <si>
+    <t>914434976</t>
+  </si>
+  <si>
+    <t>904838244</t>
+  </si>
+  <si>
+    <t>904452517</t>
+  </si>
+  <si>
+    <t>897972588</t>
+  </si>
+  <si>
+    <t>866696465</t>
+  </si>
+  <si>
+    <t>886144744</t>
+  </si>
+  <si>
+    <t>890461662</t>
+  </si>
+  <si>
+    <t>868753975</t>
+  </si>
+  <si>
+    <t>842946976</t>
+  </si>
+  <si>
+    <t>855652180</t>
+  </si>
+  <si>
+    <t>850258702</t>
+  </si>
+  <si>
+    <t>844947204</t>
+  </si>
+  <si>
+    <t>846051070</t>
+  </si>
+  <si>
+    <t>849370253</t>
+  </si>
+  <si>
+    <t>717081636</t>
+  </si>
+  <si>
+    <t>773546589</t>
+  </si>
+  <si>
+    <t>787688088</t>
+  </si>
+  <si>
+    <t>796317984</t>
+  </si>
+  <si>
+    <t>726378809</t>
+  </si>
+  <si>
+    <t>739686297</t>
+  </si>
+  <si>
+    <t>894267594</t>
+  </si>
+  <si>
+    <t>944293079</t>
+  </si>
+  <si>
+    <t>944066525</t>
+  </si>
+  <si>
+    <t>931592442</t>
+  </si>
+  <si>
+    <t>914886563</t>
+  </si>
+  <si>
+    <t>898118215</t>
+  </si>
+  <si>
+    <t>881743094</t>
+  </si>
+  <si>
+    <t>866717998</t>
+  </si>
+  <si>
+    <t>863230060</t>
+  </si>
+  <si>
+    <t>861618449</t>
+  </si>
+  <si>
+    <t>856570407</t>
+  </si>
+  <si>
+    <t>835954383</t>
+  </si>
+  <si>
+    <t>921500322</t>
+  </si>
+  <si>
+    <t>930743707</t>
+  </si>
+  <si>
+    <t>935840821</t>
+  </si>
+  <si>
+    <t>928060114</t>
+  </si>
+  <si>
+    <t>860725781</t>
+  </si>
+  <si>
+    <t>742141660</t>
+  </si>
+  <si>
+    <t>173481353</t>
+  </si>
+  <si>
+    <t>923004836</t>
+  </si>
+  <si>
+    <t>921706820</t>
+  </si>
+  <si>
+    <t>912944489</t>
+  </si>
+  <si>
+    <t>943951487</t>
+  </si>
+  <si>
+    <t>868973169</t>
+  </si>
+  <si>
+    <t>855045070</t>
+  </si>
+  <si>
+    <t>818779377</t>
+  </si>
+  <si>
+    <t>796915803</t>
+  </si>
+  <si>
+    <t>772840611</t>
+  </si>
+  <si>
+    <t>943384846</t>
+  </si>
+  <si>
+    <t>821269572</t>
+  </si>
+  <si>
+    <t>805137480</t>
+  </si>
+  <si>
+    <t>867112520</t>
+  </si>
+  <si>
+    <t>889063339</t>
+  </si>
+  <si>
+    <t>887886426</t>
+  </si>
+  <si>
+    <t>823149202</t>
+  </si>
+  <si>
+    <t>921651414</t>
+  </si>
+  <si>
+    <t>926037387</t>
+  </si>
+  <si>
+    <t>882828977</t>
+  </si>
+  <si>
+    <t>875986329</t>
+  </si>
+  <si>
+    <t>834029617</t>
+  </si>
+  <si>
+    <t>808008332</t>
+  </si>
+  <si>
+    <t>923178226</t>
+  </si>
+  <si>
+    <t>942670526</t>
+  </si>
+  <si>
+    <t>943573083</t>
+  </si>
+  <si>
+    <t>900037700</t>
+  </si>
+  <si>
+    <t>844891014</t>
+  </si>
+  <si>
+    <t>800675120</t>
+  </si>
+  <si>
+    <t>181385331</t>
+  </si>
+  <si>
+    <t>813123472</t>
+  </si>
+  <si>
+    <t>911746810</t>
+  </si>
+  <si>
+    <t>893614077</t>
+  </si>
+  <si>
+    <t>942299243</t>
+  </si>
+  <si>
+    <t>941593208</t>
+  </si>
+  <si>
+    <t>732136290</t>
+  </si>
+  <si>
+    <t>944925902</t>
+  </si>
+  <si>
+    <t>945078362</t>
+  </si>
+  <si>
+    <t>943660526</t>
+  </si>
+  <si>
+    <t>934197553</t>
+  </si>
+  <si>
+    <t>933370854</t>
+  </si>
+  <si>
+    <t>916146917</t>
+  </si>
+  <si>
+    <t>856048040</t>
+  </si>
+  <si>
+    <t>880295799</t>
+  </si>
+  <si>
+    <t>945387557</t>
+  </si>
+  <si>
+    <t>800630141</t>
+  </si>
+  <si>
+    <t>938699190</t>
+  </si>
+  <si>
+    <t>940862018</t>
+  </si>
+  <si>
+    <t>812765307</t>
+  </si>
+  <si>
+    <t>901266365</t>
+  </si>
+  <si>
+    <t>901256713</t>
+  </si>
+  <si>
+    <t>953327321</t>
+  </si>
+  <si>
+    <t>947665661</t>
   </si>
 </sst>
 </file>
@@ -655,7 +1012,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -681,7 +1038,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>6</v>
@@ -693,7 +1050,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>6</v>
@@ -705,10 +1062,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -720,7 +1077,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -732,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -741,10 +1098,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -753,10 +1110,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -765,10 +1122,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -777,10 +1134,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -789,10 +1146,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -801,10 +1158,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -813,10 +1170,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -825,10 +1182,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -837,10 +1194,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -849,10 +1206,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -861,10 +1218,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -873,10 +1230,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -885,10 +1242,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -897,10 +1254,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -909,10 +1266,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -921,10 +1278,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -933,10 +1290,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -945,10 +1302,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -957,10 +1314,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -969,10 +1326,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -981,10 +1338,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -993,10 +1350,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1005,10 +1362,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1017,10 +1374,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1029,10 +1386,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1041,10 +1398,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1053,10 +1410,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1068,7 +1425,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1080,7 +1437,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1092,7 +1449,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1104,7 +1461,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1116,7 +1473,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1128,7 +1485,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1140,7 +1497,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1152,7 +1509,7 @@
         <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1164,7 +1521,7 @@
         <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1176,7 +1533,7 @@
         <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1188,7 +1545,7 @@
         <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1200,7 +1557,7 @@
         <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1212,7 +1569,7 @@
         <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1236,84 +1593,1339 @@
         <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D48"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="6"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D49"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="6"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D50"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="6"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D51"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="6"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D52"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="6"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D53"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="6"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D54"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="6"/>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D55"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C56" s="6"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D56"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="6"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D57"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="6"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D58"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="6"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D59"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="6"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D60"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="6"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D61"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C62" s="6"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D62"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C63" s="6"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D63"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C64" s="6"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D64"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="6"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D65"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="6"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1338,31 +2950,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AEE0F6-187E-40AA-A8C0-605155DFB076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C273CAA-5650-4D8D-BCF6-7805CDC5C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="84">
   <si>
     <t>Status</t>
   </si>
@@ -48,376 +48,241 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>892790480</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>854462698</t>
-  </si>
-  <si>
-    <t>808398600</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>809750148</t>
-  </si>
-  <si>
-    <t>809422490</t>
-  </si>
-  <si>
-    <t>808892172</t>
-  </si>
-  <si>
-    <t>807890854</t>
-  </si>
-  <si>
-    <t>886900103</t>
-  </si>
-  <si>
-    <t>955371442</t>
-  </si>
-  <si>
-    <t>960912875</t>
-  </si>
-  <si>
-    <t>960117244</t>
-  </si>
-  <si>
-    <t>960086324</t>
-  </si>
-  <si>
-    <t>959439385</t>
-  </si>
-  <si>
-    <t>959200373</t>
-  </si>
-  <si>
-    <t>958644928</t>
-  </si>
-  <si>
-    <t>958298451</t>
-  </si>
-  <si>
-    <t>957187564</t>
-  </si>
-  <si>
-    <t>956203552</t>
-  </si>
-  <si>
-    <t>956200566</t>
-  </si>
-  <si>
-    <t>956181139</t>
-  </si>
-  <si>
-    <t>955465509</t>
-  </si>
-  <si>
-    <t>955449982</t>
-  </si>
-  <si>
-    <t>954805614</t>
-  </si>
-  <si>
-    <t>954524439</t>
-  </si>
-  <si>
-    <t>954244103</t>
-  </si>
-  <si>
-    <t>954216523</t>
-  </si>
-  <si>
-    <t>954117648</t>
-  </si>
-  <si>
-    <t>953832718</t>
-  </si>
-  <si>
-    <t>952785255</t>
-  </si>
-  <si>
-    <t>951232275</t>
-  </si>
-  <si>
-    <t>951225147</t>
-  </si>
-  <si>
-    <t>175126709</t>
-  </si>
-  <si>
-    <t>967180252</t>
-  </si>
-  <si>
-    <t>967101431</t>
-  </si>
-  <si>
-    <t>966811667</t>
-  </si>
-  <si>
-    <t>966498598</t>
-  </si>
-  <si>
-    <t>966490843</t>
-  </si>
-  <si>
-    <t>965823739</t>
-  </si>
-  <si>
-    <t>963630730</t>
-  </si>
-  <si>
-    <t>178422097</t>
-  </si>
-  <si>
-    <t>942250733</t>
-  </si>
-  <si>
-    <t>948178995</t>
-  </si>
-  <si>
-    <t>950204135</t>
-  </si>
-  <si>
-    <t>950444517</t>
-  </si>
-  <si>
-    <t>950251870</t>
-  </si>
-  <si>
-    <t>939345090</t>
-  </si>
-  <si>
-    <t>938484692</t>
-  </si>
-  <si>
-    <t>930207406</t>
-  </si>
-  <si>
-    <t>928922248</t>
-  </si>
-  <si>
-    <t>926381819</t>
-  </si>
-  <si>
-    <t>911186702</t>
-  </si>
-  <si>
-    <t>924998614</t>
-  </si>
-  <si>
-    <t>923146181</t>
-  </si>
-  <si>
-    <t>922719657</t>
-  </si>
-  <si>
-    <t>921278085</t>
-  </si>
-  <si>
-    <t>920877812</t>
-  </si>
-  <si>
-    <t>920089582</t>
-  </si>
-  <si>
-    <t>919383590</t>
-  </si>
-  <si>
-    <t>914380872</t>
-  </si>
-  <si>
-    <t>919257349</t>
-  </si>
-  <si>
-    <t>917463477</t>
-  </si>
-  <si>
-    <t>913190561</t>
-  </si>
-  <si>
-    <t>896051608</t>
-  </si>
-  <si>
-    <t>907822567</t>
-  </si>
-  <si>
-    <t>907769651</t>
-  </si>
-  <si>
-    <t>893636898</t>
-  </si>
-  <si>
-    <t>882012572</t>
-  </si>
-  <si>
-    <t>879712879</t>
-  </si>
-  <si>
-    <t>876482922</t>
-  </si>
-  <si>
-    <t>875458642</t>
-  </si>
-  <si>
-    <t>878819980</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>853590440</t>
-  </si>
-  <si>
-    <t>828665343</t>
-  </si>
-  <si>
-    <t>838680282</t>
-  </si>
-  <si>
-    <t>811723562</t>
-  </si>
-  <si>
-    <t>765788108</t>
-  </si>
-  <si>
-    <t>929674129</t>
-  </si>
-  <si>
-    <t>181112974</t>
-  </si>
-  <si>
-    <t>957542982</t>
-  </si>
-  <si>
-    <t>936112154</t>
-  </si>
-  <si>
-    <t>930282862</t>
-  </si>
-  <si>
-    <t>958941167</t>
-  </si>
-  <si>
-    <t>762327538</t>
-  </si>
-  <si>
-    <t>860307176</t>
-  </si>
-  <si>
-    <t>844314983</t>
-  </si>
-  <si>
-    <t>840243236</t>
-  </si>
-  <si>
-    <t>958338141</t>
-  </si>
-  <si>
-    <t>958945317</t>
-  </si>
-  <si>
-    <t>954673251</t>
-  </si>
-  <si>
-    <t>847839366</t>
-  </si>
-  <si>
-    <t>804803033</t>
-  </si>
-  <si>
-    <t>923649481</t>
-  </si>
-  <si>
-    <t>968211809</t>
-  </si>
-  <si>
-    <t>880520691</t>
-  </si>
-  <si>
-    <t>968295331</t>
-  </si>
-  <si>
-    <t>967855200</t>
-  </si>
-  <si>
-    <t>741227064</t>
-  </si>
-  <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>758475309</t>
-  </si>
-  <si>
-    <t>968189104</t>
-  </si>
-  <si>
-    <t>963183235</t>
-  </si>
-  <si>
-    <t>942007240</t>
-  </si>
-  <si>
-    <t>891932265</t>
-  </si>
-  <si>
-    <t>857240554</t>
-  </si>
-  <si>
-    <t>690278407</t>
-  </si>
-  <si>
-    <t>181446356</t>
-  </si>
-  <si>
-    <t>968322309</t>
-  </si>
-  <si>
-    <t>967741467</t>
-  </si>
-  <si>
-    <t>967737325</t>
-  </si>
-  <si>
-    <t>934115514</t>
-  </si>
-  <si>
-    <t>959353891</t>
-  </si>
-  <si>
-    <t>967660188</t>
-  </si>
-  <si>
-    <t>967477765</t>
-  </si>
-  <si>
-    <t>967409701</t>
-  </si>
-  <si>
-    <t>967315205</t>
-  </si>
-  <si>
-    <t>967128749</t>
-  </si>
-  <si>
-    <t>965937059</t>
-  </si>
-  <si>
-    <t>965223583</t>
-  </si>
-  <si>
-    <t>964253607</t>
-  </si>
-  <si>
-    <t>959078589</t>
-  </si>
-  <si>
-    <t>957396900</t>
+    <t>939942185</t>
+  </si>
+  <si>
+    <t>856885961</t>
+  </si>
+  <si>
+    <t>897069351</t>
+  </si>
+  <si>
+    <t>965835329</t>
+  </si>
+  <si>
+    <t>963407758</t>
+  </si>
+  <si>
+    <t>962977934</t>
+  </si>
+  <si>
+    <t>962078873</t>
+  </si>
+  <si>
+    <t>959437769</t>
+  </si>
+  <si>
+    <t>916948304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>872112713</t>
+  </si>
+  <si>
+    <t>865315489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>951563562</t>
+  </si>
+  <si>
+    <t>924265576</t>
+  </si>
+  <si>
+    <t>916364239</t>
+  </si>
+  <si>
+    <t>914147610</t>
+  </si>
+  <si>
+    <t>883618609</t>
+  </si>
+  <si>
+    <t>903215634</t>
+  </si>
+  <si>
+    <t>910680473</t>
+  </si>
+  <si>
+    <t>910008600</t>
+  </si>
+  <si>
+    <t>903265977</t>
+  </si>
+  <si>
+    <t>902923717</t>
+  </si>
+  <si>
+    <t>880543685</t>
+  </si>
+  <si>
+    <t>874446994</t>
+  </si>
+  <si>
+    <t>834836250</t>
+  </si>
+  <si>
+    <t>834726345</t>
+  </si>
+  <si>
+    <t>801041751</t>
+  </si>
+  <si>
+    <t>799789395</t>
+  </si>
+  <si>
+    <t>796672420</t>
+  </si>
+  <si>
+    <t>789263781</t>
+  </si>
+  <si>
+    <t>780401711</t>
+  </si>
+  <si>
+    <t>769674007</t>
+  </si>
+  <si>
+    <t>760789333</t>
+  </si>
+  <si>
+    <t>759757614</t>
+  </si>
+  <si>
+    <t>756626382</t>
+  </si>
+  <si>
+    <t>750120945</t>
+  </si>
+  <si>
+    <t>739462384</t>
+  </si>
+  <si>
+    <t>921422972</t>
+  </si>
+  <si>
+    <t>851353270</t>
+  </si>
+  <si>
+    <t>860193857</t>
+  </si>
+  <si>
+    <t>744550066</t>
+  </si>
+  <si>
+    <t>877486450</t>
+  </si>
+  <si>
+    <t>727143731</t>
+  </si>
+  <si>
+    <t>911086472</t>
+  </si>
+  <si>
+    <t>799158633</t>
+  </si>
+  <si>
+    <t>886315708</t>
+  </si>
+  <si>
+    <t>959182902</t>
+  </si>
+  <si>
+    <t>899164341</t>
+  </si>
+  <si>
+    <t>908785292</t>
+  </si>
+  <si>
+    <t>845798903</t>
+  </si>
+  <si>
+    <t>968426688</t>
+  </si>
+  <si>
+    <t>963331677</t>
+  </si>
+  <si>
+    <t>823316421</t>
+  </si>
+  <si>
+    <t>740435817</t>
+  </si>
+  <si>
+    <t>878172919</t>
+  </si>
+  <si>
+    <t>733862340</t>
+  </si>
+  <si>
+    <t>719948824</t>
+  </si>
+  <si>
+    <t>704878655</t>
+  </si>
+  <si>
+    <t>890298692</t>
+  </si>
+  <si>
+    <t>860413750</t>
+  </si>
+  <si>
+    <t>853623134</t>
+  </si>
+  <si>
+    <t>964189843</t>
+  </si>
+  <si>
+    <t>960072571</t>
+  </si>
+  <si>
+    <t>959464375</t>
+  </si>
+  <si>
+    <t>943703649</t>
+  </si>
+  <si>
+    <t>942857842</t>
+  </si>
+  <si>
+    <t>942077177</t>
+  </si>
+  <si>
+    <t>958306148</t>
+  </si>
+  <si>
+    <t>959140710</t>
+  </si>
+  <si>
+    <t>834491064</t>
+  </si>
+  <si>
+    <t>832253466</t>
+  </si>
+  <si>
+    <t>829790777</t>
+  </si>
+  <si>
+    <t>826827481</t>
+  </si>
+  <si>
+    <t>812267056</t>
   </si>
 </sst>
 </file>
@@ -903,10 +768,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>5</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -915,10 +780,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -927,10 +792,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -939,10 +804,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -951,10 +816,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -963,10 +828,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -975,10 +840,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -987,10 +852,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -999,10 +864,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1011,10 +876,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1023,10 +888,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1035,10 +900,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1047,10 +912,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1059,10 +924,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1071,10 +936,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1083,10 +948,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1095,10 +960,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1107,10 +972,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1119,10 +984,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1131,10 +996,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1143,10 +1008,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1155,10 +1020,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1167,10 +1032,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1179,10 +1044,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1191,10 +1056,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1203,10 +1068,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1215,10 +1080,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1227,10 +1092,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1239,10 +1104,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1251,10 +1116,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1263,10 +1128,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1140,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1152,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1164,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1311,10 +1176,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1323,10 +1188,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1335,10 +1200,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1347,10 +1212,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1359,10 +1224,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1371,10 +1236,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1383,10 +1248,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1395,10 +1260,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1407,10 +1272,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1419,10 +1284,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1431,10 +1296,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1443,10 +1308,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1455,10 +1320,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1467,10 +1332,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1479,10 +1344,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1491,10 +1356,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1503,10 +1368,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1515,10 +1380,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1527,10 +1392,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1539,10 +1404,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1551,10 +1416,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1563,10 +1428,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1575,10 +1440,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1587,10 +1452,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1599,10 +1464,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1611,10 +1476,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1623,10 +1488,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1635,10 +1500,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1647,10 +1512,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1659,10 +1524,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1671,10 +1536,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1683,10 +1548,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1694,10 +1559,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1705,10 +1570,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1716,10 +1581,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1727,10 +1592,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1738,10 +1603,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1749,10 +1614,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1760,531 +1625,155 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>78</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C75" s="6"/>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C76" s="6"/>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C77" s="6"/>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C78" s="6"/>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C79" s="6"/>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C80" s="6"/>
+    </row>
+    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C81" s="6"/>
+    </row>
+    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C82" s="6"/>
+    </row>
+    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C83" s="6"/>
+    </row>
+    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C84" s="6"/>
+    </row>
+    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C85" s="6"/>
+    </row>
+    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C86" s="6"/>
+    </row>
+    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C87" s="6"/>
+    </row>
+    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C88" s="6"/>
+    </row>
+    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C89" s="6"/>
+    </row>
+    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C90" s="6"/>
+    </row>
+    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C91" s="6"/>
+    </row>
+    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C92" s="6"/>
+    </row>
+    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C93" s="6"/>
+    </row>
+    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C94" s="6"/>
+    </row>
+    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C95" s="6"/>
+    </row>
+    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C96" s="6"/>
+    </row>
+    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C97" s="6"/>
+    </row>
+    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C98" s="6"/>
+    </row>
+    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C99" s="6"/>
+    </row>
+    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C100" s="6"/>
+    </row>
+    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C101" s="6"/>
+    </row>
+    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C102" s="6"/>
+    </row>
+    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C103" s="6"/>
+    </row>
+    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C104" s="6"/>
+    </row>
+    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C105" s="6"/>
+    </row>
+    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C106" s="6"/>
+    </row>
+    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C107" s="6"/>
+    </row>
+    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C108" s="6"/>
+    </row>
+    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C109" s="6"/>
+    </row>
+    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C110" s="6"/>
+    </row>
+    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C111" s="6"/>
+    </row>
+    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C112" s="6"/>
+    </row>
+    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C113" s="6"/>
+    </row>
+    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C114" s="6"/>
+    </row>
+    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C115" s="6"/>
+    </row>
+    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C116" s="6"/>
+    </row>
+    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C117" s="6"/>
+    </row>
+    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C118" s="6"/>
+    </row>
+    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C119" s="6"/>
+    </row>
+    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C120" s="6"/>
+    </row>
+    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C121" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -2309,31 +1798,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C273CAA-5650-4D8D-BCF6-7805CDC5C9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5B8B7A0-B97A-4DD9-818A-CCA7AE802931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1063" uniqueCount="365">
   <si>
     <t>Status</t>
   </si>
@@ -60,229 +60,1072 @@
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>939942185</t>
-  </si>
-  <si>
-    <t>856885961</t>
-  </si>
-  <si>
-    <t>897069351</t>
-  </si>
-  <si>
-    <t>965835329</t>
-  </si>
-  <si>
-    <t>963407758</t>
-  </si>
-  <si>
-    <t>962977934</t>
-  </si>
-  <si>
-    <t>962078873</t>
-  </si>
-  <si>
-    <t>959437769</t>
-  </si>
-  <si>
-    <t>916948304</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>872112713</t>
-  </si>
-  <si>
-    <t>865315489</t>
-  </si>
-  <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>951563562</t>
-  </si>
-  <si>
-    <t>924265576</t>
-  </si>
-  <si>
-    <t>916364239</t>
-  </si>
-  <si>
-    <t>914147610</t>
-  </si>
-  <si>
-    <t>883618609</t>
-  </si>
-  <si>
-    <t>903215634</t>
-  </si>
-  <si>
-    <t>910680473</t>
-  </si>
-  <si>
-    <t>910008600</t>
-  </si>
-  <si>
-    <t>903265977</t>
-  </si>
-  <si>
-    <t>902923717</t>
-  </si>
-  <si>
-    <t>880543685</t>
-  </si>
-  <si>
-    <t>874446994</t>
-  </si>
-  <si>
-    <t>834836250</t>
-  </si>
-  <si>
-    <t>834726345</t>
-  </si>
-  <si>
-    <t>801041751</t>
-  </si>
-  <si>
-    <t>799789395</t>
-  </si>
-  <si>
-    <t>796672420</t>
-  </si>
-  <si>
-    <t>789263781</t>
-  </si>
-  <si>
-    <t>780401711</t>
-  </si>
-  <si>
-    <t>769674007</t>
-  </si>
-  <si>
-    <t>760789333</t>
-  </si>
-  <si>
-    <t>759757614</t>
-  </si>
-  <si>
-    <t>756626382</t>
-  </si>
-  <si>
-    <t>750120945</t>
-  </si>
-  <si>
-    <t>739462384</t>
-  </si>
-  <si>
-    <t>921422972</t>
-  </si>
-  <si>
-    <t>851353270</t>
-  </si>
-  <si>
-    <t>860193857</t>
-  </si>
-  <si>
-    <t>744550066</t>
-  </si>
-  <si>
-    <t>877486450</t>
-  </si>
-  <si>
-    <t>727143731</t>
-  </si>
-  <si>
-    <t>911086472</t>
-  </si>
-  <si>
-    <t>799158633</t>
-  </si>
-  <si>
-    <t>886315708</t>
-  </si>
-  <si>
-    <t>959182902</t>
-  </si>
-  <si>
-    <t>899164341</t>
-  </si>
-  <si>
-    <t>908785292</t>
-  </si>
-  <si>
-    <t>845798903</t>
-  </si>
-  <si>
-    <t>968426688</t>
-  </si>
-  <si>
     <t>963331677</t>
   </si>
   <si>
-    <t>823316421</t>
-  </si>
-  <si>
-    <t>740435817</t>
-  </si>
-  <si>
-    <t>878172919</t>
-  </si>
-  <si>
-    <t>733862340</t>
-  </si>
-  <si>
-    <t>719948824</t>
-  </si>
-  <si>
-    <t>704878655</t>
-  </si>
-  <si>
-    <t>890298692</t>
-  </si>
-  <si>
-    <t>860413750</t>
-  </si>
-  <si>
-    <t>853623134</t>
-  </si>
-  <si>
-    <t>964189843</t>
-  </si>
-  <si>
-    <t>960072571</t>
-  </si>
-  <si>
-    <t>959464375</t>
-  </si>
-  <si>
-    <t>943703649</t>
-  </si>
-  <si>
-    <t>942857842</t>
-  </si>
-  <si>
-    <t>942077177</t>
-  </si>
-  <si>
-    <t>958306148</t>
-  </si>
-  <si>
-    <t>959140710</t>
-  </si>
-  <si>
-    <t>834491064</t>
-  </si>
-  <si>
-    <t>832253466</t>
-  </si>
-  <si>
-    <t>829790777</t>
-  </si>
-  <si>
-    <t>826827481</t>
-  </si>
-  <si>
-    <t>812267056</t>
+    <t>906982917</t>
+  </si>
+  <si>
+    <t>898450428</t>
+  </si>
+  <si>
+    <t>897926279</t>
+  </si>
+  <si>
+    <t>896082447</t>
+  </si>
+  <si>
+    <t>895514317</t>
+  </si>
+  <si>
+    <t>872878123</t>
+  </si>
+  <si>
+    <t>855720227</t>
+  </si>
+  <si>
+    <t>846244790</t>
+  </si>
+  <si>
+    <t>836961585</t>
+  </si>
+  <si>
+    <t>834854329</t>
+  </si>
+  <si>
+    <t>829657554</t>
+  </si>
+  <si>
+    <t>830100982</t>
+  </si>
+  <si>
+    <t>659285047</t>
+  </si>
+  <si>
+    <t>723820688</t>
+  </si>
+  <si>
+    <t>721323925</t>
+  </si>
+  <si>
+    <t>712086028</t>
+  </si>
+  <si>
+    <t>780585141</t>
+  </si>
+  <si>
+    <t>760459341</t>
+  </si>
+  <si>
+    <t>800743506</t>
+  </si>
+  <si>
+    <t>909528048</t>
+  </si>
+  <si>
+    <t>799103845</t>
+  </si>
+  <si>
+    <t>911617904</t>
+  </si>
+  <si>
+    <t>910221195</t>
+  </si>
+  <si>
+    <t>827831060</t>
+  </si>
+  <si>
+    <t>902961907</t>
+  </si>
+  <si>
+    <t>811766082</t>
+  </si>
+  <si>
+    <t>905594721</t>
+  </si>
+  <si>
+    <t>847003328</t>
+  </si>
+  <si>
+    <t>813157033</t>
+  </si>
+  <si>
+    <t>856769181</t>
+  </si>
+  <si>
+    <t>775110509</t>
+  </si>
+  <si>
+    <t>172455770</t>
+  </si>
+  <si>
+    <t>708039502</t>
+  </si>
+  <si>
+    <t>812025967</t>
+  </si>
+  <si>
+    <t>853433781</t>
+  </si>
+  <si>
+    <t>822910018</t>
+  </si>
+  <si>
+    <t>764665349</t>
+  </si>
+  <si>
+    <t>843618608</t>
+  </si>
+  <si>
+    <t>889148817</t>
+  </si>
+  <si>
+    <t>907844512</t>
+  </si>
+  <si>
+    <t>834029609</t>
+  </si>
+  <si>
+    <t>923213122</t>
+  </si>
+  <si>
+    <t>800478251</t>
+  </si>
+  <si>
+    <t>926785639</t>
+  </si>
+  <si>
+    <t>844571939</t>
+  </si>
+  <si>
+    <t>901455448</t>
+  </si>
+  <si>
+    <t>895392060</t>
+  </si>
+  <si>
+    <t>855824359</t>
+  </si>
+  <si>
+    <t>804619538</t>
+  </si>
+  <si>
+    <t>922676717</t>
+  </si>
+  <si>
+    <t>926164728</t>
+  </si>
+  <si>
+    <t>843455589</t>
+  </si>
+  <si>
+    <t>946039348</t>
+  </si>
+  <si>
+    <t>831270784</t>
+  </si>
+  <si>
+    <t>933867404</t>
+  </si>
+  <si>
+    <t>938335522</t>
+  </si>
+  <si>
+    <t>876181367</t>
+  </si>
+  <si>
+    <t>947826693</t>
+  </si>
+  <si>
+    <t>949229888</t>
+  </si>
+  <si>
+    <t>949219087</t>
+  </si>
+  <si>
+    <t>949028793</t>
+  </si>
+  <si>
+    <t>942916101</t>
+  </si>
+  <si>
+    <t>940533841</t>
+  </si>
+  <si>
+    <t>814620690</t>
+  </si>
+  <si>
+    <t>818996815</t>
+  </si>
+  <si>
+    <t>950454235</t>
+  </si>
+  <si>
+    <t>949306579</t>
+  </si>
+  <si>
+    <t>947789024</t>
+  </si>
+  <si>
+    <t>940646965</t>
+  </si>
+  <si>
+    <t>940443777</t>
+  </si>
+  <si>
+    <t>940315512</t>
+  </si>
+  <si>
+    <t>939911388</t>
+  </si>
+  <si>
+    <t>932424405</t>
+  </si>
+  <si>
+    <t>904974593</t>
+  </si>
+  <si>
+    <t>863435313</t>
+  </si>
+  <si>
+    <t>861583643</t>
+  </si>
+  <si>
+    <t>921382036</t>
+  </si>
+  <si>
+    <t>818282885</t>
+  </si>
+  <si>
+    <t>795430648</t>
+  </si>
+  <si>
+    <t>730565896</t>
+  </si>
+  <si>
+    <t>776512943</t>
+  </si>
+  <si>
+    <t>924546157</t>
+  </si>
+  <si>
+    <t>939888602</t>
+  </si>
+  <si>
+    <t>941740577</t>
+  </si>
+  <si>
+    <t>940695194</t>
+  </si>
+  <si>
+    <t>894871320</t>
+  </si>
+  <si>
+    <t>892036306</t>
+  </si>
+  <si>
+    <t>781434919</t>
+  </si>
+  <si>
+    <t>948762160</t>
+  </si>
+  <si>
+    <t>839516618</t>
+  </si>
+  <si>
+    <t>839516600</t>
+  </si>
+  <si>
+    <t>839516592</t>
+  </si>
+  <si>
+    <t>839516584</t>
+  </si>
+  <si>
+    <t>839516576</t>
+  </si>
+  <si>
+    <t>950862304</t>
+  </si>
+  <si>
+    <t>884698816</t>
+  </si>
+  <si>
+    <t>883249934</t>
+  </si>
+  <si>
+    <t>880281351</t>
+  </si>
+  <si>
+    <t>868005681</t>
+  </si>
+  <si>
+    <t>842264115</t>
+  </si>
+  <si>
+    <t>725377117</t>
+  </si>
+  <si>
+    <t>818769451</t>
+  </si>
+  <si>
+    <t>727840476</t>
+  </si>
+  <si>
+    <t>731606087</t>
+  </si>
+  <si>
+    <t>775510419</t>
+  </si>
+  <si>
+    <t>895987323</t>
+  </si>
+  <si>
+    <t>732565290</t>
+  </si>
+  <si>
+    <t>886869563</t>
+  </si>
+  <si>
+    <t>886869571</t>
+  </si>
+  <si>
+    <t>952668576</t>
+  </si>
+  <si>
+    <t>759865011</t>
+  </si>
+  <si>
+    <t>941622767</t>
+  </si>
+  <si>
+    <t>DUPLICIDADE</t>
+  </si>
+  <si>
+    <t>823503754</t>
+  </si>
+  <si>
+    <t>959830880</t>
+  </si>
+  <si>
+    <t>735684338</t>
+  </si>
+  <si>
+    <t>938159518</t>
+  </si>
+  <si>
+    <t>892790480</t>
+  </si>
+  <si>
+    <t>854462698</t>
+  </si>
+  <si>
+    <t>856372572</t>
+  </si>
+  <si>
+    <t>808398600</t>
+  </si>
+  <si>
+    <t>809750148</t>
+  </si>
+  <si>
+    <t>809422490</t>
+  </si>
+  <si>
+    <t>808892172</t>
+  </si>
+  <si>
+    <t>807890854</t>
+  </si>
+  <si>
+    <t>886900103</t>
+  </si>
+  <si>
+    <t>955371442</t>
+  </si>
+  <si>
+    <t>960912875</t>
+  </si>
+  <si>
+    <t>960117244</t>
+  </si>
+  <si>
+    <t>960086324</t>
+  </si>
+  <si>
+    <t>959439385</t>
+  </si>
+  <si>
+    <t>959200373</t>
+  </si>
+  <si>
+    <t>958644928</t>
+  </si>
+  <si>
+    <t>958298451</t>
+  </si>
+  <si>
+    <t>957187564</t>
+  </si>
+  <si>
+    <t>956203552</t>
+  </si>
+  <si>
+    <t>956200566</t>
+  </si>
+  <si>
+    <t>956181139</t>
+  </si>
+  <si>
+    <t>955465509</t>
+  </si>
+  <si>
+    <t>955449982</t>
+  </si>
+  <si>
+    <t>954805614</t>
+  </si>
+  <si>
+    <t>954524439</t>
+  </si>
+  <si>
+    <t>954244103</t>
+  </si>
+  <si>
+    <t>954216523</t>
+  </si>
+  <si>
+    <t>954117648</t>
+  </si>
+  <si>
+    <t>953832718</t>
+  </si>
+  <si>
+    <t>952785255</t>
+  </si>
+  <si>
+    <t>951232275</t>
+  </si>
+  <si>
+    <t>951225147</t>
+  </si>
+  <si>
+    <t>175126709</t>
+  </si>
+  <si>
+    <t>967180252</t>
+  </si>
+  <si>
+    <t>967101431</t>
+  </si>
+  <si>
+    <t>966811667</t>
+  </si>
+  <si>
+    <t>966498598</t>
+  </si>
+  <si>
+    <t>966490843</t>
+  </si>
+  <si>
+    <t>965823739</t>
+  </si>
+  <si>
+    <t>963630730</t>
+  </si>
+  <si>
+    <t>178422097</t>
+  </si>
+  <si>
+    <t>942250733</t>
+  </si>
+  <si>
+    <t>948178995</t>
+  </si>
+  <si>
+    <t>950204135</t>
+  </si>
+  <si>
+    <t>950444517</t>
+  </si>
+  <si>
+    <t>950251870</t>
+  </si>
+  <si>
+    <t>939345090</t>
+  </si>
+  <si>
+    <t>938484692</t>
+  </si>
+  <si>
+    <t>930207406</t>
+  </si>
+  <si>
+    <t>928922248</t>
+  </si>
+  <si>
+    <t>926381819</t>
+  </si>
+  <si>
+    <t>911186702</t>
+  </si>
+  <si>
+    <t>924998614</t>
+  </si>
+  <si>
+    <t>923146181</t>
+  </si>
+  <si>
+    <t>922719657</t>
+  </si>
+  <si>
+    <t>921278085</t>
+  </si>
+  <si>
+    <t>920877812</t>
+  </si>
+  <si>
+    <t>920089582</t>
+  </si>
+  <si>
+    <t>919383590</t>
+  </si>
+  <si>
+    <t>914380872</t>
+  </si>
+  <si>
+    <t>919257349</t>
+  </si>
+  <si>
+    <t>917463477</t>
+  </si>
+  <si>
+    <t>913190561</t>
+  </si>
+  <si>
+    <t>896051608</t>
+  </si>
+  <si>
+    <t>907822567</t>
+  </si>
+  <si>
+    <t>907769651</t>
+  </si>
+  <si>
+    <t>893636898</t>
+  </si>
+  <si>
+    <t>882012572</t>
+  </si>
+  <si>
+    <t>879712879</t>
+  </si>
+  <si>
+    <t>876482922</t>
+  </si>
+  <si>
+    <t>875458642</t>
+  </si>
+  <si>
+    <t>878819980</t>
+  </si>
+  <si>
+    <t>853590440</t>
+  </si>
+  <si>
+    <t>828665343</t>
+  </si>
+  <si>
+    <t>838680282</t>
+  </si>
+  <si>
+    <t>811723562</t>
+  </si>
+  <si>
+    <t>765788108</t>
+  </si>
+  <si>
+    <t>929674129</t>
+  </si>
+  <si>
+    <t>181112974</t>
+  </si>
+  <si>
+    <t>957542982</t>
+  </si>
+  <si>
+    <t>936112154</t>
+  </si>
+  <si>
+    <t>930282862</t>
+  </si>
+  <si>
+    <t>958941167</t>
+  </si>
+  <si>
+    <t>762327538</t>
+  </si>
+  <si>
+    <t>860307176</t>
+  </si>
+  <si>
+    <t>844314983</t>
+  </si>
+  <si>
+    <t>840243236</t>
+  </si>
+  <si>
+    <t>958338141</t>
+  </si>
+  <si>
+    <t>958945317</t>
+  </si>
+  <si>
+    <t>954673251</t>
+  </si>
+  <si>
+    <t>847839366</t>
+  </si>
+  <si>
+    <t>804803033</t>
+  </si>
+  <si>
+    <t>923649481</t>
+  </si>
+  <si>
+    <t>968211809</t>
+  </si>
+  <si>
+    <t>880520691</t>
+  </si>
+  <si>
+    <t>968295331</t>
+  </si>
+  <si>
+    <t>967855200</t>
+  </si>
+  <si>
+    <t>741227064</t>
+  </si>
+  <si>
+    <t>758475309</t>
+  </si>
+  <si>
+    <t>968189104</t>
+  </si>
+  <si>
+    <t>963183235</t>
+  </si>
+  <si>
+    <t>942007240</t>
+  </si>
+  <si>
+    <t>891932265</t>
+  </si>
+  <si>
+    <t>857240554</t>
+  </si>
+  <si>
+    <t>690278407</t>
+  </si>
+  <si>
+    <t>181446356</t>
+  </si>
+  <si>
+    <t>968322309</t>
+  </si>
+  <si>
+    <t>967741467</t>
+  </si>
+  <si>
+    <t>967737325</t>
+  </si>
+  <si>
+    <t>934115514</t>
+  </si>
+  <si>
+    <t>959353891</t>
+  </si>
+  <si>
+    <t>967660188</t>
+  </si>
+  <si>
+    <t>967477765</t>
+  </si>
+  <si>
+    <t>967409701</t>
+  </si>
+  <si>
+    <t>967315205</t>
+  </si>
+  <si>
+    <t>967128749</t>
+  </si>
+  <si>
+    <t>965937059</t>
+  </si>
+  <si>
+    <t>965223583</t>
+  </si>
+  <si>
+    <t>964253607</t>
+  </si>
+  <si>
+    <t>959078589</t>
+  </si>
+  <si>
+    <t>957396900</t>
+  </si>
+  <si>
+    <t>811648918</t>
+  </si>
+  <si>
+    <t>805585332</t>
+  </si>
+  <si>
+    <t>798993543</t>
+  </si>
+  <si>
+    <t>795728470</t>
+  </si>
+  <si>
+    <t>793906292</t>
+  </si>
+  <si>
+    <t>744772629</t>
+  </si>
+  <si>
+    <t>941837696</t>
+  </si>
+  <si>
+    <t>946299835</t>
+  </si>
+  <si>
+    <t>913389742</t>
+  </si>
+  <si>
+    <t>941583308</t>
+  </si>
+  <si>
+    <t>939361451</t>
+  </si>
+  <si>
+    <t>937162927</t>
+  </si>
+  <si>
+    <t>927804991</t>
+  </si>
+  <si>
+    <t>921598227</t>
+  </si>
+  <si>
+    <t>920325515</t>
+  </si>
+  <si>
+    <t>913044032</t>
+  </si>
+  <si>
+    <t>911998585</t>
+  </si>
+  <si>
+    <t>904827916</t>
+  </si>
+  <si>
+    <t>902030661</t>
+  </si>
+  <si>
+    <t>884730593</t>
+  </si>
+  <si>
+    <t>880765346</t>
+  </si>
+  <si>
+    <t>856478973</t>
+  </si>
+  <si>
+    <t>866530094</t>
+  </si>
+  <si>
+    <t>855532606</t>
+  </si>
+  <si>
+    <t>960117640</t>
+  </si>
+  <si>
+    <t>734333929</t>
+  </si>
+  <si>
+    <t>740624212</t>
+  </si>
+  <si>
+    <t>743051082</t>
+  </si>
+  <si>
+    <t>742472107</t>
+  </si>
+  <si>
+    <t>969910060</t>
+  </si>
+  <si>
+    <t>969907850</t>
+  </si>
+  <si>
+    <t>969120306</t>
+  </si>
+  <si>
+    <t>967583547</t>
+  </si>
+  <si>
+    <t>967227079</t>
+  </si>
+  <si>
+    <t>967135249</t>
+  </si>
+  <si>
+    <t>967101449</t>
+  </si>
+  <si>
+    <t>967035191</t>
+  </si>
+  <si>
+    <t>966981676</t>
+  </si>
+  <si>
+    <t>965795473</t>
+  </si>
+  <si>
+    <t>966919908</t>
+  </si>
+  <si>
+    <t>966894747</t>
+  </si>
+  <si>
+    <t>959856299</t>
+  </si>
+  <si>
+    <t>959789151</t>
+  </si>
+  <si>
+    <t>959760392</t>
+  </si>
+  <si>
+    <t>959585161</t>
+  </si>
+  <si>
+    <t>959374202</t>
+  </si>
+  <si>
+    <t>959504717</t>
+  </si>
+  <si>
+    <t>953439308</t>
+  </si>
+  <si>
+    <t>943125850</t>
+  </si>
+  <si>
+    <t>173489547</t>
+  </si>
+  <si>
+    <t>743289344</t>
+  </si>
+  <si>
+    <t>908835774</t>
+  </si>
+  <si>
+    <t>912892704</t>
+  </si>
+  <si>
+    <t>860590912</t>
+  </si>
+  <si>
+    <t>766042315</t>
+  </si>
+  <si>
+    <t>763584715</t>
+  </si>
+  <si>
+    <t>875103271</t>
+  </si>
+  <si>
+    <t>959701826</t>
+  </si>
+  <si>
+    <t>952501306</t>
+  </si>
+  <si>
+    <t>874625902</t>
+  </si>
+  <si>
+    <t>959031315</t>
+  </si>
+  <si>
+    <t>959531397</t>
+  </si>
+  <si>
+    <t>960023079</t>
+  </si>
+  <si>
+    <t>959545397</t>
+  </si>
+  <si>
+    <t>959577416</t>
+  </si>
+  <si>
+    <t>959815600</t>
+  </si>
+  <si>
+    <t>751377247</t>
+  </si>
+  <si>
+    <t>959768858</t>
+  </si>
+  <si>
+    <t>943788301</t>
+  </si>
+  <si>
+    <t>881884146</t>
+  </si>
+  <si>
+    <t>951375736</t>
+  </si>
+  <si>
+    <t>969503733</t>
+  </si>
+  <si>
+    <t>845285240</t>
+  </si>
+  <si>
+    <t>971078815</t>
+  </si>
+  <si>
+    <t>971147321</t>
+  </si>
+  <si>
+    <t>970816058</t>
+  </si>
+  <si>
+    <t>970196808</t>
+  </si>
+  <si>
+    <t>969319577</t>
+  </si>
+  <si>
+    <t>968891378</t>
+  </si>
+  <si>
+    <t>966170452</t>
+  </si>
+  <si>
+    <t>964855633</t>
+  </si>
+  <si>
+    <t>962885582</t>
+  </si>
+  <si>
+    <t>960223356</t>
+  </si>
+  <si>
+    <t>940601267</t>
+  </si>
+  <si>
+    <t>939809483</t>
+  </si>
+  <si>
+    <t>904553561</t>
+  </si>
+  <si>
+    <t>897058925</t>
+  </si>
+  <si>
+    <t>864148717</t>
+  </si>
+  <si>
+    <t>861941932</t>
+  </si>
+  <si>
+    <t>766076842</t>
+  </si>
+  <si>
+    <t>744145826</t>
+  </si>
+  <si>
+    <t>744719646</t>
+  </si>
+  <si>
+    <t>886996259</t>
+  </si>
+  <si>
+    <t>764157644</t>
+  </si>
+  <si>
+    <t>739823395</t>
+  </si>
+  <si>
+    <t>904440231</t>
+  </si>
+  <si>
+    <t>887544314</t>
+  </si>
+  <si>
+    <t>835633532</t>
+  </si>
+  <si>
+    <t>744682356</t>
+  </si>
+  <si>
+    <t>948124098</t>
+  </si>
+  <si>
+    <t>968740468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>968998991</t>
+  </si>
+  <si>
+    <t>968824775</t>
+  </si>
+  <si>
+    <t>968805972</t>
+  </si>
+  <si>
+    <t>968781512</t>
+  </si>
+  <si>
+    <t>968469159</t>
+  </si>
+  <si>
+    <t>968428007</t>
+  </si>
+  <si>
+    <t>968391668</t>
+  </si>
+  <si>
+    <t>970139105</t>
+  </si>
+  <si>
+    <t>970894147</t>
+  </si>
+  <si>
+    <t>970936633</t>
+  </si>
+  <si>
+    <t>972250298</t>
+  </si>
+  <si>
+    <t>972718419</t>
+  </si>
+  <si>
+    <t>972283273</t>
   </si>
 </sst>
 </file>
@@ -742,7 +1585,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D354"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -768,10 +1611,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -780,10 +1623,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -792,10 +1635,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -804,7 +1647,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -816,7 +1659,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>6</v>
@@ -828,7 +1671,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>6</v>
@@ -840,7 +1683,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
@@ -852,7 +1695,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>6</v>
@@ -864,10 +1707,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -876,10 +1719,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -888,10 +1731,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -900,10 +1743,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -912,10 +1755,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -924,10 +1767,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -936,10 +1779,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -948,10 +1791,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -960,10 +1803,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -972,10 +1815,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -984,10 +1827,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -996,7 +1839,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
@@ -1008,10 +1851,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1020,7 +1863,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>6</v>
@@ -1032,7 +1875,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>6</v>
@@ -1044,10 +1887,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1056,7 +1899,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1068,10 +1911,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1080,7 +1923,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1092,7 +1935,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
@@ -1104,10 +1947,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1116,7 +1959,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1128,7 +1971,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1140,10 +1983,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1152,10 +1995,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1164,10 +2007,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1176,10 +2019,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1188,10 +2031,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1200,10 +2043,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1212,7 +2055,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>7</v>
@@ -1224,10 +2067,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1236,10 +2079,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1248,10 +2091,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1260,10 +2103,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1272,10 +2115,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1284,10 +2127,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1296,7 +2139,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -1308,10 +2151,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1320,10 +2163,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1332,7 +2175,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
@@ -1344,7 +2187,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
@@ -1356,7 +2199,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>8</v>
@@ -1368,7 +2211,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>8</v>
@@ -1380,10 +2223,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1392,10 +2235,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1404,10 +2247,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1416,10 +2259,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1428,10 +2271,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1440,10 +2283,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1452,10 +2295,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1464,7 +2307,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>5</v>
@@ -1476,10 +2319,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1488,10 +2331,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1500,10 +2343,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1512,10 +2355,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1524,10 +2367,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1536,7 +2379,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>5</v>
@@ -1548,10 +2391,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1559,10 +2402,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1570,7 +2413,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>6</v>
@@ -1581,7 +2424,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>6</v>
@@ -1592,7 +2435,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>6</v>
@@ -1603,7 +2446,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>6</v>
@@ -1614,7 +2457,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
@@ -1625,7 +2468,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
@@ -1635,145 +2478,3084 @@
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C75" s="6"/>
+      <c r="A75" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C76" s="6"/>
+      <c r="A76" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C77" s="6"/>
+      <c r="A77" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C78" s="6"/>
+      <c r="A78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C79" s="6"/>
+      <c r="A79" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C80" s="6"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="6"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="6"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="6"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="6"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="6"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="6"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="6"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="6"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="6"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="6"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="6"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="6"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="6"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="6"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="6"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="6"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="6"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="6"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="6"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="6"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="6"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="6"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="6"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="6"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="6"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="6"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="6"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="6"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="6"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="6"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="6"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="6"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="6"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="6"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="6"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="6"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="6"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="6"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="6"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="6"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="6"/>
+      <c r="A80" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
@@ -1798,31 +5580,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB4BD74A-2124-4E53-AB1E-F7A9C70174CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D0501F-9DB9-4B80-8C1E-A072806A42D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16352,31 +16352,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0255E50B-8A27-4942-BB6B-A56293E718C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C9042DD-44BB-4967-BD92-5A54980A8AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="102">
   <si>
     <t>Status</t>
   </si>
@@ -325,6 +325,18 @@
   </si>
   <si>
     <t>952393324</t>
+  </si>
+  <si>
+    <t>198445722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
+  </si>
+  <si>
+    <t>198208393</t>
+  </si>
+  <si>
+    <t>199561113</t>
   </si>
 </sst>
 </file>
@@ -784,7 +796,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -810,10 +822,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>9</v>
+        <v>98</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -822,10 +834,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -834,10 +846,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>11</v>
+        <v>101</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>5</v>
+        <v>99</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -846,7 +858,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>5</v>
@@ -858,7 +870,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>5</v>
@@ -870,7 +882,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>5</v>
@@ -882,7 +894,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>5</v>
@@ -894,7 +906,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>5</v>
@@ -906,7 +918,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>5</v>
@@ -918,7 +930,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>5</v>
@@ -930,7 +942,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>5</v>
@@ -942,7 +954,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>5</v>
@@ -954,7 +966,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>5</v>
@@ -966,7 +978,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>5</v>
@@ -978,7 +990,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>5</v>
@@ -990,7 +1002,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>5</v>
@@ -1002,7 +1014,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>5</v>
@@ -1014,7 +1026,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>5</v>
@@ -1026,7 +1038,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>5</v>
@@ -1038,7 +1050,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>5</v>
@@ -1050,10 +1062,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1074,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1086,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1086,7 +1098,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>7</v>
@@ -1098,7 +1110,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>7</v>
@@ -1110,7 +1122,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>7</v>
@@ -1122,7 +1134,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>7</v>
@@ -1134,10 +1146,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1146,10 +1158,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1158,10 +1170,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1170,10 +1182,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1182,10 +1194,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1194,7 +1206,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>5</v>
@@ -1206,7 +1218,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>5</v>
@@ -1218,7 +1230,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>5</v>
@@ -1230,10 +1242,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1242,10 +1254,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1254,7 +1266,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>5</v>
@@ -1266,7 +1278,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
@@ -1278,10 +1290,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1302,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1302,7 +1314,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
@@ -1314,7 +1326,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>5</v>
@@ -1326,10 +1338,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1350,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1350,7 +1362,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>5</v>
@@ -1362,7 +1374,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>5</v>
@@ -1374,7 +1386,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>5</v>
@@ -1386,7 +1398,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>5</v>
@@ -1398,7 +1410,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>5</v>
@@ -1410,7 +1422,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>5</v>
@@ -1422,7 +1434,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>5</v>
@@ -1434,10 +1446,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1458,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1470,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1470,7 +1482,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>7</v>
@@ -1482,7 +1494,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>7</v>
@@ -1494,7 +1506,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>7</v>
@@ -1506,10 +1518,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1518,7 +1530,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>7</v>
@@ -1530,10 +1542,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1542,10 +1554,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1554,10 +1566,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1566,7 +1578,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>6</v>
@@ -1578,7 +1590,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>6</v>
@@ -1590,7 +1602,7 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>6</v>
@@ -1601,7 +1613,7 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>6</v>
@@ -1612,7 +1624,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>6</v>
@@ -1623,7 +1635,7 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>6</v>
@@ -1634,7 +1646,7 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>6</v>
@@ -1645,7 +1657,7 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>6</v>
@@ -1656,7 +1668,7 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>6</v>
@@ -1667,7 +1679,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
@@ -1678,10 +1690,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1689,10 +1701,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1700,10 +1712,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1711,7 +1723,7 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>5</v>
@@ -1722,7 +1734,7 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>5</v>
@@ -1733,7 +1745,7 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B80" s="5" t="s">
         <v>5</v>
@@ -1744,7 +1756,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>5</v>
@@ -1755,7 +1767,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>5</v>
@@ -1766,7 +1778,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B83" s="5" t="s">
         <v>5</v>
@@ -1777,7 +1789,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>5</v>
@@ -1788,7 +1800,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>5</v>
@@ -1799,7 +1811,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>5</v>
@@ -1810,7 +1822,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>5</v>
@@ -1821,7 +1833,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>5</v>
@@ -1832,7 +1844,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>5</v>
@@ -1843,12 +1855,45 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C90" s="6" t="s">
+      <c r="B93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1875,31 +1920,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{417545BD-0565-4C6C-B1DF-17DCF5E4112F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90CA4B2-7274-4ABA-B924-9D7C520FACFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="143">
   <si>
     <t>Status</t>
   </si>
@@ -60,403 +60,406 @@
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>179512359</t>
-  </si>
-  <si>
-    <t>939256321</t>
-  </si>
-  <si>
-    <t>909173449</t>
-  </si>
-  <si>
-    <t>932235983</t>
-  </si>
-  <si>
-    <t>879398174</t>
-  </si>
-  <si>
-    <t>882179603</t>
-  </si>
-  <si>
-    <t>763224569</t>
-  </si>
-  <si>
-    <t>856779495</t>
-  </si>
-  <si>
-    <t>850817911</t>
-  </si>
-  <si>
-    <t>856462571</t>
-  </si>
-  <si>
-    <t>935964878</t>
-  </si>
-  <si>
-    <t>920503103</t>
-  </si>
-  <si>
-    <t>878611403</t>
-  </si>
-  <si>
-    <t>899171726</t>
-  </si>
-  <si>
-    <t>882631926</t>
-  </si>
-  <si>
-    <t>882045390</t>
-  </si>
-  <si>
-    <t>896430422</t>
-  </si>
-  <si>
-    <t>764962381</t>
-  </si>
-  <si>
-    <t>778501274</t>
-  </si>
-  <si>
-    <t>770018061</t>
-  </si>
-  <si>
-    <t>818566154</t>
-  </si>
-  <si>
-    <t>956255586</t>
-  </si>
-  <si>
-    <t>746679509</t>
-  </si>
-  <si>
-    <t>955360387</t>
-  </si>
-  <si>
-    <t>917608543</t>
-  </si>
-  <si>
-    <t>922719665</t>
-  </si>
-  <si>
-    <t>859663308</t>
-  </si>
-  <si>
-    <t>184863524</t>
-  </si>
-  <si>
-    <t>928986722</t>
-  </si>
-  <si>
-    <t>935119259</t>
-  </si>
-  <si>
-    <t>932648573</t>
-  </si>
-  <si>
-    <t>889507244</t>
-  </si>
-  <si>
-    <t>832902302</t>
-  </si>
-  <si>
-    <t>949235174</t>
-  </si>
-  <si>
-    <t>755884297</t>
-  </si>
-  <si>
-    <t>777270798</t>
-  </si>
-  <si>
-    <t>909236725</t>
-  </si>
-  <si>
-    <t>761129612</t>
-  </si>
-  <si>
-    <t>959545405</t>
-  </si>
-  <si>
-    <t>932214020</t>
-  </si>
-  <si>
-    <t>868609276</t>
-  </si>
-  <si>
-    <t>788054785</t>
-  </si>
-  <si>
-    <t>750950721</t>
-  </si>
-  <si>
-    <t>190149215</t>
-  </si>
-  <si>
-    <t>797117797</t>
-  </si>
-  <si>
-    <t>801189352</t>
-  </si>
-  <si>
-    <t>770798860</t>
-  </si>
-  <si>
-    <t>767149978</t>
-  </si>
-  <si>
-    <t>936531148</t>
-  </si>
-  <si>
-    <t>889875823</t>
-  </si>
-  <si>
-    <t>763779950</t>
-  </si>
-  <si>
-    <t>781600675</t>
-  </si>
-  <si>
-    <t>782462091</t>
-  </si>
-  <si>
-    <t>785079272</t>
-  </si>
-  <si>
-    <t>784954020</t>
-  </si>
-  <si>
-    <t>832345189</t>
-  </si>
-  <si>
-    <t>857272466</t>
-  </si>
-  <si>
-    <t>831842897</t>
-  </si>
-  <si>
-    <t>939522011</t>
-  </si>
-  <si>
-    <t>200746794</t>
-  </si>
-  <si>
-    <t>201131087</t>
-  </si>
-  <si>
-    <t>200882417</t>
-  </si>
-  <si>
-    <t>939057109</t>
-  </si>
-  <si>
-    <t>905838680</t>
-  </si>
-  <si>
-    <t>910320450</t>
-  </si>
-  <si>
-    <t>973022647</t>
-  </si>
-  <si>
-    <t>969586225</t>
-  </si>
-  <si>
-    <t>968331698</t>
-  </si>
-  <si>
-    <t>968171227</t>
-  </si>
-  <si>
-    <t>748327438</t>
-  </si>
-  <si>
-    <t>708006923</t>
-  </si>
-  <si>
-    <t>686740766</t>
-  </si>
-  <si>
-    <t>201072257</t>
-  </si>
-  <si>
-    <t>200163982</t>
-  </si>
-  <si>
-    <t>198633913</t>
-  </si>
-  <si>
-    <t>193228073</t>
-  </si>
-  <si>
-    <t>192850265</t>
-  </si>
-  <si>
-    <t>176590150</t>
-  </si>
-  <si>
-    <t>931161438</t>
-  </si>
-  <si>
-    <t>942953328</t>
-  </si>
-  <si>
-    <t>940145638</t>
-  </si>
-  <si>
-    <t>916149515</t>
-  </si>
-  <si>
-    <t>908318995</t>
-  </si>
-  <si>
-    <t>889193797</t>
-  </si>
-  <si>
-    <t>888927005</t>
-  </si>
-  <si>
-    <t>867580536</t>
-  </si>
-  <si>
-    <t>850655071</t>
-  </si>
-  <si>
-    <t>845152853</t>
-  </si>
-  <si>
-    <t>840333086</t>
-  </si>
-  <si>
-    <t>838273377</t>
-  </si>
-  <si>
-    <t>838273369</t>
-  </si>
-  <si>
-    <t>830566729</t>
-  </si>
-  <si>
-    <t>819393038</t>
-  </si>
-  <si>
-    <t>817386323</t>
-  </si>
-  <si>
-    <t>815742139</t>
-  </si>
-  <si>
-    <t>797454885</t>
-  </si>
-  <si>
-    <t>771393406</t>
-  </si>
-  <si>
-    <t>763727686</t>
-  </si>
-  <si>
-    <t>769076690</t>
-  </si>
-  <si>
-    <t>814534917</t>
-  </si>
-  <si>
-    <t>806824318</t>
-  </si>
-  <si>
-    <t>784548152</t>
-  </si>
-  <si>
-    <t>901172019</t>
-  </si>
-  <si>
-    <t>939654780</t>
-  </si>
-  <si>
-    <t>963281336</t>
-  </si>
-  <si>
-    <t>765423169</t>
-  </si>
-  <si>
-    <t>785742390</t>
-  </si>
-  <si>
-    <t>785712609</t>
-  </si>
-  <si>
-    <t>932867801</t>
-  </si>
-  <si>
-    <t>763606088</t>
-  </si>
-  <si>
-    <t>910872377</t>
-  </si>
-  <si>
-    <t>851524052</t>
-  </si>
-  <si>
-    <t>202807040</t>
-  </si>
-  <si>
     <t xml:space="preserve">NOSSO NUMERO NÃO IDENTIFICADO - INEXISTENTE            </t>
   </si>
   <si>
-    <t>203679455</t>
-  </si>
-  <si>
-    <t>202955146</t>
-  </si>
-  <si>
-    <t>884263116</t>
-  </si>
-  <si>
-    <t>940794138</t>
-  </si>
-  <si>
-    <t>909916979</t>
-  </si>
-  <si>
-    <t>811512684</t>
-  </si>
-  <si>
-    <t>834875951</t>
-  </si>
-  <si>
-    <t>858225158</t>
-  </si>
-  <si>
-    <t>785531454</t>
-  </si>
-  <si>
-    <t>970101105</t>
-  </si>
-  <si>
-    <t>942000559</t>
-  </si>
-  <si>
-    <t>940448669</t>
-  </si>
-  <si>
-    <t>938930181</t>
-  </si>
-  <si>
-    <t>908928512</t>
-  </si>
-  <si>
-    <t>884744297</t>
-  </si>
-  <si>
-    <t>884724836</t>
-  </si>
-  <si>
-    <t>835876438</t>
-  </si>
-  <si>
-    <t>835771068</t>
+    <t>963221779</t>
+  </si>
+  <si>
+    <t>960989675</t>
+  </si>
+  <si>
+    <t>947455014</t>
+  </si>
+  <si>
+    <t>194429514</t>
+  </si>
+  <si>
+    <t>720434707</t>
+  </si>
+  <si>
+    <t>763537838</t>
+  </si>
+  <si>
+    <t>202042200</t>
+  </si>
+  <si>
+    <t>202032193</t>
+  </si>
+  <si>
+    <t>196891489</t>
+  </si>
+  <si>
+    <t>199268503</t>
+  </si>
+  <si>
+    <t>201177031</t>
+  </si>
+  <si>
+    <t>196459535</t>
+  </si>
+  <si>
+    <t>193993106</t>
+  </si>
+  <si>
+    <t>192227233</t>
+  </si>
+  <si>
+    <t>192156705</t>
+  </si>
+  <si>
+    <t>185756446</t>
+  </si>
+  <si>
+    <t>964590735</t>
+  </si>
+  <si>
+    <t>190940829</t>
+  </si>
+  <si>
+    <t>179446020</t>
+  </si>
+  <si>
+    <t>176384059</t>
+  </si>
+  <si>
+    <t>931372316</t>
+  </si>
+  <si>
+    <t>938967951</t>
+  </si>
+  <si>
+    <t>931207553</t>
+  </si>
+  <si>
+    <t>929545493</t>
+  </si>
+  <si>
+    <t>920914060</t>
+  </si>
+  <si>
+    <t>917852141</t>
+  </si>
+  <si>
+    <t>852383458</t>
+  </si>
+  <si>
+    <t>880654755</t>
+  </si>
+  <si>
+    <t>880793934</t>
+  </si>
+  <si>
+    <t>831562255</t>
+  </si>
+  <si>
+    <t>834713061</t>
+  </si>
+  <si>
+    <t>832085793</t>
+  </si>
+  <si>
+    <t>830531442</t>
+  </si>
+  <si>
+    <t>830253450</t>
+  </si>
+  <si>
+    <t>809942414</t>
+  </si>
+  <si>
+    <t>902362296</t>
+  </si>
+  <si>
+    <t>966085718</t>
+  </si>
+  <si>
+    <t>192225583</t>
+  </si>
+  <si>
+    <t>191010689</t>
+  </si>
+  <si>
+    <t>882894219</t>
+  </si>
+  <si>
+    <t>884094271</t>
+  </si>
+  <si>
+    <t>903841686</t>
+  </si>
+  <si>
+    <t>930361484</t>
+  </si>
+  <si>
+    <t>192616534</t>
+  </si>
+  <si>
+    <t>191335144</t>
+  </si>
+  <si>
+    <t>777365341</t>
+  </si>
+  <si>
+    <t>201684002</t>
+  </si>
+  <si>
+    <t>202136846</t>
+  </si>
+  <si>
+    <t>196786861</t>
+  </si>
+  <si>
+    <t>202184002</t>
+  </si>
+  <si>
+    <t>199699624</t>
+  </si>
+  <si>
+    <t>945483372</t>
+  </si>
+  <si>
+    <t>861391997</t>
+  </si>
+  <si>
+    <t>852655970</t>
+  </si>
+  <si>
+    <t>828982722</t>
+  </si>
+  <si>
+    <t>828982714</t>
+  </si>
+  <si>
+    <t>791721917</t>
+  </si>
+  <si>
+    <t>967666177</t>
+  </si>
+  <si>
+    <t>972017184</t>
+  </si>
+  <si>
+    <t>908145042</t>
+  </si>
+  <si>
+    <t>901460802</t>
+  </si>
+  <si>
+    <t>888807926</t>
+  </si>
+  <si>
+    <t>200845927</t>
+  </si>
+  <si>
+    <t>762620726</t>
+  </si>
+  <si>
+    <t>203782242</t>
+  </si>
+  <si>
+    <t>203375773</t>
+  </si>
+  <si>
+    <t>202548735</t>
+  </si>
+  <si>
+    <t>202495408</t>
+  </si>
+  <si>
+    <t>202000455</t>
+  </si>
+  <si>
+    <t>198643961</t>
+  </si>
+  <si>
+    <t>192281057</t>
+  </si>
+  <si>
+    <t>191732621</t>
+  </si>
+  <si>
+    <t>185369737</t>
+  </si>
+  <si>
+    <t>181936067</t>
+  </si>
+  <si>
+    <t>181304621</t>
+  </si>
+  <si>
+    <t>968957278</t>
+  </si>
+  <si>
+    <t>883836672</t>
+  </si>
+  <si>
+    <t>883650750</t>
+  </si>
+  <si>
+    <t>968542534</t>
+  </si>
+  <si>
+    <t>966853164</t>
+  </si>
+  <si>
+    <t>190952295</t>
+  </si>
+  <si>
+    <t>812130346</t>
+  </si>
+  <si>
+    <t>808928596</t>
+  </si>
+  <si>
+    <t>898016476</t>
+  </si>
+  <si>
+    <t>865068492</t>
+  </si>
+  <si>
+    <t>176041634</t>
+  </si>
+  <si>
+    <t>185381104</t>
+  </si>
+  <si>
+    <t>952804015</t>
+  </si>
+  <si>
+    <t>936495856</t>
+  </si>
+  <si>
+    <t>857302909</t>
+  </si>
+  <si>
+    <t>810391346</t>
+  </si>
+  <si>
+    <t>743382529</t>
+  </si>
+  <si>
+    <t>200197899</t>
+  </si>
+  <si>
+    <t>200730301</t>
+  </si>
+  <si>
+    <t>812488694</t>
+  </si>
+  <si>
+    <t>808953396</t>
+  </si>
+  <si>
+    <t>753916224</t>
+  </si>
+  <si>
+    <t>748335829</t>
+  </si>
+  <si>
+    <t>203057280</t>
+  </si>
+  <si>
+    <t>201981093</t>
+  </si>
+  <si>
+    <t>200799868</t>
+  </si>
+  <si>
+    <t>198662599</t>
+  </si>
+  <si>
+    <t>198208310</t>
+  </si>
+  <si>
+    <t>196752988</t>
+  </si>
+  <si>
+    <t>194627794</t>
+  </si>
+  <si>
+    <t>193747932</t>
+  </si>
+  <si>
+    <t>193742701</t>
+  </si>
+  <si>
+    <t>193142472</t>
+  </si>
+  <si>
+    <t>937648594</t>
+  </si>
+  <si>
+    <t>959664560</t>
+  </si>
+  <si>
+    <t>193140484</t>
+  </si>
+  <si>
+    <t>192539702</t>
+  </si>
+  <si>
+    <t>192292211</t>
+  </si>
+  <si>
+    <t>956693950</t>
+  </si>
+  <si>
+    <t>946438466</t>
+  </si>
+  <si>
+    <t>927820567</t>
+  </si>
+  <si>
+    <t>922107572</t>
+  </si>
+  <si>
+    <t>867558094</t>
+  </si>
+  <si>
+    <t>893451959</t>
+  </si>
+  <si>
+    <t>883699922</t>
+  </si>
+  <si>
+    <t>204270890</t>
+  </si>
+  <si>
+    <t>762944282</t>
+  </si>
+  <si>
+    <t>761911225</t>
+  </si>
+  <si>
+    <t>913579870</t>
+  </si>
+  <si>
+    <t>970972489</t>
+  </si>
+  <si>
+    <t>834129987</t>
+  </si>
+  <si>
+    <t>787731102</t>
+  </si>
+  <si>
+    <t>812826885</t>
+  </si>
+  <si>
+    <t>204752301</t>
+  </si>
+  <si>
+    <t>204994705</t>
+  </si>
+  <si>
+    <t>204961183</t>
+  </si>
+  <si>
+    <t>204803211</t>
+  </si>
+  <si>
+    <t>204401412</t>
   </si>
 </sst>
 </file>
@@ -945,7 +948,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -957,7 +960,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -969,7 +972,7 @@
         <v>12</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -981,7 +984,7 @@
         <v>13</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -993,7 +996,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -1005,7 +1008,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1017,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -1029,7 +1032,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -1041,7 +1044,7 @@
         <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1053,7 +1056,7 @@
         <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1137,7 +1140,7 @@
         <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1149,7 +1152,7 @@
         <v>27</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1161,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1173,7 +1176,7 @@
         <v>29</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1185,7 +1188,7 @@
         <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1197,7 +1200,7 @@
         <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1209,7 +1212,7 @@
         <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1221,7 +1224,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1233,7 +1236,7 @@
         <v>34</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1245,7 +1248,7 @@
         <v>35</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1293,7 +1296,7 @@
         <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1305,7 +1308,7 @@
         <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1317,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1353,7 +1356,7 @@
         <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1365,7 +1368,7 @@
         <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1377,7 +1380,7 @@
         <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1389,7 +1392,7 @@
         <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1401,7 +1404,7 @@
         <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1413,7 +1416,7 @@
         <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1425,7 +1428,7 @@
         <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1437,7 +1440,7 @@
         <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1461,7 +1464,7 @@
         <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1473,7 +1476,7 @@
         <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1497,7 +1500,7 @@
         <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1509,7 +1512,7 @@
         <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1521,7 +1524,7 @@
         <v>58</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1545,7 +1548,7 @@
         <v>60</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1557,7 +1560,7 @@
         <v>61</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1569,7 +1572,7 @@
         <v>62</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1581,7 +1584,7 @@
         <v>63</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1593,7 +1596,7 @@
         <v>64</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1605,7 +1608,7 @@
         <v>65</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1617,7 +1620,7 @@
         <v>66</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1629,7 +1632,7 @@
         <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1641,7 +1644,7 @@
         <v>68</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1653,7 +1656,7 @@
         <v>69</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1665,7 +1668,7 @@
         <v>70</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1677,7 +1680,7 @@
         <v>71</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1689,7 +1692,7 @@
         <v>72</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1701,7 +1704,7 @@
         <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1713,7 +1716,7 @@
         <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1725,7 +1728,7 @@
         <v>75</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1736,7 +1739,7 @@
         <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1747,7 +1750,7 @@
         <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1758,7 +1761,7 @@
         <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1769,7 +1772,7 @@
         <v>79</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1780,7 +1783,7 @@
         <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1791,7 +1794,7 @@
         <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1802,7 +1805,7 @@
         <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1813,7 +1816,7 @@
         <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1824,7 +1827,7 @@
         <v>84</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1835,7 +1838,7 @@
         <v>85</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1846,7 +1849,7 @@
         <v>86</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1857,7 +1860,7 @@
         <v>87</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1868,7 +1871,7 @@
         <v>88</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1879,7 +1882,7 @@
         <v>89</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1890,7 +1893,7 @@
         <v>90</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1901,7 +1904,7 @@
         <v>91</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1912,7 +1915,7 @@
         <v>92</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -2033,7 +2036,7 @@
         <v>103</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2044,7 +2047,7 @@
         <v>104</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2055,7 +2058,7 @@
         <v>105</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2066,7 +2069,7 @@
         <v>106</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2077,7 +2080,7 @@
         <v>107</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2165,7 +2168,7 @@
         <v>115</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>4</v>
@@ -2176,7 +2179,7 @@
         <v>116</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>4</v>
@@ -2187,7 +2190,7 @@
         <v>117</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>4</v>
@@ -2198,7 +2201,7 @@
         <v>118</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>4</v>
@@ -2209,7 +2212,7 @@
         <v>119</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>4</v>
@@ -2220,7 +2223,7 @@
         <v>120</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>4</v>
@@ -2231,7 +2234,7 @@
         <v>121</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>4</v>
@@ -2242,7 +2245,7 @@
         <v>122</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>4</v>
@@ -2250,10 +2253,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>4</v>
@@ -2261,10 +2264,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>123</v>
+        <v>6</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>4</v>
@@ -2272,10 +2275,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>4</v>
@@ -2283,10 +2286,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>4</v>
@@ -2294,10 +2297,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>4</v>
@@ -2305,10 +2308,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>4</v>
@@ -2316,10 +2319,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>4</v>
@@ -2327,7 +2330,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>8</v>
@@ -2338,7 +2341,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>8</v>
@@ -2349,7 +2352,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>8</v>
@@ -2360,7 +2363,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>8</v>
@@ -2371,7 +2374,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>8</v>
@@ -2382,7 +2385,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>8</v>
@@ -2393,7 +2396,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>8</v>
@@ -2404,7 +2407,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>8</v>
@@ -2415,10 +2418,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>4</v>
@@ -2426,10 +2429,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>4</v>
@@ -2437,20 +2440,36 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B132" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="6"/>
+      <c r="B133" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="6"/>
+      <c r="A134" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C135" s="6"/>
@@ -3012,31 +3031,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB142188-4F65-4FDD-8FD6-C2A3AFA64515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DA52F3-179A-46B3-834E-37702A508E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="82">
   <si>
     <t>Status</t>
   </si>
@@ -48,220 +48,235 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>807506815</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>758688604</t>
-  </si>
-  <si>
-    <t>239738994</t>
-  </si>
-  <si>
-    <t>237212554</t>
-  </si>
-  <si>
-    <t>229735232</t>
-  </si>
-  <si>
-    <t>214446803</t>
-  </si>
-  <si>
-    <t>205383221</t>
-  </si>
-  <si>
-    <t>199873302</t>
-  </si>
-  <si>
-    <t>197550738</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>961698770</t>
-  </si>
-  <si>
-    <t>950696538</t>
-  </si>
-  <si>
-    <t>949017895</t>
-  </si>
-  <si>
-    <t>958003281</t>
-  </si>
-  <si>
-    <t>781492412</t>
-  </si>
-  <si>
-    <t>917666277</t>
-  </si>
-  <si>
-    <t>946052788</t>
-  </si>
-  <si>
-    <t>922986264</t>
-  </si>
-  <si>
-    <t>920051483</t>
-  </si>
-  <si>
-    <t>918064019</t>
-  </si>
-  <si>
-    <t>917357794</t>
-  </si>
-  <si>
-    <t>915155968</t>
-  </si>
-  <si>
-    <t>893502793</t>
-  </si>
-  <si>
-    <t>892427521</t>
-  </si>
-  <si>
-    <t>878269020</t>
-  </si>
-  <si>
-    <t>871051748</t>
-  </si>
-  <si>
-    <t>816789543</t>
-  </si>
-  <si>
-    <t>837257462</t>
-  </si>
-  <si>
-    <t>811759392</t>
-  </si>
-  <si>
-    <t>203410547</t>
-  </si>
-  <si>
-    <t>236816173</t>
-  </si>
-  <si>
-    <t>239433273</t>
-  </si>
-  <si>
-    <t>240130272</t>
-  </si>
-  <si>
-    <t>239952389</t>
-  </si>
-  <si>
-    <t>239922556</t>
-  </si>
-  <si>
-    <t>239412269</t>
-  </si>
-  <si>
-    <t>239323128</t>
-  </si>
-  <si>
-    <t>239007382</t>
-  </si>
-  <si>
-    <t>238110393</t>
-  </si>
-  <si>
-    <t>237835495</t>
-  </si>
-  <si>
-    <t>226633364</t>
-  </si>
-  <si>
-    <t>235248188</t>
-  </si>
-  <si>
-    <t>231843743</t>
-  </si>
-  <si>
-    <t>230456257</t>
-  </si>
-  <si>
-    <t>230056149</t>
-  </si>
-  <si>
-    <t>219627241</t>
-  </si>
-  <si>
-    <t>216104509</t>
-  </si>
-  <si>
-    <t>185988239</t>
-  </si>
-  <si>
-    <t>181163985</t>
-  </si>
-  <si>
-    <t>957475886</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>819370077</t>
-  </si>
-  <si>
-    <t>920317710</t>
-  </si>
-  <si>
-    <t>942659446</t>
-  </si>
-  <si>
-    <t>962890228</t>
-  </si>
-  <si>
-    <t>972681542</t>
-  </si>
-  <si>
-    <t>184602526</t>
-  </si>
-  <si>
-    <t>199778519</t>
-  </si>
-  <si>
-    <t>914495977</t>
-  </si>
-  <si>
-    <t>888518788</t>
-  </si>
-  <si>
-    <t>830357178</t>
-  </si>
-  <si>
-    <t>197757200</t>
-  </si>
-  <si>
-    <t>957491925</t>
-  </si>
-  <si>
-    <t>228349050</t>
-  </si>
-  <si>
-    <t>924975125</t>
-  </si>
-  <si>
-    <t>239294790</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>206949483</t>
-  </si>
-  <si>
-    <t>230778684</t>
-  </si>
-  <si>
-    <t>230379129</t>
-  </si>
-  <si>
-    <t>892101456</t>
+    <t>199327150</t>
+  </si>
+  <si>
+    <t>818623690</t>
+  </si>
+  <si>
+    <t>224964043</t>
+  </si>
+  <si>
+    <t>922065754</t>
+  </si>
+  <si>
+    <t>210000422</t>
+  </si>
+  <si>
+    <t>213096211</t>
+  </si>
+  <si>
+    <t>230100319</t>
+  </si>
+  <si>
+    <t>230423059</t>
+  </si>
+  <si>
+    <t>229974518</t>
+  </si>
+  <si>
+    <t>897888073</t>
+  </si>
+  <si>
+    <t>900279997</t>
+  </si>
+  <si>
+    <t>214543351</t>
+  </si>
+  <si>
+    <t>224944797</t>
+  </si>
+  <si>
+    <t>224954143</t>
+  </si>
+  <si>
+    <t>230634218</t>
+  </si>
+  <si>
+    <t>240837322</t>
+  </si>
+  <si>
+    <t>190884704</t>
+  </si>
+  <si>
+    <t>184783680</t>
+  </si>
+  <si>
+    <t>974216065</t>
+  </si>
+  <si>
+    <t>956913697</t>
+  </si>
+  <si>
+    <t>809693991</t>
+  </si>
+  <si>
+    <t>242159899</t>
+  </si>
+  <si>
+    <t>242063075</t>
+  </si>
+  <si>
+    <t>241753130</t>
+  </si>
+  <si>
+    <t>241748601</t>
+  </si>
+  <si>
+    <t>230602033</t>
+  </si>
+  <si>
+    <t>796934242</t>
+  </si>
+  <si>
+    <t>942308580</t>
+  </si>
+  <si>
+    <t>227994062</t>
+  </si>
+  <si>
+    <t>773927946</t>
+  </si>
+  <si>
+    <t>242847147</t>
+  </si>
+  <si>
+    <t>964229524</t>
+  </si>
+  <si>
+    <t>957894094</t>
+  </si>
+  <si>
+    <t>953382219</t>
+  </si>
+  <si>
+    <t>952144693</t>
+  </si>
+  <si>
+    <t>864594522</t>
+  </si>
+  <si>
+    <t>794470439</t>
+  </si>
+  <si>
+    <t>242334567</t>
+  </si>
+  <si>
+    <t>231374913</t>
+  </si>
+  <si>
+    <t>228954180</t>
+  </si>
+  <si>
+    <t>214410429</t>
+  </si>
+  <si>
+    <t>214216800</t>
+  </si>
+  <si>
+    <t>844583009</t>
+  </si>
+  <si>
+    <t>952032914</t>
+  </si>
+  <si>
+    <t>963249895</t>
+  </si>
+  <si>
+    <t>973311115</t>
+  </si>
+  <si>
+    <t>957392248</t>
+  </si>
+  <si>
+    <t>948168079</t>
+  </si>
+  <si>
+    <t>917159216</t>
+  </si>
+  <si>
+    <t>916094836</t>
+  </si>
+  <si>
+    <t>899674570</t>
+  </si>
+  <si>
+    <t>894828247</t>
+  </si>
+  <si>
+    <t>893309512</t>
+  </si>
+  <si>
+    <t>827286083</t>
+  </si>
+  <si>
+    <t>231290721</t>
+  </si>
+  <si>
+    <t>791972494</t>
+  </si>
+  <si>
+    <t>820516395</t>
+  </si>
+  <si>
+    <t>820304644</t>
+  </si>
+  <si>
+    <t>819018692</t>
+  </si>
+  <si>
+    <t>242681397</t>
+  </si>
+  <si>
+    <t>784139358</t>
+  </si>
+  <si>
+    <t>780953158</t>
+  </si>
+  <si>
+    <t>241902679</t>
+  </si>
+  <si>
+    <t>242295297</t>
+  </si>
+  <si>
+    <t>236773747</t>
+  </si>
+  <si>
+    <t>235062654</t>
+  </si>
+  <si>
+    <t>232448633</t>
+  </si>
+  <si>
+    <t>231585740</t>
+  </si>
+  <si>
+    <t>231288824</t>
+  </si>
+  <si>
+    <t>227281387</t>
+  </si>
+  <si>
+    <t>230871307</t>
+  </si>
+  <si>
+    <t>229947373</t>
+  </si>
+  <si>
+    <t>224200968</t>
+  </si>
+  <si>
+    <t>215557269</t>
   </si>
 </sst>
 </file>
@@ -721,7 +736,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D69"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -747,10 +762,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -759,10 +774,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -771,10 +786,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -783,10 +798,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -795,10 +810,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -807,10 +822,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -819,7 +834,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
@@ -831,10 +846,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -843,10 +858,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -855,10 +870,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -867,10 +882,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -879,10 +894,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -891,10 +906,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -903,10 +918,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -915,10 +930,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -927,10 +942,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -942,7 +957,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -954,7 +969,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -966,7 +981,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -978,7 +993,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -990,7 +1005,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1002,7 +1017,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1014,7 +1029,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1026,7 +1041,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1038,7 +1053,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1050,7 +1065,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1062,7 +1077,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1074,7 +1089,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1086,7 +1101,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1098,7 +1113,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1110,7 +1125,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1122,7 +1137,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1134,7 +1149,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1146,7 +1161,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1158,7 +1173,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1170,7 +1185,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1182,7 +1197,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1194,7 +1209,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1206,7 +1221,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1218,7 +1233,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1230,7 +1245,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1242,7 +1257,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1254,7 +1269,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1266,7 +1281,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1278,7 +1293,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1290,7 +1305,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1302,7 +1317,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1314,7 +1329,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1326,7 +1341,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1335,10 +1350,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1347,10 +1362,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1359,10 +1374,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1371,10 +1386,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1383,10 +1398,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1395,7 +1410,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>6</v>
@@ -1407,7 +1422,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>6</v>
@@ -1419,10 +1434,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1431,10 +1446,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1443,7 +1458,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>6</v>
@@ -1455,10 +1470,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1467,7 +1482,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>6</v>
@@ -1479,7 +1494,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>6</v>
@@ -1491,10 +1506,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1503,10 +1518,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1515,10 +1530,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1527,10 +1542,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1538,10 +1553,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1549,12 +1564,89 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B69" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C69" s="6" t="s">
+      <c r="B71" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1581,31 +1673,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03DA52F3-179A-46B3-834E-37702A508E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3887B9C4-2523-4F25-962E-1071EB57B7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1150" uniqueCount="390">
   <si>
     <t>Status</t>
   </si>
@@ -57,226 +57,1150 @@
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>199327150</t>
-  </si>
-  <si>
-    <t>818623690</t>
-  </si>
-  <si>
-    <t>224964043</t>
-  </si>
-  <si>
-    <t>922065754</t>
-  </si>
-  <si>
-    <t>210000422</t>
-  </si>
-  <si>
-    <t>213096211</t>
-  </si>
-  <si>
-    <t>230100319</t>
-  </si>
-  <si>
-    <t>230423059</t>
-  </si>
-  <si>
-    <t>229974518</t>
-  </si>
-  <si>
-    <t>897888073</t>
-  </si>
-  <si>
-    <t>900279997</t>
-  </si>
-  <si>
-    <t>214543351</t>
-  </si>
-  <si>
-    <t>224944797</t>
-  </si>
-  <si>
-    <t>224954143</t>
-  </si>
-  <si>
-    <t>230634218</t>
-  </si>
-  <si>
-    <t>240837322</t>
-  </si>
-  <si>
-    <t>190884704</t>
-  </si>
-  <si>
-    <t>184783680</t>
-  </si>
-  <si>
-    <t>974216065</t>
-  </si>
-  <si>
-    <t>956913697</t>
-  </si>
-  <si>
-    <t>809693991</t>
-  </si>
-  <si>
-    <t>242159899</t>
-  </si>
-  <si>
-    <t>242063075</t>
-  </si>
-  <si>
-    <t>241753130</t>
-  </si>
-  <si>
-    <t>241748601</t>
-  </si>
-  <si>
-    <t>230602033</t>
-  </si>
-  <si>
-    <t>796934242</t>
-  </si>
-  <si>
-    <t>942308580</t>
-  </si>
-  <si>
-    <t>227994062</t>
-  </si>
-  <si>
-    <t>773927946</t>
-  </si>
-  <si>
-    <t>242847147</t>
-  </si>
-  <si>
-    <t>964229524</t>
-  </si>
-  <si>
-    <t>957894094</t>
-  </si>
-  <si>
-    <t>953382219</t>
-  </si>
-  <si>
-    <t>952144693</t>
-  </si>
-  <si>
-    <t>864594522</t>
-  </si>
-  <si>
-    <t>794470439</t>
-  </si>
-  <si>
-    <t>242334567</t>
-  </si>
-  <si>
-    <t>231374913</t>
-  </si>
-  <si>
-    <t>228954180</t>
-  </si>
-  <si>
-    <t>214410429</t>
-  </si>
-  <si>
-    <t>214216800</t>
-  </si>
-  <si>
-    <t>844583009</t>
-  </si>
-  <si>
-    <t>952032914</t>
-  </si>
-  <si>
-    <t>963249895</t>
-  </si>
-  <si>
-    <t>973311115</t>
-  </si>
-  <si>
-    <t>957392248</t>
-  </si>
-  <si>
-    <t>948168079</t>
-  </si>
-  <si>
-    <t>917159216</t>
-  </si>
-  <si>
-    <t>916094836</t>
-  </si>
-  <si>
-    <t>899674570</t>
-  </si>
-  <si>
-    <t>894828247</t>
-  </si>
-  <si>
-    <t>893309512</t>
-  </si>
-  <si>
-    <t>827286083</t>
-  </si>
-  <si>
-    <t>231290721</t>
-  </si>
-  <si>
-    <t>791972494</t>
-  </si>
-  <si>
-    <t>820516395</t>
-  </si>
-  <si>
-    <t>820304644</t>
-  </si>
-  <si>
-    <t>819018692</t>
-  </si>
-  <si>
-    <t>242681397</t>
-  </si>
-  <si>
-    <t>784139358</t>
-  </si>
-  <si>
-    <t>780953158</t>
-  </si>
-  <si>
-    <t>241902679</t>
-  </si>
-  <si>
-    <t>242295297</t>
-  </si>
-  <si>
-    <t>236773747</t>
-  </si>
-  <si>
-    <t>235062654</t>
-  </si>
-  <si>
-    <t>232448633</t>
-  </si>
-  <si>
-    <t>231585740</t>
-  </si>
-  <si>
-    <t>231288824</t>
-  </si>
-  <si>
-    <t>227281387</t>
-  </si>
-  <si>
-    <t>230871307</t>
-  </si>
-  <si>
-    <t>229947373</t>
-  </si>
-  <si>
-    <t>224200968</t>
-  </si>
-  <si>
-    <t>215557269</t>
+    <t>910107816</t>
+  </si>
+  <si>
+    <t>191106883</t>
+  </si>
+  <si>
+    <t>970415448</t>
+  </si>
+  <si>
+    <t>206737524</t>
+  </si>
+  <si>
+    <t>230565958</t>
+  </si>
+  <si>
+    <t>230565529</t>
+  </si>
+  <si>
+    <t>240285191</t>
+  </si>
+  <si>
+    <t>214807095</t>
+  </si>
+  <si>
+    <t>183614639</t>
+  </si>
+  <si>
+    <t>211425875</t>
+  </si>
+  <si>
+    <t>210826602</t>
+  </si>
+  <si>
+    <t>210798876</t>
+  </si>
+  <si>
+    <t>209747470</t>
+  </si>
+  <si>
+    <t>209106610</t>
+  </si>
+  <si>
+    <t>194913533</t>
+  </si>
+  <si>
+    <t>187674290</t>
+  </si>
+  <si>
+    <t>184100067</t>
+  </si>
+  <si>
+    <t>184086118</t>
+  </si>
+  <si>
+    <t>183699812</t>
+  </si>
+  <si>
+    <t>868765284</t>
+  </si>
+  <si>
+    <t>953279928</t>
+  </si>
+  <si>
+    <t>953087388</t>
+  </si>
+  <si>
+    <t>880008382</t>
+  </si>
+  <si>
+    <t>878266810</t>
+  </si>
+  <si>
+    <t>213902822</t>
+  </si>
+  <si>
+    <t>230815395</t>
+  </si>
+  <si>
+    <t>231778477</t>
+  </si>
+  <si>
+    <t>231342266</t>
+  </si>
+  <si>
+    <t>231707690</t>
+  </si>
+  <si>
+    <t>231446729</t>
+  </si>
+  <si>
+    <t>228250712</t>
+  </si>
+  <si>
+    <t>231216783</t>
+  </si>
+  <si>
+    <t>222841649</t>
+  </si>
+  <si>
+    <t>917425161</t>
+  </si>
+  <si>
+    <t>231564968</t>
+  </si>
+  <si>
+    <t>197617719</t>
+  </si>
+  <si>
+    <t>191226327</t>
+  </si>
+  <si>
+    <t>191402050</t>
+  </si>
+  <si>
+    <t>233040074</t>
+  </si>
+  <si>
+    <t>232609770</t>
+  </si>
+  <si>
+    <t>195794288</t>
+  </si>
+  <si>
+    <t>234465098</t>
+  </si>
+  <si>
+    <t>235264953</t>
+  </si>
+  <si>
+    <t>240746259</t>
+  </si>
+  <si>
+    <t>240340491</t>
+  </si>
+  <si>
+    <t>239110343</t>
+  </si>
+  <si>
+    <t>235429424</t>
+  </si>
+  <si>
+    <t>235057100</t>
+  </si>
+  <si>
+    <t>920838384</t>
+  </si>
+  <si>
+    <t>199774468</t>
+  </si>
+  <si>
+    <t>975322417</t>
+  </si>
+  <si>
+    <t>974426599</t>
+  </si>
+  <si>
+    <t>969970783</t>
+  </si>
+  <si>
+    <t>952837668</t>
+  </si>
+  <si>
+    <t>939666503</t>
+  </si>
+  <si>
+    <t>936987902</t>
+  </si>
+  <si>
+    <t>224209472</t>
+  </si>
+  <si>
+    <t>220482735</t>
+  </si>
+  <si>
+    <t>218440687</t>
+  </si>
+  <si>
+    <t>217937618</t>
+  </si>
+  <si>
+    <t>217613078</t>
+  </si>
+  <si>
+    <t>217224694</t>
+  </si>
+  <si>
+    <t>216041602</t>
+  </si>
+  <si>
+    <t>211999655</t>
+  </si>
+  <si>
+    <t>207354675</t>
+  </si>
+  <si>
+    <t>174520472</t>
+  </si>
+  <si>
+    <t>852729791</t>
+  </si>
+  <si>
+    <t>848638379</t>
+  </si>
+  <si>
+    <t>844011209</t>
+  </si>
+  <si>
+    <t>801314125</t>
+  </si>
+  <si>
+    <t>797780560</t>
+  </si>
+  <si>
+    <t>775561719</t>
+  </si>
+  <si>
+    <t>789240458</t>
+  </si>
+  <si>
+    <t>235039116</t>
+  </si>
+  <si>
+    <t>239624913</t>
+  </si>
+  <si>
+    <t>239391828</t>
+  </si>
+  <si>
+    <t>235384256</t>
+  </si>
+  <si>
+    <t>239168390</t>
+  </si>
+  <si>
+    <t>238709905</t>
+  </si>
+  <si>
+    <t>238095214</t>
+  </si>
+  <si>
+    <t>234595522</t>
+  </si>
+  <si>
+    <t>174841670</t>
+  </si>
+  <si>
+    <t>939415158</t>
+  </si>
+  <si>
+    <t>948595362</t>
+  </si>
+  <si>
+    <t>931816627</t>
+  </si>
+  <si>
+    <t>929087462</t>
+  </si>
+  <si>
+    <t>971508449</t>
+  </si>
+  <si>
+    <t>969453194</t>
+  </si>
+  <si>
+    <t>963157114</t>
+  </si>
+  <si>
+    <t>955919216</t>
+  </si>
+  <si>
+    <t>210814780</t>
+  </si>
+  <si>
+    <t>232531859</t>
+  </si>
+  <si>
+    <t>233027493</t>
+  </si>
+  <si>
+    <t>234251001</t>
+  </si>
+  <si>
+    <t>234056764</t>
+  </si>
+  <si>
+    <t>233661077</t>
+  </si>
+  <si>
+    <t>233078439</t>
+  </si>
+  <si>
+    <t>233067465</t>
+  </si>
+  <si>
+    <t>232919716</t>
+  </si>
+  <si>
+    <t>232746614</t>
+  </si>
+  <si>
+    <t>232699862</t>
+  </si>
+  <si>
+    <t>232668362</t>
+  </si>
+  <si>
+    <t>232455331</t>
+  </si>
+  <si>
+    <t>232250989</t>
+  </si>
+  <si>
+    <t>232216790</t>
+  </si>
+  <si>
+    <t>231170329</t>
+  </si>
+  <si>
+    <t>230822128</t>
+  </si>
+  <si>
+    <t>227968264</t>
+  </si>
+  <si>
+    <t>229391804</t>
+  </si>
+  <si>
+    <t>225551450</t>
+  </si>
+  <si>
+    <t>223645122</t>
+  </si>
+  <si>
+    <t>214814372</t>
+  </si>
+  <si>
+    <t>214076949</t>
+  </si>
+  <si>
+    <t>213118874</t>
+  </si>
+  <si>
+    <t>202741561</t>
+  </si>
+  <si>
+    <t>196254548</t>
+  </si>
+  <si>
+    <t>199536412</t>
+  </si>
+  <si>
+    <t>194901769</t>
+  </si>
+  <si>
+    <t>188602142</t>
+  </si>
+  <si>
+    <t>183778145</t>
+  </si>
+  <si>
+    <t>843670682</t>
+  </si>
+  <si>
+    <t>920476987</t>
+  </si>
+  <si>
+    <t>920924911</t>
+  </si>
+  <si>
+    <t>920861154</t>
+  </si>
+  <si>
+    <t>914735182</t>
+  </si>
+  <si>
+    <t>904873308</t>
+  </si>
+  <si>
+    <t>895128662</t>
+  </si>
+  <si>
+    <t>891673471</t>
+  </si>
+  <si>
+    <t>888346008</t>
+  </si>
+  <si>
+    <t>881743128</t>
+  </si>
+  <si>
+    <t>877213953</t>
+  </si>
+  <si>
+    <t>872954536</t>
+  </si>
+  <si>
+    <t>860369853</t>
+  </si>
+  <si>
+    <t>849885615</t>
+  </si>
+  <si>
+    <t>841785813</t>
+  </si>
+  <si>
+    <t>829367378</t>
+  </si>
+  <si>
+    <t>821295775</t>
+  </si>
+  <si>
+    <t>820648651</t>
+  </si>
+  <si>
+    <t>820111221</t>
+  </si>
+  <si>
+    <t>814699835</t>
+  </si>
+  <si>
+    <t>790641009</t>
+  </si>
+  <si>
+    <t>244491381</t>
+  </si>
+  <si>
+    <t>244449751</t>
+  </si>
+  <si>
+    <t>244301929</t>
+  </si>
+  <si>
+    <t>244254243</t>
+  </si>
+  <si>
+    <t>244140830</t>
+  </si>
+  <si>
+    <t>244104828</t>
+  </si>
+  <si>
+    <t>244082321</t>
+  </si>
+  <si>
+    <t>244007674</t>
+  </si>
+  <si>
+    <t>243998535</t>
+  </si>
+  <si>
+    <t>243968728</t>
+  </si>
+  <si>
+    <t>243355413</t>
+  </si>
+  <si>
+    <t>242240020</t>
+  </si>
+  <si>
+    <t>242226193</t>
+  </si>
+  <si>
+    <t>242121907</t>
+  </si>
+  <si>
+    <t>800332219</t>
+  </si>
+  <si>
+    <t>969017650</t>
+  </si>
+  <si>
+    <t>971714799</t>
+  </si>
+  <si>
+    <t>952769713</t>
+  </si>
+  <si>
+    <t>928090699</t>
+  </si>
+  <si>
+    <t>937380040</t>
+  </si>
+  <si>
+    <t>219575499</t>
+  </si>
+  <si>
+    <t>232113583</t>
+  </si>
+  <si>
+    <t>232965560</t>
+  </si>
+  <si>
+    <t>233892821</t>
+  </si>
+  <si>
+    <t>232493738</t>
+  </si>
+  <si>
+    <t>224794812</t>
+  </si>
+  <si>
+    <t>229279231</t>
+  </si>
+  <si>
+    <t>188404317</t>
+  </si>
+  <si>
+    <t>201639014</t>
+  </si>
+  <si>
+    <t>203931799</t>
+  </si>
+  <si>
+    <t>208428601</t>
+  </si>
+  <si>
+    <t>204093003</t>
+  </si>
+  <si>
+    <t>185586306</t>
+  </si>
+  <si>
+    <t>853053258</t>
+  </si>
+  <si>
+    <t>885775324</t>
+  </si>
+  <si>
+    <t>896919515</t>
+  </si>
+  <si>
+    <t>814283176</t>
+  </si>
+  <si>
+    <t>830677062</t>
+  </si>
+  <si>
+    <t>810955116</t>
+  </si>
+  <si>
+    <t>212189322</t>
+  </si>
+  <si>
+    <t>223395876</t>
+  </si>
+  <si>
+    <t>228678334</t>
+  </si>
+  <si>
+    <t>233974660</t>
+  </si>
+  <si>
+    <t>849444694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>919032783</t>
+  </si>
+  <si>
+    <t>234384448</t>
+  </si>
+  <si>
+    <t>914349406</t>
+  </si>
+  <si>
+    <t>909149472</t>
+  </si>
+  <si>
+    <t>230328415</t>
+  </si>
+  <si>
+    <t>223315767</t>
+  </si>
+  <si>
+    <t>206521340</t>
+  </si>
+  <si>
+    <t>935345995</t>
+  </si>
+  <si>
+    <t>185924465</t>
+  </si>
+  <si>
+    <t>854546292</t>
+  </si>
+  <si>
+    <t>874222130</t>
+  </si>
+  <si>
+    <t>837223522</t>
+  </si>
+  <si>
+    <t>234447484</t>
+  </si>
+  <si>
+    <t>234399529</t>
+  </si>
+  <si>
+    <t>850886163</t>
+  </si>
+  <si>
+    <t>912358052</t>
+  </si>
+  <si>
+    <t>233402241</t>
+  </si>
+  <si>
+    <t>232181523</t>
+  </si>
+  <si>
+    <t>946353020</t>
+  </si>
+  <si>
+    <t>921989541</t>
+  </si>
+  <si>
+    <t>789526401</t>
+  </si>
+  <si>
+    <t>911943854</t>
+  </si>
+  <si>
+    <t>942807656</t>
+  </si>
+  <si>
+    <t>967752993</t>
+  </si>
+  <si>
+    <t>233868730</t>
+  </si>
+  <si>
+    <t>866855871</t>
+  </si>
+  <si>
+    <t>972792711</t>
+  </si>
+  <si>
+    <t>223612189</t>
+  </si>
+  <si>
+    <t>188790673</t>
+  </si>
+  <si>
+    <t>817207669</t>
+  </si>
+  <si>
+    <t>235497025</t>
+  </si>
+  <si>
+    <t>885330799</t>
+  </si>
+  <si>
+    <t>883368510</t>
+  </si>
+  <si>
+    <t>921975375</t>
+  </si>
+  <si>
+    <t>902300049</t>
+  </si>
+  <si>
+    <t>202134379</t>
+  </si>
+  <si>
+    <t>228728758</t>
+  </si>
+  <si>
+    <t>233359557</t>
+  </si>
+  <si>
+    <t>230822011</t>
+  </si>
+  <si>
+    <t>969284474</t>
+  </si>
+  <si>
+    <t>968150916</t>
+  </si>
+  <si>
+    <t>938203050</t>
+  </si>
+  <si>
+    <t>963533165</t>
+  </si>
+  <si>
+    <t>234826133</t>
+  </si>
+  <si>
+    <t>232783229</t>
+  </si>
+  <si>
+    <t>230632956</t>
+  </si>
+  <si>
+    <t>229943422</t>
+  </si>
+  <si>
+    <t>216454144</t>
+  </si>
+  <si>
+    <t>935138291</t>
+  </si>
+  <si>
+    <t>972802197</t>
+  </si>
+  <si>
+    <t>205713708</t>
+  </si>
+  <si>
+    <t>744526280</t>
+  </si>
+  <si>
+    <t>877825582</t>
+  </si>
+  <si>
+    <t>916491453</t>
+  </si>
+  <si>
+    <t>869607634</t>
+  </si>
+  <si>
+    <t>234646168</t>
+  </si>
+  <si>
+    <t>208383707</t>
+  </si>
+  <si>
+    <t>210525030</t>
+  </si>
+  <si>
+    <t>228718999</t>
+  </si>
+  <si>
+    <t>244056812</t>
+  </si>
+  <si>
+    <t>226866600</t>
+  </si>
+  <si>
+    <t>221718244</t>
+  </si>
+  <si>
+    <t>776760583</t>
+  </si>
+  <si>
+    <t>234281727</t>
+  </si>
+  <si>
+    <t>221568086</t>
+  </si>
+  <si>
+    <t>220371755</t>
+  </si>
+  <si>
+    <t>220244770</t>
+  </si>
+  <si>
+    <t>209885429</t>
+  </si>
+  <si>
+    <t>975407721</t>
+  </si>
+  <si>
+    <t>184241606</t>
+  </si>
+  <si>
+    <t>176969594</t>
+  </si>
+  <si>
+    <t>969269731</t>
+  </si>
+  <si>
+    <t>939826735</t>
+  </si>
+  <si>
+    <t>887143307</t>
+  </si>
+  <si>
+    <t>833135001</t>
+  </si>
+  <si>
+    <t>806043877</t>
+  </si>
+  <si>
+    <t>822448118</t>
+  </si>
+  <si>
+    <t>823510254</t>
+  </si>
+  <si>
+    <t>848247395</t>
+  </si>
+  <si>
+    <t>845878028</t>
+  </si>
+  <si>
+    <t>842907762</t>
+  </si>
+  <si>
+    <t>838826547</t>
+  </si>
+  <si>
+    <t>821269606</t>
+  </si>
+  <si>
+    <t>794881718</t>
+  </si>
+  <si>
+    <t>794830624</t>
+  </si>
+  <si>
+    <t>210188854</t>
+  </si>
+  <si>
+    <t>234134926</t>
+  </si>
+  <si>
+    <t>789461039</t>
+  </si>
+  <si>
+    <t>787508476</t>
+  </si>
+  <si>
+    <t>787169543</t>
+  </si>
+  <si>
+    <t>245746486</t>
+  </si>
+  <si>
+    <t>245388818</t>
+  </si>
+  <si>
+    <t>245362078</t>
+  </si>
+  <si>
+    <t>244638890</t>
+  </si>
+  <si>
+    <t>242981060</t>
+  </si>
+  <si>
+    <t>239755238</t>
+  </si>
+  <si>
+    <t>236658625</t>
+  </si>
+  <si>
+    <t>234597312</t>
+  </si>
+  <si>
+    <t>233382286</t>
+  </si>
+  <si>
+    <t>233089451</t>
+  </si>
+  <si>
+    <t>233010879</t>
+  </si>
+  <si>
+    <t>232796171</t>
+  </si>
+  <si>
+    <t>221101854</t>
+  </si>
+  <si>
+    <t>227591520</t>
+  </si>
+  <si>
+    <t>232780837</t>
+  </si>
+  <si>
+    <t>232531172</t>
+  </si>
+  <si>
+    <t>224464929</t>
+  </si>
+  <si>
+    <t>224408769</t>
+  </si>
+  <si>
+    <t>223492517</t>
+  </si>
+  <si>
+    <t>222447249</t>
+  </si>
+  <si>
+    <t>215949227</t>
+  </si>
+  <si>
+    <t>214793626</t>
+  </si>
+  <si>
+    <t>213869336</t>
+  </si>
+  <si>
+    <t>210910513</t>
+  </si>
+  <si>
+    <t>210744599</t>
+  </si>
+  <si>
+    <t>938561663</t>
+  </si>
+  <si>
+    <t>183691991</t>
+  </si>
+  <si>
+    <t>205834496</t>
+  </si>
+  <si>
+    <t>204712503</t>
+  </si>
+  <si>
+    <t>202380469</t>
+  </si>
+  <si>
+    <t>195624360</t>
+  </si>
+  <si>
+    <t>194906297</t>
+  </si>
+  <si>
+    <t>193232851</t>
+  </si>
+  <si>
+    <t>189326824</t>
+  </si>
+  <si>
+    <t>186571646</t>
+  </si>
+  <si>
+    <t>974552709</t>
+  </si>
+  <si>
+    <t>966795910</t>
+  </si>
+  <si>
+    <t>957957024</t>
+  </si>
+  <si>
+    <t>949627958</t>
+  </si>
+  <si>
+    <t>942577515</t>
+  </si>
+  <si>
+    <t>936614928</t>
+  </si>
+  <si>
+    <t>927226963</t>
+  </si>
+  <si>
+    <t>926082086</t>
+  </si>
+  <si>
+    <t>924285277</t>
+  </si>
+  <si>
+    <t>920872037</t>
+  </si>
+  <si>
+    <t>914474121</t>
+  </si>
+  <si>
+    <t>868639042</t>
+  </si>
+  <si>
+    <t>867948204</t>
+  </si>
+  <si>
+    <t>859612321</t>
+  </si>
+  <si>
+    <t>850704903</t>
+  </si>
+  <si>
+    <t>871218198</t>
+  </si>
+  <si>
+    <t>799687953</t>
+  </si>
+  <si>
+    <t>814160945</t>
+  </si>
+  <si>
+    <t>235013194</t>
+  </si>
+  <si>
+    <t>754577595</t>
+  </si>
+  <si>
+    <t>926322599</t>
+  </si>
+  <si>
+    <t>939888636</t>
+  </si>
+  <si>
+    <t>232735880</t>
+  </si>
+  <si>
+    <t>235050840</t>
+  </si>
+  <si>
+    <t>189126992</t>
+  </si>
+  <si>
+    <t>235750712</t>
+  </si>
+  <si>
+    <t>234250110</t>
+  </si>
+  <si>
+    <t>858504099</t>
+  </si>
+  <si>
+    <t>246087914</t>
+  </si>
+  <si>
+    <t>246842169</t>
+  </si>
+  <si>
+    <t>936906753</t>
+  </si>
+  <si>
+    <t>913187146</t>
+  </si>
+  <si>
+    <t>956432458</t>
+  </si>
+  <si>
+    <t>847101635</t>
+  </si>
+  <si>
+    <t>184936270</t>
+  </si>
+  <si>
+    <t>183249295</t>
+  </si>
+  <si>
+    <t>190843965</t>
+  </si>
+  <si>
+    <t>965854502</t>
+  </si>
+  <si>
+    <t>968318877</t>
+  </si>
+  <si>
+    <t>899521169</t>
+  </si>
+  <si>
+    <t>856719400</t>
+  </si>
+  <si>
+    <t>896875808</t>
+  </si>
+  <si>
+    <t>804802340</t>
+  </si>
+  <si>
+    <t>800811832</t>
+  </si>
+  <si>
+    <t>795762925</t>
+  </si>
+  <si>
+    <t>247045150</t>
+  </si>
+  <si>
+    <t>247030848</t>
+  </si>
+  <si>
+    <t>246476026</t>
+  </si>
+  <si>
+    <t>246468254</t>
+  </si>
+  <si>
+    <t>246431518</t>
+  </si>
+  <si>
+    <t>244121707</t>
+  </si>
+  <si>
+    <t>237009737</t>
+  </si>
+  <si>
+    <t>236977462</t>
+  </si>
+  <si>
+    <t>234083115</t>
+  </si>
+  <si>
+    <t>233868805</t>
+  </si>
+  <si>
+    <t>208696736</t>
+  </si>
+  <si>
+    <t>202356733</t>
+  </si>
+  <si>
+    <t>202356725</t>
+  </si>
+  <si>
+    <t>192227142</t>
+  </si>
+  <si>
+    <t>198844932</t>
+  </si>
+  <si>
+    <t>755502279</t>
+  </si>
+  <si>
+    <t>881245686</t>
+  </si>
+  <si>
+    <t>821754540</t>
+  </si>
+  <si>
+    <t>800662367</t>
+  </si>
+  <si>
+    <t>774558914</t>
+  </si>
+  <si>
+    <t>217378755</t>
+  </si>
+  <si>
+    <t>235802109</t>
+  </si>
+  <si>
+    <t>193142548</t>
+  </si>
+  <si>
+    <t>811972839</t>
+  </si>
+  <si>
+    <t>887894537</t>
+  </si>
+  <si>
+    <t>863522334</t>
   </si>
 </sst>
 </file>
@@ -736,7 +1660,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D383"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -765,7 +1689,7 @@
         <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -777,7 +1701,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -789,7 +1713,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -801,7 +1725,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -813,7 +1737,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -825,7 +1749,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -837,7 +1761,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -849,7 +1773,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -909,7 +1833,7 @@
         <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -921,7 +1845,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -945,7 +1869,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -954,10 +1878,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -966,10 +1890,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -978,10 +1902,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -990,10 +1914,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1002,10 +1926,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1014,10 +1938,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1026,10 +1950,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1038,10 +1962,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1050,10 +1974,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1986,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1998,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1086,10 +2010,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1098,7 +2022,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
@@ -1110,7 +2034,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1122,7 +2046,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1134,10 +2058,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1146,10 +2070,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1158,10 +2082,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1170,10 +2094,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1182,7 +2106,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>5</v>
@@ -1194,7 +2118,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>5</v>
@@ -1206,10 +2130,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1218,10 +2142,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1230,10 +2154,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1242,10 +2166,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1254,10 +2178,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1266,10 +2190,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1278,10 +2202,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1290,10 +2214,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1302,10 +2226,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1314,10 +2238,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1326,10 +2250,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1338,10 +2262,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1350,10 +2274,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1362,10 +2286,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1374,10 +2298,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1386,10 +2310,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1398,10 +2322,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1410,10 +2334,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1422,10 +2346,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1434,10 +2358,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1446,10 +2370,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1458,10 +2382,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1470,10 +2394,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1482,10 +2406,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1494,10 +2418,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1506,10 +2430,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1518,10 +2442,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1530,10 +2454,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1542,10 +2466,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1553,10 +2477,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1564,10 +2488,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1575,10 +2499,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1586,10 +2510,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1597,10 +2521,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1608,10 +2532,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1619,7 +2543,7 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>6</v>
@@ -1630,7 +2554,7 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>6</v>
@@ -1641,12 +2565,3389 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C383" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1673,31 +5974,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8849E1D-3139-4AD3-91B7-9CB4791B481C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2173E26A-C70A-44B8-AFF0-160490DC1FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="250">
   <si>
     <t>Status</t>
   </si>
@@ -48,412 +48,739 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>825270907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>911482267</t>
-  </si>
-  <si>
-    <t>932285616</t>
-  </si>
-  <si>
-    <t>956984003</t>
-  </si>
-  <si>
-    <t>956985596</t>
-  </si>
-  <si>
-    <t>956009272</t>
-  </si>
-  <si>
-    <t>932769734</t>
-  </si>
-  <si>
-    <t>944469455</t>
-  </si>
-  <si>
-    <t>947048207</t>
-  </si>
-  <si>
-    <t>929407876</t>
-  </si>
-  <si>
-    <t>930716984</t>
-  </si>
-  <si>
-    <t>920710948</t>
-  </si>
-  <si>
-    <t>928326200</t>
-  </si>
-  <si>
-    <t>927311328</t>
-  </si>
-  <si>
-    <t>919506752</t>
-  </si>
-  <si>
-    <t>910129984</t>
-  </si>
-  <si>
-    <t>908593787</t>
-  </si>
-  <si>
-    <t>898866748</t>
-  </si>
-  <si>
-    <t>903823973</t>
-  </si>
-  <si>
-    <t>902700602</t>
-  </si>
-  <si>
-    <t>901739981</t>
-  </si>
-  <si>
-    <t>897489708</t>
-  </si>
-  <si>
-    <t>895000176</t>
-  </si>
-  <si>
-    <t>882224011</t>
-  </si>
-  <si>
-    <t>893935373</t>
-  </si>
-  <si>
-    <t>891375911</t>
-  </si>
-  <si>
-    <t>880366228</t>
-  </si>
-  <si>
-    <t>877473979</t>
-  </si>
-  <si>
-    <t>876330634</t>
-  </si>
-  <si>
-    <t>876146600</t>
-  </si>
-  <si>
-    <t>850263637</t>
-  </si>
-  <si>
-    <t>870244484</t>
-  </si>
-  <si>
-    <t>874739984</t>
-  </si>
-  <si>
-    <t>866474913</t>
-  </si>
-  <si>
-    <t>860038870</t>
-  </si>
-  <si>
-    <t>849998301</t>
-  </si>
-  <si>
-    <t>834006326</t>
-  </si>
-  <si>
-    <t>841613759</t>
-  </si>
-  <si>
-    <t>840538189</t>
-  </si>
-  <si>
-    <t>840468700</t>
-  </si>
-  <si>
-    <t>827979059</t>
-  </si>
-  <si>
-    <t>814231647</t>
-  </si>
-  <si>
-    <t>817586930</t>
-  </si>
-  <si>
-    <t>800928487</t>
-  </si>
-  <si>
-    <t>805363110</t>
-  </si>
-  <si>
-    <t>809129558</t>
-  </si>
-  <si>
-    <t>808922185</t>
-  </si>
-  <si>
-    <t>801943550</t>
-  </si>
-  <si>
-    <t>780994863</t>
-  </si>
-  <si>
-    <t>794968960</t>
-  </si>
-  <si>
-    <t>797507039</t>
-  </si>
-  <si>
-    <t>768054060</t>
-  </si>
-  <si>
-    <t>231556899</t>
-  </si>
-  <si>
-    <t>231557285</t>
-  </si>
-  <si>
-    <t>231556915</t>
-  </si>
-  <si>
-    <t>223483920</t>
-  </si>
-  <si>
-    <t>223483938</t>
-  </si>
-  <si>
-    <t>204585222</t>
-  </si>
-  <si>
-    <t>203556505</t>
-  </si>
-  <si>
-    <t>203268317</t>
-  </si>
-  <si>
-    <t>199416516</t>
-  </si>
-  <si>
-    <t>203017490</t>
-  </si>
-  <si>
-    <t>200405094</t>
-  </si>
-  <si>
-    <t>973044732</t>
-  </si>
-  <si>
-    <t>182794580</t>
-  </si>
-  <si>
-    <t>181383583</t>
-  </si>
-  <si>
-    <t>179291137</t>
-  </si>
-  <si>
-    <t>177344037</t>
-  </si>
-  <si>
-    <t>969666258</t>
-  </si>
-  <si>
-    <t>968281125</t>
-  </si>
-  <si>
-    <t>924399706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>802111777</t>
-  </si>
-  <si>
-    <t>230998365</t>
-  </si>
-  <si>
-    <t>236166728</t>
-  </si>
-  <si>
-    <t>236900969</t>
-  </si>
-  <si>
-    <t>238513026</t>
-  </si>
-  <si>
-    <t>934264320</t>
-  </si>
-  <si>
-    <t>812647539</t>
-  </si>
-  <si>
-    <t>839386863</t>
-  </si>
-  <si>
-    <t>875606299</t>
-  </si>
-  <si>
-    <t>875144218</t>
-  </si>
-  <si>
-    <t>863210237</t>
-  </si>
-  <si>
-    <t>871876441</t>
-  </si>
-  <si>
-    <t>871259440</t>
-  </si>
-  <si>
-    <t>866340155</t>
-  </si>
-  <si>
-    <t>852018930</t>
-  </si>
-  <si>
-    <t>846908733</t>
-  </si>
-  <si>
-    <t>836814503</t>
-  </si>
-  <si>
-    <t>817677309</t>
-  </si>
-  <si>
-    <t>829013378</t>
-  </si>
-  <si>
-    <t>816067858</t>
-  </si>
-  <si>
-    <t>810638555</t>
-  </si>
-  <si>
-    <t>809695095</t>
-  </si>
-  <si>
-    <t>804763187</t>
-  </si>
-  <si>
-    <t>774855260</t>
-  </si>
-  <si>
-    <t>794978134</t>
-  </si>
-  <si>
-    <t>208379382</t>
-  </si>
-  <si>
-    <t>237001007</t>
-  </si>
-  <si>
-    <t>244689018</t>
-  </si>
-  <si>
-    <t>241578180</t>
-  </si>
-  <si>
-    <t>236899237</t>
-  </si>
-  <si>
-    <t>234397275</t>
-  </si>
-  <si>
-    <t>230126546</t>
-  </si>
-  <si>
-    <t>216983316</t>
-  </si>
-  <si>
-    <t>195406586</t>
-  </si>
-  <si>
-    <t>194843946</t>
-  </si>
-  <si>
-    <t>184468464</t>
-  </si>
-  <si>
-    <t>177746686</t>
-  </si>
-  <si>
-    <t>947549535</t>
-  </si>
-  <si>
-    <t>955891654</t>
-  </si>
-  <si>
-    <t>961131400</t>
-  </si>
-  <si>
-    <t>957553112</t>
-  </si>
-  <si>
-    <t>955844455</t>
-  </si>
-  <si>
-    <t>955670777</t>
-  </si>
-  <si>
-    <t>955387372</t>
-  </si>
-  <si>
-    <t>951147879</t>
-  </si>
-  <si>
-    <t>933493755</t>
-  </si>
-  <si>
-    <t>928212111</t>
-  </si>
-  <si>
-    <t>932008943</t>
-  </si>
-  <si>
-    <t>932196128</t>
-  </si>
-  <si>
-    <t>894255375</t>
-  </si>
-  <si>
-    <t>896579830</t>
-  </si>
-  <si>
-    <t>896818006</t>
-  </si>
-  <si>
-    <t>876020870</t>
-  </si>
-  <si>
-    <t>892059076</t>
-  </si>
-  <si>
-    <t>880310820</t>
-  </si>
-  <si>
-    <t>896373283</t>
-  </si>
-  <si>
-    <t>180857330</t>
-  </si>
-  <si>
-    <t>185327784</t>
-  </si>
-  <si>
-    <t>180855599</t>
-  </si>
-  <si>
-    <t>958372116</t>
-  </si>
-  <si>
-    <t>941070835</t>
-  </si>
-  <si>
-    <t>902586167</t>
-  </si>
-  <si>
-    <t>895607921</t>
+    <t>216642573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>804293771</t>
+  </si>
+  <si>
+    <t>906247444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>934288303</t>
+  </si>
+  <si>
+    <t>832037448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>246094779</t>
+  </si>
+  <si>
+    <t>250726167</t>
+  </si>
+  <si>
+    <t>962675439</t>
+  </si>
+  <si>
+    <t>962069401</t>
+  </si>
+  <si>
+    <t>960532137</t>
+  </si>
+  <si>
+    <t>906439215</t>
+  </si>
+  <si>
+    <t>906198639</t>
+  </si>
+  <si>
+    <t>906029131</t>
+  </si>
+  <si>
+    <t>905602805</t>
+  </si>
+  <si>
+    <t>904152802</t>
+  </si>
+  <si>
+    <t>900268982</t>
+  </si>
+  <si>
+    <t>899126423</t>
+  </si>
+  <si>
+    <t>806120402</t>
+  </si>
+  <si>
+    <t>897266346</t>
+  </si>
+  <si>
+    <t>878200116</t>
+  </si>
+  <si>
+    <t>876035944</t>
+  </si>
+  <si>
+    <t>805624008</t>
+  </si>
+  <si>
+    <t>805559519</t>
+  </si>
+  <si>
+    <t>234488314</t>
+  </si>
+  <si>
+    <t>217159387</t>
+  </si>
+  <si>
+    <t>197901469</t>
+  </si>
+  <si>
+    <t>197839784</t>
+  </si>
+  <si>
+    <t>225284250</t>
+  </si>
+  <si>
+    <t>854393620</t>
+  </si>
+  <si>
+    <t>225290356</t>
+  </si>
+  <si>
+    <t>964481919</t>
+  </si>
+  <si>
+    <t>928792708</t>
+  </si>
+  <si>
+    <t>892782958</t>
+  </si>
+  <si>
+    <t>937076291</t>
+  </si>
+  <si>
+    <t>937935777</t>
+  </si>
+  <si>
+    <t>937436669</t>
+  </si>
+  <si>
+    <t>190782320</t>
+  </si>
+  <si>
+    <t>196674232</t>
+  </si>
+  <si>
+    <t>749346791</t>
+  </si>
+  <si>
+    <t>?????</t>
+  </si>
+  <si>
+    <t>763779950</t>
+  </si>
+  <si>
+    <t>756625947</t>
+  </si>
+  <si>
+    <t>759263860</t>
+  </si>
+  <si>
+    <t>761321284</t>
+  </si>
+  <si>
+    <t>761911225</t>
+  </si>
+  <si>
+    <t>765423169</t>
+  </si>
+  <si>
+    <t>763606088</t>
+  </si>
+  <si>
+    <t>763224569</t>
+  </si>
+  <si>
+    <t>762944282</t>
+  </si>
+  <si>
+    <t>767051216</t>
+  </si>
+  <si>
+    <t>767505328</t>
+  </si>
+  <si>
+    <t>771409087</t>
+  </si>
+  <si>
+    <t>184104119</t>
+  </si>
+  <si>
+    <t>771139460</t>
+  </si>
+  <si>
+    <t>772424549</t>
+  </si>
+  <si>
+    <t>773056126</t>
+  </si>
+  <si>
+    <t>774406759</t>
+  </si>
+  <si>
+    <t>774055663</t>
+  </si>
+  <si>
+    <t>775071990</t>
+  </si>
+  <si>
+    <t>780480251</t>
+  </si>
+  <si>
+    <t>781600675</t>
+  </si>
+  <si>
+    <t>970972489</t>
+  </si>
+  <si>
+    <t>782462091</t>
+  </si>
+  <si>
+    <t>785079272</t>
+  </si>
+  <si>
+    <t>784954020</t>
+  </si>
+  <si>
+    <t>785742390</t>
+  </si>
+  <si>
+    <t>892101449</t>
+  </si>
+  <si>
+    <t>785712609</t>
+  </si>
+  <si>
+    <t>785531454</t>
+  </si>
+  <si>
+    <t>787731102</t>
+  </si>
+  <si>
+    <t>787761406</t>
+  </si>
+  <si>
+    <t>789919937</t>
+  </si>
+  <si>
+    <t>790367787</t>
+  </si>
+  <si>
+    <t>791947348</t>
+  </si>
+  <si>
+    <t>792658050</t>
+  </si>
+  <si>
+    <t>793474960</t>
+  </si>
+  <si>
+    <t>793749965</t>
+  </si>
+  <si>
+    <t>794297618</t>
+  </si>
+  <si>
+    <t>793878061</t>
+  </si>
+  <si>
+    <t>799582402</t>
+  </si>
+  <si>
+    <t>797949801</t>
+  </si>
+  <si>
+    <t>795991334</t>
+  </si>
+  <si>
+    <t>797837790</t>
+  </si>
+  <si>
+    <t>804584385</t>
+  </si>
+  <si>
+    <t>805129479</t>
+  </si>
+  <si>
+    <t>806509273</t>
+  </si>
+  <si>
+    <t>806026401</t>
+  </si>
+  <si>
+    <t>808129765</t>
+  </si>
+  <si>
+    <t>809550522</t>
+  </si>
+  <si>
+    <t>811512684</t>
+  </si>
+  <si>
+    <t>812544421</t>
+  </si>
+  <si>
+    <t>812826885</t>
+  </si>
+  <si>
+    <t>814707117</t>
+  </si>
+  <si>
+    <t>814060434</t>
+  </si>
+  <si>
+    <t>814300590</t>
+  </si>
+  <si>
+    <t>815080944</t>
+  </si>
+  <si>
+    <t>819825989</t>
+  </si>
+  <si>
+    <t>818307476</t>
+  </si>
+  <si>
+    <t>820710345</t>
+  </si>
+  <si>
+    <t>820252439</t>
+  </si>
+  <si>
+    <t>823380583</t>
+  </si>
+  <si>
+    <t>834875951</t>
+  </si>
+  <si>
+    <t>828705917</t>
+  </si>
+  <si>
+    <t>831842897</t>
+  </si>
+  <si>
+    <t>832345189</t>
+  </si>
+  <si>
+    <t>833038320</t>
+  </si>
+  <si>
+    <t>833537826</t>
+  </si>
+  <si>
+    <t>834129987</t>
+  </si>
+  <si>
+    <t>835771068</t>
+  </si>
+  <si>
+    <t>837117286</t>
+  </si>
+  <si>
+    <t>835876438</t>
+  </si>
+  <si>
+    <t>836146013</t>
+  </si>
+  <si>
+    <t>840311280</t>
+  </si>
+  <si>
+    <t>837291024</t>
+  </si>
+  <si>
+    <t>837866361</t>
+  </si>
+  <si>
+    <t>838498073</t>
+  </si>
+  <si>
+    <t>839027699</t>
+  </si>
+  <si>
+    <t>839881616</t>
+  </si>
+  <si>
+    <t>906352947</t>
+  </si>
+  <si>
+    <t>840212884</t>
+  </si>
+  <si>
+    <t>842108031</t>
+  </si>
+  <si>
+    <t>841225158</t>
+  </si>
+  <si>
+    <t>841263001</t>
+  </si>
+  <si>
+    <t>841997350</t>
+  </si>
+  <si>
+    <t>843408190</t>
+  </si>
+  <si>
+    <t>849184951</t>
+  </si>
+  <si>
+    <t>850817911</t>
+  </si>
+  <si>
+    <t>850895123</t>
+  </si>
+  <si>
+    <t>851386148</t>
+  </si>
+  <si>
+    <t>851524052</t>
+  </si>
+  <si>
+    <t>852287352</t>
+  </si>
+  <si>
+    <t>852322787</t>
+  </si>
+  <si>
+    <t>906976075</t>
+  </si>
+  <si>
+    <t>852947690</t>
+  </si>
+  <si>
+    <t>856462571</t>
+  </si>
+  <si>
+    <t>856779495</t>
+  </si>
+  <si>
+    <t>856352392</t>
+  </si>
+  <si>
+    <t>857272466</t>
+  </si>
+  <si>
+    <t>858225158</t>
+  </si>
+  <si>
+    <t>860410970</t>
+  </si>
+  <si>
+    <t>861632119</t>
+  </si>
+  <si>
+    <t>862964859</t>
+  </si>
+  <si>
+    <t>863597526</t>
+  </si>
+  <si>
+    <t>866155223</t>
+  </si>
+  <si>
+    <t>867485884</t>
+  </si>
+  <si>
+    <t>868035944</t>
+  </si>
+  <si>
+    <t>868248315</t>
+  </si>
+  <si>
+    <t>868675418</t>
+  </si>
+  <si>
+    <t>869300289</t>
+  </si>
+  <si>
+    <t>882179603</t>
+  </si>
+  <si>
+    <t>878073612</t>
+  </si>
+  <si>
+    <t>10777289964QFILIPIAC</t>
+  </si>
+  <si>
+    <t>877516892</t>
+  </si>
+  <si>
+    <t>877607022</t>
+  </si>
+  <si>
+    <t>878457351</t>
+  </si>
+  <si>
+    <t>878486491</t>
+  </si>
+  <si>
+    <t>879398174</t>
+  </si>
+  <si>
+    <t>880481761</t>
+  </si>
+  <si>
+    <t>880029834</t>
+  </si>
+  <si>
+    <t>924250347</t>
+  </si>
+  <si>
+    <t>882992021</t>
+  </si>
+  <si>
+    <t>884744297</t>
+  </si>
+  <si>
+    <t>884263116</t>
+  </si>
+  <si>
+    <t>884724836</t>
+  </si>
+  <si>
+    <t>885426472</t>
+  </si>
+  <si>
+    <t>887258741</t>
+  </si>
+  <si>
+    <t>887489635</t>
+  </si>
+  <si>
+    <t>890372513</t>
+  </si>
+  <si>
+    <t>888607839</t>
+  </si>
+  <si>
+    <t>889076448</t>
+  </si>
+  <si>
+    <t>889664706</t>
+  </si>
+  <si>
+    <t>890864444</t>
+  </si>
+  <si>
+    <t>889752733</t>
+  </si>
+  <si>
+    <t>890159365</t>
+  </si>
+  <si>
+    <t>894195316</t>
+  </si>
+  <si>
+    <t>891902797</t>
+  </si>
+  <si>
+    <t>896206319</t>
+  </si>
+  <si>
+    <t>892661319</t>
+  </si>
+  <si>
+    <t>894024623</t>
+  </si>
+  <si>
+    <t>895257537</t>
+  </si>
+  <si>
+    <t>898281500</t>
+  </si>
+  <si>
+    <t>898647015</t>
+  </si>
+  <si>
+    <t>899142537</t>
+  </si>
+  <si>
+    <t>903102717</t>
+  </si>
+  <si>
+    <t>904780404</t>
+  </si>
+  <si>
+    <t>907304517</t>
+  </si>
+  <si>
+    <t>907940385</t>
+  </si>
+  <si>
+    <t>907471936</t>
+  </si>
+  <si>
+    <t>908246667</t>
+  </si>
+  <si>
+    <t>908928512</t>
+  </si>
+  <si>
+    <t>909084331</t>
+  </si>
+  <si>
+    <t>909173449</t>
+  </si>
+  <si>
+    <t>909916979</t>
+  </si>
+  <si>
+    <t>910872377</t>
+  </si>
+  <si>
+    <t>913579870</t>
+  </si>
+  <si>
+    <t>915406494</t>
+  </si>
+  <si>
+    <t>916607710</t>
+  </si>
+  <si>
+    <t>916316239</t>
+  </si>
+  <si>
+    <t>918806112</t>
+  </si>
+  <si>
+    <t>921061374</t>
+  </si>
+  <si>
+    <t>921270199</t>
+  </si>
+  <si>
+    <t>924000270</t>
+  </si>
+  <si>
+    <t>926175674</t>
+  </si>
+  <si>
+    <t>927956171</t>
+  </si>
+  <si>
+    <t>930014471</t>
+  </si>
+  <si>
+    <t>932235983</t>
+  </si>
+  <si>
+    <t>930940139</t>
+  </si>
+  <si>
+    <t>932146438</t>
+  </si>
+  <si>
+    <t>932867801</t>
+  </si>
+  <si>
+    <t>933110102</t>
+  </si>
+  <si>
+    <t>934249412</t>
+  </si>
+  <si>
+    <t>939256321</t>
+  </si>
+  <si>
+    <t>936311541</t>
+  </si>
+  <si>
+    <t>938930181</t>
+  </si>
+  <si>
+    <t>939522011</t>
+  </si>
+  <si>
+    <t>940794138</t>
+  </si>
+  <si>
+    <t>942000559</t>
+  </si>
+  <si>
+    <t>940448669</t>
+  </si>
+  <si>
+    <t>942310719</t>
+  </si>
+  <si>
+    <t>943100945</t>
+  </si>
+  <si>
+    <t>946602988</t>
+  </si>
+  <si>
+    <t>946860768</t>
+  </si>
+  <si>
+    <t>950852750</t>
+  </si>
+  <si>
+    <t>948342013</t>
+  </si>
+  <si>
+    <t>949400059</t>
+  </si>
+  <si>
+    <t>949858058</t>
+  </si>
+  <si>
+    <t>950183289</t>
+  </si>
+  <si>
+    <t>951134927</t>
+  </si>
+  <si>
+    <t>951833197</t>
+  </si>
+  <si>
+    <t>952172587</t>
+  </si>
+  <si>
+    <t>961969742</t>
+  </si>
+  <si>
+    <t>963721604</t>
+  </si>
+  <si>
+    <t>962884429</t>
+  </si>
+  <si>
+    <t>963650902</t>
+  </si>
+  <si>
+    <t>963748979</t>
+  </si>
+  <si>
+    <t>963757889</t>
+  </si>
+  <si>
+    <t>970101105</t>
+  </si>
+  <si>
+    <t>974971008</t>
+  </si>
+  <si>
+    <t>185545633</t>
+  </si>
+  <si>
+    <t>185927211</t>
+  </si>
+  <si>
+    <t>188577682</t>
+  </si>
+  <si>
+    <t>190003222</t>
   </si>
 </sst>
 </file>
@@ -913,7 +1240,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D135"/>
+  <dimension ref="A1:D242"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -966,7 +1293,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -975,10 +1302,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -987,10 +1314,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -999,10 +1326,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1011,7 +1338,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>6</v>
@@ -1023,7 +1350,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>6</v>
@@ -1035,7 +1362,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>6</v>
@@ -1047,7 +1374,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>6</v>
@@ -1059,7 +1386,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>6</v>
@@ -1071,7 +1398,7 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>6</v>
@@ -1083,7 +1410,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>6</v>
@@ -1095,7 +1422,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>6</v>
@@ -1107,7 +1434,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>6</v>
@@ -1119,7 +1446,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>6</v>
@@ -1131,7 +1458,7 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>6</v>
@@ -1143,7 +1470,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>6</v>
@@ -1155,7 +1482,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>6</v>
@@ -1167,7 +1494,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>6</v>
@@ -1179,7 +1506,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>6</v>
@@ -1191,7 +1518,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>6</v>
@@ -1203,7 +1530,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>6</v>
@@ -1215,7 +1542,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
@@ -1227,7 +1554,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1239,7 +1566,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>6</v>
@@ -1251,7 +1578,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1263,10 +1590,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1602,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1614,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1299,7 +1626,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1311,7 +1638,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
@@ -1323,7 +1650,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
@@ -1335,10 +1662,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1347,10 +1674,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1359,10 +1686,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1371,10 +1698,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1383,10 +1710,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1395,10 +1722,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1407,10 +1734,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1419,10 +1746,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1431,10 +1758,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1443,10 +1770,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1455,10 +1782,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1467,10 +1794,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1479,10 +1806,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1491,10 +1818,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1503,10 +1830,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1515,10 +1842,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1527,10 +1854,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1539,10 +1866,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1551,10 +1878,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1563,10 +1890,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1575,10 +1902,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1587,10 +1914,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1599,10 +1926,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1611,10 +1938,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1623,10 +1950,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1635,10 +1962,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1647,10 +1974,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1659,10 +1986,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1671,10 +1998,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1683,10 +2010,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1695,10 +2022,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1707,10 +2034,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1719,10 +2046,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1730,10 +2057,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1741,10 +2068,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1752,10 +2079,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1763,10 +2090,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1774,10 +2101,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1785,10 +2112,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1796,10 +2123,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1807,10 +2134,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1818,10 +2145,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1829,10 +2156,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1840,10 +2167,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1851,10 +2178,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1862,10 +2189,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1873,10 +2200,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1884,10 +2211,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1895,10 +2222,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1906,10 +2233,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1917,10 +2244,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1928,10 +2255,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -1939,10 +2266,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -1950,10 +2277,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -1961,10 +2288,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -1972,10 +2299,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -1983,10 +2310,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -1994,10 +2321,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -2005,10 +2332,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -2016,10 +2343,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -2027,10 +2354,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2038,10 +2365,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2049,10 +2376,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2060,10 +2387,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2071,10 +2398,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2082,10 +2409,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>4</v>
@@ -2093,10 +2420,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2104,10 +2431,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>4</v>
@@ -2115,10 +2442,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>4</v>
@@ -2126,10 +2453,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>4</v>
@@ -2137,10 +2464,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>4</v>
@@ -2148,10 +2475,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>4</v>
@@ -2159,10 +2486,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>4</v>
@@ -2170,10 +2497,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>4</v>
@@ -2181,10 +2508,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>4</v>
@@ -2192,10 +2519,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>4</v>
@@ -2203,10 +2530,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>4</v>
@@ -2214,10 +2541,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>4</v>
@@ -2225,10 +2552,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>4</v>
@@ -2236,10 +2563,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>4</v>
@@ -2247,10 +2574,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>4</v>
@@ -2258,10 +2585,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>4</v>
@@ -2269,10 +2596,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>4</v>
@@ -2280,10 +2607,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>4</v>
@@ -2291,10 +2618,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>4</v>
@@ -2302,10 +2629,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>4</v>
@@ -2313,10 +2640,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>4</v>
@@ -2324,10 +2651,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>4</v>
@@ -2335,10 +2662,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>4</v>
@@ -2346,10 +2673,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>4</v>
@@ -2357,10 +2684,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>4</v>
@@ -2368,10 +2695,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>4</v>
@@ -2379,10 +2706,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>4</v>
@@ -2390,10 +2717,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>4</v>
@@ -2401,10 +2728,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>4</v>
@@ -2412,10 +2739,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>4</v>
@@ -2423,10 +2750,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>4</v>
@@ -2434,10 +2761,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>4</v>
@@ -2445,10 +2772,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>4</v>
@@ -2456,10 +2783,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>4</v>
@@ -2467,12 +2794,1189 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C242" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2499,31 +4003,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2173E26A-C70A-44B8-AFF0-160490DC1FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4148184D-3A13-490B-A951-FDABF566582D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="727" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="266">
   <si>
     <t>Status</t>
   </si>
@@ -48,739 +48,787 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>216642573</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>804293771</t>
-  </si>
-  <si>
-    <t>906247444</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>934288303</t>
-  </si>
-  <si>
-    <t>832037448</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>246094779</t>
-  </si>
-  <si>
-    <t>250726167</t>
-  </si>
-  <si>
-    <t>962675439</t>
-  </si>
-  <si>
-    <t>962069401</t>
-  </si>
-  <si>
-    <t>960532137</t>
-  </si>
-  <si>
-    <t>906439215</t>
-  </si>
-  <si>
-    <t>906198639</t>
-  </si>
-  <si>
-    <t>906029131</t>
-  </si>
-  <si>
-    <t>905602805</t>
-  </si>
-  <si>
-    <t>904152802</t>
-  </si>
-  <si>
-    <t>900268982</t>
-  </si>
-  <si>
-    <t>899126423</t>
-  </si>
-  <si>
-    <t>806120402</t>
-  </si>
-  <si>
-    <t>897266346</t>
-  </si>
-  <si>
-    <t>878200116</t>
-  </si>
-  <si>
-    <t>876035944</t>
-  </si>
-  <si>
-    <t>805624008</t>
-  </si>
-  <si>
-    <t>805559519</t>
-  </si>
-  <si>
-    <t>234488314</t>
-  </si>
-  <si>
-    <t>217159387</t>
-  </si>
-  <si>
-    <t>197901469</t>
-  </si>
-  <si>
-    <t>197839784</t>
-  </si>
-  <si>
-    <t>225284250</t>
-  </si>
-  <si>
-    <t>854393620</t>
-  </si>
-  <si>
-    <t>225290356</t>
-  </si>
-  <si>
-    <t>964481919</t>
-  </si>
-  <si>
-    <t>928792708</t>
-  </si>
-  <si>
-    <t>892782958</t>
-  </si>
-  <si>
-    <t>937076291</t>
-  </si>
-  <si>
-    <t>937935777</t>
-  </si>
-  <si>
-    <t>937436669</t>
-  </si>
-  <si>
-    <t>190782320</t>
-  </si>
-  <si>
-    <t>196674232</t>
-  </si>
-  <si>
-    <t>749346791</t>
-  </si>
-  <si>
-    <t>?????</t>
-  </si>
-  <si>
-    <t>763779950</t>
-  </si>
-  <si>
-    <t>756625947</t>
-  </si>
-  <si>
-    <t>759263860</t>
-  </si>
-  <si>
-    <t>761321284</t>
-  </si>
-  <si>
-    <t>761911225</t>
-  </si>
-  <si>
-    <t>765423169</t>
-  </si>
-  <si>
-    <t>763606088</t>
-  </si>
-  <si>
-    <t>763224569</t>
-  </si>
-  <si>
-    <t>762944282</t>
-  </si>
-  <si>
-    <t>767051216</t>
-  </si>
-  <si>
-    <t>767505328</t>
-  </si>
-  <si>
-    <t>771409087</t>
-  </si>
-  <si>
-    <t>184104119</t>
-  </si>
-  <si>
-    <t>771139460</t>
-  </si>
-  <si>
-    <t>772424549</t>
-  </si>
-  <si>
-    <t>773056126</t>
-  </si>
-  <si>
-    <t>774406759</t>
-  </si>
-  <si>
-    <t>774055663</t>
-  </si>
-  <si>
-    <t>775071990</t>
-  </si>
-  <si>
-    <t>780480251</t>
-  </si>
-  <si>
-    <t>781600675</t>
-  </si>
-  <si>
-    <t>970972489</t>
-  </si>
-  <si>
-    <t>782462091</t>
-  </si>
-  <si>
-    <t>785079272</t>
-  </si>
-  <si>
-    <t>784954020</t>
-  </si>
-  <si>
-    <t>785742390</t>
-  </si>
-  <si>
-    <t>892101449</t>
-  </si>
-  <si>
-    <t>785712609</t>
-  </si>
-  <si>
-    <t>785531454</t>
-  </si>
-  <si>
-    <t>787731102</t>
-  </si>
-  <si>
-    <t>787761406</t>
-  </si>
-  <si>
-    <t>789919937</t>
-  </si>
-  <si>
-    <t>790367787</t>
-  </si>
-  <si>
-    <t>791947348</t>
-  </si>
-  <si>
-    <t>792658050</t>
-  </si>
-  <si>
-    <t>793474960</t>
-  </si>
-  <si>
-    <t>793749965</t>
-  </si>
-  <si>
-    <t>794297618</t>
-  </si>
-  <si>
-    <t>793878061</t>
-  </si>
-  <si>
-    <t>799582402</t>
-  </si>
-  <si>
-    <t>797949801</t>
-  </si>
-  <si>
-    <t>795991334</t>
-  </si>
-  <si>
-    <t>797837790</t>
-  </si>
-  <si>
-    <t>804584385</t>
-  </si>
-  <si>
-    <t>805129479</t>
-  </si>
-  <si>
-    <t>806509273</t>
-  </si>
-  <si>
-    <t>806026401</t>
-  </si>
-  <si>
-    <t>808129765</t>
-  </si>
-  <si>
-    <t>809550522</t>
-  </si>
-  <si>
-    <t>811512684</t>
-  </si>
-  <si>
-    <t>812544421</t>
-  </si>
-  <si>
-    <t>812826885</t>
-  </si>
-  <si>
-    <t>814707117</t>
-  </si>
-  <si>
-    <t>814060434</t>
-  </si>
-  <si>
-    <t>814300590</t>
-  </si>
-  <si>
-    <t>815080944</t>
-  </si>
-  <si>
-    <t>819825989</t>
-  </si>
-  <si>
-    <t>818307476</t>
-  </si>
-  <si>
-    <t>820710345</t>
-  </si>
-  <si>
-    <t>820252439</t>
-  </si>
-  <si>
-    <t>823380583</t>
-  </si>
-  <si>
-    <t>834875951</t>
-  </si>
-  <si>
-    <t>828705917</t>
-  </si>
-  <si>
-    <t>831842897</t>
-  </si>
-  <si>
-    <t>832345189</t>
-  </si>
-  <si>
-    <t>833038320</t>
-  </si>
-  <si>
-    <t>833537826</t>
-  </si>
-  <si>
-    <t>834129987</t>
-  </si>
-  <si>
-    <t>835771068</t>
-  </si>
-  <si>
-    <t>837117286</t>
-  </si>
-  <si>
-    <t>835876438</t>
-  </si>
-  <si>
-    <t>836146013</t>
-  </si>
-  <si>
-    <t>840311280</t>
-  </si>
-  <si>
-    <t>837291024</t>
-  </si>
-  <si>
-    <t>837866361</t>
-  </si>
-  <si>
-    <t>838498073</t>
-  </si>
-  <si>
-    <t>839027699</t>
-  </si>
-  <si>
-    <t>839881616</t>
-  </si>
-  <si>
-    <t>906352947</t>
-  </si>
-  <si>
-    <t>840212884</t>
-  </si>
-  <si>
-    <t>842108031</t>
-  </si>
-  <si>
-    <t>841225158</t>
-  </si>
-  <si>
-    <t>841263001</t>
-  </si>
-  <si>
-    <t>841997350</t>
-  </si>
-  <si>
-    <t>843408190</t>
-  </si>
-  <si>
-    <t>849184951</t>
-  </si>
-  <si>
-    <t>850817911</t>
-  </si>
-  <si>
-    <t>850895123</t>
-  </si>
-  <si>
-    <t>851386148</t>
-  </si>
-  <si>
-    <t>851524052</t>
-  </si>
-  <si>
-    <t>852287352</t>
-  </si>
-  <si>
-    <t>852322787</t>
-  </si>
-  <si>
-    <t>906976075</t>
-  </si>
-  <si>
-    <t>852947690</t>
-  </si>
-  <si>
-    <t>856462571</t>
-  </si>
-  <si>
-    <t>856779495</t>
-  </si>
-  <si>
-    <t>856352392</t>
-  </si>
-  <si>
-    <t>857272466</t>
-  </si>
-  <si>
-    <t>858225158</t>
-  </si>
-  <si>
-    <t>860410970</t>
-  </si>
-  <si>
-    <t>861632119</t>
-  </si>
-  <si>
-    <t>862964859</t>
-  </si>
-  <si>
-    <t>863597526</t>
-  </si>
-  <si>
-    <t>866155223</t>
-  </si>
-  <si>
-    <t>867485884</t>
-  </si>
-  <si>
-    <t>868035944</t>
-  </si>
-  <si>
-    <t>868248315</t>
-  </si>
-  <si>
-    <t>868675418</t>
-  </si>
-  <si>
-    <t>869300289</t>
-  </si>
-  <si>
-    <t>882179603</t>
-  </si>
-  <si>
-    <t>878073612</t>
-  </si>
-  <si>
-    <t>10777289964QFILIPIAC</t>
-  </si>
-  <si>
-    <t>877516892</t>
-  </si>
-  <si>
-    <t>877607022</t>
-  </si>
-  <si>
-    <t>878457351</t>
-  </si>
-  <si>
-    <t>878486491</t>
-  </si>
-  <si>
-    <t>879398174</t>
-  </si>
-  <si>
-    <t>880481761</t>
-  </si>
-  <si>
-    <t>880029834</t>
-  </si>
-  <si>
-    <t>924250347</t>
-  </si>
-  <si>
-    <t>882992021</t>
-  </si>
-  <si>
-    <t>884744297</t>
-  </si>
-  <si>
-    <t>884263116</t>
-  </si>
-  <si>
-    <t>884724836</t>
-  </si>
-  <si>
-    <t>885426472</t>
-  </si>
-  <si>
-    <t>887258741</t>
-  </si>
-  <si>
-    <t>887489635</t>
-  </si>
-  <si>
-    <t>890372513</t>
-  </si>
-  <si>
-    <t>888607839</t>
-  </si>
-  <si>
-    <t>889076448</t>
-  </si>
-  <si>
-    <t>889664706</t>
-  </si>
-  <si>
-    <t>890864444</t>
-  </si>
-  <si>
-    <t>889752733</t>
-  </si>
-  <si>
-    <t>890159365</t>
-  </si>
-  <si>
-    <t>894195316</t>
-  </si>
-  <si>
-    <t>891902797</t>
-  </si>
-  <si>
-    <t>896206319</t>
-  </si>
-  <si>
-    <t>892661319</t>
-  </si>
-  <si>
-    <t>894024623</t>
-  </si>
-  <si>
-    <t>895257537</t>
-  </si>
-  <si>
-    <t>898281500</t>
-  </si>
-  <si>
-    <t>898647015</t>
-  </si>
-  <si>
-    <t>899142537</t>
-  </si>
-  <si>
-    <t>903102717</t>
-  </si>
-  <si>
-    <t>904780404</t>
-  </si>
-  <si>
-    <t>907304517</t>
-  </si>
-  <si>
-    <t>907940385</t>
-  </si>
-  <si>
-    <t>907471936</t>
-  </si>
-  <si>
-    <t>908246667</t>
-  </si>
-  <si>
-    <t>908928512</t>
-  </si>
-  <si>
-    <t>909084331</t>
-  </si>
-  <si>
-    <t>909173449</t>
-  </si>
-  <si>
-    <t>909916979</t>
-  </si>
-  <si>
-    <t>910872377</t>
-  </si>
-  <si>
-    <t>913579870</t>
-  </si>
-  <si>
-    <t>915406494</t>
-  </si>
-  <si>
-    <t>916607710</t>
-  </si>
-  <si>
-    <t>916316239</t>
-  </si>
-  <si>
-    <t>918806112</t>
-  </si>
-  <si>
-    <t>921061374</t>
-  </si>
-  <si>
-    <t>921270199</t>
-  </si>
-  <si>
-    <t>924000270</t>
-  </si>
-  <si>
-    <t>926175674</t>
-  </si>
-  <si>
-    <t>927956171</t>
-  </si>
-  <si>
-    <t>930014471</t>
-  </si>
-  <si>
-    <t>932235983</t>
-  </si>
-  <si>
-    <t>930940139</t>
-  </si>
-  <si>
-    <t>932146438</t>
-  </si>
-  <si>
-    <t>932867801</t>
-  </si>
-  <si>
-    <t>933110102</t>
-  </si>
-  <si>
-    <t>934249412</t>
-  </si>
-  <si>
-    <t>939256321</t>
-  </si>
-  <si>
-    <t>936311541</t>
-  </si>
-  <si>
-    <t>938930181</t>
-  </si>
-  <si>
-    <t>939522011</t>
-  </si>
-  <si>
-    <t>940794138</t>
-  </si>
-  <si>
-    <t>942000559</t>
-  </si>
-  <si>
-    <t>940448669</t>
-  </si>
-  <si>
-    <t>942310719</t>
-  </si>
-  <si>
-    <t>943100945</t>
-  </si>
-  <si>
-    <t>946602988</t>
-  </si>
-  <si>
-    <t>946860768</t>
-  </si>
-  <si>
-    <t>950852750</t>
-  </si>
-  <si>
-    <t>948342013</t>
-  </si>
-  <si>
-    <t>949400059</t>
-  </si>
-  <si>
-    <t>949858058</t>
-  </si>
-  <si>
-    <t>950183289</t>
-  </si>
-  <si>
-    <t>951134927</t>
-  </si>
-  <si>
-    <t>951833197</t>
-  </si>
-  <si>
-    <t>952172587</t>
-  </si>
-  <si>
-    <t>961969742</t>
-  </si>
-  <si>
-    <t>963721604</t>
-  </si>
-  <si>
-    <t>962884429</t>
-  </si>
-  <si>
-    <t>963650902</t>
-  </si>
-  <si>
-    <t>963748979</t>
-  </si>
-  <si>
-    <t>963757889</t>
-  </si>
-  <si>
-    <t>970101105</t>
-  </si>
-  <si>
-    <t>974971008</t>
-  </si>
-  <si>
-    <t>185545633</t>
-  </si>
-  <si>
-    <t>185927211</t>
-  </si>
-  <si>
-    <t>188577682</t>
-  </si>
-  <si>
-    <t>190003222</t>
+    <t>204870780</t>
+  </si>
+  <si>
+    <t>214112777</t>
+  </si>
+  <si>
+    <t>243830852</t>
+  </si>
+  <si>
+    <t>243309196</t>
+  </si>
+  <si>
+    <t>237916402</t>
+  </si>
+  <si>
+    <t>189722402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>958188348</t>
+  </si>
+  <si>
+    <t>956135861</t>
+  </si>
+  <si>
+    <t>174469423</t>
+  </si>
+  <si>
+    <t>185605767</t>
+  </si>
+  <si>
+    <t>184472748</t>
+  </si>
+  <si>
+    <t>953593245</t>
+  </si>
+  <si>
+    <t>934236807</t>
+  </si>
+  <si>
+    <t>913657577</t>
+  </si>
+  <si>
+    <t>221780376</t>
+  </si>
+  <si>
+    <t>221353893</t>
+  </si>
+  <si>
+    <t>218839201</t>
+  </si>
+  <si>
+    <t>218407223</t>
+  </si>
+  <si>
+    <t>217656630</t>
+  </si>
+  <si>
+    <t>216706493</t>
+  </si>
+  <si>
+    <t>233313547</t>
+  </si>
+  <si>
+    <t>242416703</t>
+  </si>
+  <si>
+    <t>880583483</t>
+  </si>
+  <si>
+    <t>879121543</t>
+  </si>
+  <si>
+    <t>878779879</t>
+  </si>
+  <si>
+    <t>877897748</t>
+  </si>
+  <si>
+    <t>872854363</t>
+  </si>
+  <si>
+    <t>833170446</t>
+  </si>
+  <si>
+    <t>830102483</t>
+  </si>
+  <si>
+    <t>807033026</t>
+  </si>
+  <si>
+    <t>757101971</t>
+  </si>
+  <si>
+    <t>749755611</t>
+  </si>
+  <si>
+    <t>251299867</t>
+  </si>
+  <si>
+    <t>246129179</t>
+  </si>
+  <si>
+    <t>805289521</t>
+  </si>
+  <si>
+    <t>767487022</t>
+  </si>
+  <si>
+    <t>230780169</t>
+  </si>
+  <si>
+    <t>230778940</t>
+  </si>
+  <si>
+    <t>230760567</t>
+  </si>
+  <si>
+    <t>230756672</t>
+  </si>
+  <si>
+    <t>230738902</t>
+  </si>
+  <si>
+    <t>230685079</t>
+  </si>
+  <si>
+    <t>230682795</t>
+  </si>
+  <si>
+    <t>230679908</t>
+  </si>
+  <si>
+    <t>230634820</t>
+  </si>
+  <si>
+    <t>230608766</t>
+  </si>
+  <si>
+    <t>230602116</t>
+  </si>
+  <si>
+    <t>230580189</t>
+  </si>
+  <si>
+    <t>230571931</t>
+  </si>
+  <si>
+    <t>230571501</t>
+  </si>
+  <si>
+    <t>230533600</t>
+  </si>
+  <si>
+    <t>230503843</t>
+  </si>
+  <si>
+    <t>230471926</t>
+  </si>
+  <si>
+    <t>230471389</t>
+  </si>
+  <si>
+    <t>230462297</t>
+  </si>
+  <si>
+    <t>230437646</t>
+  </si>
+  <si>
+    <t>230436143</t>
+  </si>
+  <si>
+    <t>230427027</t>
+  </si>
+  <si>
+    <t>230418927</t>
+  </si>
+  <si>
+    <t>230412946</t>
+  </si>
+  <si>
+    <t>230403382</t>
+  </si>
+  <si>
+    <t>230381075</t>
+  </si>
+  <si>
+    <t>230379228</t>
+  </si>
+  <si>
+    <t>230378121</t>
+  </si>
+  <si>
+    <t>230378006</t>
+  </si>
+  <si>
+    <t>230374716</t>
+  </si>
+  <si>
+    <t>230336129</t>
+  </si>
+  <si>
+    <t>229976331</t>
+  </si>
+  <si>
+    <t>229956523</t>
+  </si>
+  <si>
+    <t>229952423</t>
+  </si>
+  <si>
+    <t>229915776</t>
+  </si>
+  <si>
+    <t>229912765</t>
+  </si>
+  <si>
+    <t>229883909</t>
+  </si>
+  <si>
+    <t>229881879</t>
+  </si>
+  <si>
+    <t>229862853</t>
+  </si>
+  <si>
+    <t>229831874</t>
+  </si>
+  <si>
+    <t>229812742</t>
+  </si>
+  <si>
+    <t>229775931</t>
+  </si>
+  <si>
+    <t>229749753</t>
+  </si>
+  <si>
+    <t>229749399</t>
+  </si>
+  <si>
+    <t>229749191</t>
+  </si>
+  <si>
+    <t>229748888</t>
+  </si>
+  <si>
+    <t>229748631</t>
+  </si>
+  <si>
+    <t>229745819</t>
+  </si>
+  <si>
+    <t>229673763</t>
+  </si>
+  <si>
+    <t>229410232</t>
+  </si>
+  <si>
+    <t>229031467</t>
+  </si>
+  <si>
+    <t>228775718</t>
+  </si>
+  <si>
+    <t>228660704</t>
+  </si>
+  <si>
+    <t>228627943</t>
+  </si>
+  <si>
+    <t>228350025</t>
+  </si>
+  <si>
+    <t>227821208</t>
+  </si>
+  <si>
+    <t>227540030</t>
+  </si>
+  <si>
+    <t>227428228</t>
+  </si>
+  <si>
+    <t>227191420</t>
+  </si>
+  <si>
+    <t>226254849</t>
+  </si>
+  <si>
+    <t>226230039</t>
+  </si>
+  <si>
+    <t>226105629</t>
+  </si>
+  <si>
+    <t>225279680</t>
+  </si>
+  <si>
+    <t>225042153</t>
+  </si>
+  <si>
+    <t>223582481</t>
+  </si>
+  <si>
+    <t>230330205</t>
+  </si>
+  <si>
+    <t>230328209</t>
+  </si>
+  <si>
+    <t>230323374</t>
+  </si>
+  <si>
+    <t>230303939</t>
+  </si>
+  <si>
+    <t>230293254</t>
+  </si>
+  <si>
+    <t>230248373</t>
+  </si>
+  <si>
+    <t>230243549</t>
+  </si>
+  <si>
+    <t>230212700</t>
+  </si>
+  <si>
+    <t>230205803</t>
+  </si>
+  <si>
+    <t>230171724</t>
+  </si>
+  <si>
+    <t>230164950</t>
+  </si>
+  <si>
+    <t>230164372</t>
+  </si>
+  <si>
+    <t>230117719</t>
+  </si>
+  <si>
+    <t>230008652</t>
+  </si>
+  <si>
+    <t>230128500</t>
+  </si>
+  <si>
+    <t>222126470</t>
+  </si>
+  <si>
+    <t>789603481</t>
+  </si>
+  <si>
+    <t>245999325</t>
+  </si>
+  <si>
+    <t>250923806</t>
+  </si>
+  <si>
+    <t>250646035</t>
+  </si>
+  <si>
+    <t>245570878</t>
+  </si>
+  <si>
+    <t>245529080</t>
+  </si>
+  <si>
+    <t>245426469</t>
+  </si>
+  <si>
+    <t>245254986</t>
+  </si>
+  <si>
+    <t>245053263</t>
+  </si>
+  <si>
+    <t>244177055</t>
+  </si>
+  <si>
+    <t>243946427</t>
+  </si>
+  <si>
+    <t>829575921</t>
+  </si>
+  <si>
+    <t>855935924</t>
+  </si>
+  <si>
+    <t>848316323</t>
+  </si>
+  <si>
+    <t>839832361</t>
+  </si>
+  <si>
+    <t>827860713</t>
+  </si>
+  <si>
+    <t>803130610</t>
+  </si>
+  <si>
+    <t>228409805</t>
+  </si>
+  <si>
+    <t>225705197</t>
+  </si>
+  <si>
+    <t>224456594</t>
+  </si>
+  <si>
+    <t>221814043</t>
+  </si>
+  <si>
+    <t>907255107</t>
+  </si>
+  <si>
+    <t>907254100</t>
+  </si>
+  <si>
+    <t>905887547</t>
+  </si>
+  <si>
+    <t>904259722</t>
+  </si>
+  <si>
+    <t>899204543</t>
+  </si>
+  <si>
+    <t>897935387</t>
+  </si>
+  <si>
+    <t>213428364</t>
+  </si>
+  <si>
+    <t>215477872</t>
+  </si>
+  <si>
+    <t>213040292</t>
+  </si>
+  <si>
+    <t>212516474</t>
+  </si>
+  <si>
+    <t>194875468</t>
+  </si>
+  <si>
+    <t>205127339</t>
+  </si>
+  <si>
+    <t>199856844</t>
+  </si>
+  <si>
+    <t>955574631</t>
+  </si>
+  <si>
+    <t>958302162</t>
+  </si>
+  <si>
+    <t>965966736</t>
+  </si>
+  <si>
+    <t>961646332</t>
+  </si>
+  <si>
+    <t>952819427</t>
+  </si>
+  <si>
+    <t>950256762</t>
+  </si>
+  <si>
+    <t>942686241</t>
+  </si>
+  <si>
+    <t>931815603</t>
+  </si>
+  <si>
+    <t>221132172</t>
+  </si>
+  <si>
+    <t>221013695</t>
+  </si>
+  <si>
+    <t>219616210</t>
+  </si>
+  <si>
+    <t>234826083</t>
+  </si>
+  <si>
+    <t>236087445</t>
+  </si>
+  <si>
+    <t>234826828</t>
+  </si>
+  <si>
+    <t>250353574</t>
+  </si>
+  <si>
+    <t>199340963</t>
+  </si>
+  <si>
+    <t>923822690</t>
+  </si>
+  <si>
+    <t>899130896</t>
+  </si>
+  <si>
+    <t>951082043</t>
+  </si>
+  <si>
+    <t>961169756</t>
+  </si>
+  <si>
+    <t>244566760</t>
+  </si>
+  <si>
+    <t>244544544</t>
+  </si>
+  <si>
+    <t>825779881</t>
+  </si>
+  <si>
+    <t>855112243</t>
+  </si>
+  <si>
+    <t>830831578</t>
+  </si>
+  <si>
+    <t>228308247</t>
+  </si>
+  <si>
+    <t>883626180</t>
+  </si>
+  <si>
+    <t>967058904</t>
+  </si>
+  <si>
+    <t>220536597</t>
+  </si>
+  <si>
+    <t>244007575</t>
+  </si>
+  <si>
+    <t>245837822</t>
+  </si>
+  <si>
+    <t>242717886</t>
+  </si>
+  <si>
+    <t>960528614</t>
+  </si>
+  <si>
+    <t>225127269</t>
+  </si>
+  <si>
+    <t>237752146</t>
+  </si>
+  <si>
+    <t>238716843</t>
+  </si>
+  <si>
+    <t>239725314</t>
+  </si>
+  <si>
+    <t>239112612</t>
+  </si>
+  <si>
+    <t>969785009</t>
+  </si>
+  <si>
+    <t>926295761</t>
+  </si>
+  <si>
+    <t>925410783</t>
+  </si>
+  <si>
+    <t>903453839</t>
+  </si>
+  <si>
+    <t>913646281</t>
+  </si>
+  <si>
+    <t>910543465</t>
+  </si>
+  <si>
+    <t>902707128</t>
+  </si>
+  <si>
+    <t>902331747</t>
+  </si>
+  <si>
+    <t>217417223</t>
+  </si>
+  <si>
+    <t>189257227</t>
+  </si>
+  <si>
+    <t>198589255</t>
+  </si>
+  <si>
+    <t>205748316</t>
+  </si>
+  <si>
+    <t>205486040</t>
+  </si>
+  <si>
+    <t>184029522</t>
+  </si>
+  <si>
+    <t>186435891</t>
+  </si>
+  <si>
+    <t>185035684</t>
+  </si>
+  <si>
+    <t>971894070</t>
+  </si>
+  <si>
+    <t>240603641</t>
+  </si>
+  <si>
+    <t>888658329</t>
+  </si>
+  <si>
+    <t>242102006</t>
+  </si>
+  <si>
+    <t>241800881</t>
+  </si>
+  <si>
+    <t>241040652</t>
+  </si>
+  <si>
+    <t>237835487</t>
+  </si>
+  <si>
+    <t>237911288</t>
+  </si>
+  <si>
+    <t>237702695</t>
+  </si>
+  <si>
+    <t>867645495</t>
+  </si>
+  <si>
+    <t>871154138</t>
+  </si>
+  <si>
+    <t>838040594</t>
+  </si>
+  <si>
+    <t>840653152</t>
+  </si>
+  <si>
+    <t>226945792</t>
+  </si>
+  <si>
+    <t>229284389</t>
+  </si>
+  <si>
+    <t>243891623</t>
+  </si>
+  <si>
+    <t>208960793</t>
+  </si>
+  <si>
+    <t>213727476</t>
+  </si>
+  <si>
+    <t>193275439</t>
+  </si>
+  <si>
+    <t>244449850</t>
+  </si>
+  <si>
+    <t>245619220</t>
+  </si>
+  <si>
+    <t>244734657</t>
+  </si>
+  <si>
+    <t>245134204</t>
+  </si>
+  <si>
+    <t>840223006</t>
+  </si>
+  <si>
+    <t>889851733</t>
+  </si>
+  <si>
+    <t>953407834</t>
+  </si>
+  <si>
+    <t>962813303</t>
+  </si>
+  <si>
+    <t>894628951</t>
+  </si>
+  <si>
+    <t>888767112</t>
+  </si>
+  <si>
+    <t>974648887</t>
+  </si>
+  <si>
+    <t>245876614</t>
+  </si>
+  <si>
+    <t>844968929</t>
+  </si>
+  <si>
+    <t>231806062</t>
+  </si>
+  <si>
+    <t>246052306</t>
+  </si>
+  <si>
+    <t>955092287</t>
+  </si>
+  <si>
+    <t>896680521</t>
+  </si>
+  <si>
+    <t>929902116</t>
+  </si>
+  <si>
+    <t>921055483</t>
+  </si>
+  <si>
+    <t>243331653</t>
+  </si>
+  <si>
+    <t>242370652</t>
+  </si>
+  <si>
+    <t>201665324</t>
+  </si>
+  <si>
+    <t>215050901</t>
+  </si>
+  <si>
+    <t>210942557</t>
+  </si>
+  <si>
+    <t>819284617</t>
+  </si>
+  <si>
+    <t>819255575</t>
+  </si>
+  <si>
+    <t>237083773</t>
+  </si>
+  <si>
+    <t>239661667</t>
+  </si>
+  <si>
+    <t>892446356</t>
+  </si>
+  <si>
+    <t>207583638</t>
+  </si>
+  <si>
+    <t>224641716</t>
+  </si>
+  <si>
+    <t>252578814</t>
+  </si>
+  <si>
+    <t>252231141</t>
   </si>
 </sst>
 </file>
@@ -1240,7 +1288,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D242"/>
+  <dimension ref="A1:D258"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -1266,10 +1314,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>4</v>
@@ -1278,10 +1326,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1338,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1350,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1362,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -1329,7 +1377,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1386,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>14</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1398,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1410,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1422,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1434,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1446,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1458,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1470,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1482,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1494,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1506,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1470,10 +1518,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1482,10 +1530,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1542,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1506,10 +1554,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1518,10 +1566,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1578,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1542,10 +1590,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1554,10 +1602,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1566,10 +1614,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1578,10 +1626,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1590,10 +1638,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1602,10 +1650,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1614,10 +1662,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1626,10 +1674,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1638,10 +1686,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1650,10 +1698,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1662,10 +1710,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1674,10 +1722,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1686,10 +1734,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1698,10 +1746,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1710,10 +1758,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1722,10 +1770,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1737,7 +1785,7 @@
         <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1749,7 +1797,7 @@
         <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1761,7 +1809,7 @@
         <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1773,7 +1821,7 @@
         <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1785,7 +1833,7 @@
         <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1797,7 +1845,7 @@
         <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1809,7 +1857,7 @@
         <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1821,7 +1869,7 @@
         <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1833,7 +1881,7 @@
         <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1845,7 +1893,7 @@
         <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1857,7 +1905,7 @@
         <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1869,7 +1917,7 @@
         <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1881,7 +1929,7 @@
         <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1893,7 +1941,7 @@
         <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1905,7 +1953,7 @@
         <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1917,7 +1965,7 @@
         <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1929,7 +1977,7 @@
         <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1941,7 +1989,7 @@
         <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1953,7 +2001,7 @@
         <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1965,7 +2013,7 @@
         <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1977,7 +2025,7 @@
         <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1989,7 +2037,7 @@
         <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -2001,7 +2049,7 @@
         <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -2013,7 +2061,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -2025,7 +2073,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -2037,7 +2085,7 @@
         <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -2049,7 +2097,7 @@
         <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -2060,7 +2108,7 @@
         <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -2071,7 +2119,7 @@
         <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -2082,7 +2130,7 @@
         <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -2093,7 +2141,7 @@
         <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -2104,7 +2152,7 @@
         <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -2115,7 +2163,7 @@
         <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -2126,7 +2174,7 @@
         <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -2137,7 +2185,7 @@
         <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -2148,7 +2196,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -2159,7 +2207,7 @@
         <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -2170,7 +2218,7 @@
         <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -2181,7 +2229,7 @@
         <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -2192,7 +2240,7 @@
         <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -2203,7 +2251,7 @@
         <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -2214,7 +2262,7 @@
         <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -2225,7 +2273,7 @@
         <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -2236,7 +2284,7 @@
         <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -2247,7 +2295,7 @@
         <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -2258,7 +2306,7 @@
         <v>93</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -2269,7 +2317,7 @@
         <v>94</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -2280,7 +2328,7 @@
         <v>95</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -2291,7 +2339,7 @@
         <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -2302,7 +2350,7 @@
         <v>97</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -2313,7 +2361,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -2324,7 +2372,7 @@
         <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -2335,7 +2383,7 @@
         <v>100</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -2346,7 +2394,7 @@
         <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -2357,7 +2405,7 @@
         <v>102</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2368,7 +2416,7 @@
         <v>103</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2379,7 +2427,7 @@
         <v>104</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2390,7 +2438,7 @@
         <v>105</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2401,7 +2449,7 @@
         <v>106</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2412,7 +2460,7 @@
         <v>107</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>4</v>
@@ -2423,7 +2471,7 @@
         <v>108</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2434,7 +2482,7 @@
         <v>109</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>4</v>
@@ -2445,7 +2493,7 @@
         <v>110</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>4</v>
@@ -2456,7 +2504,7 @@
         <v>111</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>4</v>
@@ -2467,7 +2515,7 @@
         <v>112</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>4</v>
@@ -2478,7 +2526,7 @@
         <v>113</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>4</v>
@@ -2489,7 +2537,7 @@
         <v>114</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>4</v>
@@ -2500,7 +2548,7 @@
         <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>4</v>
@@ -2511,7 +2559,7 @@
         <v>116</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>4</v>
@@ -2522,7 +2570,7 @@
         <v>117</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>4</v>
@@ -2533,7 +2581,7 @@
         <v>118</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>4</v>
@@ -2544,7 +2592,7 @@
         <v>119</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>4</v>
@@ -2555,7 +2603,7 @@
         <v>120</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>4</v>
@@ -2566,7 +2614,7 @@
         <v>121</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>4</v>
@@ -2577,7 +2625,7 @@
         <v>122</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>4</v>
@@ -2588,7 +2636,7 @@
         <v>123</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>4</v>
@@ -2599,7 +2647,7 @@
         <v>124</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>4</v>
@@ -2610,7 +2658,7 @@
         <v>125</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>4</v>
@@ -2621,7 +2669,7 @@
         <v>126</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>4</v>
@@ -2632,7 +2680,7 @@
         <v>127</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>4</v>
@@ -2643,7 +2691,7 @@
         <v>128</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>4</v>
@@ -2654,7 +2702,7 @@
         <v>129</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>4</v>
@@ -2665,7 +2713,7 @@
         <v>130</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>4</v>
@@ -2676,7 +2724,7 @@
         <v>131</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>4</v>
@@ -2687,7 +2735,7 @@
         <v>132</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>4</v>
@@ -2698,7 +2746,7 @@
         <v>133</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>4</v>
@@ -2709,7 +2757,7 @@
         <v>134</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>4</v>
@@ -2720,7 +2768,7 @@
         <v>135</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>4</v>
@@ -2731,7 +2779,7 @@
         <v>136</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>4</v>
@@ -2742,7 +2790,7 @@
         <v>137</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>4</v>
@@ -2753,7 +2801,7 @@
         <v>138</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>4</v>
@@ -2764,7 +2812,7 @@
         <v>139</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>4</v>
@@ -2775,7 +2823,7 @@
         <v>140</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>4</v>
@@ -2786,7 +2834,7 @@
         <v>141</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>4</v>
@@ -2797,7 +2845,7 @@
         <v>142</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>4</v>
@@ -2808,7 +2856,7 @@
         <v>143</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>4</v>
@@ -2819,7 +2867,7 @@
         <v>144</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>4</v>
@@ -2830,7 +2878,7 @@
         <v>145</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>4</v>
@@ -2841,7 +2889,7 @@
         <v>146</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>4</v>
@@ -2852,7 +2900,7 @@
         <v>147</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>4</v>
@@ -2863,7 +2911,7 @@
         <v>148</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>4</v>
@@ -2874,7 +2922,7 @@
         <v>149</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>4</v>
@@ -2885,7 +2933,7 @@
         <v>150</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>4</v>
@@ -2896,7 +2944,7 @@
         <v>151</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>4</v>
@@ -2907,7 +2955,7 @@
         <v>152</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>4</v>
@@ -2918,7 +2966,7 @@
         <v>153</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>4</v>
@@ -2929,7 +2977,7 @@
         <v>154</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>4</v>
@@ -2940,7 +2988,7 @@
         <v>155</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>4</v>
@@ -2951,7 +2999,7 @@
         <v>156</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>4</v>
@@ -2962,7 +3010,7 @@
         <v>157</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>4</v>
@@ -2973,7 +3021,7 @@
         <v>158</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>4</v>
@@ -2984,7 +3032,7 @@
         <v>159</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>4</v>
@@ -2995,7 +3043,7 @@
         <v>160</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>4</v>
@@ -3006,7 +3054,7 @@
         <v>161</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>4</v>
@@ -3017,7 +3065,7 @@
         <v>162</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>4</v>
@@ -3028,7 +3076,7 @@
         <v>163</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>4</v>
@@ -3039,7 +3087,7 @@
         <v>164</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>4</v>
@@ -3050,7 +3098,7 @@
         <v>165</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>4</v>
@@ -3061,7 +3109,7 @@
         <v>166</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>4</v>
@@ -3072,7 +3120,7 @@
         <v>167</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>4</v>
@@ -3083,7 +3131,7 @@
         <v>168</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>4</v>
@@ -3094,7 +3142,7 @@
         <v>169</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>4</v>
@@ -3105,7 +3153,7 @@
         <v>170</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>4</v>
@@ -3116,7 +3164,7 @@
         <v>171</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>4</v>
@@ -3127,7 +3175,7 @@
         <v>172</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>4</v>
@@ -3138,7 +3186,7 @@
         <v>173</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>4</v>
@@ -3149,7 +3197,7 @@
         <v>174</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>4</v>
@@ -3160,7 +3208,7 @@
         <v>175</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>4</v>
@@ -3171,7 +3219,7 @@
         <v>176</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>4</v>
@@ -3182,7 +3230,7 @@
         <v>177</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>4</v>
@@ -3193,7 +3241,7 @@
         <v>178</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>4</v>
@@ -3204,7 +3252,7 @@
         <v>179</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>4</v>
@@ -3215,7 +3263,7 @@
         <v>180</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>4</v>
@@ -3226,7 +3274,7 @@
         <v>181</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>4</v>
@@ -3237,7 +3285,7 @@
         <v>182</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>4</v>
@@ -3248,7 +3296,7 @@
         <v>183</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>4</v>
@@ -3259,7 +3307,7 @@
         <v>184</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>47</v>
+        <v>6</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>4</v>
@@ -3270,7 +3318,7 @@
         <v>185</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>4</v>
@@ -3281,7 +3329,7 @@
         <v>186</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>4</v>
@@ -3292,7 +3340,7 @@
         <v>187</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>4</v>
@@ -3303,7 +3351,7 @@
         <v>188</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>4</v>
@@ -3314,7 +3362,7 @@
         <v>189</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>4</v>
@@ -3325,7 +3373,7 @@
         <v>190</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>4</v>
@@ -3336,7 +3384,7 @@
         <v>191</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>4</v>
@@ -3347,7 +3395,7 @@
         <v>192</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>4</v>
@@ -3358,7 +3406,7 @@
         <v>193</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>4</v>
@@ -3369,7 +3417,7 @@
         <v>194</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>4</v>
@@ -3380,7 +3428,7 @@
         <v>195</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>4</v>
@@ -3391,7 +3439,7 @@
         <v>196</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>4</v>
@@ -3402,7 +3450,7 @@
         <v>197</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>4</v>
@@ -3413,7 +3461,7 @@
         <v>198</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>4</v>
@@ -3424,7 +3472,7 @@
         <v>199</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>4</v>
@@ -3435,7 +3483,7 @@
         <v>200</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>4</v>
@@ -3446,7 +3494,7 @@
         <v>201</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>4</v>
@@ -3457,7 +3505,7 @@
         <v>202</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>4</v>
@@ -3468,7 +3516,7 @@
         <v>203</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>4</v>
@@ -3479,7 +3527,7 @@
         <v>204</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>4</v>
@@ -3490,7 +3538,7 @@
         <v>205</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>4</v>
@@ -3501,7 +3549,7 @@
         <v>206</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>4</v>
@@ -3512,7 +3560,7 @@
         <v>207</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>4</v>
@@ -3523,7 +3571,7 @@
         <v>208</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>4</v>
@@ -3534,7 +3582,7 @@
         <v>209</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>4</v>
@@ -3545,7 +3593,7 @@
         <v>210</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>4</v>
@@ -3556,7 +3604,7 @@
         <v>211</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>4</v>
@@ -3567,7 +3615,7 @@
         <v>212</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>4</v>
@@ -3578,7 +3626,7 @@
         <v>213</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>4</v>
@@ -3589,7 +3637,7 @@
         <v>214</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>4</v>
@@ -3600,7 +3648,7 @@
         <v>215</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>4</v>
@@ -3611,7 +3659,7 @@
         <v>216</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>4</v>
@@ -3622,7 +3670,7 @@
         <v>217</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>4</v>
@@ -3633,7 +3681,7 @@
         <v>218</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>4</v>
@@ -3644,7 +3692,7 @@
         <v>219</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>4</v>
@@ -3655,7 +3703,7 @@
         <v>220</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>4</v>
@@ -3666,7 +3714,7 @@
         <v>221</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>4</v>
@@ -3677,7 +3725,7 @@
         <v>222</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>4</v>
@@ -3688,7 +3736,7 @@
         <v>223</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>4</v>
@@ -3699,7 +3747,7 @@
         <v>224</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>4</v>
@@ -3710,7 +3758,7 @@
         <v>225</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>4</v>
@@ -3721,7 +3769,7 @@
         <v>226</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>4</v>
@@ -3732,7 +3780,7 @@
         <v>227</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>4</v>
@@ -3743,7 +3791,7 @@
         <v>228</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>4</v>
@@ -3754,7 +3802,7 @@
         <v>229</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>4</v>
@@ -3765,7 +3813,7 @@
         <v>230</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>4</v>
@@ -3776,7 +3824,7 @@
         <v>231</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>4</v>
@@ -3787,7 +3835,7 @@
         <v>232</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>4</v>
@@ -3798,7 +3846,7 @@
         <v>233</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>4</v>
@@ -3809,7 +3857,7 @@
         <v>234</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>4</v>
@@ -3820,7 +3868,7 @@
         <v>235</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>4</v>
@@ -3831,7 +3879,7 @@
         <v>236</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C229" s="6" t="s">
         <v>4</v>
@@ -3842,7 +3890,7 @@
         <v>237</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>4</v>
@@ -3853,7 +3901,7 @@
         <v>238</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>4</v>
@@ -3864,7 +3912,7 @@
         <v>239</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C232" s="6" t="s">
         <v>4</v>
@@ -3875,7 +3923,7 @@
         <v>240</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>4</v>
@@ -3886,7 +3934,7 @@
         <v>241</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>4</v>
@@ -3897,7 +3945,7 @@
         <v>242</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>4</v>
@@ -3908,7 +3956,7 @@
         <v>243</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>4</v>
@@ -3919,7 +3967,7 @@
         <v>244</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>4</v>
@@ -3930,7 +3978,7 @@
         <v>245</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>4</v>
@@ -3941,7 +3989,7 @@
         <v>246</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>4</v>
@@ -3952,7 +4000,7 @@
         <v>247</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>4</v>
@@ -3963,7 +4011,7 @@
         <v>248</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>4</v>
@@ -3974,9 +4022,185 @@
         <v>249</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C258" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4003,31 +4227,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983C1301-ED71-4E90-9A4E-1D4B6EF63B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96058F-172D-4185-A972-36B8C5466158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="85">
   <si>
     <t>Status</t>
   </si>
@@ -48,298 +48,244 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>968449540</t>
+    <t>223709290</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>938515446</t>
+    <t>217252372</t>
+  </si>
+  <si>
+    <t>204365104</t>
+  </si>
+  <si>
+    <t>203121953</t>
+  </si>
+  <si>
+    <t>963418508</t>
+  </si>
+  <si>
+    <t>249660287</t>
+  </si>
+  <si>
+    <t>975805320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>250348251</t>
+  </si>
+  <si>
+    <t>249937974</t>
+  </si>
+  <si>
+    <t>176041659</t>
+  </si>
+  <si>
+    <t>175115728</t>
+  </si>
+  <si>
+    <t>174675672</t>
+  </si>
+  <si>
+    <t>866055142</t>
+  </si>
+  <si>
+    <t>926646989</t>
+  </si>
+  <si>
+    <t>915617439</t>
+  </si>
+  <si>
+    <t>905756098</t>
+  </si>
+  <si>
+    <t>241827090</t>
+  </si>
+  <si>
+    <t>231288832</t>
+  </si>
+  <si>
+    <t>220545861</t>
+  </si>
+  <si>
+    <t>217504772</t>
+  </si>
+  <si>
+    <t>219613944</t>
+  </si>
+  <si>
+    <t>804653487</t>
+  </si>
+  <si>
+    <t>829076862</t>
+  </si>
+  <si>
+    <t>811179005</t>
+  </si>
+  <si>
+    <t>805386897</t>
+  </si>
+  <si>
+    <t>952544074</t>
+  </si>
+  <si>
+    <t>959767199</t>
+  </si>
+  <si>
+    <t>975195680</t>
+  </si>
+  <si>
+    <t>969723026</t>
+  </si>
+  <si>
+    <t>191299118</t>
+  </si>
+  <si>
+    <t>200439192</t>
+  </si>
+  <si>
+    <t>187297092</t>
+  </si>
+  <si>
+    <t>238388460</t>
+  </si>
+  <si>
+    <t>257019582</t>
+  </si>
+  <si>
+    <t>256928205</t>
+  </si>
+  <si>
+    <t>256156971</t>
+  </si>
+  <si>
+    <t>255824629</t>
+  </si>
+  <si>
+    <t>254566916</t>
+  </si>
+  <si>
+    <t>254541448</t>
+  </si>
+  <si>
+    <t>253356079</t>
+  </si>
+  <si>
+    <t>252835974</t>
+  </si>
+  <si>
+    <t>252707348</t>
+  </si>
+  <si>
+    <t>249753462</t>
+  </si>
+  <si>
+    <t>250612243</t>
+  </si>
+  <si>
+    <t>250444704</t>
+  </si>
+  <si>
+    <t>250313701</t>
+  </si>
+  <si>
+    <t>250057910</t>
+  </si>
+  <si>
+    <t>250049792</t>
+  </si>
+  <si>
+    <t>249650478</t>
+  </si>
+  <si>
+    <t>245793678</t>
+  </si>
+  <si>
+    <t>240314728</t>
+  </si>
+  <si>
+    <t>205894516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>814665331</t>
+  </si>
+  <si>
+    <t>833312618</t>
+  </si>
+  <si>
+    <t>931989937</t>
+  </si>
+  <si>
+    <t>941361986</t>
+  </si>
+  <si>
+    <t>865351203</t>
+  </si>
+  <si>
+    <t>250001199</t>
+  </si>
+  <si>
+    <t>250346321</t>
+  </si>
+  <si>
+    <t>250686205</t>
+  </si>
+  <si>
+    <t>250422767</t>
+  </si>
+  <si>
+    <t>250274291</t>
+  </si>
+  <si>
+    <t>880963263</t>
+  </si>
+  <si>
+    <t>912603929</t>
+  </si>
+  <si>
+    <t>239132537</t>
+  </si>
+  <si>
+    <t>249716295</t>
+  </si>
+  <si>
+    <t>250366311</t>
+  </si>
+  <si>
+    <t>249758420</t>
+  </si>
+  <si>
+    <t>249749924</t>
+  </si>
+  <si>
+    <t>246584373</t>
+  </si>
+  <si>
+    <t>246807543</t>
+  </si>
+  <si>
+    <t>250728825</t>
+  </si>
+  <si>
+    <t>215917976</t>
+  </si>
+  <si>
+    <t>206787156</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>885910673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>746648074</t>
-  </si>
-  <si>
-    <t>746634520</t>
-  </si>
-  <si>
-    <t>249515325</t>
-  </si>
-  <si>
-    <t>248776209</t>
-  </si>
-  <si>
-    <t>881494219</t>
-  </si>
-  <si>
-    <t>244395343</t>
-  </si>
-  <si>
-    <t>235365990</t>
-  </si>
-  <si>
-    <t>234475907</t>
-  </si>
-  <si>
-    <t>233955040</t>
-  </si>
-  <si>
-    <t>232998462</t>
-  </si>
-  <si>
-    <t>224506109</t>
-  </si>
-  <si>
-    <t>975986435</t>
-  </si>
-  <si>
-    <t>970994764</t>
-  </si>
-  <si>
-    <t>949367332</t>
-  </si>
-  <si>
-    <t>949775351</t>
-  </si>
-  <si>
-    <t>912802794</t>
-  </si>
-  <si>
-    <t>199252382</t>
-  </si>
-  <si>
-    <t>875582326</t>
-  </si>
-  <si>
-    <t>854284324</t>
-  </si>
-  <si>
-    <t>857658193</t>
-  </si>
-  <si>
-    <t>855992834</t>
-  </si>
-  <si>
-    <t>751118369</t>
-  </si>
-  <si>
-    <t>831340728</t>
-  </si>
-  <si>
-    <t>834248118</t>
-  </si>
-  <si>
-    <t>795844681</t>
-  </si>
-  <si>
-    <t>256572284</t>
-  </si>
-  <si>
-    <t>256333356</t>
-  </si>
-  <si>
-    <t>883487559</t>
-  </si>
-  <si>
-    <t>240992200</t>
-  </si>
-  <si>
-    <t>252890623</t>
-  </si>
-  <si>
-    <t>255904462</t>
-  </si>
-  <si>
-    <t>255873337</t>
-  </si>
-  <si>
-    <t>255701306</t>
-  </si>
-  <si>
-    <t>255207601</t>
-  </si>
-  <si>
-    <t>255143012</t>
-  </si>
-  <si>
-    <t>255141016</t>
-  </si>
-  <si>
-    <t>254959533</t>
-  </si>
-  <si>
-    <t>250126517</t>
-  </si>
-  <si>
-    <t>249339080</t>
-  </si>
-  <si>
-    <t>249264593</t>
-  </si>
-  <si>
-    <t>248802690</t>
-  </si>
-  <si>
-    <t>234333643</t>
-  </si>
-  <si>
-    <t>210160234</t>
-  </si>
-  <si>
-    <t>952478422</t>
-  </si>
-  <si>
-    <t>195525039</t>
-  </si>
-  <si>
-    <t>192033813</t>
-  </si>
-  <si>
-    <t>185948548</t>
-  </si>
-  <si>
-    <t>185946492</t>
-  </si>
-  <si>
-    <t>972808251</t>
-  </si>
-  <si>
-    <t>963568153</t>
-  </si>
-  <si>
-    <t>952306078</t>
-  </si>
-  <si>
-    <t>941284535</t>
-  </si>
-  <si>
-    <t>941583332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>910859184</t>
-  </si>
-  <si>
-    <t>918868336</t>
-  </si>
-  <si>
-    <t>909244026</t>
-  </si>
-  <si>
-    <t>204354231</t>
-  </si>
-  <si>
-    <t>248825089</t>
-  </si>
-  <si>
-    <t>883929717</t>
-  </si>
-  <si>
-    <t>854644824</t>
-  </si>
-  <si>
-    <t>814259515</t>
-  </si>
-  <si>
-    <t>832458073</t>
-  </si>
-  <si>
-    <t>835199625</t>
-  </si>
-  <si>
-    <t>818089207</t>
-  </si>
-  <si>
-    <t>808928612</t>
-  </si>
-  <si>
-    <t>805856501</t>
-  </si>
-  <si>
-    <t>877135255</t>
-  </si>
-  <si>
-    <t>233897861</t>
-  </si>
-  <si>
-    <t>228764316</t>
-  </si>
-  <si>
-    <t>955004308</t>
-  </si>
-  <si>
-    <t>191838501</t>
-  </si>
-  <si>
-    <t>970171520</t>
-  </si>
-  <si>
-    <t>253809861</t>
-  </si>
-  <si>
-    <t>967168141</t>
-  </si>
-  <si>
-    <t>886315732</t>
-  </si>
-  <si>
-    <t>247755774</t>
-  </si>
-  <si>
-    <t>217098833</t>
-  </si>
-  <si>
-    <t>197234234</t>
-  </si>
-  <si>
-    <t>956247435</t>
-  </si>
-  <si>
-    <t>249541198</t>
-  </si>
-  <si>
-    <t>888411141</t>
-  </si>
-  <si>
-    <t>913874024</t>
-  </si>
-  <si>
-    <t>966206306</t>
-  </si>
-  <si>
-    <t>960374290</t>
-  </si>
-  <si>
-    <t>858938909</t>
-  </si>
-  <si>
-    <t>851353304</t>
-  </si>
-  <si>
-    <t>835723549</t>
-  </si>
-  <si>
-    <t>257570378</t>
-  </si>
-  <si>
-    <t>257268395</t>
-  </si>
-  <si>
-    <t>252786532</t>
-  </si>
-  <si>
-    <t>249615521</t>
+    <t>258328388</t>
+  </si>
+  <si>
+    <t>250377268</t>
   </si>
 </sst>
 </file>
@@ -799,7 +745,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -840,7 +786,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -849,10 +795,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -861,10 +807,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -873,10 +819,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -885,10 +831,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -897,10 +843,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -909,10 +855,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -921,10 +867,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -933,10 +879,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -945,10 +891,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -957,10 +903,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -969,10 +915,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -981,10 +927,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -993,10 +939,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1005,10 +951,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1017,10 +963,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1029,10 +975,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1041,10 +987,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1053,10 +999,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1065,7 +1011,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>6</v>
@@ -1077,7 +1023,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>6</v>
@@ -1089,7 +1035,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>6</v>
@@ -1101,7 +1047,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
@@ -1113,7 +1059,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1125,7 +1071,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>6</v>
@@ -1137,7 +1083,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1149,7 +1095,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
@@ -1161,7 +1107,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
@@ -1173,7 +1119,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1185,7 +1131,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1197,7 +1143,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
@@ -1209,7 +1155,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
@@ -1221,7 +1167,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
@@ -1233,7 +1179,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
@@ -1245,7 +1191,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
@@ -1257,7 +1203,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
@@ -1269,7 +1215,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
@@ -1281,7 +1227,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
@@ -1293,7 +1239,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
@@ -1305,7 +1251,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
@@ -1317,7 +1263,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
@@ -1329,7 +1275,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
@@ -1341,7 +1287,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
@@ -1353,7 +1299,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -1365,7 +1311,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
@@ -1377,7 +1323,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
@@ -1389,7 +1335,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
@@ -1401,7 +1347,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
@@ -1413,7 +1359,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
@@ -1425,7 +1371,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
@@ -1437,10 +1383,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B53" s="5" t="s">
         <v>59</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1452,7 +1398,7 @@
         <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1464,7 +1410,7 @@
         <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1476,7 +1422,7 @@
         <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>59</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1488,7 +1434,7 @@
         <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1497,10 +1443,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1509,10 +1455,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1521,10 +1467,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1533,10 +1479,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1545,10 +1491,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1557,10 +1503,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1569,10 +1515,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1581,10 +1527,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1593,10 +1539,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1605,10 +1551,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1616,10 +1562,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1627,10 +1573,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1638,10 +1584,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1649,10 +1595,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1660,10 +1606,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1671,10 +1617,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1682,10 +1628,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1693,10 +1639,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B75" s="5" t="s">
         <v>82</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>64</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1707,7 +1653,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1718,207 +1664,9 @@
         <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96058F-172D-4185-A972-36B8C5466158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC3207A7-7C26-42EB-AF48-CAE9ACD96C0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1210" uniqueCount="410">
   <si>
     <t>Status</t>
   </si>
@@ -48,244 +48,1219 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>223709290</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>217252372</t>
-  </si>
-  <si>
-    <t>204365104</t>
-  </si>
-  <si>
-    <t>203121953</t>
-  </si>
-  <si>
-    <t>963418508</t>
-  </si>
-  <si>
-    <t>249660287</t>
-  </si>
-  <si>
-    <t>975805320</t>
-  </si>
-  <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>250348251</t>
-  </si>
-  <si>
-    <t>249937974</t>
-  </si>
-  <si>
-    <t>176041659</t>
-  </si>
-  <si>
-    <t>175115728</t>
-  </si>
-  <si>
-    <t>174675672</t>
-  </si>
-  <si>
-    <t>866055142</t>
-  </si>
-  <si>
-    <t>926646989</t>
-  </si>
-  <si>
-    <t>915617439</t>
-  </si>
-  <si>
-    <t>905756098</t>
-  </si>
-  <si>
-    <t>241827090</t>
-  </si>
-  <si>
-    <t>231288832</t>
-  </si>
-  <si>
-    <t>220545861</t>
-  </si>
-  <si>
-    <t>217504772</t>
-  </si>
-  <si>
-    <t>219613944</t>
-  </si>
-  <si>
-    <t>804653487</t>
-  </si>
-  <si>
-    <t>829076862</t>
-  </si>
-  <si>
-    <t>811179005</t>
-  </si>
-  <si>
-    <t>805386897</t>
-  </si>
-  <si>
-    <t>952544074</t>
-  </si>
-  <si>
-    <t>959767199</t>
-  </si>
-  <si>
-    <t>975195680</t>
-  </si>
-  <si>
-    <t>969723026</t>
-  </si>
-  <si>
-    <t>191299118</t>
-  </si>
-  <si>
-    <t>200439192</t>
-  </si>
-  <si>
-    <t>187297092</t>
-  </si>
-  <si>
-    <t>238388460</t>
-  </si>
-  <si>
-    <t>257019582</t>
-  </si>
-  <si>
-    <t>256928205</t>
-  </si>
-  <si>
-    <t>256156971</t>
-  </si>
-  <si>
-    <t>255824629</t>
-  </si>
-  <si>
-    <t>254566916</t>
-  </si>
-  <si>
-    <t>254541448</t>
-  </si>
-  <si>
-    <t>253356079</t>
-  </si>
-  <si>
-    <t>252835974</t>
-  </si>
-  <si>
-    <t>252707348</t>
-  </si>
-  <si>
-    <t>249753462</t>
-  </si>
-  <si>
-    <t>250612243</t>
-  </si>
-  <si>
-    <t>250444704</t>
-  </si>
-  <si>
-    <t>250313701</t>
-  </si>
-  <si>
-    <t>250057910</t>
-  </si>
-  <si>
-    <t>250049792</t>
-  </si>
-  <si>
-    <t>249650478</t>
-  </si>
-  <si>
-    <t>245793678</t>
-  </si>
-  <si>
-    <t>240314728</t>
-  </si>
-  <si>
-    <t>205894516</t>
-  </si>
-  <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>814665331</t>
-  </si>
-  <si>
-    <t>833312618</t>
-  </si>
-  <si>
-    <t>931989937</t>
-  </si>
-  <si>
-    <t>941361986</t>
-  </si>
-  <si>
-    <t>865351203</t>
-  </si>
-  <si>
-    <t>250001199</t>
-  </si>
-  <si>
-    <t>250346321</t>
-  </si>
-  <si>
-    <t>250686205</t>
-  </si>
-  <si>
-    <t>250422767</t>
-  </si>
-  <si>
-    <t>250274291</t>
-  </si>
-  <si>
-    <t>880963263</t>
-  </si>
-  <si>
-    <t>912603929</t>
-  </si>
-  <si>
-    <t>239132537</t>
-  </si>
-  <si>
-    <t>249716295</t>
-  </si>
-  <si>
-    <t>250366311</t>
-  </si>
-  <si>
-    <t>249758420</t>
-  </si>
-  <si>
-    <t>249749924</t>
-  </si>
-  <si>
-    <t>246584373</t>
-  </si>
-  <si>
-    <t>246807543</t>
-  </si>
-  <si>
-    <t>250728825</t>
-  </si>
-  <si>
-    <t>215917976</t>
-  </si>
-  <si>
-    <t>206787156</t>
-  </si>
-  <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>258328388</t>
-  </si>
-  <si>
-    <t>250377268</t>
+    <t>960258683</t>
+  </si>
+  <si>
+    <t>194563650</t>
+  </si>
+  <si>
+    <t>919770200</t>
+  </si>
+  <si>
+    <t>911324758</t>
+  </si>
+  <si>
+    <t>900900766</t>
+  </si>
+  <si>
+    <t>958398053</t>
+  </si>
+  <si>
+    <t>251155440</t>
+  </si>
+  <si>
+    <t>224412365</t>
+  </si>
+  <si>
+    <t>905170373</t>
+  </si>
+  <si>
+    <t>217982879</t>
+  </si>
+  <si>
+    <t>211737253</t>
+  </si>
+  <si>
+    <t>946780180</t>
+  </si>
+  <si>
+    <t>943841738</t>
+  </si>
+  <si>
+    <t>223892989</t>
+  </si>
+  <si>
+    <t>217314966</t>
+  </si>
+  <si>
+    <t>218689432</t>
+  </si>
+  <si>
+    <t>209894454</t>
+  </si>
+  <si>
+    <t>213674348</t>
+  </si>
+  <si>
+    <t>946727199</t>
+  </si>
+  <si>
+    <t>191106875</t>
+  </si>
+  <si>
+    <t>188919504</t>
+  </si>
+  <si>
+    <t>975324488</t>
+  </si>
+  <si>
+    <t>182877393</t>
+  </si>
+  <si>
+    <t>181991526</t>
+  </si>
+  <si>
+    <t>181763107</t>
+  </si>
+  <si>
+    <t>178820563</t>
+  </si>
+  <si>
+    <t>175195928</t>
+  </si>
+  <si>
+    <t>175186299</t>
+  </si>
+  <si>
+    <t>175130594</t>
+  </si>
+  <si>
+    <t>967823323</t>
+  </si>
+  <si>
+    <t>958083655</t>
+  </si>
+  <si>
+    <t>963948942</t>
+  </si>
+  <si>
+    <t>963894781</t>
+  </si>
+  <si>
+    <t>963841808</t>
+  </si>
+  <si>
+    <t>957476959</t>
+  </si>
+  <si>
+    <t>957474590</t>
+  </si>
+  <si>
+    <t>950322085</t>
+  </si>
+  <si>
+    <t>944266802</t>
+  </si>
+  <si>
+    <t>941361598</t>
+  </si>
+  <si>
+    <t>887398000</t>
+  </si>
+  <si>
+    <t>884699194</t>
+  </si>
+  <si>
+    <t>882340551</t>
+  </si>
+  <si>
+    <t>869877898</t>
+  </si>
+  <si>
+    <t>863474999</t>
+  </si>
+  <si>
+    <t>858888567</t>
+  </si>
+  <si>
+    <t>917994927</t>
+  </si>
+  <si>
+    <t>923230423</t>
+  </si>
+  <si>
+    <t>914670470</t>
+  </si>
+  <si>
+    <t>905797472</t>
+  </si>
+  <si>
+    <t>904251158</t>
+  </si>
+  <si>
+    <t>893194294</t>
+  </si>
+  <si>
+    <t>906160928</t>
+  </si>
+  <si>
+    <t>905967562</t>
+  </si>
+  <si>
+    <t>934889068</t>
+  </si>
+  <si>
+    <t>932996857</t>
+  </si>
+  <si>
+    <t>252531706</t>
+  </si>
+  <si>
+    <t>245065002</t>
+  </si>
+  <si>
+    <t>240005672</t>
+  </si>
+  <si>
+    <t>238215911</t>
+  </si>
+  <si>
+    <t>237039064</t>
+  </si>
+  <si>
+    <t>236961235</t>
+  </si>
+  <si>
+    <t>236549774</t>
+  </si>
+  <si>
+    <t>825779329</t>
+  </si>
+  <si>
+    <t>809001013</t>
+  </si>
+  <si>
+    <t>766190833</t>
+  </si>
+  <si>
+    <t>258632383</t>
+  </si>
+  <si>
+    <t>258658099</t>
+  </si>
+  <si>
+    <t>212860773</t>
+  </si>
+  <si>
+    <t>220882298</t>
+  </si>
+  <si>
+    <t>209670433</t>
+  </si>
+  <si>
+    <t>211463843</t>
+  </si>
+  <si>
+    <t>211463645</t>
+  </si>
+  <si>
+    <t>209121213</t>
+  </si>
+  <si>
+    <t>205983996</t>
+  </si>
+  <si>
+    <t>205765039</t>
+  </si>
+  <si>
+    <t>944250780</t>
+  </si>
+  <si>
+    <t>194787812</t>
+  </si>
+  <si>
+    <t>195826437</t>
+  </si>
+  <si>
+    <t>194445031</t>
+  </si>
+  <si>
+    <t>193596644</t>
+  </si>
+  <si>
+    <t>205654985</t>
+  </si>
+  <si>
+    <t>201402454</t>
+  </si>
+  <si>
+    <t>200411522</t>
+  </si>
+  <si>
+    <t>199747738</t>
+  </si>
+  <si>
+    <t>966025409</t>
+  </si>
+  <si>
+    <t>176804742</t>
+  </si>
+  <si>
+    <t>973053261</t>
+  </si>
+  <si>
+    <t>971581362</t>
+  </si>
+  <si>
+    <t>970558288</t>
+  </si>
+  <si>
+    <t>959270954</t>
+  </si>
+  <si>
+    <t>962778944</t>
+  </si>
+  <si>
+    <t>959315858</t>
+  </si>
+  <si>
+    <t>234644924</t>
+  </si>
+  <si>
+    <t>244050211</t>
+  </si>
+  <si>
+    <t>250381054</t>
+  </si>
+  <si>
+    <t>250190224</t>
+  </si>
+  <si>
+    <t>249911599</t>
+  </si>
+  <si>
+    <t>249752050</t>
+  </si>
+  <si>
+    <t>248722922</t>
+  </si>
+  <si>
+    <t>247623907</t>
+  </si>
+  <si>
+    <t>240452205</t>
+  </si>
+  <si>
+    <t>234232662</t>
+  </si>
+  <si>
+    <t>234026635</t>
+  </si>
+  <si>
+    <t>233795289</t>
+  </si>
+  <si>
+    <t>231880935</t>
+  </si>
+  <si>
+    <t>230752721</t>
+  </si>
+  <si>
+    <t>230445029</t>
+  </si>
+  <si>
+    <t>229071901</t>
+  </si>
+  <si>
+    <t>228640615</t>
+  </si>
+  <si>
+    <t>805206541</t>
+  </si>
+  <si>
+    <t>858533338</t>
+  </si>
+  <si>
+    <t>876230024</t>
+  </si>
+  <si>
+    <t>884398748</t>
+  </si>
+  <si>
+    <t>887269870</t>
+  </si>
+  <si>
+    <t>886725435</t>
+  </si>
+  <si>
+    <t>886693443</t>
+  </si>
+  <si>
+    <t>885641740</t>
+  </si>
+  <si>
+    <t>880205582</t>
+  </si>
+  <si>
+    <t>874152394</t>
+  </si>
+  <si>
+    <t>861573115</t>
+  </si>
+  <si>
+    <t>861514002</t>
+  </si>
+  <si>
+    <t>861032591</t>
+  </si>
+  <si>
+    <t>860799505</t>
+  </si>
+  <si>
+    <t>860401524</t>
+  </si>
+  <si>
+    <t>851963375</t>
+  </si>
+  <si>
+    <t>851851224</t>
+  </si>
+  <si>
+    <t>845126253</t>
+  </si>
+  <si>
+    <t>938118928</t>
+  </si>
+  <si>
+    <t>905548115</t>
+  </si>
+  <si>
+    <t>897673814</t>
+  </si>
+  <si>
+    <t>901476147</t>
+  </si>
+  <si>
+    <t>902105901</t>
+  </si>
+  <si>
+    <t>899424828</t>
+  </si>
+  <si>
+    <t>899046183</t>
+  </si>
+  <si>
+    <t>898942291</t>
+  </si>
+  <si>
+    <t>892372206</t>
+  </si>
+  <si>
+    <t>914461979</t>
+  </si>
+  <si>
+    <t>924602513</t>
+  </si>
+  <si>
+    <t>931227817</t>
+  </si>
+  <si>
+    <t>930850163</t>
+  </si>
+  <si>
+    <t>925083861</t>
+  </si>
+  <si>
+    <t>912634809</t>
+  </si>
+  <si>
+    <t>911145971</t>
+  </si>
+  <si>
+    <t>908839305</t>
+  </si>
+  <si>
+    <t>940353208</t>
+  </si>
+  <si>
+    <t>943561310</t>
+  </si>
+  <si>
+    <t>815296060</t>
+  </si>
+  <si>
+    <t>815230853</t>
+  </si>
+  <si>
+    <t>814563437</t>
+  </si>
+  <si>
+    <t>259149098</t>
+  </si>
+  <si>
+    <t>259118929</t>
+  </si>
+  <si>
+    <t>259113656</t>
+  </si>
+  <si>
+    <t>258868284</t>
+  </si>
+  <si>
+    <t>258863889</t>
+  </si>
+  <si>
+    <t>258801236</t>
+  </si>
+  <si>
+    <t>258603640</t>
+  </si>
+  <si>
+    <t>258564032</t>
+  </si>
+  <si>
+    <t>254622701</t>
+  </si>
+  <si>
+    <t>251256016</t>
+  </si>
+  <si>
+    <t>251733816</t>
+  </si>
+  <si>
+    <t>251143701</t>
+  </si>
+  <si>
+    <t>250941493</t>
+  </si>
+  <si>
+    <t>257053433</t>
+  </si>
+  <si>
+    <t>254944717</t>
+  </si>
+  <si>
+    <t>254668498</t>
+  </si>
+  <si>
+    <t>252985829</t>
+  </si>
+  <si>
+    <t>250953126</t>
+  </si>
+  <si>
+    <t>960361644</t>
+  </si>
+  <si>
+    <t>199386545</t>
+  </si>
+  <si>
+    <t>201020116</t>
+  </si>
+  <si>
+    <t>200479321</t>
+  </si>
+  <si>
+    <t>192863904</t>
+  </si>
+  <si>
+    <t>198497376</t>
+  </si>
+  <si>
+    <t>197707379</t>
+  </si>
+  <si>
+    <t>197067592</t>
+  </si>
+  <si>
+    <t>186426726</t>
+  </si>
+  <si>
+    <t>186123703</t>
+  </si>
+  <si>
+    <t>185275900</t>
+  </si>
+  <si>
+    <t>205107232</t>
+  </si>
+  <si>
+    <t>204945301</t>
+  </si>
+  <si>
+    <t>204923399</t>
+  </si>
+  <si>
+    <t>204635910</t>
+  </si>
+  <si>
+    <t>204625705</t>
+  </si>
+  <si>
+    <t>204546356</t>
+  </si>
+  <si>
+    <t>204310134</t>
+  </si>
+  <si>
+    <t>204142263</t>
+  </si>
+  <si>
+    <t>202984062</t>
+  </si>
+  <si>
+    <t>201651746</t>
+  </si>
+  <si>
+    <t>970922633</t>
+  </si>
+  <si>
+    <t>973311479</t>
+  </si>
+  <si>
+    <t>970765503</t>
+  </si>
+  <si>
+    <t>968209563</t>
+  </si>
+  <si>
+    <t>969489172</t>
+  </si>
+  <si>
+    <t>968811178</t>
+  </si>
+  <si>
+    <t>968273379</t>
+  </si>
+  <si>
+    <t>962815308</t>
+  </si>
+  <si>
+    <t>963266360</t>
+  </si>
+  <si>
+    <t>955172618</t>
+  </si>
+  <si>
+    <t>944299738</t>
+  </si>
+  <si>
+    <t>954327403</t>
+  </si>
+  <si>
+    <t>948513084</t>
+  </si>
+  <si>
+    <t>233270937</t>
+  </si>
+  <si>
+    <t>243343856</t>
+  </si>
+  <si>
+    <t>250416207</t>
+  </si>
+  <si>
+    <t>233152424</t>
+  </si>
+  <si>
+    <t>229243872</t>
+  </si>
+  <si>
+    <t>206687729</t>
+  </si>
+  <si>
+    <t>211227651</t>
+  </si>
+  <si>
+    <t>213208774</t>
+  </si>
+  <si>
+    <t>208093165</t>
+  </si>
+  <si>
+    <t>207713987</t>
+  </si>
+  <si>
+    <t>207519269</t>
+  </si>
+  <si>
+    <t>207276399</t>
+  </si>
+  <si>
+    <t>230483608</t>
+  </si>
+  <si>
+    <t>231471750</t>
+  </si>
+  <si>
+    <t>232629828</t>
+  </si>
+  <si>
+    <t>232241053</t>
+  </si>
+  <si>
+    <t>231043740</t>
+  </si>
+  <si>
+    <t>224592760</t>
+  </si>
+  <si>
+    <t>216699524</t>
+  </si>
+  <si>
+    <t>814074807</t>
+  </si>
+  <si>
+    <t>860631245</t>
+  </si>
+  <si>
+    <t>878442411</t>
+  </si>
+  <si>
+    <t>886457666</t>
+  </si>
+  <si>
+    <t>883088860</t>
+  </si>
+  <si>
+    <t>878332711</t>
+  </si>
+  <si>
+    <t>863786590</t>
+  </si>
+  <si>
+    <t>862295262</t>
+  </si>
+  <si>
+    <t>861166878</t>
+  </si>
+  <si>
+    <t>854518663</t>
+  </si>
+  <si>
+    <t>853473837</t>
+  </si>
+  <si>
+    <t>836923551</t>
+  </si>
+  <si>
+    <t>836676092</t>
+  </si>
+  <si>
+    <t>836672257</t>
+  </si>
+  <si>
+    <t>836629364</t>
+  </si>
+  <si>
+    <t>943783286</t>
+  </si>
+  <si>
+    <t>912691544</t>
+  </si>
+  <si>
+    <t>924704822</t>
+  </si>
+  <si>
+    <t>923645497</t>
+  </si>
+  <si>
+    <t>922617315</t>
+  </si>
+  <si>
+    <t>920408899</t>
+  </si>
+  <si>
+    <t>909090015</t>
+  </si>
+  <si>
+    <t>904996158</t>
+  </si>
+  <si>
+    <t>903922437</t>
+  </si>
+  <si>
+    <t>901962286</t>
+  </si>
+  <si>
+    <t>911960577</t>
+  </si>
+  <si>
+    <t>910487192</t>
+  </si>
+  <si>
+    <t>906764018</t>
+  </si>
+  <si>
+    <t>942525365</t>
+  </si>
+  <si>
+    <t>938918103</t>
+  </si>
+  <si>
+    <t>941668596</t>
+  </si>
+  <si>
+    <t>936941131</t>
+  </si>
+  <si>
+    <t>938555616</t>
+  </si>
+  <si>
+    <t>836600316</t>
+  </si>
+  <si>
+    <t>836530042</t>
+  </si>
+  <si>
+    <t>834860987</t>
+  </si>
+  <si>
+    <t>833322765</t>
+  </si>
+  <si>
+    <t>832747715</t>
+  </si>
+  <si>
+    <t>832720175</t>
+  </si>
+  <si>
+    <t>831561778</t>
+  </si>
+  <si>
+    <t>830198465</t>
+  </si>
+  <si>
+    <t>829937485</t>
+  </si>
+  <si>
+    <t>813422429</t>
+  </si>
+  <si>
+    <t>810539472</t>
+  </si>
+  <si>
+    <t>810812101</t>
+  </si>
+  <si>
+    <t>803393432</t>
+  </si>
+  <si>
+    <t>799321983</t>
+  </si>
+  <si>
+    <t>237654276</t>
+  </si>
+  <si>
+    <t>869369284</t>
+  </si>
+  <si>
+    <t>213615697</t>
+  </si>
+  <si>
+    <t>953528092</t>
+  </si>
+  <si>
+    <t>812374159</t>
+  </si>
+  <si>
+    <t>796273336</t>
+  </si>
+  <si>
+    <t>249605118</t>
+  </si>
+  <si>
+    <t>246125730</t>
+  </si>
+  <si>
+    <t>251821306</t>
+  </si>
+  <si>
+    <t>217473713</t>
+  </si>
+  <si>
+    <t>938967191</t>
+  </si>
+  <si>
+    <t>890446671</t>
+  </si>
+  <si>
+    <t>893043921</t>
+  </si>
+  <si>
+    <t>904057415</t>
+  </si>
+  <si>
+    <t>900689351</t>
+  </si>
+  <si>
+    <t>942066493</t>
+  </si>
+  <si>
+    <t>915944999</t>
+  </si>
+  <si>
+    <t>938141375</t>
+  </si>
+  <si>
+    <t>229672013</t>
+  </si>
+  <si>
+    <t>199279773</t>
+  </si>
+  <si>
+    <t>196539435</t>
+  </si>
+  <si>
+    <t>934067483</t>
+  </si>
+  <si>
+    <t>890718061</t>
+  </si>
+  <si>
+    <t>891885786</t>
+  </si>
+  <si>
+    <t>954326066</t>
+  </si>
+  <si>
+    <t>957503729</t>
+  </si>
+  <si>
+    <t>959786025</t>
+  </si>
+  <si>
+    <t>949173029</t>
+  </si>
+  <si>
+    <t>225378193</t>
+  </si>
+  <si>
+    <t>248160529</t>
+  </si>
+  <si>
+    <t>810315790</t>
+  </si>
+  <si>
+    <t>821892688</t>
+  </si>
+  <si>
+    <t>208904999</t>
+  </si>
+  <si>
+    <t>952757874</t>
+  </si>
+  <si>
+    <t>177842360</t>
+  </si>
+  <si>
+    <t>952025520</t>
+  </si>
+  <si>
+    <t>971136530</t>
+  </si>
+  <si>
+    <t>184937591</t>
+  </si>
+  <si>
+    <t>205774957</t>
+  </si>
+  <si>
+    <t>225765324</t>
+  </si>
+  <si>
+    <t>218301343</t>
+  </si>
+  <si>
+    <t>814730952</t>
+  </si>
+  <si>
+    <t>899461440</t>
+  </si>
+  <si>
+    <t>861367443</t>
+  </si>
+  <si>
+    <t>931367779</t>
+  </si>
+  <si>
+    <t>908561081</t>
+  </si>
+  <si>
+    <t>786164834</t>
+  </si>
+  <si>
+    <t>792669750</t>
+  </si>
+  <si>
+    <t>814188771</t>
+  </si>
+  <si>
+    <t>902002512</t>
+  </si>
+  <si>
+    <t>943335632</t>
+  </si>
+  <si>
+    <t>938645110</t>
+  </si>
+  <si>
+    <t>892047956</t>
+  </si>
+  <si>
+    <t>188140143</t>
+  </si>
+  <si>
+    <t>201376237</t>
+  </si>
+  <si>
+    <t>201511569</t>
+  </si>
+  <si>
+    <t>929068173</t>
+  </si>
+  <si>
+    <t>924943636</t>
+  </si>
+  <si>
+    <t>914097757</t>
+  </si>
+  <si>
+    <t>910813603</t>
+  </si>
+  <si>
+    <t>964117349</t>
+  </si>
+  <si>
+    <t>955866037</t>
+  </si>
+  <si>
+    <t>938611179</t>
+  </si>
+  <si>
+    <t>823998970</t>
+  </si>
+  <si>
+    <t>861752321</t>
+  </si>
+  <si>
+    <t>867627030</t>
+  </si>
+  <si>
+    <t>833110749</t>
+  </si>
+  <si>
+    <t>843167986</t>
+  </si>
+  <si>
+    <t>856512367</t>
+  </si>
+  <si>
+    <t>874792140</t>
+  </si>
+  <si>
+    <t>884639117</t>
+  </si>
+  <si>
+    <t>872425768</t>
+  </si>
+  <si>
+    <t>852273527</t>
+  </si>
+  <si>
+    <t>855077560</t>
+  </si>
+  <si>
+    <t>932553179</t>
+  </si>
+  <si>
+    <t>933287934</t>
+  </si>
+  <si>
+    <t>912362575</t>
+  </si>
+  <si>
+    <t>891401295</t>
+  </si>
+  <si>
+    <t>888248964</t>
+  </si>
+  <si>
+    <t>906105113</t>
+  </si>
+  <si>
+    <t>960951964</t>
+  </si>
+  <si>
+    <t>207225677</t>
+  </si>
+  <si>
+    <t>212513539</t>
+  </si>
+  <si>
+    <t>212211134</t>
+  </si>
+  <si>
+    <t>202581660</t>
+  </si>
+  <si>
+    <t>194558940</t>
+  </si>
+  <si>
+    <t>968817779</t>
+  </si>
+  <si>
+    <t>183933039</t>
+  </si>
+  <si>
+    <t>976076863</t>
+  </si>
+  <si>
+    <t>947406850</t>
+  </si>
+  <si>
+    <t>250599663</t>
+  </si>
+  <si>
+    <t>212714814</t>
+  </si>
+  <si>
+    <t>887133613</t>
+  </si>
+  <si>
+    <t>191345259</t>
+  </si>
+  <si>
+    <t>187797216</t>
+  </si>
+  <si>
+    <t>885026710</t>
+  </si>
+  <si>
+    <t>877435069</t>
+  </si>
+  <si>
+    <t>199830435</t>
+  </si>
+  <si>
+    <t>863045062</t>
+  </si>
+  <si>
+    <t>907367985</t>
+  </si>
+  <si>
+    <t>904846627</t>
+  </si>
+  <si>
+    <t>901960843</t>
+  </si>
+  <si>
+    <t>933745675</t>
+  </si>
+  <si>
+    <t>912132754</t>
+  </si>
+  <si>
+    <t>910854821</t>
+  </si>
+  <si>
+    <t>212002566</t>
+  </si>
+  <si>
+    <t>221887692</t>
+  </si>
+  <si>
+    <t>207425780</t>
+  </si>
+  <si>
+    <t>205708203</t>
+  </si>
+  <si>
+    <t>950415889</t>
+  </si>
+  <si>
+    <t>184763666</t>
+  </si>
+  <si>
+    <t>961564014</t>
+  </si>
+  <si>
+    <t>961331083</t>
+  </si>
+  <si>
+    <t>956226462</t>
+  </si>
+  <si>
+    <t>956955433</t>
+  </si>
+  <si>
+    <t>953640236</t>
+  </si>
+  <si>
+    <t>940437043</t>
+  </si>
+  <si>
+    <t>938206160</t>
+  </si>
+  <si>
+    <t>230124228</t>
+  </si>
+  <si>
+    <t>228140285</t>
+  </si>
+  <si>
+    <t>822521096</t>
+  </si>
+  <si>
+    <t>909440665</t>
+  </si>
+  <si>
+    <t>208480677</t>
+  </si>
+  <si>
+    <t>972504892</t>
+  </si>
+  <si>
+    <t>971149814</t>
+  </si>
+  <si>
+    <t>251867770</t>
+  </si>
+  <si>
+    <t>947568824</t>
+  </si>
+  <si>
+    <t>837254295</t>
+  </si>
+  <si>
+    <t>958851499</t>
+  </si>
+  <si>
+    <t>233465883</t>
+  </si>
+  <si>
+    <t>259383309</t>
+  </si>
+  <si>
+    <t>259043903</t>
+  </si>
+  <si>
+    <t>258906423</t>
+  </si>
+  <si>
+    <t>255734299</t>
   </si>
 </sst>
 </file>
@@ -745,7 +1720,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D77"/>
+  <dimension ref="A1:D403"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -771,7 +1746,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>6</v>
@@ -783,7 +1758,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>6</v>
@@ -795,7 +1770,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>6</v>
@@ -807,7 +1782,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>6</v>
@@ -819,7 +1794,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>6</v>
@@ -831,7 +1806,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>6</v>
@@ -843,10 +1818,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -855,10 +1830,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -867,10 +1842,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -879,10 +1854,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -891,10 +1866,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -903,10 +1878,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -915,10 +1890,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -927,10 +1902,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -939,10 +1914,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -951,10 +1926,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -963,10 +1938,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -975,10 +1950,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -987,10 +1962,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -999,10 +1974,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1011,7 +1986,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>6</v>
@@ -1023,7 +1998,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>6</v>
@@ -1035,7 +2010,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>6</v>
@@ -1047,7 +2022,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
@@ -1059,7 +2034,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1071,7 +2046,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>6</v>
@@ -1083,7 +2058,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1095,7 +2070,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
@@ -1107,7 +2082,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
@@ -1119,7 +2094,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1131,7 +2106,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1143,7 +2118,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
@@ -1155,7 +2130,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
@@ -1167,7 +2142,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
@@ -1179,7 +2154,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
@@ -1191,7 +2166,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
@@ -1203,7 +2178,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
@@ -1215,7 +2190,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
@@ -1227,7 +2202,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
@@ -1239,7 +2214,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
@@ -1251,7 +2226,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
@@ -1263,7 +2238,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
@@ -1275,7 +2250,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
@@ -1287,7 +2262,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
@@ -1299,7 +2274,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -1311,7 +2286,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
@@ -1323,7 +2298,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
@@ -1335,7 +2310,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
@@ -1347,7 +2322,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
@@ -1359,7 +2334,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
@@ -1371,7 +2346,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
@@ -1383,10 +2358,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1395,10 +2370,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1407,10 +2382,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1419,10 +2394,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1431,7 +2406,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>6</v>
@@ -1443,10 +2418,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1455,7 +2430,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>6</v>
@@ -1467,7 +2442,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>6</v>
@@ -1479,10 +2454,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1491,7 +2466,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>6</v>
@@ -1503,7 +2478,7 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>6</v>
@@ -1515,7 +2490,7 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>6</v>
@@ -1527,7 +2502,7 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>6</v>
@@ -1539,7 +2514,7 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>6</v>
@@ -1551,10 +2526,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1562,10 +2537,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1573,10 +2548,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1584,10 +2559,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1595,10 +2570,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1606,10 +2581,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1617,10 +2592,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1628,10 +2603,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1639,10 +2614,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1653,7 +2628,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1664,9 +2639,3595 @@
         <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A323" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C323" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A324" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C324" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A325" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C325" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A326" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C326" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A327" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C327" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A328" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C328" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A329" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C329" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A330" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C330" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A331" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C331" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A332" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C332" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A333" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C333" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A334" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C334" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A335" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C335" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A336" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C336" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A337" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C337" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A338" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C338" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A339" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C339" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A340" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C340" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A341" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C341" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A342" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C342" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A343" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C343" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A344" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C344" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A345" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A346" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C346" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A347" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C347" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A348" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C348" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A349" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C349" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A350" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C350" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A351" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C351" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A352" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C352" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A353" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C353" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A354" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C354" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A355" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C355" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A356" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C356" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A357" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C357" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A358" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C358" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A359" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C359" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A360" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C360" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A361" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C361" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A362" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C362" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A363" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C363" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A364" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C364" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A365" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C365" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A366" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C366" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A367" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C367" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A368" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C368" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A369" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C369" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A370" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C370" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A371" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C371" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A372" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C372" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A373" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C373" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A374" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C374" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A375" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C375" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A376" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C376" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A377" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C377" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A378" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C378" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A379" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C379" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A380" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C380" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A381" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C381" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A382" s="4" t="s">
+        <v>388</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C382" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A383" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C383" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A384" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C384" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A385" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C385" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A386" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C386" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A387" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C387" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A388" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C388" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A389" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C389" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A390" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C390" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A391" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C391" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A392" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C392" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A393" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C393" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A394" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C394" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A395" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C395" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A396" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C396" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A397" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C397" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A398" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C398" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A399" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C399" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A400" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C400" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A401" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C401" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A402" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C402" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A403" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C403" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -1693,31 +6254,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B59A46C8-FEDC-4548-958E-10947FCCC6D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E2182E-AF06-49B4-8F3F-D8952F3D596F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="93">
   <si>
     <t>Status</t>
   </si>
@@ -48,346 +48,268 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>871729772</t>
+    <t>825900826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>884205661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>243802232</t>
+  </si>
+  <si>
+    <t>243750043</t>
+  </si>
+  <si>
+    <t>243442575</t>
+  </si>
+  <si>
+    <t>239988524</t>
+  </si>
+  <si>
+    <t>233846603</t>
+  </si>
+  <si>
+    <t>212111896</t>
+  </si>
+  <si>
+    <t>187222645</t>
+  </si>
+  <si>
+    <t>971348242</t>
+  </si>
+  <si>
+    <t>970496240</t>
+  </si>
+  <si>
+    <t>956541068</t>
+  </si>
+  <si>
+    <t>940836244</t>
+  </si>
+  <si>
+    <t>926539986</t>
+  </si>
+  <si>
+    <t>922362714</t>
+  </si>
+  <si>
+    <t>914015726</t>
+  </si>
+  <si>
+    <t>859685947</t>
+  </si>
+  <si>
+    <t>858965720</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>862981184</t>
-  </si>
-  <si>
-    <t>915971398</t>
-  </si>
-  <si>
-    <t>915793206</t>
-  </si>
-  <si>
-    <t>915681021</t>
-  </si>
-  <si>
-    <t>915088623</t>
-  </si>
-  <si>
-    <t>914456680</t>
-  </si>
-  <si>
-    <t>913939611</t>
-  </si>
-  <si>
-    <t>913770792</t>
-  </si>
-  <si>
-    <t>910302367</t>
-  </si>
-  <si>
-    <t>909937447</t>
-  </si>
-  <si>
-    <t>904953647</t>
-  </si>
-  <si>
-    <t>971107432</t>
-  </si>
-  <si>
-    <t>970793364</t>
-  </si>
-  <si>
-    <t>970032730</t>
-  </si>
-  <si>
-    <t>958996633</t>
-  </si>
-  <si>
-    <t>939646851</t>
-  </si>
-  <si>
-    <t>942982764</t>
-  </si>
-  <si>
-    <t>942099411</t>
-  </si>
-  <si>
-    <t>938092362</t>
-  </si>
-  <si>
-    <t>936835150</t>
-  </si>
-  <si>
-    <t>929761595</t>
-  </si>
-  <si>
-    <t>925990701</t>
-  </si>
-  <si>
-    <t>967850961</t>
-  </si>
-  <si>
-    <t>954846956</t>
-  </si>
-  <si>
-    <t>944667918</t>
-  </si>
-  <si>
-    <t>944564362</t>
-  </si>
-  <si>
-    <t>191947757</t>
-  </si>
-  <si>
-    <t>188257178</t>
-  </si>
-  <si>
-    <t>835954623</t>
-  </si>
-  <si>
-    <t>812496374</t>
-  </si>
-  <si>
-    <t>829595424</t>
-  </si>
-  <si>
-    <t>815686856</t>
-  </si>
-  <si>
-    <t>815600048</t>
-  </si>
-  <si>
-    <t>808564565</t>
-  </si>
-  <si>
-    <t>806797860</t>
-  </si>
-  <si>
-    <t>257561245</t>
-  </si>
-  <si>
-    <t>260384080</t>
-  </si>
-  <si>
-    <t>260139609</t>
-  </si>
-  <si>
-    <t>259651853</t>
-  </si>
-  <si>
-    <t>259600579</t>
-  </si>
-  <si>
-    <t>259569808</t>
-  </si>
-  <si>
-    <t>259383291</t>
-  </si>
-  <si>
-    <t>259218091</t>
-  </si>
-  <si>
-    <t>259068280</t>
-  </si>
-  <si>
-    <t>259049512</t>
-  </si>
-  <si>
-    <t>258896830</t>
-  </si>
-  <si>
-    <t>249466339</t>
-  </si>
-  <si>
-    <t>249627476</t>
-  </si>
-  <si>
-    <t>248712311</t>
-  </si>
-  <si>
-    <t>250216839</t>
+    <t>188476786</t>
+  </si>
+  <si>
+    <t>236652438</t>
+  </si>
+  <si>
+    <t>240878763</t>
+  </si>
+  <si>
+    <t>236074468</t>
+  </si>
+  <si>
+    <t>226023491</t>
+  </si>
+  <si>
+    <t>225527021</t>
+  </si>
+  <si>
+    <t>209753692</t>
+  </si>
+  <si>
+    <t>208450589</t>
+  </si>
+  <si>
+    <t>208218523</t>
+  </si>
+  <si>
+    <t>207017546</t>
+  </si>
+  <si>
+    <t>206675393</t>
+  </si>
+  <si>
+    <t>205126851</t>
+  </si>
+  <si>
+    <t>914706431</t>
+  </si>
+  <si>
+    <t>957611217</t>
+  </si>
+  <si>
+    <t>972644557</t>
+  </si>
+  <si>
+    <t>930154459</t>
+  </si>
+  <si>
+    <t>943207492</t>
+  </si>
+  <si>
+    <t>918319090</t>
+  </si>
+  <si>
+    <t>912866088</t>
+  </si>
+  <si>
+    <t>911292716</t>
+  </si>
+  <si>
+    <t>879177552</t>
+  </si>
+  <si>
+    <t>888012980</t>
+  </si>
+  <si>
+    <t>845551187</t>
+  </si>
+  <si>
+    <t>829007347</t>
+  </si>
+  <si>
+    <t>838881591</t>
+  </si>
+  <si>
+    <t>833525649</t>
+  </si>
+  <si>
+    <t>820665192</t>
+  </si>
+  <si>
+    <t>261287233</t>
+  </si>
+  <si>
+    <t>261267680</t>
+  </si>
+  <si>
+    <t>261164416</t>
+  </si>
+  <si>
+    <t>259957425</t>
+  </si>
+  <si>
+    <t>259861114</t>
+  </si>
+  <si>
+    <t>259853731</t>
+  </si>
+  <si>
+    <t>258633068</t>
+  </si>
+  <si>
+    <t>249035639</t>
+  </si>
+  <si>
+    <t>257490809</t>
+  </si>
+  <si>
+    <t>255211454</t>
+  </si>
+  <si>
+    <t>219164864</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>230948394</t>
-  </si>
-  <si>
-    <t>205363207</t>
-  </si>
-  <si>
-    <t>220948479</t>
-  </si>
-  <si>
-    <t>209965668</t>
-  </si>
-  <si>
-    <t>209911712</t>
-  </si>
-  <si>
-    <t>209861479</t>
-  </si>
-  <si>
-    <t>824516425</t>
-  </si>
-  <si>
-    <t>839498536</t>
-  </si>
-  <si>
-    <t>851800742</t>
-  </si>
-  <si>
-    <t>862401365</t>
-  </si>
-  <si>
-    <t>914074509</t>
-  </si>
-  <si>
-    <t>866638897</t>
-  </si>
-  <si>
-    <t>919254841</t>
-  </si>
-  <si>
-    <t>944978554</t>
-  </si>
-  <si>
-    <t>963524552</t>
-  </si>
-  <si>
-    <t>957100146</t>
-  </si>
-  <si>
-    <t>816469120</t>
-  </si>
-  <si>
-    <t>959189485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>947963645</t>
-  </si>
-  <si>
-    <t>190871032</t>
-  </si>
-  <si>
-    <t>190507404</t>
-  </si>
-  <si>
-    <t>177230384</t>
-  </si>
-  <si>
-    <t>179306935</t>
-  </si>
-  <si>
-    <t>180924783</t>
-  </si>
-  <si>
-    <t>790300085</t>
-  </si>
-  <si>
-    <t>828991806</t>
-  </si>
-  <si>
-    <t>251059576</t>
-  </si>
-  <si>
-    <t>231013958</t>
-  </si>
-  <si>
-    <t>232130470</t>
-  </si>
-  <si>
-    <t>231003090</t>
-  </si>
-  <si>
-    <t>230960969</t>
-  </si>
-  <si>
-    <t>229282052</t>
-  </si>
-  <si>
-    <t>227633660</t>
-  </si>
-  <si>
-    <t>224942049</t>
-  </si>
-  <si>
-    <t>227001256</t>
-  </si>
-  <si>
-    <t>213072675</t>
-  </si>
-  <si>
-    <t>251355776</t>
-  </si>
-  <si>
-    <t>251296582</t>
-  </si>
-  <si>
-    <t>206642864</t>
-  </si>
-  <si>
-    <t>220693588</t>
-  </si>
-  <si>
-    <t>213848967</t>
-  </si>
-  <si>
-    <t>218380206</t>
-  </si>
-  <si>
-    <t>199524368</t>
-  </si>
-  <si>
-    <t>199004288</t>
-  </si>
-  <si>
-    <t>194555532</t>
-  </si>
-  <si>
-    <t>196182418</t>
-  </si>
-  <si>
-    <t>198358503</t>
-  </si>
-  <si>
-    <t>197966702</t>
-  </si>
-  <si>
-    <t>793400312</t>
-  </si>
-  <si>
-    <t>894168529</t>
-  </si>
-  <si>
-    <t>869175004</t>
-  </si>
-  <si>
-    <t>848210633</t>
-  </si>
-  <si>
-    <t>856421791</t>
-  </si>
-  <si>
-    <t>860185325</t>
-  </si>
-  <si>
-    <t>902565484</t>
-  </si>
-  <si>
-    <t>916536430</t>
-  </si>
-  <si>
-    <t>189865938</t>
-  </si>
-  <si>
-    <t>962191692</t>
-  </si>
-  <si>
-    <t>924971546</t>
-  </si>
-  <si>
-    <t>969527732</t>
+    <t>236679761</t>
+  </si>
+  <si>
+    <t>195626704</t>
+  </si>
+  <si>
+    <t>205999521</t>
+  </si>
+  <si>
+    <t>817017498</t>
+  </si>
+  <si>
+    <t>910823628</t>
+  </si>
+  <si>
+    <t>966849428</t>
+  </si>
+  <si>
+    <t>946516956</t>
+  </si>
+  <si>
+    <t>918440052</t>
+  </si>
+  <si>
+    <t>930724574</t>
+  </si>
+  <si>
+    <t>231754742</t>
+  </si>
+  <si>
+    <t>252009042</t>
+  </si>
+  <si>
+    <t>252003961</t>
+  </si>
+  <si>
+    <t>196574119</t>
+  </si>
+  <si>
+    <t>861479875</t>
+  </si>
+  <si>
+    <t>962911057</t>
+  </si>
+  <si>
+    <t>259383317</t>
+  </si>
+  <si>
+    <t>261086171</t>
+  </si>
+  <si>
+    <t>963898014</t>
+  </si>
+  <si>
+    <t>948178029</t>
+  </si>
+  <si>
+    <t>961566761</t>
+  </si>
+  <si>
+    <t>971248848</t>
+  </si>
+  <si>
+    <t>911199507</t>
+  </si>
+  <si>
+    <t>187873157</t>
+  </si>
+  <si>
+    <t>968189690</t>
+  </si>
+  <si>
+    <t>233386337</t>
+  </si>
+  <si>
+    <t>210126532</t>
+  </si>
+  <si>
+    <t>202605857</t>
+  </si>
+  <si>
+    <t>201914342</t>
   </si>
 </sst>
 </file>
@@ -847,7 +769,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D112"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -888,7 +810,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -897,10 +819,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -909,10 +831,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -921,10 +843,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -933,10 +855,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -945,10 +867,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -957,10 +879,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -969,10 +891,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -981,10 +903,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -993,10 +915,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1005,10 +927,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1017,10 +939,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1029,10 +951,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1041,10 +963,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1053,10 +975,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1065,10 +987,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1077,10 +999,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1089,10 +1011,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1101,10 +1023,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1113,10 +1035,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1125,10 +1047,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1137,10 +1059,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1149,10 +1071,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1083,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1173,10 +1095,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1185,10 +1107,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1197,10 +1119,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1209,10 +1131,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1221,10 +1143,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1233,10 +1155,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1245,10 +1167,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1257,10 +1179,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1269,10 +1191,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1281,10 +1203,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1293,10 +1215,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1305,10 +1227,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1317,10 +1239,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1329,10 +1251,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1341,10 +1263,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1353,10 +1275,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1365,10 +1287,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1377,10 +1299,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1389,10 +1311,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1401,10 +1323,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1413,10 +1335,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1425,10 +1347,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1437,10 +1359,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1449,10 +1371,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1461,10 +1383,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1473,10 +1395,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1485,10 +1407,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1497,10 +1419,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1509,10 +1431,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1521,10 +1443,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1533,10 +1455,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1545,10 +1467,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1557,10 +1479,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>57</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1569,10 +1491,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1581,10 +1503,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1593,10 +1515,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1605,10 +1527,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1617,10 +1539,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1629,10 +1551,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1641,10 +1563,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1653,10 +1575,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1664,10 +1586,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1675,10 +1597,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1686,10 +1608,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1697,10 +1619,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1708,10 +1630,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1719,10 +1641,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>76</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1730,10 +1652,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1741,10 +1663,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1752,10 +1674,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1763,10 +1685,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>76</v>
+        <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1774,10 +1696,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1785,10 +1707,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1796,10 +1718,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1807,10 +1729,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1818,10 +1740,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1829,10 +1751,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1840,10 +1762,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1851,309 +1773,12 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>76</v>
+        <v>25</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C112" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E2182E-AF06-49B4-8F3F-D8952F3D596F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E68646-11F0-45D3-B772-B8435FEEDD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
   <si>
     <t>Status</t>
   </si>
@@ -48,268 +48,154 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>825900826</t>
+    <t>810974968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>809655867</t>
+  </si>
+  <si>
+    <t>230492526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>222454682</t>
+  </si>
+  <si>
+    <t>223167606</t>
+  </si>
+  <si>
+    <t>231597026</t>
+  </si>
+  <si>
+    <t>231222484</t>
+  </si>
+  <si>
+    <t>231048897</t>
+  </si>
+  <si>
+    <t>231003801</t>
+  </si>
+  <si>
+    <t>230870846</t>
+  </si>
+  <si>
+    <t>841324142</t>
+  </si>
+  <si>
+    <t>230817029</t>
+  </si>
+  <si>
+    <t>241111404</t>
+  </si>
+  <si>
+    <t>236896928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>961521519</t>
+  </si>
+  <si>
+    <t>944197148</t>
+  </si>
+  <si>
+    <t>965325719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>250636705</t>
+  </si>
+  <si>
+    <t>861209561</t>
+  </si>
+  <si>
+    <t>937797904</t>
+  </si>
+  <si>
+    <t>252003102</t>
+  </si>
+  <si>
+    <t>231170337</t>
+  </si>
+  <si>
+    <t>916623972</t>
+  </si>
+  <si>
+    <t>782123222</t>
+  </si>
+  <si>
+    <t>969922792</t>
+  </si>
+  <si>
+    <t>179869767</t>
+  </si>
+  <si>
+    <t>824773430</t>
+  </si>
+  <si>
+    <t>861408155</t>
+  </si>
+  <si>
+    <t>211022029</t>
+  </si>
+  <si>
+    <t>187639160</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>884205661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>243802232</t>
-  </si>
-  <si>
-    <t>243750043</t>
-  </si>
-  <si>
-    <t>243442575</t>
-  </si>
-  <si>
-    <t>239988524</t>
-  </si>
-  <si>
-    <t>233846603</t>
-  </si>
-  <si>
-    <t>212111896</t>
-  </si>
-  <si>
-    <t>187222645</t>
-  </si>
-  <si>
-    <t>971348242</t>
-  </si>
-  <si>
-    <t>970496240</t>
-  </si>
-  <si>
-    <t>956541068</t>
-  </si>
-  <si>
-    <t>940836244</t>
-  </si>
-  <si>
-    <t>926539986</t>
-  </si>
-  <si>
-    <t>922362714</t>
-  </si>
-  <si>
-    <t>914015726</t>
-  </si>
-  <si>
-    <t>859685947</t>
-  </si>
-  <si>
-    <t>858965720</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>188476786</t>
-  </si>
-  <si>
-    <t>236652438</t>
-  </si>
-  <si>
-    <t>240878763</t>
-  </si>
-  <si>
-    <t>236074468</t>
-  </si>
-  <si>
-    <t>226023491</t>
-  </si>
-  <si>
-    <t>225527021</t>
-  </si>
-  <si>
-    <t>209753692</t>
-  </si>
-  <si>
-    <t>208450589</t>
-  </si>
-  <si>
-    <t>208218523</t>
-  </si>
-  <si>
-    <t>207017546</t>
-  </si>
-  <si>
-    <t>206675393</t>
-  </si>
-  <si>
-    <t>205126851</t>
-  </si>
-  <si>
-    <t>914706431</t>
-  </si>
-  <si>
-    <t>957611217</t>
-  </si>
-  <si>
-    <t>972644557</t>
-  </si>
-  <si>
-    <t>930154459</t>
-  </si>
-  <si>
-    <t>943207492</t>
-  </si>
-  <si>
-    <t>918319090</t>
-  </si>
-  <si>
-    <t>912866088</t>
-  </si>
-  <si>
-    <t>911292716</t>
-  </si>
-  <si>
-    <t>879177552</t>
-  </si>
-  <si>
-    <t>888012980</t>
-  </si>
-  <si>
-    <t>845551187</t>
-  </si>
-  <si>
-    <t>829007347</t>
-  </si>
-  <si>
-    <t>838881591</t>
-  </si>
-  <si>
-    <t>833525649</t>
-  </si>
-  <si>
-    <t>820665192</t>
-  </si>
-  <si>
-    <t>261287233</t>
-  </si>
-  <si>
-    <t>261267680</t>
-  </si>
-  <si>
-    <t>261164416</t>
-  </si>
-  <si>
-    <t>259957425</t>
-  </si>
-  <si>
-    <t>259861114</t>
-  </si>
-  <si>
-    <t>259853731</t>
-  </si>
-  <si>
-    <t>258633068</t>
-  </si>
-  <si>
-    <t>249035639</t>
-  </si>
-  <si>
-    <t>257490809</t>
-  </si>
-  <si>
-    <t>255211454</t>
-  </si>
-  <si>
-    <t>219164864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>236679761</t>
-  </si>
-  <si>
-    <t>195626704</t>
-  </si>
-  <si>
-    <t>205999521</t>
-  </si>
-  <si>
-    <t>817017498</t>
-  </si>
-  <si>
-    <t>910823628</t>
-  </si>
-  <si>
-    <t>966849428</t>
-  </si>
-  <si>
-    <t>946516956</t>
-  </si>
-  <si>
-    <t>918440052</t>
-  </si>
-  <si>
-    <t>930724574</t>
-  </si>
-  <si>
-    <t>231754742</t>
-  </si>
-  <si>
-    <t>252009042</t>
-  </si>
-  <si>
-    <t>252003961</t>
-  </si>
-  <si>
-    <t>196574119</t>
-  </si>
-  <si>
-    <t>861479875</t>
-  </si>
-  <si>
-    <t>962911057</t>
-  </si>
-  <si>
-    <t>259383317</t>
-  </si>
-  <si>
-    <t>261086171</t>
-  </si>
-  <si>
-    <t>963898014</t>
-  </si>
-  <si>
-    <t>948178029</t>
-  </si>
-  <si>
-    <t>961566761</t>
-  </si>
-  <si>
-    <t>971248848</t>
-  </si>
-  <si>
-    <t>911199507</t>
-  </si>
-  <si>
-    <t>187873157</t>
-  </si>
-  <si>
-    <t>968189690</t>
-  </si>
-  <si>
-    <t>233386337</t>
-  </si>
-  <si>
-    <t>210126532</t>
-  </si>
-  <si>
-    <t>202605857</t>
-  </si>
-  <si>
-    <t>201914342</t>
+    <t>924549623</t>
+  </si>
+  <si>
+    <t>956615219</t>
+  </si>
+  <si>
+    <t>954861302</t>
+  </si>
+  <si>
+    <t>946313438</t>
+  </si>
+  <si>
+    <t>946313420</t>
+  </si>
+  <si>
+    <t>941150595</t>
+  </si>
+  <si>
+    <t>207515333</t>
+  </si>
+  <si>
+    <t>189183670</t>
+  </si>
+  <si>
+    <t>971152032</t>
+  </si>
+  <si>
+    <t>182391262</t>
+  </si>
+  <si>
+    <t>181301197</t>
+  </si>
+  <si>
+    <t>966509030</t>
+  </si>
+  <si>
+    <t>746780828</t>
+  </si>
+  <si>
+    <t>262555851</t>
+  </si>
+  <si>
+    <t>903558603</t>
   </si>
 </sst>
 </file>
@@ -769,7 +655,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -810,7 +696,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -819,10 +705,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>9</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -834,7 +720,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -846,7 +732,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -858,7 +744,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -870,7 +756,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -882,7 +768,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -894,7 +780,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -906,7 +792,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -918,7 +804,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -930,7 +816,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -942,7 +828,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -954,7 +840,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -963,10 +849,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -975,10 +861,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -987,10 +873,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -999,10 +885,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1011,7 +897,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>25</v>
@@ -1023,10 +909,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1035,10 +921,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1047,7 +933,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>25</v>
@@ -1059,7 +945,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>25</v>
@@ -1071,10 +957,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1083,10 +969,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1095,10 +981,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1107,10 +993,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1119,7 +1005,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>25</v>
@@ -1131,7 +1017,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>25</v>
@@ -1143,10 +1029,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1155,10 +1041,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1167,10 +1053,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>25</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1179,10 +1065,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1191,10 +1077,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1203,10 +1089,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1215,10 +1101,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1227,10 +1113,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1239,10 +1125,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1251,10 +1137,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1263,10 +1149,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1161,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1173,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1185,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1311,7 +1197,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>25</v>
@@ -1323,7 +1209,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>25</v>
@@ -1334,453 +1220,84 @@
       <c r="D46"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A47" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C47" s="6"/>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>4</v>
-      </c>
+      <c r="C48" s="6"/>
       <c r="D48"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C49" s="6"/>
       <c r="D49"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C50" s="6"/>
       <c r="D50"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C51" s="6"/>
       <c r="D51"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C52" s="6"/>
       <c r="D52"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="6"/>
       <c r="D53"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C54" s="6"/>
       <c r="D54"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C55" s="6"/>
       <c r="D55"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C56" s="6"/>
       <c r="D56"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C57" s="6"/>
       <c r="D57"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C58" s="6"/>
       <c r="D58"/>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C59" s="6"/>
       <c r="D59"/>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C60" s="6"/>
       <c r="D60"/>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C61" s="6"/>
       <c r="D61"/>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C62" s="6"/>
       <c r="D62"/>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C63" s="6"/>
       <c r="D63"/>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C64" s="6"/>
       <c r="D64"/>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C65" s="6"/>
       <c r="D65"/>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>4</v>
-      </c>
+    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C66" s="6"/>
       <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36E68646-11F0-45D3-B772-B8435FEEDD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB106CEC-4AC0-4C24-B7D0-5201E9262CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="332">
   <si>
     <t>Status</t>
   </si>
@@ -48,154 +48,985 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>810974968</t>
+    <t>820629511</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>809655867</t>
-  </si>
-  <si>
-    <t>230492526</t>
+    <t>892797048</t>
+  </si>
+  <si>
+    <t>948257286</t>
+  </si>
+  <si>
+    <t>237046770</t>
   </si>
   <si>
     <t xml:space="preserve">PAGO A MENOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
   </si>
   <si>
-    <t>222454682</t>
-  </si>
-  <si>
-    <t>223167606</t>
-  </si>
-  <si>
-    <t>231597026</t>
-  </si>
-  <si>
-    <t>231222484</t>
-  </si>
-  <si>
-    <t>231048897</t>
-  </si>
-  <si>
-    <t>231003801</t>
-  </si>
-  <si>
-    <t>230870846</t>
-  </si>
-  <si>
-    <t>841324142</t>
-  </si>
-  <si>
-    <t>230817029</t>
-  </si>
-  <si>
-    <t>241111404</t>
-  </si>
-  <si>
-    <t>236896928</t>
+    <t>242698813</t>
+  </si>
+  <si>
+    <t>176055477</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>961521519</t>
-  </si>
-  <si>
-    <t>944197148</t>
-  </si>
-  <si>
-    <t>965325719</t>
+    <t>916578630</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>250636705</t>
-  </si>
-  <si>
-    <t>861209561</t>
-  </si>
-  <si>
-    <t>937797904</t>
-  </si>
-  <si>
-    <t>252003102</t>
-  </si>
-  <si>
-    <t>231170337</t>
-  </si>
-  <si>
-    <t>916623972</t>
-  </si>
-  <si>
-    <t>782123222</t>
-  </si>
-  <si>
-    <t>969922792</t>
-  </si>
-  <si>
-    <t>179869767</t>
-  </si>
-  <si>
-    <t>824773430</t>
-  </si>
-  <si>
-    <t>861408155</t>
-  </si>
-  <si>
-    <t>211022029</t>
-  </si>
-  <si>
-    <t>187639160</t>
+    <t>915076792</t>
+  </si>
+  <si>
+    <t>895866444</t>
+  </si>
+  <si>
+    <t>956865186</t>
+  </si>
+  <si>
+    <t>946950718</t>
+  </si>
+  <si>
+    <t>945318263</t>
+  </si>
+  <si>
+    <t>944165038</t>
+  </si>
+  <si>
+    <t>930308493</t>
+  </si>
+  <si>
+    <t>208813604</t>
+  </si>
+  <si>
+    <t>212143519</t>
+  </si>
+  <si>
+    <t>974361762</t>
+  </si>
+  <si>
+    <t>186945113</t>
+  </si>
+  <si>
+    <t>191895394</t>
+  </si>
+  <si>
+    <t>178793653</t>
+  </si>
+  <si>
+    <t>183128648</t>
+  </si>
+  <si>
+    <t>262403060</t>
+  </si>
+  <si>
+    <t>261951804</t>
+  </si>
+  <si>
+    <t>261723393</t>
+  </si>
+  <si>
+    <t>258838782</t>
+  </si>
+  <si>
+    <t>256325204</t>
+  </si>
+  <si>
+    <t>254664539</t>
+  </si>
+  <si>
+    <t>252852664</t>
+  </si>
+  <si>
+    <t>252552256</t>
+  </si>
+  <si>
+    <t>252425644</t>
+  </si>
+  <si>
+    <t>252326198</t>
+  </si>
+  <si>
+    <t>231464771</t>
+  </si>
+  <si>
+    <t>237159342</t>
+  </si>
+  <si>
+    <t>236822973</t>
+  </si>
+  <si>
+    <t>229809078</t>
+  </si>
+  <si>
+    <t>228470278</t>
+  </si>
+  <si>
+    <t>225476518</t>
+  </si>
+  <si>
+    <t>217027642</t>
+  </si>
+  <si>
+    <t>215000534</t>
+  </si>
+  <si>
+    <t>214970141</t>
+  </si>
+  <si>
+    <t>890395795</t>
+  </si>
+  <si>
+    <t>887793283</t>
+  </si>
+  <si>
+    <t>887298119</t>
+  </si>
+  <si>
+    <t>887045916</t>
+  </si>
+  <si>
+    <t>885125041</t>
+  </si>
+  <si>
+    <t>862817735</t>
+  </si>
+  <si>
+    <t>852227424</t>
+  </si>
+  <si>
+    <t>828231005</t>
+  </si>
+  <si>
+    <t>823035484</t>
+  </si>
+  <si>
+    <t>815686609</t>
+  </si>
+  <si>
+    <t>814478008</t>
+  </si>
+  <si>
+    <t>812907370</t>
+  </si>
+  <si>
+    <t>251629295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>214770145</t>
+  </si>
+  <si>
+    <t>209363096</t>
+  </si>
+  <si>
+    <t>206861902</t>
+  </si>
+  <si>
+    <t>969005523</t>
+  </si>
+  <si>
+    <t>965060977</t>
+  </si>
+  <si>
+    <t>250953712</t>
+  </si>
+  <si>
+    <t>244441725</t>
+  </si>
+  <si>
+    <t>859696274</t>
+  </si>
+  <si>
+    <t>892602966</t>
+  </si>
+  <si>
+    <t>869656656</t>
+  </si>
+  <si>
+    <t>237732692</t>
+  </si>
+  <si>
+    <t>817790789</t>
+  </si>
+  <si>
+    <t>879379612</t>
+  </si>
+  <si>
+    <t>230632600</t>
+  </si>
+  <si>
+    <t>184940181</t>
+  </si>
+  <si>
+    <t>235471541</t>
+  </si>
+  <si>
+    <t>844620165</t>
+  </si>
+  <si>
+    <t>946864349</t>
+  </si>
+  <si>
+    <t>972799765</t>
+  </si>
+  <si>
+    <t>252258441</t>
+  </si>
+  <si>
+    <t>216182208</t>
+  </si>
+  <si>
+    <t>194383364</t>
+  </si>
+  <si>
+    <t>219591694</t>
+  </si>
+  <si>
+    <t>189917168</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>924549623</t>
-  </si>
-  <si>
-    <t>956615219</t>
-  </si>
-  <si>
-    <t>954861302</t>
-  </si>
-  <si>
-    <t>946313438</t>
-  </si>
-  <si>
-    <t>946313420</t>
-  </si>
-  <si>
-    <t>941150595</t>
-  </si>
-  <si>
-    <t>207515333</t>
-  </si>
-  <si>
-    <t>189183670</t>
-  </si>
-  <si>
-    <t>971152032</t>
-  </si>
-  <si>
-    <t>182391262</t>
-  </si>
-  <si>
-    <t>181301197</t>
-  </si>
-  <si>
-    <t>966509030</t>
-  </si>
-  <si>
-    <t>746780828</t>
-  </si>
-  <si>
-    <t>262555851</t>
-  </si>
-  <si>
-    <t>903558603</t>
+    <t>220982221</t>
+  </si>
+  <si>
+    <t>826091328</t>
+  </si>
+  <si>
+    <t>891079612</t>
+  </si>
+  <si>
+    <t>826853727</t>
+  </si>
+  <si>
+    <t>252833912</t>
+  </si>
+  <si>
+    <t>226334344</t>
+  </si>
+  <si>
+    <t>202775080</t>
+  </si>
+  <si>
+    <t>193639469</t>
+  </si>
+  <si>
+    <t>817512845</t>
+  </si>
+  <si>
+    <t>839832833</t>
+  </si>
+  <si>
+    <t>925306072</t>
+  </si>
+  <si>
+    <t>953029026</t>
+  </si>
+  <si>
+    <t>208452486</t>
+  </si>
+  <si>
+    <t>838459257</t>
+  </si>
+  <si>
+    <t>915090678</t>
+  </si>
+  <si>
+    <t>252833326</t>
+  </si>
+  <si>
+    <t>252796671</t>
+  </si>
+  <si>
+    <t>252662394</t>
+  </si>
+  <si>
+    <t>204838613</t>
+  </si>
+  <si>
+    <t>197375946</t>
+  </si>
+  <si>
+    <t>951314255</t>
+  </si>
+  <si>
+    <t>932202041</t>
+  </si>
+  <si>
+    <t>804821217</t>
+  </si>
+  <si>
+    <t>229319839</t>
+  </si>
+  <si>
+    <t>235790502</t>
+  </si>
+  <si>
+    <t>931645596</t>
+  </si>
+  <si>
+    <t>944002512</t>
+  </si>
+  <si>
+    <t>933491429</t>
+  </si>
+  <si>
+    <t>928814247</t>
+  </si>
+  <si>
+    <t>824203123</t>
+  </si>
+  <si>
+    <t>921894022</t>
+  </si>
+  <si>
+    <t>914627660</t>
+  </si>
+  <si>
+    <t>889815381</t>
+  </si>
+  <si>
+    <t>905677799</t>
+  </si>
+  <si>
+    <t>924975133</t>
+  </si>
+  <si>
+    <t>838727380</t>
+  </si>
+  <si>
+    <t>918309992</t>
+  </si>
+  <si>
+    <t>910699507</t>
+  </si>
+  <si>
+    <t>975079728</t>
+  </si>
+  <si>
+    <t>973076650</t>
+  </si>
+  <si>
+    <t>973076643</t>
+  </si>
+  <si>
+    <t>951698251</t>
+  </si>
+  <si>
+    <t>934576418</t>
+  </si>
+  <si>
+    <t>923927994</t>
+  </si>
+  <si>
+    <t>902562853</t>
+  </si>
+  <si>
+    <t>889350017</t>
+  </si>
+  <si>
+    <t>857146330</t>
+  </si>
+  <si>
+    <t>852282742</t>
+  </si>
+  <si>
+    <t>845440753</t>
+  </si>
+  <si>
+    <t>836633234</t>
+  </si>
+  <si>
+    <t>818519443</t>
+  </si>
+  <si>
+    <t>264070297</t>
+  </si>
+  <si>
+    <t>264014956</t>
+  </si>
+  <si>
+    <t>263704052</t>
+  </si>
+  <si>
+    <t>262680113</t>
+  </si>
+  <si>
+    <t>237528389</t>
+  </si>
+  <si>
+    <t>235819558</t>
+  </si>
+  <si>
+    <t>235625385</t>
+  </si>
+  <si>
+    <t>231301569</t>
+  </si>
+  <si>
+    <t>230835328</t>
+  </si>
+  <si>
+    <t>226705642</t>
+  </si>
+  <si>
+    <t>211636190</t>
+  </si>
+  <si>
+    <t>204639532</t>
+  </si>
+  <si>
+    <t>198854923</t>
+  </si>
+  <si>
+    <t>195548940</t>
+  </si>
+  <si>
+    <t>186488346</t>
+  </si>
+  <si>
+    <t>264193479</t>
+  </si>
+  <si>
+    <t>838805368</t>
+  </si>
+  <si>
+    <t>820466500</t>
+  </si>
+  <si>
+    <t>264532387</t>
+  </si>
+  <si>
+    <t>264479019</t>
+  </si>
+  <si>
+    <t>260292531</t>
+  </si>
+  <si>
+    <t>252995026</t>
+  </si>
+  <si>
+    <t>201721267</t>
+  </si>
+  <si>
+    <t>861975963</t>
+  </si>
+  <si>
+    <t>917739934</t>
+  </si>
+  <si>
+    <t>883316741</t>
+  </si>
+  <si>
+    <t>262369279</t>
+  </si>
+  <si>
+    <t>253200202</t>
+  </si>
+  <si>
+    <t>241170533</t>
+  </si>
+  <si>
+    <t>238156305</t>
+  </si>
+  <si>
+    <t>175255763</t>
+  </si>
+  <si>
+    <t>972469013</t>
+  </si>
+  <si>
+    <t>181513098</t>
+  </si>
+  <si>
+    <t>179770833</t>
+  </si>
+  <si>
+    <t>175255755</t>
+  </si>
+  <si>
+    <t>929904690</t>
+  </si>
+  <si>
+    <t>926516174</t>
+  </si>
+  <si>
+    <t>925653523</t>
+  </si>
+  <si>
+    <t>934233341</t>
+  </si>
+  <si>
+    <t>951220148</t>
+  </si>
+  <si>
+    <t>947059907</t>
+  </si>
+  <si>
+    <t>943305759</t>
+  </si>
+  <si>
+    <t>238560860</t>
+  </si>
+  <si>
+    <t>259444200</t>
+  </si>
+  <si>
+    <t>841979507</t>
+  </si>
+  <si>
+    <t>825784246</t>
+  </si>
+  <si>
+    <t>813176041</t>
+  </si>
+  <si>
+    <t>811266133</t>
+  </si>
+  <si>
+    <t>810104194</t>
+  </si>
+  <si>
+    <t>263828992</t>
+  </si>
+  <si>
+    <t>263628715</t>
+  </si>
+  <si>
+    <t>263514204</t>
+  </si>
+  <si>
+    <t>262461308</t>
+  </si>
+  <si>
+    <t>247800745</t>
+  </si>
+  <si>
+    <t>253353910</t>
+  </si>
+  <si>
+    <t>253775781</t>
+  </si>
+  <si>
+    <t>253557882</t>
+  </si>
+  <si>
+    <t>253390417</t>
+  </si>
+  <si>
+    <t>231441951</t>
+  </si>
+  <si>
+    <t>219024142</t>
+  </si>
+  <si>
+    <t>208617245</t>
+  </si>
+  <si>
+    <t>207225891</t>
+  </si>
+  <si>
+    <t>205902285</t>
+  </si>
+  <si>
+    <t>197108461</t>
+  </si>
+  <si>
+    <t>193935818</t>
+  </si>
+  <si>
+    <t>882857224</t>
+  </si>
+  <si>
+    <t>920855644</t>
+  </si>
+  <si>
+    <t>916662830</t>
+  </si>
+  <si>
+    <t>915395416</t>
+  </si>
+  <si>
+    <t>894832801</t>
+  </si>
+  <si>
+    <t>876479936</t>
+  </si>
+  <si>
+    <t>873315935</t>
+  </si>
+  <si>
+    <t>864955269</t>
+  </si>
+  <si>
+    <t>861686438</t>
+  </si>
+  <si>
+    <t>860519630</t>
+  </si>
+  <si>
+    <t>894973654</t>
+  </si>
+  <si>
+    <t>943062285</t>
+  </si>
+  <si>
+    <t>882480985</t>
+  </si>
+  <si>
+    <t>245906916</t>
+  </si>
+  <si>
+    <t>245572460</t>
+  </si>
+  <si>
+    <t>254050358</t>
+  </si>
+  <si>
+    <t>253808186</t>
+  </si>
+  <si>
+    <t>254269651</t>
+  </si>
+  <si>
+    <t>252787928</t>
+  </si>
+  <si>
+    <t>253687937</t>
+  </si>
+  <si>
+    <t>244492165</t>
+  </si>
+  <si>
+    <t>203872217</t>
+  </si>
+  <si>
+    <t>936440522</t>
+  </si>
+  <si>
+    <t>974574208</t>
+  </si>
+  <si>
+    <t>252665967</t>
+  </si>
+  <si>
+    <t>853336851</t>
+  </si>
+  <si>
+    <t>923028694</t>
+  </si>
+  <si>
+    <t>251459149</t>
+  </si>
+  <si>
+    <t>199553185</t>
+  </si>
+  <si>
+    <t>238676351</t>
+  </si>
+  <si>
+    <t>253957090</t>
+  </si>
+  <si>
+    <t>816546513</t>
+  </si>
+  <si>
+    <t>257099840</t>
+  </si>
+  <si>
+    <t>255193843</t>
+  </si>
+  <si>
+    <t>254359023</t>
+  </si>
+  <si>
+    <t>257485015</t>
+  </si>
+  <si>
+    <t>178761254</t>
+  </si>
+  <si>
+    <t>246693125</t>
+  </si>
+  <si>
+    <t>246491918</t>
+  </si>
+  <si>
+    <t>245389576</t>
+  </si>
+  <si>
+    <t>239287612</t>
+  </si>
+  <si>
+    <t>223056189</t>
+  </si>
+  <si>
+    <t>203654342</t>
+  </si>
+  <si>
+    <t>200532384</t>
+  </si>
+  <si>
+    <t>178761262</t>
+  </si>
+  <si>
+    <t>815742154</t>
+  </si>
+  <si>
+    <t>848124123</t>
+  </si>
+  <si>
+    <t>829226434</t>
+  </si>
+  <si>
+    <t>264495858</t>
+  </si>
+  <si>
+    <t>257689350</t>
+  </si>
+  <si>
+    <t>257316533</t>
+  </si>
+  <si>
+    <t>949247138</t>
+  </si>
+  <si>
+    <t>946525569</t>
+  </si>
+  <si>
+    <t>940148566</t>
+  </si>
+  <si>
+    <t>912313941</t>
+  </si>
+  <si>
+    <t>918388905</t>
+  </si>
+  <si>
+    <t>179188374</t>
+  </si>
+  <si>
+    <t>222873196</t>
+  </si>
+  <si>
+    <t>242906430</t>
+  </si>
+  <si>
+    <t>242932865</t>
+  </si>
+  <si>
+    <t>246743052</t>
+  </si>
+  <si>
+    <t>247832649</t>
+  </si>
+  <si>
+    <t>247423183</t>
+  </si>
+  <si>
+    <t>230469391</t>
+  </si>
+  <si>
+    <t>228366609</t>
+  </si>
+  <si>
+    <t>226237935</t>
+  </si>
+  <si>
+    <t>225337801</t>
+  </si>
+  <si>
+    <t>216886386</t>
+  </si>
+  <si>
+    <t>213695210</t>
+  </si>
+  <si>
+    <t>202939694</t>
+  </si>
+  <si>
+    <t>212028256</t>
+  </si>
+  <si>
+    <t>210870527</t>
+  </si>
+  <si>
+    <t>196628345</t>
+  </si>
+  <si>
+    <t>185749813</t>
+  </si>
+  <si>
+    <t>184031387</t>
+  </si>
+  <si>
+    <t>966510855</t>
+  </si>
+  <si>
+    <t>865550945</t>
+  </si>
+  <si>
+    <t>257016067</t>
+  </si>
+  <si>
+    <t>253867810</t>
+  </si>
+  <si>
+    <t>251167429</t>
+  </si>
+  <si>
+    <t>249545769</t>
+  </si>
+  <si>
+    <t>841759172</t>
+  </si>
+  <si>
+    <t>844893119</t>
+  </si>
+  <si>
+    <t>862209644</t>
+  </si>
+  <si>
+    <t>861167140</t>
+  </si>
+  <si>
+    <t>759123015</t>
+  </si>
+  <si>
+    <t>729304570</t>
+  </si>
+  <si>
+    <t>258493000</t>
+  </si>
+  <si>
+    <t>263695169</t>
+  </si>
+  <si>
+    <t>265040455</t>
+  </si>
+  <si>
+    <t>264637848</t>
+  </si>
+  <si>
+    <t>262735925</t>
+  </si>
+  <si>
+    <t>260200203</t>
+  </si>
+  <si>
+    <t>256928924</t>
+  </si>
+  <si>
+    <t>255661807</t>
+  </si>
+  <si>
+    <t>254788783</t>
+  </si>
+  <si>
+    <t>254492782</t>
+  </si>
+  <si>
+    <t>254480100</t>
+  </si>
+  <si>
+    <t>957392255</t>
+  </si>
+  <si>
+    <t>952032922</t>
+  </si>
+  <si>
+    <t>949708600</t>
+  </si>
+  <si>
+    <t>929502742</t>
+  </si>
+  <si>
+    <t>921264093</t>
+  </si>
+  <si>
+    <t>927438782</t>
+  </si>
+  <si>
+    <t>964848448</t>
+  </si>
+  <si>
+    <t>245166933</t>
+  </si>
+  <si>
+    <t>255258646</t>
+  </si>
+  <si>
+    <t>248971735</t>
+  </si>
+  <si>
+    <t>248941035</t>
+  </si>
+  <si>
+    <t>807544550</t>
+  </si>
+  <si>
+    <t>861508558</t>
+  </si>
+  <si>
+    <t>861487878</t>
+  </si>
+  <si>
+    <t>229772789</t>
+  </si>
+  <si>
+    <t>254897436</t>
+  </si>
+  <si>
+    <t>254775244</t>
+  </si>
+  <si>
+    <t>249868971</t>
+  </si>
+  <si>
+    <t>231265798</t>
+  </si>
+  <si>
+    <t>256644786</t>
+  </si>
+  <si>
+    <t>939408229</t>
+  </si>
+  <si>
+    <t>223488960</t>
+  </si>
+  <si>
+    <t>948506062</t>
+  </si>
+  <si>
+    <t>870250689</t>
+  </si>
+  <si>
+    <t>213767365</t>
+  </si>
+  <si>
+    <t>257482095</t>
+  </si>
+  <si>
+    <t>252208693</t>
+  </si>
+  <si>
+    <t>257535819</t>
+  </si>
+  <si>
+    <t>966986857</t>
+  </si>
+  <si>
+    <t>201580986</t>
   </si>
 </sst>
 </file>
@@ -655,7 +1486,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -708,7 +1539,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -717,10 +1548,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>9</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -732,7 +1563,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -744,7 +1575,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -753,10 +1584,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -765,10 +1596,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -777,10 +1608,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -789,10 +1620,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -801,10 +1632,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -813,10 +1644,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -825,10 +1656,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -837,10 +1668,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -849,10 +1680,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -861,10 +1692,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -873,10 +1704,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -888,7 +1719,7 @@
         <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -900,7 +1731,7 @@
         <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -912,7 +1743,7 @@
         <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -924,7 +1755,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -936,7 +1767,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -948,7 +1779,7 @@
         <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -960,7 +1791,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -972,7 +1803,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -984,7 +1815,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -996,7 +1827,7 @@
         <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1008,7 +1839,7 @@
         <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1020,7 +1851,7 @@
         <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1032,7 +1863,7 @@
         <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1041,10 +1872,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1053,10 +1884,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1065,10 +1896,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1077,10 +1908,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1089,10 +1920,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1101,10 +1932,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1113,10 +1944,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1125,10 +1956,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1137,10 +1968,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1149,10 +1980,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1992,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1173,10 +2004,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1185,10 +2016,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1197,10 +2028,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1209,95 +2040,3071 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B46" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D46"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C47" s="6"/>
+      <c r="B47" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D47"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C48" s="6"/>
+      <c r="A48" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D48"/>
     </row>
-    <row r="49" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C49" s="6"/>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D49"/>
     </row>
-    <row r="50" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C50" s="6"/>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D50"/>
     </row>
-    <row r="51" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C51" s="6"/>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D51"/>
     </row>
-    <row r="52" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C52" s="6"/>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D52"/>
     </row>
-    <row r="53" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C53" s="6"/>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D53"/>
     </row>
-    <row r="54" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C54" s="6"/>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D54"/>
     </row>
-    <row r="55" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C55" s="6"/>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D55"/>
     </row>
-    <row r="56" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C56" s="6"/>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D56"/>
     </row>
-    <row r="57" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C57" s="6"/>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D57"/>
     </row>
-    <row r="58" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C58" s="6"/>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D58"/>
     </row>
-    <row r="59" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C59" s="6"/>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D59"/>
     </row>
-    <row r="60" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C60" s="6"/>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D60"/>
     </row>
-    <row r="61" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C61" s="6"/>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D61"/>
     </row>
-    <row r="62" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C62" s="6"/>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D62"/>
     </row>
-    <row r="63" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C63" s="6"/>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D63"/>
     </row>
-    <row r="64" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C64" s="6"/>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D64"/>
     </row>
-    <row r="65" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C65" s="6"/>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D65"/>
     </row>
-    <row r="66" spans="3:4" x14ac:dyDescent="0.25">
-      <c r="C66" s="6"/>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>4</v>
+      </c>
       <c r="D66"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A70" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C172" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C173" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C174" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C175" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C176" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C177" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C178" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C181" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C182" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C183" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C184" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C186" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C187" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C188" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C189" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C190" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C191" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C192" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C193" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C194" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C195" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C197" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C204" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C205" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C206" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C208" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C209" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C212" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C213" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C214" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C215" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C216" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C217" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C218" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C226" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C227" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C228" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C229" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C230" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C231" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C232" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C233" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C234" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C235" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C236" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C237" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C238" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C244" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C245" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C246" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C247" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C248" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C249" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C251" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C252" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C253" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C254" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C255" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C256" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C257" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C258" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C259" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C260" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C261" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C262" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C263" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C264" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C265" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C268" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C269" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C272" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C273" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C274" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C276" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C277" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C278" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A279" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C279" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A280" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C280" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A281" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C281" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A282" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A283" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A284" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A285" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A286" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A287" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A288" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A289" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A290" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A291" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A292" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A293" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A294" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A295" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A296" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C296" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A297" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C297" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A298" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C298" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A299" s="4" t="s">
+        <v>308</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C299" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A300" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C300" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A301" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C301" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A302" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C302" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A303" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C303" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A304" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C304" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A305" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C305" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A306" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C306" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A307" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C307" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A308" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A309" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C309" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A310" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C310" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A311" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C311" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A312" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C312" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A313" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C313" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A314" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A315" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A316" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C316" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A317" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C317" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A318" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C318" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A319" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C319" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A320" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C320" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A321" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C321" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A322" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C322" s="6" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D5A32-B278-468C-9939-C2C0E91682B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7F4480-4A4A-487B-B124-DD8BB75A33AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="99">
   <si>
     <t>Status</t>
   </si>
@@ -48,238 +48,286 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>253796027</t>
+    <t>959425970</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>956282028</t>
-  </si>
-  <si>
-    <t>250929167</t>
-  </si>
-  <si>
-    <t>866329489</t>
+    <t>836315212</t>
+  </si>
+  <si>
+    <t>229337773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>936607005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>900996731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>814929273</t>
+  </si>
+  <si>
+    <t>872742865</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>224180392</t>
-  </si>
-  <si>
-    <t>231127584</t>
-  </si>
-  <si>
-    <t>200472532</t>
-  </si>
-  <si>
-    <t>233094824</t>
-  </si>
-  <si>
-    <t>975581145</t>
-  </si>
-  <si>
-    <t>892661756</t>
-  </si>
-  <si>
-    <t>215565734</t>
-  </si>
-  <si>
-    <t>866430907</t>
-  </si>
-  <si>
-    <t>856614262</t>
-  </si>
-  <si>
-    <t>830735290</t>
-  </si>
-  <si>
-    <t>788076606</t>
-  </si>
-  <si>
-    <t>247386992</t>
-  </si>
-  <si>
-    <t>245227370</t>
-  </si>
-  <si>
-    <t>239996436</t>
-  </si>
-  <si>
-    <t>260508068</t>
-  </si>
-  <si>
-    <t>258672686</t>
-  </si>
-  <si>
-    <t>257186738</t>
-  </si>
-  <si>
-    <t>237546605</t>
-  </si>
-  <si>
-    <t>256734231</t>
-  </si>
-  <si>
-    <t>242519951</t>
-  </si>
-  <si>
-    <t>217362361</t>
-  </si>
-  <si>
-    <t>228713073</t>
-  </si>
-  <si>
-    <t>226718579</t>
-  </si>
-  <si>
-    <t>195624378</t>
-  </si>
-  <si>
-    <t>213463130</t>
-  </si>
-  <si>
-    <t>209716350</t>
-  </si>
-  <si>
-    <t>208179824</t>
-  </si>
-  <si>
-    <t>207119284</t>
-  </si>
-  <si>
-    <t>836474746</t>
-  </si>
-  <si>
-    <t>969017668</t>
-  </si>
-  <si>
-    <t>953345018</t>
-  </si>
-  <si>
-    <t>959425970</t>
-  </si>
-  <si>
-    <t>949682540</t>
-  </si>
-  <si>
-    <t>942099874</t>
-  </si>
-  <si>
-    <t>941207536</t>
-  </si>
-  <si>
-    <t>939425728</t>
-  </si>
-  <si>
-    <t>923641405</t>
-  </si>
-  <si>
-    <t>185927948</t>
-  </si>
-  <si>
-    <t>184586349</t>
-  </si>
-  <si>
-    <t>184532277</t>
-  </si>
-  <si>
-    <t>880208453</t>
-  </si>
-  <si>
-    <t>891855482</t>
-  </si>
-  <si>
-    <t>897580662</t>
-  </si>
-  <si>
-    <t>844874614</t>
-  </si>
-  <si>
-    <t>844095822</t>
-  </si>
-  <si>
-    <t>842221792</t>
-  </si>
-  <si>
-    <t>841545035</t>
-  </si>
-  <si>
-    <t>836315212</t>
-  </si>
-  <si>
-    <t>835968243</t>
-  </si>
-  <si>
-    <t>820324758</t>
-  </si>
-  <si>
-    <t>809694007</t>
-  </si>
-  <si>
-    <t>807719202</t>
-  </si>
-  <si>
-    <t>267395261</t>
-  </si>
-  <si>
-    <t>266718398</t>
-  </si>
-  <si>
-    <t>266426349</t>
-  </si>
-  <si>
-    <t>266042443</t>
-  </si>
-  <si>
-    <t>263462750</t>
-  </si>
-  <si>
-    <t>263089686</t>
-  </si>
-  <si>
-    <t>262478229</t>
-  </si>
-  <si>
-    <t>208525992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>215726591</t>
-  </si>
-  <si>
-    <t>229337773</t>
-  </si>
-  <si>
-    <t>212276137</t>
-  </si>
-  <si>
-    <t>185004441</t>
-  </si>
-  <si>
-    <t>922556018</t>
-  </si>
-  <si>
-    <t>939969865</t>
-  </si>
-  <si>
-    <t>945544405</t>
-  </si>
-  <si>
-    <t>215304167</t>
-  </si>
-  <si>
-    <t>257610380</t>
-  </si>
-  <si>
-    <t>255506416</t>
-  </si>
-  <si>
-    <t>228916429</t>
+    <t>922358308</t>
+  </si>
+  <si>
+    <t>184862328</t>
+  </si>
+  <si>
+    <t>966986162</t>
+  </si>
+  <si>
+    <t>957564630</t>
+  </si>
+  <si>
+    <t>950135669</t>
+  </si>
+  <si>
+    <t>196397032</t>
+  </si>
+  <si>
+    <t>186382515</t>
+  </si>
+  <si>
+    <t>853289712</t>
+  </si>
+  <si>
+    <t>851723787</t>
+  </si>
+  <si>
+    <t>267503443</t>
+  </si>
+  <si>
+    <t>262453289</t>
+  </si>
+  <si>
+    <t>260322932</t>
+  </si>
+  <si>
+    <t>259461360</t>
+  </si>
+  <si>
+    <t>248301339</t>
+  </si>
+  <si>
+    <t>248038469</t>
+  </si>
+  <si>
+    <t>247891942</t>
+  </si>
+  <si>
+    <t>243625716</t>
+  </si>
+  <si>
+    <t>259147969</t>
+  </si>
+  <si>
+    <t>261159127</t>
+  </si>
+  <si>
+    <t>259065567</t>
+  </si>
+  <si>
+    <t>258850191</t>
+  </si>
+  <si>
+    <t>240791347</t>
+  </si>
+  <si>
+    <t>234030595</t>
+  </si>
+  <si>
+    <t>232077432</t>
+  </si>
+  <si>
+    <t>205850591</t>
+  </si>
+  <si>
+    <t>864612936</t>
+  </si>
+  <si>
+    <t>917944591</t>
+  </si>
+  <si>
+    <t>896875816</t>
+  </si>
+  <si>
+    <t>186891747</t>
+  </si>
+  <si>
+    <t>947692087</t>
+  </si>
+  <si>
+    <t>968191993</t>
+  </si>
+  <si>
+    <t>970943175</t>
+  </si>
+  <si>
+    <t>924148129</t>
+  </si>
+  <si>
+    <t>924098308</t>
+  </si>
+  <si>
+    <t>196889046</t>
+  </si>
+  <si>
+    <t>879668519</t>
+  </si>
+  <si>
+    <t>777015813</t>
+  </si>
+  <si>
+    <t>843642632</t>
+  </si>
+  <si>
+    <t>841360906</t>
+  </si>
+  <si>
+    <t>267535650</t>
+  </si>
+  <si>
+    <t>268779950</t>
+  </si>
+  <si>
+    <t>268698812</t>
+  </si>
+  <si>
+    <t>268606419</t>
+  </si>
+  <si>
+    <t>268352667</t>
+  </si>
+  <si>
+    <t>268188293</t>
+  </si>
+  <si>
+    <t>267839292</t>
+  </si>
+  <si>
+    <t>267611261</t>
+  </si>
+  <si>
+    <t>266585516</t>
+  </si>
+  <si>
+    <t>266546229</t>
+  </si>
+  <si>
+    <t>266241540</t>
+  </si>
+  <si>
+    <t>265459440</t>
+  </si>
+  <si>
+    <t>265306427</t>
+  </si>
+  <si>
+    <t>263410692</t>
+  </si>
+  <si>
+    <t>255824561</t>
+  </si>
+  <si>
+    <t>916781119</t>
+  </si>
+  <si>
+    <t>242357238</t>
+  </si>
+  <si>
+    <t>185591322</t>
+  </si>
+  <si>
+    <t>938409889</t>
+  </si>
+  <si>
+    <t>949414845</t>
+  </si>
+  <si>
+    <t>950196422</t>
+  </si>
+  <si>
+    <t>859667754</t>
+  </si>
+  <si>
+    <t>224899330</t>
+  </si>
+  <si>
+    <t>256683503</t>
+  </si>
+  <si>
+    <t>259152936</t>
+  </si>
+  <si>
+    <t>243342403</t>
+  </si>
+  <si>
+    <t>202589499</t>
+  </si>
+  <si>
+    <t>268435421</t>
+  </si>
+  <si>
+    <t>250380460</t>
+  </si>
+  <si>
+    <t>246173508</t>
+  </si>
+  <si>
+    <t>268862251</t>
+  </si>
+  <si>
+    <t>869402663</t>
+  </si>
+  <si>
+    <t>869266431</t>
+  </si>
+  <si>
+    <t>868819214</t>
+  </si>
+  <si>
+    <t>822740647</t>
+  </si>
+  <si>
+    <t>237191170</t>
+  </si>
+  <si>
+    <t>189630399</t>
+  </si>
+  <si>
+    <t>870346339</t>
+  </si>
+  <si>
+    <t>868058938</t>
+  </si>
+  <si>
+    <t>847492216</t>
+  </si>
+  <si>
+    <t>808002798</t>
+  </si>
+  <si>
+    <t>846198129</t>
+  </si>
+  <si>
+    <t>898070705</t>
   </si>
 </sst>
 </file>
@@ -739,7 +787,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -792,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -801,10 +849,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -813,10 +861,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -825,10 +873,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -837,10 +885,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -849,10 +897,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -861,10 +909,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -873,10 +921,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -885,10 +933,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -897,10 +945,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -909,10 +957,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -921,10 +969,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -933,10 +981,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -945,10 +993,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -957,10 +1005,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -969,10 +1017,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -981,10 +1029,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -993,10 +1041,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1005,10 +1053,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1017,10 +1065,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1029,10 +1077,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1041,7 +1089,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>6</v>
@@ -1053,7 +1101,7 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>6</v>
@@ -1065,7 +1113,7 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>6</v>
@@ -1077,7 +1125,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1089,7 +1137,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
@@ -1101,7 +1149,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
@@ -1113,7 +1161,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1125,7 +1173,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1137,7 +1185,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
@@ -1149,7 +1197,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
@@ -1161,7 +1209,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
@@ -1173,7 +1221,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
@@ -1185,7 +1233,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
@@ -1197,7 +1245,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
@@ -1209,7 +1257,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
@@ -1221,7 +1269,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
@@ -1233,7 +1281,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
@@ -1245,7 +1293,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
@@ -1257,7 +1305,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
@@ -1269,7 +1317,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
@@ -1281,7 +1329,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
@@ -1293,7 +1341,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -1305,7 +1353,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
@@ -1317,7 +1365,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
@@ -1329,7 +1377,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
@@ -1341,7 +1389,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
@@ -1353,7 +1401,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
@@ -1365,7 +1413,7 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>6</v>
@@ -1377,7 +1425,7 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>6</v>
@@ -1389,7 +1437,7 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>6</v>
@@ -1401,7 +1449,7 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>6</v>
@@ -1413,7 +1461,7 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>6</v>
@@ -1425,7 +1473,7 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>6</v>
@@ -1437,7 +1485,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>6</v>
@@ -1449,7 +1497,7 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>6</v>
@@ -1461,7 +1509,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>6</v>
@@ -1473,7 +1521,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>6</v>
@@ -1485,10 +1533,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1497,10 +1545,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1509,10 +1557,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1521,10 +1569,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1533,10 +1581,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1545,10 +1593,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1556,10 +1604,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1567,10 +1615,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1578,10 +1626,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1589,10 +1637,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1600,10 +1648,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1611,10 +1659,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1622,10 +1670,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1633,10 +1681,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1644,12 +1692,166 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C90" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C7F4480-4A4A-487B-B124-DD8BB75A33AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EC01BB-0BE6-488A-B1C3-3BEB579D87D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="54">
   <si>
     <t>Status</t>
   </si>
@@ -48,286 +48,151 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>959425970</t>
+    <t>252382159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>929068470</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>836315212</t>
-  </si>
-  <si>
-    <t>229337773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>936607005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>900996731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>814929273</t>
-  </si>
-  <si>
-    <t>872742865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>922358308</t>
-  </si>
-  <si>
-    <t>184862328</t>
-  </si>
-  <si>
-    <t>966986162</t>
-  </si>
-  <si>
-    <t>957564630</t>
-  </si>
-  <si>
-    <t>950135669</t>
-  </si>
-  <si>
-    <t>196397032</t>
-  </si>
-  <si>
-    <t>186382515</t>
-  </si>
-  <si>
-    <t>853289712</t>
-  </si>
-  <si>
-    <t>851723787</t>
-  </si>
-  <si>
-    <t>267503443</t>
-  </si>
-  <si>
-    <t>262453289</t>
-  </si>
-  <si>
-    <t>260322932</t>
-  </si>
-  <si>
-    <t>259461360</t>
-  </si>
-  <si>
-    <t>248301339</t>
-  </si>
-  <si>
-    <t>248038469</t>
-  </si>
-  <si>
-    <t>247891942</t>
-  </si>
-  <si>
-    <t>243625716</t>
-  </si>
-  <si>
-    <t>259147969</t>
-  </si>
-  <si>
-    <t>261159127</t>
-  </si>
-  <si>
-    <t>259065567</t>
-  </si>
-  <si>
-    <t>258850191</t>
-  </si>
-  <si>
-    <t>240791347</t>
-  </si>
-  <si>
-    <t>234030595</t>
-  </si>
-  <si>
-    <t>232077432</t>
-  </si>
-  <si>
-    <t>205850591</t>
-  </si>
-  <si>
-    <t>864612936</t>
-  </si>
-  <si>
-    <t>917944591</t>
-  </si>
-  <si>
-    <t>896875816</t>
-  </si>
-  <si>
-    <t>186891747</t>
-  </si>
-  <si>
-    <t>947692087</t>
-  </si>
-  <si>
-    <t>968191993</t>
-  </si>
-  <si>
-    <t>970943175</t>
-  </si>
-  <si>
-    <t>924148129</t>
-  </si>
-  <si>
-    <t>924098308</t>
-  </si>
-  <si>
-    <t>196889046</t>
-  </si>
-  <si>
-    <t>879668519</t>
-  </si>
-  <si>
-    <t>777015813</t>
-  </si>
-  <si>
-    <t>843642632</t>
-  </si>
-  <si>
-    <t>841360906</t>
-  </si>
-  <si>
-    <t>267535650</t>
-  </si>
-  <si>
-    <t>268779950</t>
-  </si>
-  <si>
-    <t>268698812</t>
-  </si>
-  <si>
-    <t>268606419</t>
-  </si>
-  <si>
-    <t>268352667</t>
-  </si>
-  <si>
-    <t>268188293</t>
-  </si>
-  <si>
-    <t>267839292</t>
-  </si>
-  <si>
-    <t>267611261</t>
-  </si>
-  <si>
-    <t>266585516</t>
-  </si>
-  <si>
-    <t>266546229</t>
-  </si>
-  <si>
-    <t>266241540</t>
-  </si>
-  <si>
-    <t>265459440</t>
-  </si>
-  <si>
-    <t>265306427</t>
-  </si>
-  <si>
-    <t>263410692</t>
-  </si>
-  <si>
-    <t>255824561</t>
-  </si>
-  <si>
-    <t>916781119</t>
-  </si>
-  <si>
-    <t>242357238</t>
-  </si>
-  <si>
-    <t>185591322</t>
-  </si>
-  <si>
-    <t>938409889</t>
-  </si>
-  <si>
-    <t>949414845</t>
-  </si>
-  <si>
-    <t>950196422</t>
-  </si>
-  <si>
-    <t>859667754</t>
-  </si>
-  <si>
-    <t>224899330</t>
-  </si>
-  <si>
-    <t>256683503</t>
-  </si>
-  <si>
-    <t>259152936</t>
-  </si>
-  <si>
-    <t>243342403</t>
-  </si>
-  <si>
-    <t>202589499</t>
-  </si>
-  <si>
-    <t>268435421</t>
-  </si>
-  <si>
-    <t>250380460</t>
-  </si>
-  <si>
-    <t>246173508</t>
-  </si>
-  <si>
-    <t>268862251</t>
-  </si>
-  <si>
-    <t>869402663</t>
-  </si>
-  <si>
-    <t>869266431</t>
-  </si>
-  <si>
-    <t>868819214</t>
-  </si>
-  <si>
-    <t>822740647</t>
-  </si>
-  <si>
-    <t>237191170</t>
-  </si>
-  <si>
-    <t>189630399</t>
-  </si>
-  <si>
-    <t>870346339</t>
-  </si>
-  <si>
-    <t>868058938</t>
-  </si>
-  <si>
-    <t>847492216</t>
-  </si>
-  <si>
-    <t>808002798</t>
-  </si>
-  <si>
-    <t>846198129</t>
-  </si>
-  <si>
-    <t>898070705</t>
+    <t>952018988</t>
+  </si>
+  <si>
+    <t>265842868</t>
+  </si>
+  <si>
+    <t>212289684</t>
+  </si>
+  <si>
+    <t>198432076</t>
+  </si>
+  <si>
+    <t>902128424</t>
+  </si>
+  <si>
+    <t>259867087</t>
+  </si>
+  <si>
+    <t>904313230</t>
+  </si>
+  <si>
+    <t>192005670</t>
+  </si>
+  <si>
+    <t>844576094</t>
+  </si>
+  <si>
+    <t>973047305</t>
+  </si>
+  <si>
+    <t>175440076</t>
+  </si>
+  <si>
+    <t>175022767</t>
+  </si>
+  <si>
+    <t>923384865</t>
+  </si>
+  <si>
+    <t>921486282</t>
+  </si>
+  <si>
+    <t>260327238</t>
+  </si>
+  <si>
+    <t>267376691</t>
+  </si>
+  <si>
+    <t>267056962</t>
+  </si>
+  <si>
+    <t>266232937</t>
+  </si>
+  <si>
+    <t>265844484</t>
+  </si>
+  <si>
+    <t>263819603</t>
+  </si>
+  <si>
+    <t>263446035</t>
+  </si>
+  <si>
+    <t>259539322</t>
+  </si>
+  <si>
+    <t>259452716</t>
+  </si>
+  <si>
+    <t>259132151</t>
+  </si>
+  <si>
+    <t>259106577</t>
+  </si>
+  <si>
+    <t>258602329</t>
+  </si>
+  <si>
+    <t>256252663</t>
+  </si>
+  <si>
+    <t>247610466</t>
+  </si>
+  <si>
+    <t>241304041</t>
+  </si>
+  <si>
+    <t>219912288</t>
+  </si>
+  <si>
+    <t>213967510</t>
+  </si>
+  <si>
+    <t>192704173</t>
+  </si>
+  <si>
+    <t>194821934</t>
+  </si>
+  <si>
+    <t>193928706</t>
+  </si>
+  <si>
+    <t>909015061</t>
+  </si>
+  <si>
+    <t>905247031</t>
+  </si>
+  <si>
+    <t>819412952</t>
+  </si>
+  <si>
+    <t>269727222</t>
+  </si>
+  <si>
+    <t>269555300</t>
+  </si>
+  <si>
+    <t>269493122</t>
+  </si>
+  <si>
+    <t>963998558</t>
+  </si>
+  <si>
+    <t>185753203</t>
+  </si>
+  <si>
+    <t>963429208</t>
+  </si>
+  <si>
+    <t>955197847</t>
+  </si>
+  <si>
+    <t>953785189</t>
   </si>
 </sst>
 </file>
@@ -787,7 +652,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -828,7 +693,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -837,10 +702,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -852,7 +717,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -861,10 +726,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -873,10 +738,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -885,10 +750,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -897,10 +762,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -909,10 +774,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -921,10 +786,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -933,10 +798,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -945,10 +810,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -957,10 +822,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -969,10 +834,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -981,10 +846,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -993,10 +858,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1005,10 +870,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1017,10 +882,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1029,10 +894,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1041,10 +906,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1053,10 +918,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1065,10 +930,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1077,10 +942,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1089,10 +954,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1101,10 +966,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1113,10 +978,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1125,10 +990,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1137,10 +1002,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1149,10 +1014,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1026,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1173,10 +1038,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1185,10 +1050,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1197,10 +1062,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1209,10 +1074,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1221,10 +1086,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1233,10 +1098,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1245,10 +1110,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1257,10 +1122,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1269,10 +1134,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1281,10 +1146,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1293,10 +1158,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1305,10 +1170,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1317,10 +1182,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1329,10 +1194,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1341,10 +1206,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1353,10 +1218,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1365,495 +1230,15 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
       </c>
       <c r="D48"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D49"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A50" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D50"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D51"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A53" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D53"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="B55" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D57"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="B58" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D58"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D59"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A61" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D62"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D63"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D64"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A65" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D65"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A66" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="D66"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A68" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A69" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A70" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D7" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28A843F2-EF43-482E-81D4-88841010A9A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC125675-BF61-4C75-A245-8A685A3BA3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="113">
   <si>
     <t>Status</t>
   </si>
@@ -48,484 +48,328 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>205674165</t>
+    <t>263943676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>262066180</t>
+  </si>
+  <si>
+    <t>211513092</t>
+  </si>
+  <si>
+    <t>209512478</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>202741504</t>
+    <t>251581736</t>
+  </si>
+  <si>
+    <t>899272839</t>
+  </si>
+  <si>
+    <t>883139648</t>
+  </si>
+  <si>
+    <t>883139630</t>
+  </si>
+  <si>
+    <t>857001329</t>
+  </si>
+  <si>
+    <t>848412874</t>
+  </si>
+  <si>
+    <t>831863752</t>
+  </si>
+  <si>
+    <t>831863745</t>
+  </si>
+  <si>
+    <t>830320135</t>
+  </si>
+  <si>
+    <t>825971082</t>
+  </si>
+  <si>
+    <t>818312039</t>
+  </si>
+  <si>
+    <t>766190841</t>
+  </si>
+  <si>
+    <t>271637948</t>
+  </si>
+  <si>
+    <t>236610717</t>
+  </si>
+  <si>
+    <t>236608398</t>
+  </si>
+  <si>
+    <t>219293309</t>
+  </si>
+  <si>
+    <t>216136501</t>
+  </si>
+  <si>
+    <t>202379750</t>
+  </si>
+  <si>
+    <t>186920835</t>
+  </si>
+  <si>
+    <t>924209400</t>
+  </si>
+  <si>
+    <t>188745867</t>
+  </si>
+  <si>
+    <t>184652760</t>
+  </si>
+  <si>
+    <t>183783798</t>
+  </si>
+  <si>
+    <t>926094917</t>
+  </si>
+  <si>
+    <t>950864839</t>
+  </si>
+  <si>
+    <t>950847370</t>
+  </si>
+  <si>
+    <t>947169680</t>
+  </si>
+  <si>
+    <t>941651691</t>
+  </si>
+  <si>
+    <t>235042151</t>
+  </si>
+  <si>
+    <t>840787307</t>
+  </si>
+  <si>
+    <t>867225934</t>
+  </si>
+  <si>
+    <t>900815410</t>
+  </si>
+  <si>
+    <t>908794005</t>
+  </si>
+  <si>
+    <t>908204120</t>
+  </si>
+  <si>
+    <t>898020098</t>
+  </si>
+  <si>
+    <t>894138985</t>
+  </si>
+  <si>
+    <t>847644675</t>
+  </si>
+  <si>
+    <t>853060618</t>
+  </si>
+  <si>
+    <t>851291249</t>
+  </si>
+  <si>
+    <t>847451485</t>
+  </si>
+  <si>
+    <t>846413858</t>
+  </si>
+  <si>
+    <t>845803216</t>
+  </si>
+  <si>
+    <t>271705703</t>
+  </si>
+  <si>
+    <t>784275640</t>
+  </si>
+  <si>
+    <t>801873732</t>
+  </si>
+  <si>
+    <t>272493416</t>
+  </si>
+  <si>
+    <t>265305668</t>
+  </si>
+  <si>
+    <t>271224895</t>
+  </si>
+  <si>
+    <t>271005658</t>
+  </si>
+  <si>
+    <t>270771508</t>
+  </si>
+  <si>
+    <t>270759172</t>
+  </si>
+  <si>
+    <t>270748894</t>
+  </si>
+  <si>
+    <t>270743820</t>
+  </si>
+  <si>
+    <t>270738754</t>
+  </si>
+  <si>
+    <t>270732799</t>
+  </si>
+  <si>
+    <t>270712643</t>
+  </si>
+  <si>
+    <t>270674819</t>
+  </si>
+  <si>
+    <t>268228404</t>
+  </si>
+  <si>
+    <t>265767446</t>
+  </si>
+  <si>
+    <t>263848701</t>
+  </si>
+  <si>
+    <t>262837606</t>
+  </si>
+  <si>
+    <t>253607182</t>
+  </si>
+  <si>
+    <t>261513869</t>
+  </si>
+  <si>
+    <t>262083656</t>
+  </si>
+  <si>
+    <t>260877760</t>
+  </si>
+  <si>
+    <t>260556059</t>
+  </si>
+  <si>
+    <t>258102940</t>
+  </si>
+  <si>
+    <t>256332168</t>
+  </si>
+  <si>
+    <t>238230191</t>
+  </si>
+  <si>
+    <t>245216233</t>
+  </si>
+  <si>
+    <t>244350199</t>
+  </si>
+  <si>
+    <t>243496845</t>
+  </si>
+  <si>
+    <t>210296491</t>
+  </si>
+  <si>
+    <t>212614279</t>
+  </si>
+  <si>
+    <t>215894324</t>
+  </si>
+  <si>
+    <t>215123237</t>
+  </si>
+  <si>
+    <t>212935039</t>
+  </si>
+  <si>
+    <t>191307218</t>
+  </si>
+  <si>
+    <t>964883528</t>
+  </si>
+  <si>
+    <t>956053841</t>
+  </si>
+  <si>
+    <t>954831040</t>
+  </si>
+  <si>
+    <t>920025370</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>953421652</t>
-  </si>
-  <si>
-    <t>252346998</t>
-  </si>
-  <si>
-    <t>949042125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>940020393</t>
-  </si>
-  <si>
-    <t>859919916</t>
-  </si>
-  <si>
-    <t>259468571</t>
-  </si>
-  <si>
-    <t>971473214</t>
-  </si>
-  <si>
-    <t>235354614</t>
-  </si>
-  <si>
-    <t>259428641</t>
-  </si>
-  <si>
-    <t>923456093</t>
-  </si>
-  <si>
-    <t>947297077</t>
-  </si>
-  <si>
-    <t>262917549</t>
-  </si>
-  <si>
-    <t>262713955</t>
-  </si>
-  <si>
-    <t>850817440</t>
-  </si>
-  <si>
-    <t>828952279</t>
-  </si>
-  <si>
-    <t>258623150</t>
-  </si>
-  <si>
-    <t>258222599</t>
-  </si>
-  <si>
-    <t>233390396</t>
-  </si>
-  <si>
-    <t>205341153</t>
+    <t>219001835</t>
+  </si>
+  <si>
+    <t>881717585</t>
+  </si>
+  <si>
+    <t>902145428</t>
+  </si>
+  <si>
+    <t>899348902</t>
+  </si>
+  <si>
+    <t>784688354</t>
+  </si>
+  <si>
+    <t>252503754</t>
+  </si>
+  <si>
+    <t>208498042</t>
+  </si>
+  <si>
+    <t>240052807</t>
+  </si>
+  <si>
+    <t>210001834</t>
+  </si>
+  <si>
+    <t>931275261</t>
+  </si>
+  <si>
+    <t>969816184</t>
+  </si>
+  <si>
+    <t>244588699</t>
+  </si>
+  <si>
+    <t>214158663</t>
+  </si>
+  <si>
+    <t>242236705</t>
+  </si>
+  <si>
+    <t>272133137</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>205797925</t>
-  </si>
-  <si>
-    <t>952450181</t>
-  </si>
-  <si>
-    <t>976361901</t>
-  </si>
-  <si>
-    <t>960720765</t>
-  </si>
-  <si>
-    <t>957548039</t>
-  </si>
-  <si>
-    <t>944771009</t>
-  </si>
-  <si>
-    <t>937175812</t>
-  </si>
-  <si>
-    <t>928291107</t>
-  </si>
-  <si>
-    <t>829635220</t>
-  </si>
-  <si>
-    <t>267015752</t>
-  </si>
-  <si>
-    <t>812486755</t>
-  </si>
-  <si>
-    <t>801331368</t>
-  </si>
-  <si>
-    <t>270697703</t>
-  </si>
-  <si>
-    <t>263409736</t>
-  </si>
-  <si>
-    <t>249960042</t>
-  </si>
-  <si>
-    <t>914161439</t>
-  </si>
-  <si>
-    <t>909423778</t>
-  </si>
-  <si>
-    <t>908077070</t>
-  </si>
-  <si>
-    <t>876954797</t>
-  </si>
-  <si>
-    <t>873714616</t>
-  </si>
-  <si>
-    <t>858730892</t>
-  </si>
-  <si>
-    <t>249867791</t>
-  </si>
-  <si>
-    <t>244360560</t>
-  </si>
-  <si>
-    <t>228349027</t>
-  </si>
-  <si>
-    <t>224205496</t>
-  </si>
-  <si>
-    <t>221239779</t>
-  </si>
-  <si>
-    <t>188564953</t>
-  </si>
-  <si>
-    <t>183249303</t>
-  </si>
-  <si>
-    <t>175222813</t>
-  </si>
-  <si>
-    <t>962470500</t>
-  </si>
-  <si>
-    <t>877348478</t>
-  </si>
-  <si>
-    <t>921443317</t>
-  </si>
-  <si>
-    <t>946223355</t>
-  </si>
-  <si>
-    <t>934444823</t>
-  </si>
-  <si>
-    <t>899838712</t>
-  </si>
-  <si>
-    <t>899100568</t>
-  </si>
-  <si>
-    <t>894644156</t>
-  </si>
-  <si>
-    <t>221165719</t>
-  </si>
-  <si>
-    <t>858727039</t>
-  </si>
-  <si>
-    <t>846500795</t>
-  </si>
-  <si>
-    <t>848278465</t>
-  </si>
-  <si>
-    <t>838101008</t>
-  </si>
-  <si>
-    <t>263439246</t>
-  </si>
-  <si>
-    <t>270663275</t>
-  </si>
-  <si>
-    <t>821678772</t>
-  </si>
-  <si>
-    <t>271427167</t>
-  </si>
-  <si>
-    <t>270944360</t>
-  </si>
-  <si>
-    <t>270843752</t>
-  </si>
-  <si>
-    <t>270816592</t>
-  </si>
-  <si>
-    <t>270750940</t>
-  </si>
-  <si>
-    <t>268181728</t>
-  </si>
-  <si>
-    <t>265804868</t>
-  </si>
-  <si>
-    <t>263800314</t>
-  </si>
-  <si>
-    <t>263316337</t>
-  </si>
-  <si>
-    <t>262779741</t>
-  </si>
-  <si>
-    <t>872888809</t>
-  </si>
-  <si>
-    <t>869786529</t>
-  </si>
-  <si>
-    <t>865112175</t>
-  </si>
-  <si>
-    <t>864659556</t>
-  </si>
-  <si>
-    <t>854964024</t>
-  </si>
-  <si>
-    <t>247445004</t>
-  </si>
-  <si>
-    <t>260130202</t>
-  </si>
-  <si>
-    <t>262137528</t>
-  </si>
-  <si>
-    <t>261506798</t>
-  </si>
-  <si>
-    <t>261284453</t>
-  </si>
-  <si>
-    <t>261276285</t>
-  </si>
-  <si>
-    <t>258648660</t>
-  </si>
-  <si>
-    <t>248148474</t>
-  </si>
-  <si>
-    <t>252304773</t>
-  </si>
-  <si>
-    <t>247970225</t>
-  </si>
-  <si>
-    <t>246386779</t>
-  </si>
-  <si>
-    <t>228588772</t>
-  </si>
-  <si>
-    <t>227752866</t>
-  </si>
-  <si>
-    <t>224064877</t>
-  </si>
-  <si>
-    <t>215898192</t>
-  </si>
-  <si>
-    <t>215366455</t>
-  </si>
-  <si>
-    <t>214879599</t>
-  </si>
-  <si>
-    <t>218246464</t>
-  </si>
-  <si>
-    <t>840618635</t>
-  </si>
-  <si>
-    <t>262226248</t>
-  </si>
-  <si>
-    <t>821806092</t>
-  </si>
-  <si>
-    <t>880736925</t>
-  </si>
-  <si>
-    <t>932648284</t>
-  </si>
-  <si>
-    <t>956089084</t>
-  </si>
-  <si>
-    <t>921769216</t>
-  </si>
-  <si>
-    <t>913258251</t>
-  </si>
-  <si>
-    <t>875034013</t>
-  </si>
-  <si>
-    <t>239703022</t>
-  </si>
-  <si>
-    <t>261048981</t>
-  </si>
-  <si>
-    <t>238457273</t>
-  </si>
-  <si>
-    <t>221359650</t>
-  </si>
-  <si>
-    <t>216944896</t>
-  </si>
-  <si>
-    <t>216355051</t>
-  </si>
-  <si>
-    <t>214262408</t>
-  </si>
-  <si>
-    <t>183163207</t>
-  </si>
-  <si>
-    <t>894577844</t>
-  </si>
-  <si>
-    <t>245181718</t>
-  </si>
-  <si>
-    <t>261503548</t>
-  </si>
-  <si>
-    <t>915042992</t>
-  </si>
-  <si>
-    <t>260762962</t>
-  </si>
-  <si>
-    <t>262413333</t>
-  </si>
-  <si>
-    <t>971125087</t>
-  </si>
-  <si>
-    <t>853725558</t>
-  </si>
-  <si>
-    <t>259420424</t>
-  </si>
-  <si>
-    <t>229849595</t>
-  </si>
-  <si>
-    <t>206003083</t>
-  </si>
-  <si>
-    <t>254751930</t>
-  </si>
-  <si>
-    <t>262370962</t>
-  </si>
-  <si>
-    <t>175600802</t>
-  </si>
-  <si>
-    <t>937127094</t>
-  </si>
-  <si>
-    <t>950738637</t>
-  </si>
-  <si>
-    <t>263271342</t>
-  </si>
-  <si>
-    <t>260633700</t>
-  </si>
-  <si>
-    <t>242999989</t>
-  </si>
-  <si>
-    <t>250154097</t>
-  </si>
-  <si>
-    <t>233408271</t>
-  </si>
-  <si>
-    <t>263070520</t>
-  </si>
-  <si>
-    <t>906964402</t>
-  </si>
-  <si>
-    <t>957454956</t>
-  </si>
-  <si>
-    <t>962326959</t>
-  </si>
-  <si>
-    <t>967349782</t>
-  </si>
-  <si>
-    <t>896409525</t>
-  </si>
-  <si>
-    <t>890045143</t>
-  </si>
-  <si>
-    <t>975005764</t>
-  </si>
-  <si>
-    <t>254347275</t>
-  </si>
-  <si>
-    <t>255052015</t>
-  </si>
-  <si>
-    <t>260865310</t>
-  </si>
-  <si>
-    <t>200214645</t>
-  </si>
-  <si>
-    <t>917488508</t>
-  </si>
-  <si>
-    <t>232870240</t>
-  </si>
-  <si>
-    <t>224849830</t>
-  </si>
-  <si>
-    <t>205586088</t>
-  </si>
-  <si>
-    <t>262960424</t>
-  </si>
-  <si>
-    <t>270790417</t>
-  </si>
-  <si>
-    <t>270844180</t>
+    <t>271806048</t>
+  </si>
+  <si>
+    <t>271754693</t>
+  </si>
+  <si>
+    <t>272940721</t>
   </si>
 </sst>
 </file>
@@ -985,7 +829,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D157"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -1026,7 +870,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -1035,7 +879,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>6</v>
@@ -1047,10 +891,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -1062,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -1071,10 +915,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1083,10 +927,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -1095,10 +939,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -1107,10 +951,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1119,10 +963,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1131,10 +975,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1143,10 +987,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1155,10 +999,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1167,10 +1011,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1179,10 +1023,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1191,10 +1035,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1203,10 +1047,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1215,10 +1059,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1227,10 +1071,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1239,10 +1083,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1251,10 +1095,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1263,10 +1107,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1119,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1131,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1143,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1311,10 +1155,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1323,7 +1167,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
@@ -1335,7 +1179,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
@@ -1347,7 +1191,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
@@ -1359,7 +1203,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
@@ -1371,7 +1215,7 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>6</v>
@@ -1383,7 +1227,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>6</v>
@@ -1395,7 +1239,7 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>6</v>
@@ -1407,7 +1251,7 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>6</v>
@@ -1419,7 +1263,7 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>6</v>
@@ -1431,7 +1275,7 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>6</v>
@@ -1443,7 +1287,7 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>6</v>
@@ -1455,7 +1299,7 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>6</v>
@@ -1467,7 +1311,7 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>6</v>
@@ -1479,7 +1323,7 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>6</v>
@@ -1491,7 +1335,7 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>6</v>
@@ -1503,7 +1347,7 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>6</v>
@@ -1515,7 +1359,7 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>6</v>
@@ -1527,7 +1371,7 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>6</v>
@@ -1539,7 +1383,7 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>6</v>
@@ -1551,7 +1395,7 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>6</v>
@@ -1563,7 +1407,7 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>6</v>
@@ -1575,7 +1419,7 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>6</v>
@@ -1587,7 +1431,7 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>6</v>
@@ -1599,7 +1443,7 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>6</v>
@@ -1611,10 +1455,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1623,10 +1467,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1635,10 +1479,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1647,10 +1491,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1659,10 +1503,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1671,10 +1515,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1683,10 +1527,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1695,10 +1539,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1707,10 +1551,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1719,10 +1563,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1731,10 +1575,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1743,10 +1587,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1755,10 +1599,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1767,10 +1611,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1779,10 +1623,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1791,10 +1635,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1802,10 +1646,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1813,10 +1657,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1824,10 +1668,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1835,10 +1679,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1846,10 +1690,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1857,10 +1701,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1868,10 +1712,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1879,10 +1723,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1890,10 +1734,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1901,10 +1745,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1912,10 +1756,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1923,10 +1767,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1934,10 +1778,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1945,10 +1789,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1956,10 +1800,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1967,10 +1811,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1978,10 +1822,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1989,10 +1833,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -2000,10 +1844,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -2011,10 +1855,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -2022,10 +1866,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -2033,10 +1877,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -2044,10 +1888,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -2055,10 +1899,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -2066,10 +1910,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -2077,10 +1921,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -2088,10 +1932,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>12</v>
+        <v>93</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -2099,10 +1943,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2110,10 +1954,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2121,10 +1965,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2132,10 +1976,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2143,10 +1987,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2154,10 +1998,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>4</v>
@@ -2165,10 +2009,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2176,10 +2020,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B102" s="5" t="s">
         <v>109</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>4</v>
@@ -2190,7 +2034,7 @@
         <v>110</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>8</v>
+        <v>109</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>4</v>
@@ -2201,7 +2045,7 @@
         <v>111</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>4</v>
@@ -2212,581 +2056,9 @@
         <v>112</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="B106" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B107" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B108" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="B109" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B110" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B111" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A112" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="B113" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="B115" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B117" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B118" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B119" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B120" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B121" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="B122" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B123" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C124" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A125" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B125" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C125" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A126" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="B126" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C126" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A127" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="B127" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C127" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A128" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="B128" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C128" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A129" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C129" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A130" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="B130" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C130" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B131" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A132" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="B132" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A133" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B133" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A134" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="B134" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A135" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="B135" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A136" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B136" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A137" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B137" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A138" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="B138" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="B139" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A140" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="B140" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="B141" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A142" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="B142" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B143" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A144" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="B144" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A145" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="B145" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A146" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="B146" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A147" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="B147" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C147" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A148" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B148" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C148" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A149" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="B149" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A150" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="B150" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A151" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="B151" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A152" s="4" t="s">
-        <v>159</v>
-      </c>
-      <c r="B152" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A153" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B153" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C153" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A154" s="4" t="s">
-        <v>161</v>
-      </c>
-      <c r="B154" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C154" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A155" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="B155" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A156" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A157" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="B157" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C157" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC125675-BF61-4C75-A245-8A685A3BA3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A080A7-473B-442D-94C4-05E039B78DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
   <si>
     <t>Status</t>
   </si>
@@ -48,328 +48,223 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>263943676</t>
+    <t>200689333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>232069561</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>262066180</t>
-  </si>
-  <si>
-    <t>211513092</t>
-  </si>
-  <si>
-    <t>209512478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>251581736</t>
-  </si>
-  <si>
-    <t>899272839</t>
-  </si>
-  <si>
-    <t>883139648</t>
-  </si>
-  <si>
-    <t>883139630</t>
-  </si>
-  <si>
-    <t>857001329</t>
-  </si>
-  <si>
-    <t>848412874</t>
-  </si>
-  <si>
-    <t>831863752</t>
-  </si>
-  <si>
-    <t>831863745</t>
-  </si>
-  <si>
-    <t>830320135</t>
-  </si>
-  <si>
-    <t>825971082</t>
-  </si>
-  <si>
-    <t>818312039</t>
-  </si>
-  <si>
-    <t>766190841</t>
-  </si>
-  <si>
-    <t>271637948</t>
-  </si>
-  <si>
-    <t>236610717</t>
-  </si>
-  <si>
-    <t>236608398</t>
-  </si>
-  <si>
-    <t>219293309</t>
-  </si>
-  <si>
-    <t>216136501</t>
-  </si>
-  <si>
-    <t>202379750</t>
-  </si>
-  <si>
-    <t>186920835</t>
-  </si>
-  <si>
-    <t>924209400</t>
-  </si>
-  <si>
-    <t>188745867</t>
-  </si>
-  <si>
-    <t>184652760</t>
-  </si>
-  <si>
-    <t>183783798</t>
-  </si>
-  <si>
-    <t>926094917</t>
-  </si>
-  <si>
-    <t>950864839</t>
-  </si>
-  <si>
-    <t>950847370</t>
-  </si>
-  <si>
-    <t>947169680</t>
-  </si>
-  <si>
-    <t>941651691</t>
-  </si>
-  <si>
-    <t>235042151</t>
-  </si>
-  <si>
-    <t>840787307</t>
-  </si>
-  <si>
-    <t>867225934</t>
-  </si>
-  <si>
-    <t>900815410</t>
-  </si>
-  <si>
-    <t>908794005</t>
-  </si>
-  <si>
-    <t>908204120</t>
-  </si>
-  <si>
-    <t>898020098</t>
-  </si>
-  <si>
-    <t>894138985</t>
-  </si>
-  <si>
-    <t>847644675</t>
-  </si>
-  <si>
-    <t>853060618</t>
-  </si>
-  <si>
-    <t>851291249</t>
-  </si>
-  <si>
-    <t>847451485</t>
-  </si>
-  <si>
-    <t>846413858</t>
-  </si>
-  <si>
-    <t>845803216</t>
-  </si>
-  <si>
-    <t>271705703</t>
-  </si>
-  <si>
-    <t>784275640</t>
-  </si>
-  <si>
-    <t>801873732</t>
-  </si>
-  <si>
-    <t>272493416</t>
-  </si>
-  <si>
-    <t>265305668</t>
-  </si>
-  <si>
-    <t>271224895</t>
-  </si>
-  <si>
-    <t>271005658</t>
-  </si>
-  <si>
-    <t>270771508</t>
-  </si>
-  <si>
-    <t>270759172</t>
-  </si>
-  <si>
-    <t>270748894</t>
-  </si>
-  <si>
-    <t>270743820</t>
-  </si>
-  <si>
-    <t>270738754</t>
-  </si>
-  <si>
-    <t>270732799</t>
-  </si>
-  <si>
-    <t>270712643</t>
-  </si>
-  <si>
-    <t>270674819</t>
-  </si>
-  <si>
-    <t>268228404</t>
-  </si>
-  <si>
-    <t>265767446</t>
-  </si>
-  <si>
-    <t>263848701</t>
-  </si>
-  <si>
-    <t>262837606</t>
-  </si>
-  <si>
-    <t>253607182</t>
-  </si>
-  <si>
-    <t>261513869</t>
-  </si>
-  <si>
-    <t>262083656</t>
-  </si>
-  <si>
-    <t>260877760</t>
-  </si>
-  <si>
-    <t>260556059</t>
-  </si>
-  <si>
-    <t>258102940</t>
-  </si>
-  <si>
-    <t>256332168</t>
-  </si>
-  <si>
-    <t>238230191</t>
-  </si>
-  <si>
-    <t>245216233</t>
-  </si>
-  <si>
-    <t>244350199</t>
-  </si>
-  <si>
-    <t>243496845</t>
-  </si>
-  <si>
-    <t>210296491</t>
-  </si>
-  <si>
-    <t>212614279</t>
-  </si>
-  <si>
-    <t>215894324</t>
-  </si>
-  <si>
-    <t>215123237</t>
-  </si>
-  <si>
-    <t>212935039</t>
-  </si>
-  <si>
-    <t>191307218</t>
-  </si>
-  <si>
-    <t>964883528</t>
-  </si>
-  <si>
-    <t>956053841</t>
-  </si>
-  <si>
-    <t>954831040</t>
-  </si>
-  <si>
-    <t>920025370</t>
+    <t>976012330</t>
+  </si>
+  <si>
+    <t>912084112</t>
+  </si>
+  <si>
+    <t>886303068</t>
+  </si>
+  <si>
+    <t>857001311</t>
+  </si>
+  <si>
+    <t>848833004</t>
+  </si>
+  <si>
+    <t>825746138</t>
+  </si>
+  <si>
+    <t>803234610</t>
+  </si>
+  <si>
+    <t>269362392</t>
+  </si>
+  <si>
+    <t>252860147</t>
+  </si>
+  <si>
+    <t>250213570</t>
+  </si>
+  <si>
+    <t>249930698</t>
+  </si>
+  <si>
+    <t>960818072</t>
+  </si>
+  <si>
+    <t>959387857</t>
+  </si>
+  <si>
+    <t>956145845</t>
+  </si>
+  <si>
+    <t>848503441</t>
+  </si>
+  <si>
+    <t>925410494</t>
+  </si>
+  <si>
+    <t>946581877</t>
+  </si>
+  <si>
+    <t>934345319</t>
+  </si>
+  <si>
+    <t>930833136</t>
+  </si>
+  <si>
+    <t>871137091</t>
+  </si>
+  <si>
+    <t>874608155</t>
+  </si>
+  <si>
+    <t>874357563</t>
+  </si>
+  <si>
+    <t>866897915</t>
+  </si>
+  <si>
+    <t>836855159</t>
+  </si>
+  <si>
+    <t>273313183</t>
+  </si>
+  <si>
+    <t>273283030</t>
+  </si>
+  <si>
+    <t>273162028</t>
+  </si>
+  <si>
+    <t>258098023</t>
+  </si>
+  <si>
+    <t>269604488</t>
+  </si>
+  <si>
+    <t>272860093</t>
+  </si>
+  <si>
+    <t>272854377</t>
+  </si>
+  <si>
+    <t>272816533</t>
+  </si>
+  <si>
+    <t>272754619</t>
+  </si>
+  <si>
+    <t>272745005</t>
+  </si>
+  <si>
+    <t>272558226</t>
+  </si>
+  <si>
+    <t>272414263</t>
+  </si>
+  <si>
+    <t>272256540</t>
+  </si>
+  <si>
+    <t>271932281</t>
+  </si>
+  <si>
+    <t>271604294</t>
+  </si>
+  <si>
+    <t>266237498</t>
+  </si>
+  <si>
+    <t>264628706</t>
+  </si>
+  <si>
+    <t>262163656</t>
+  </si>
+  <si>
+    <t>258829104</t>
+  </si>
+  <si>
+    <t>257538284</t>
+  </si>
+  <si>
+    <t>255276671</t>
+  </si>
+  <si>
+    <t>247344074</t>
+  </si>
+  <si>
+    <t>229314947</t>
+  </si>
+  <si>
+    <t>219686312</t>
+  </si>
+  <si>
+    <t>211946995</t>
+  </si>
+  <si>
+    <t>199466933</t>
+  </si>
+  <si>
+    <t>969685506</t>
+  </si>
+  <si>
+    <t>962793620</t>
+  </si>
+  <si>
+    <t>261468429</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>219001835</t>
-  </si>
-  <si>
-    <t>881717585</t>
-  </si>
-  <si>
-    <t>902145428</t>
-  </si>
-  <si>
-    <t>899348902</t>
-  </si>
-  <si>
-    <t>784688354</t>
-  </si>
-  <si>
-    <t>252503754</t>
-  </si>
-  <si>
-    <t>208498042</t>
-  </si>
-  <si>
-    <t>240052807</t>
-  </si>
-  <si>
-    <t>210001834</t>
-  </si>
-  <si>
-    <t>931275261</t>
-  </si>
-  <si>
-    <t>969816184</t>
-  </si>
-  <si>
-    <t>244588699</t>
-  </si>
-  <si>
-    <t>214158663</t>
-  </si>
-  <si>
-    <t>242236705</t>
-  </si>
-  <si>
-    <t>272133137</t>
+    <t>887195141</t>
+  </si>
+  <si>
+    <t>886507205</t>
+  </si>
+  <si>
+    <t>263591053</t>
+  </si>
+  <si>
+    <t>264330352</t>
+  </si>
+  <si>
+    <t>929817538</t>
+  </si>
+  <si>
+    <t>263461661</t>
+  </si>
+  <si>
+    <t>263220778</t>
+  </si>
+  <si>
+    <t>217537129</t>
+  </si>
+  <si>
+    <t>253912020</t>
+  </si>
+  <si>
+    <t>213110194</t>
+  </si>
+  <si>
+    <t>273366876</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>271806048</t>
+    <t>273189286</t>
   </si>
   <si>
     <t>271754693</t>
   </si>
   <si>
-    <t>272940721</t>
+    <t>273114276</t>
   </si>
 </sst>
 </file>
@@ -829,7 +724,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -870,7 +765,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -879,7 +774,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>6</v>
@@ -891,10 +786,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -906,7 +801,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -918,7 +813,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -930,7 +825,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -942,7 +837,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -954,7 +849,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -966,7 +861,7 @@
         <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -978,7 +873,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -990,7 +885,7 @@
         <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1002,7 +897,7 @@
         <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1014,7 +909,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1026,7 +921,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1038,7 +933,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1050,7 +945,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1062,7 +957,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1074,7 +969,7 @@
         <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1086,7 +981,7 @@
         <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1098,7 +993,7 @@
         <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1110,7 +1005,7 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1122,7 +1017,7 @@
         <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1134,7 +1029,7 @@
         <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1146,7 +1041,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1158,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1170,7 +1065,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1182,7 +1077,7 @@
         <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1194,7 +1089,7 @@
         <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1206,7 +1101,7 @@
         <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1218,7 +1113,7 @@
         <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1230,7 +1125,7 @@
         <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1242,7 +1137,7 @@
         <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1254,7 +1149,7 @@
         <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1266,7 +1161,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1278,7 +1173,7 @@
         <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1290,7 +1185,7 @@
         <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1302,7 +1197,7 @@
         <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1314,7 +1209,7 @@
         <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1326,7 +1221,7 @@
         <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1338,7 +1233,7 @@
         <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1350,7 +1245,7 @@
         <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1362,7 +1257,7 @@
         <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1374,7 +1269,7 @@
         <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1386,7 +1281,7 @@
         <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1398,7 +1293,7 @@
         <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1410,7 +1305,7 @@
         <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1422,7 +1317,7 @@
         <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1434,7 +1329,7 @@
         <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1446,7 +1341,7 @@
         <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1458,7 +1353,7 @@
         <v>57</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1470,7 +1365,7 @@
         <v>58</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1482,7 +1377,7 @@
         <v>59</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1494,7 +1389,7 @@
         <v>60</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1506,7 +1401,7 @@
         <v>61</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1515,10 +1410,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>62</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1527,10 +1422,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1539,10 +1434,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1551,7 +1446,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>6</v>
@@ -1563,7 +1458,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>6</v>
@@ -1575,7 +1470,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>6</v>
@@ -1587,10 +1482,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1599,10 +1494,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1611,10 +1506,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1623,10 +1518,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1635,10 +1530,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1646,10 +1541,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1657,7 +1552,7 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>6</v>
@@ -1668,397 +1563,12 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>6</v>
+        <v>62</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A71" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A72" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A73" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A75" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B99" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B100" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="B101" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="B102" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C102" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="B103" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="C103" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B104" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C104" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B105" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C105" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1A080A7-473B-442D-94C4-05E039B78DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8002B963-6444-4C02-93CF-26A1B8C438C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DescarteIncidencia" sheetId="3" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="106">
   <si>
     <t>Status</t>
   </si>
@@ -48,223 +48,307 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>200689333</t>
+    <t>265069918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>959918420</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>217489636</t>
+  </si>
+  <si>
+    <t>198553863</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>232069561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>976012330</t>
-  </si>
-  <si>
-    <t>912084112</t>
-  </si>
-  <si>
-    <t>886303068</t>
-  </si>
-  <si>
-    <t>857001311</t>
-  </si>
-  <si>
-    <t>848833004</t>
-  </si>
-  <si>
-    <t>825746138</t>
-  </si>
-  <si>
-    <t>803234610</t>
-  </si>
-  <si>
-    <t>269362392</t>
-  </si>
-  <si>
-    <t>252860147</t>
-  </si>
-  <si>
-    <t>250213570</t>
-  </si>
-  <si>
-    <t>249930698</t>
-  </si>
-  <si>
-    <t>960818072</t>
-  </si>
-  <si>
-    <t>959387857</t>
-  </si>
-  <si>
-    <t>956145845</t>
-  </si>
-  <si>
-    <t>848503441</t>
-  </si>
-  <si>
-    <t>925410494</t>
-  </si>
-  <si>
-    <t>946581877</t>
-  </si>
-  <si>
-    <t>934345319</t>
-  </si>
-  <si>
-    <t>930833136</t>
-  </si>
-  <si>
-    <t>871137091</t>
-  </si>
-  <si>
-    <t>874608155</t>
-  </si>
-  <si>
-    <t>874357563</t>
-  </si>
-  <si>
-    <t>866897915</t>
-  </si>
-  <si>
-    <t>836855159</t>
-  </si>
-  <si>
-    <t>273313183</t>
-  </si>
-  <si>
-    <t>273283030</t>
-  </si>
-  <si>
-    <t>273162028</t>
-  </si>
-  <si>
-    <t>258098023</t>
-  </si>
-  <si>
-    <t>269604488</t>
-  </si>
-  <si>
-    <t>272860093</t>
-  </si>
-  <si>
-    <t>272854377</t>
-  </si>
-  <si>
-    <t>272816533</t>
-  </si>
-  <si>
-    <t>272754619</t>
-  </si>
-  <si>
-    <t>272745005</t>
-  </si>
-  <si>
-    <t>272558226</t>
-  </si>
-  <si>
-    <t>272414263</t>
-  </si>
-  <si>
-    <t>272256540</t>
-  </si>
-  <si>
-    <t>271932281</t>
-  </si>
-  <si>
-    <t>271604294</t>
-  </si>
-  <si>
-    <t>266237498</t>
-  </si>
-  <si>
-    <t>264628706</t>
-  </si>
-  <si>
-    <t>262163656</t>
-  </si>
-  <si>
-    <t>258829104</t>
-  </si>
-  <si>
-    <t>257538284</t>
-  </si>
-  <si>
-    <t>255276671</t>
-  </si>
-  <si>
-    <t>247344074</t>
-  </si>
-  <si>
-    <t>229314947</t>
-  </si>
-  <si>
-    <t>219686312</t>
-  </si>
-  <si>
-    <t>211946995</t>
-  </si>
-  <si>
-    <t>199466933</t>
-  </si>
-  <si>
-    <t>969685506</t>
-  </si>
-  <si>
-    <t>962793620</t>
-  </si>
-  <si>
-    <t>261468429</t>
+    <t>273141832</t>
+  </si>
+  <si>
+    <t>903498057</t>
+  </si>
+  <si>
+    <t>901909568</t>
+  </si>
+  <si>
+    <t>874047388</t>
+  </si>
+  <si>
+    <t>845530793</t>
+  </si>
+  <si>
+    <t>833906906</t>
+  </si>
+  <si>
+    <t>273093017</t>
+  </si>
+  <si>
+    <t>973512639</t>
+  </si>
+  <si>
+    <t>968318885</t>
+  </si>
+  <si>
+    <t>925471512</t>
+  </si>
+  <si>
+    <t>273589907</t>
+  </si>
+  <si>
+    <t>274422801</t>
+  </si>
+  <si>
+    <t>274215098</t>
+  </si>
+  <si>
+    <t>274105455</t>
+  </si>
+  <si>
+    <t>274101157</t>
+  </si>
+  <si>
+    <t>273761191</t>
+  </si>
+  <si>
+    <t>272662382</t>
+  </si>
+  <si>
+    <t>272418207</t>
+  </si>
+  <si>
+    <t>272058086</t>
+  </si>
+  <si>
+    <t>271730552</t>
+  </si>
+  <si>
+    <t>265319677</t>
+  </si>
+  <si>
+    <t>271426854</t>
+  </si>
+  <si>
+    <t>269849943</t>
+  </si>
+  <si>
+    <t>268942129</t>
+  </si>
+  <si>
+    <t>268089061</t>
+  </si>
+  <si>
+    <t>264893771</t>
+  </si>
+  <si>
+    <t>264750757</t>
+  </si>
+  <si>
+    <t>263908448</t>
+  </si>
+  <si>
+    <t>257795231</t>
+  </si>
+  <si>
+    <t>248876645</t>
+  </si>
+  <si>
+    <t>247254232</t>
+  </si>
+  <si>
+    <t>222193892</t>
+  </si>
+  <si>
+    <t>215895297</t>
+  </si>
+  <si>
+    <t>950738744</t>
+  </si>
+  <si>
+    <t>960381154</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>887195141</t>
-  </si>
-  <si>
-    <t>886507205</t>
-  </si>
-  <si>
-    <t>263591053</t>
-  </si>
-  <si>
-    <t>264330352</t>
-  </si>
-  <si>
-    <t>929817538</t>
-  </si>
-  <si>
-    <t>263461661</t>
-  </si>
-  <si>
-    <t>263220778</t>
-  </si>
-  <si>
-    <t>217537129</t>
-  </si>
-  <si>
-    <t>253912020</t>
-  </si>
-  <si>
-    <t>213110194</t>
-  </si>
-  <si>
-    <t>273366876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
+    <t>821329731</t>
+  </si>
+  <si>
+    <t>887726085</t>
+  </si>
+  <si>
+    <t>901440903</t>
+  </si>
+  <si>
+    <t>217232663</t>
+  </si>
+  <si>
+    <t>235851320</t>
+  </si>
+  <si>
+    <t>226920241</t>
+  </si>
+  <si>
+    <t>220034957</t>
+  </si>
+  <si>
+    <t>199001904</t>
+  </si>
+  <si>
+    <t>195058189</t>
+  </si>
+  <si>
+    <t>959393525</t>
+  </si>
+  <si>
+    <t>958088670</t>
+  </si>
+  <si>
+    <t>956599199</t>
+  </si>
+  <si>
+    <t>944138027</t>
+  </si>
+  <si>
+    <t>932639424</t>
+  </si>
+  <si>
+    <t>263080842</t>
+  </si>
+  <si>
+    <t>230208013</t>
+  </si>
+  <si>
+    <t>259461139</t>
+  </si>
+  <si>
+    <t>273908248</t>
+  </si>
+  <si>
+    <t>896851957</t>
+  </si>
+  <si>
+    <t>878674625</t>
+  </si>
+  <si>
+    <t>960822462</t>
+  </si>
+  <si>
+    <t>960121436</t>
+  </si>
+  <si>
+    <t>946565086</t>
+  </si>
+  <si>
+    <t>931711844</t>
+  </si>
+  <si>
+    <t>930453331</t>
+  </si>
+  <si>
+    <t>872772565</t>
+  </si>
+  <si>
+    <t>861696445</t>
+  </si>
+  <si>
+    <t>849600196</t>
+  </si>
+  <si>
+    <t>849067552</t>
+  </si>
+  <si>
+    <t>827095401</t>
+  </si>
+  <si>
+    <t>275255382</t>
+  </si>
+  <si>
+    <t>275141772</t>
+  </si>
+  <si>
+    <t>274889157</t>
+  </si>
+  <si>
+    <t>274416217</t>
+  </si>
+  <si>
+    <t>273797393</t>
   </si>
   <si>
     <t>273189286</t>
   </si>
   <si>
-    <t>271754693</t>
-  </si>
-  <si>
-    <t>273114276</t>
+    <t>265313449</t>
+  </si>
+  <si>
+    <t>255286530</t>
+  </si>
+  <si>
+    <t>249638366</t>
+  </si>
+  <si>
+    <t>248939716</t>
+  </si>
+  <si>
+    <t>246086577</t>
+  </si>
+  <si>
+    <t>222753620</t>
+  </si>
+  <si>
+    <t>220115392</t>
+  </si>
+  <si>
+    <t>217907280</t>
+  </si>
+  <si>
+    <t>213695129</t>
+  </si>
+  <si>
+    <t>195603984</t>
+  </si>
+  <si>
+    <t>194407320</t>
+  </si>
+  <si>
+    <t>194361709</t>
+  </si>
+  <si>
+    <t>193874561</t>
+  </si>
+  <si>
+    <t>188743458</t>
+  </si>
+  <si>
+    <t>852671316</t>
+  </si>
+  <si>
+    <t>929519217</t>
+  </si>
+  <si>
+    <t>905023168</t>
+  </si>
+  <si>
+    <t>852953649</t>
+  </si>
+  <si>
+    <t>188506939</t>
+  </si>
+  <si>
+    <t>966029971</t>
+  </si>
+  <si>
+    <t>251286682</t>
+  </si>
+  <si>
+    <t>248884599</t>
   </si>
 </sst>
 </file>
@@ -724,7 +808,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:D98"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -777,7 +861,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -789,7 +873,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -798,10 +882,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -810,10 +894,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -822,10 +906,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -834,10 +918,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -846,10 +930,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -858,10 +942,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -870,10 +954,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -882,10 +966,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -894,7 +978,7 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>6</v>
@@ -906,7 +990,7 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>6</v>
@@ -918,7 +1002,7 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>6</v>
@@ -930,10 +1014,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -942,10 +1026,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -954,10 +1038,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -966,10 +1050,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -978,10 +1062,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -990,10 +1074,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1002,10 +1086,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1014,10 +1098,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1026,10 +1110,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1038,10 +1122,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1050,10 +1134,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1062,10 +1146,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1074,10 +1158,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1086,10 +1170,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1098,10 +1182,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1110,10 +1194,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1122,10 +1206,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1134,10 +1218,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1146,10 +1230,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1158,10 +1242,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1170,10 +1254,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1182,10 +1266,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1194,10 +1278,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1206,10 +1290,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1218,10 +1302,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1230,10 +1314,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>47</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1242,10 +1326,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1254,10 +1338,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1266,10 +1350,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1278,10 +1362,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1290,10 +1374,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1386,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1398,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1326,10 +1410,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1422,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1434,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1446,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1458,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1470,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1482,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1494,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1506,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1518,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>62</v>
+        <v>11</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1446,7 +1530,7 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>6</v>
@@ -1458,7 +1542,7 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>6</v>
@@ -1470,7 +1554,7 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>6</v>
@@ -1482,10 +1566,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1578,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1506,10 +1590,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1518,10 +1602,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1614,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1544,7 +1628,7 @@
         <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1566,9 +1650,317 @@
         <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>62</v>
+        <v>6</v>
       </c>
       <c r="C70" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8002B963-6444-4C02-93CF-26A1B8C438C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7306CFB8-3292-499C-87DB-131EBD712B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="101">
   <si>
     <t>Status</t>
   </si>
@@ -48,307 +48,292 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>265069918</t>
+    <t>867867081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>191212798</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>959918420</t>
+    <t>844110472</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>217489636</t>
-  </si>
-  <si>
-    <t>198553863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>273141832</t>
-  </si>
-  <si>
-    <t>903498057</t>
-  </si>
-  <si>
-    <t>901909568</t>
-  </si>
-  <si>
-    <t>874047388</t>
-  </si>
-  <si>
-    <t>845530793</t>
-  </si>
-  <si>
-    <t>833906906</t>
-  </si>
-  <si>
-    <t>273093017</t>
-  </si>
-  <si>
-    <t>973512639</t>
-  </si>
-  <si>
-    <t>968318885</t>
-  </si>
-  <si>
-    <t>925471512</t>
-  </si>
-  <si>
-    <t>273589907</t>
-  </si>
-  <si>
-    <t>274422801</t>
-  </si>
-  <si>
-    <t>274215098</t>
-  </si>
-  <si>
-    <t>274105455</t>
-  </si>
-  <si>
-    <t>274101157</t>
-  </si>
-  <si>
-    <t>273761191</t>
-  </si>
-  <si>
-    <t>272662382</t>
-  </si>
-  <si>
-    <t>272418207</t>
-  </si>
-  <si>
-    <t>272058086</t>
-  </si>
-  <si>
-    <t>271730552</t>
-  </si>
-  <si>
-    <t>265319677</t>
-  </si>
-  <si>
-    <t>271426854</t>
-  </si>
-  <si>
-    <t>269849943</t>
-  </si>
-  <si>
-    <t>268942129</t>
-  </si>
-  <si>
-    <t>268089061</t>
-  </si>
-  <si>
-    <t>264893771</t>
-  </si>
-  <si>
-    <t>264750757</t>
-  </si>
-  <si>
-    <t>263908448</t>
-  </si>
-  <si>
-    <t>257795231</t>
-  </si>
-  <si>
-    <t>248876645</t>
-  </si>
-  <si>
-    <t>247254232</t>
-  </si>
-  <si>
-    <t>222193892</t>
-  </si>
-  <si>
-    <t>215895297</t>
-  </si>
-  <si>
-    <t>950738744</t>
-  </si>
-  <si>
-    <t>960381154</t>
+    <t>266316953</t>
+  </si>
+  <si>
+    <t>192907248</t>
+  </si>
+  <si>
+    <t>255108650</t>
+  </si>
+  <si>
+    <t>253192839</t>
+  </si>
+  <si>
+    <t>241886898</t>
+  </si>
+  <si>
+    <t>175081227</t>
+  </si>
+  <si>
+    <t>959166434</t>
+  </si>
+  <si>
+    <t>953158072</t>
+  </si>
+  <si>
+    <t>913004689</t>
+  </si>
+  <si>
+    <t>900637293</t>
+  </si>
+  <si>
+    <t>875642112</t>
+  </si>
+  <si>
+    <t>821746199</t>
+  </si>
+  <si>
+    <t>271566592</t>
+  </si>
+  <si>
+    <t>270986734</t>
+  </si>
+  <si>
+    <t>974079174</t>
+  </si>
+  <si>
+    <t>265929046</t>
+  </si>
+  <si>
+    <t>266422165</t>
+  </si>
+  <si>
+    <t>221135340</t>
+  </si>
+  <si>
+    <t>252992924</t>
+  </si>
+  <si>
+    <t>264749924</t>
+  </si>
+  <si>
+    <t>260105311</t>
+  </si>
+  <si>
+    <t>244947291</t>
+  </si>
+  <si>
+    <t>218704918</t>
+  </si>
+  <si>
+    <t>214072161</t>
+  </si>
+  <si>
+    <t>213829462</t>
+  </si>
+  <si>
+    <t>204835346</t>
+  </si>
+  <si>
+    <t>193376351</t>
+  </si>
+  <si>
+    <t>200666935</t>
+  </si>
+  <si>
+    <t>198185567</t>
+  </si>
+  <si>
+    <t>197162880</t>
+  </si>
+  <si>
+    <t>951549744</t>
+  </si>
+  <si>
+    <t>957506854</t>
+  </si>
+  <si>
+    <t>955212356</t>
+  </si>
+  <si>
+    <t>948363506</t>
+  </si>
+  <si>
+    <t>942008404</t>
+  </si>
+  <si>
+    <t>932909512</t>
+  </si>
+  <si>
+    <t>931044386</t>
+  </si>
+  <si>
+    <t>928684798</t>
+  </si>
+  <si>
+    <t>849762095</t>
+  </si>
+  <si>
+    <t>827548607</t>
+  </si>
+  <si>
+    <t>819764196</t>
+  </si>
+  <si>
+    <t>826148219</t>
+  </si>
+  <si>
+    <t>826140828</t>
+  </si>
+  <si>
+    <t>823435080</t>
+  </si>
+  <si>
+    <t>803731151</t>
+  </si>
+  <si>
+    <t>275860660</t>
+  </si>
+  <si>
+    <t>274282486</t>
+  </si>
+  <si>
+    <t>273741706</t>
+  </si>
+  <si>
+    <t>273486096</t>
+  </si>
+  <si>
+    <t>273366876</t>
+  </si>
+  <si>
+    <t>272992797</t>
+  </si>
+  <si>
+    <t>270903721</t>
+  </si>
+  <si>
+    <t>270502101</t>
+  </si>
+  <si>
+    <t>267066649</t>
+  </si>
+  <si>
+    <t>266479033</t>
+  </si>
+  <si>
+    <t>827590369</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>821329731</t>
-  </si>
-  <si>
-    <t>887726085</t>
-  </si>
-  <si>
-    <t>901440903</t>
-  </si>
-  <si>
-    <t>217232663</t>
-  </si>
-  <si>
-    <t>235851320</t>
-  </si>
-  <si>
-    <t>226920241</t>
-  </si>
-  <si>
-    <t>220034957</t>
-  </si>
-  <si>
-    <t>199001904</t>
-  </si>
-  <si>
-    <t>195058189</t>
-  </si>
-  <si>
-    <t>959393525</t>
-  </si>
-  <si>
-    <t>958088670</t>
-  </si>
-  <si>
-    <t>956599199</t>
-  </si>
-  <si>
-    <t>944138027</t>
-  </si>
-  <si>
-    <t>932639424</t>
-  </si>
-  <si>
-    <t>263080842</t>
-  </si>
-  <si>
-    <t>230208013</t>
-  </si>
-  <si>
-    <t>259461139</t>
-  </si>
-  <si>
-    <t>273908248</t>
-  </si>
-  <si>
-    <t>896851957</t>
-  </si>
-  <si>
-    <t>878674625</t>
-  </si>
-  <si>
-    <t>960822462</t>
-  </si>
-  <si>
-    <t>960121436</t>
-  </si>
-  <si>
-    <t>946565086</t>
-  </si>
-  <si>
-    <t>931711844</t>
-  </si>
-  <si>
-    <t>930453331</t>
-  </si>
-  <si>
-    <t>872772565</t>
-  </si>
-  <si>
-    <t>861696445</t>
-  </si>
-  <si>
-    <t>849600196</t>
-  </si>
-  <si>
-    <t>849067552</t>
-  </si>
-  <si>
-    <t>827095401</t>
-  </si>
-  <si>
-    <t>275255382</t>
-  </si>
-  <si>
-    <t>275141772</t>
-  </si>
-  <si>
-    <t>274889157</t>
-  </si>
-  <si>
-    <t>274416217</t>
-  </si>
-  <si>
-    <t>273797393</t>
-  </si>
-  <si>
-    <t>273189286</t>
-  </si>
-  <si>
-    <t>265313449</t>
-  </si>
-  <si>
-    <t>255286530</t>
-  </si>
-  <si>
-    <t>249638366</t>
-  </si>
-  <si>
-    <t>248939716</t>
-  </si>
-  <si>
-    <t>246086577</t>
-  </si>
-  <si>
-    <t>222753620</t>
-  </si>
-  <si>
-    <t>220115392</t>
-  </si>
-  <si>
-    <t>217907280</t>
-  </si>
-  <si>
-    <t>213695129</t>
-  </si>
-  <si>
-    <t>195603984</t>
-  </si>
-  <si>
-    <t>194407320</t>
-  </si>
-  <si>
-    <t>194361709</t>
-  </si>
-  <si>
-    <t>193874561</t>
-  </si>
-  <si>
-    <t>188743458</t>
-  </si>
-  <si>
-    <t>852671316</t>
-  </si>
-  <si>
-    <t>929519217</t>
-  </si>
-  <si>
-    <t>905023168</t>
-  </si>
-  <si>
-    <t>852953649</t>
-  </si>
-  <si>
-    <t>188506939</t>
-  </si>
-  <si>
-    <t>966029971</t>
-  </si>
-  <si>
-    <t>251286682</t>
-  </si>
-  <si>
-    <t>248884599</t>
+    <t>179707942</t>
+  </si>
+  <si>
+    <t>238209245</t>
+  </si>
+  <si>
+    <t>179708361</t>
+  </si>
+  <si>
+    <t>904152810</t>
+  </si>
+  <si>
+    <t>849850528</t>
+  </si>
+  <si>
+    <t>266494321</t>
+  </si>
+  <si>
+    <t>924970670</t>
+  </si>
+  <si>
+    <t>911168122</t>
+  </si>
+  <si>
+    <t>903217564</t>
+  </si>
+  <si>
+    <t>844684898</t>
+  </si>
+  <si>
+    <t>898721471</t>
+  </si>
+  <si>
+    <t>931976686</t>
+  </si>
+  <si>
+    <t>910543473</t>
+  </si>
+  <si>
+    <t>963059427</t>
+  </si>
+  <si>
+    <t>210222794</t>
+  </si>
+  <si>
+    <t>867912788</t>
+  </si>
+  <si>
+    <t>186347302</t>
+  </si>
+  <si>
+    <t>217894983</t>
+  </si>
+  <si>
+    <t>232632053</t>
+  </si>
+  <si>
+    <t>193447079</t>
+  </si>
+  <si>
+    <t>266482466</t>
+  </si>
+  <si>
+    <t>244497685</t>
+  </si>
+  <si>
+    <t>262995222</t>
+  </si>
+  <si>
+    <t>264232889</t>
+  </si>
+  <si>
+    <t>205065232</t>
+  </si>
+  <si>
+    <t>960570889</t>
+  </si>
+  <si>
+    <t>869889141</t>
+  </si>
+  <si>
+    <t>913430454</t>
+  </si>
+  <si>
+    <t>252948363</t>
+  </si>
+  <si>
+    <t>253506533</t>
+  </si>
+  <si>
+    <t>275422164</t>
+  </si>
+  <si>
+    <t>275741944</t>
+  </si>
+  <si>
+    <t>275606956</t>
   </si>
 </sst>
 </file>
@@ -808,7 +793,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D98"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -861,7 +846,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -870,10 +855,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>10</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -885,7 +870,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -897,7 +882,7 @@
         <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -909,7 +894,7 @@
         <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -921,7 +906,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -933,7 +918,7 @@
         <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -945,7 +930,7 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -957,7 +942,7 @@
         <v>18</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -969,7 +954,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1029,7 +1014,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1041,7 +1026,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1053,7 +1038,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1065,7 +1050,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1077,7 +1062,7 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1089,7 +1074,7 @@
         <v>29</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1101,7 +1086,7 @@
         <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1113,7 +1098,7 @@
         <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1125,7 +1110,7 @@
         <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1137,7 +1122,7 @@
         <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1149,7 +1134,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1161,7 +1146,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1173,7 +1158,7 @@
         <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1185,7 +1170,7 @@
         <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1197,7 +1182,7 @@
         <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1209,7 +1194,7 @@
         <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1221,7 +1206,7 @@
         <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1233,7 +1218,7 @@
         <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1245,7 +1230,7 @@
         <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1257,7 +1242,7 @@
         <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1269,7 +1254,7 @@
         <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1281,7 +1266,7 @@
         <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1293,7 +1278,7 @@
         <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1302,10 +1287,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1314,10 +1299,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1326,10 +1311,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1338,10 +1323,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1350,10 +1335,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1362,10 +1347,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1374,10 +1359,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1386,10 +1371,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1398,10 +1383,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1410,10 +1395,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1422,10 +1407,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1434,10 +1419,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1446,10 +1431,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1458,10 +1443,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1470,10 +1455,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1482,10 +1467,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1494,10 +1479,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1506,7 +1491,7 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>8</v>
@@ -1518,10 +1503,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1530,10 +1515,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B60" s="5" t="s">
         <v>67</v>
-      </c>
-      <c r="B60" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1545,7 +1530,7 @@
         <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1557,7 +1542,7 @@
         <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1569,7 +1554,7 @@
         <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1581,7 +1566,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1593,7 +1578,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1605,7 +1590,7 @@
         <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1617,7 +1602,7 @@
         <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1683,7 +1668,7 @@
         <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1694,7 +1679,7 @@
         <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1705,7 +1690,7 @@
         <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1716,7 +1701,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1738,7 +1723,7 @@
         <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1749,7 +1734,7 @@
         <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1760,7 +1745,7 @@
         <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1771,7 +1756,7 @@
         <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1782,7 +1767,7 @@
         <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1793,7 +1778,7 @@
         <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1804,7 +1789,7 @@
         <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1815,7 +1800,7 @@
         <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1859,7 +1844,7 @@
         <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -1870,7 +1855,7 @@
         <v>97</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -1881,7 +1866,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -1892,7 +1877,7 @@
         <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -1903,64 +1888,9 @@
         <v>100</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B98" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C98" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7306CFB8-3292-499C-87DB-131EBD712B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1438ADB1-21ED-43DC-A2C0-7A3A45AD6746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="517" uniqueCount="180">
   <si>
     <t>Status</t>
   </si>
@@ -48,292 +48,529 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>867867081</t>
+    <t>198470340</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>198280046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
+  </si>
+  <si>
+    <t>265696553</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>191212798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>844110472</t>
+    <t>921151670</t>
+  </si>
+  <si>
+    <t>203363886</t>
+  </si>
+  <si>
+    <t>200888174</t>
+  </si>
+  <si>
+    <t>869299903</t>
+  </si>
+  <si>
+    <t>268311135</t>
+  </si>
+  <si>
+    <t>267151953</t>
+  </si>
+  <si>
+    <t>263220273</t>
+  </si>
+  <si>
+    <t>243448655</t>
+  </si>
+  <si>
+    <t>821780792</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>266316953</t>
-  </si>
-  <si>
-    <t>192907248</t>
-  </si>
-  <si>
-    <t>255108650</t>
-  </si>
-  <si>
-    <t>253192839</t>
-  </si>
-  <si>
-    <t>241886898</t>
-  </si>
-  <si>
-    <t>175081227</t>
-  </si>
-  <si>
-    <t>959166434</t>
-  </si>
-  <si>
-    <t>953158072</t>
-  </si>
-  <si>
-    <t>913004689</t>
-  </si>
-  <si>
-    <t>900637293</t>
-  </si>
-  <si>
-    <t>875642112</t>
-  </si>
-  <si>
-    <t>821746199</t>
-  </si>
-  <si>
-    <t>271566592</t>
-  </si>
-  <si>
-    <t>270986734</t>
-  </si>
-  <si>
-    <t>974079174</t>
-  </si>
-  <si>
-    <t>265929046</t>
-  </si>
-  <si>
-    <t>266422165</t>
-  </si>
-  <si>
-    <t>221135340</t>
-  </si>
-  <si>
-    <t>252992924</t>
-  </si>
-  <si>
-    <t>264749924</t>
-  </si>
-  <si>
-    <t>260105311</t>
-  </si>
-  <si>
-    <t>244947291</t>
-  </si>
-  <si>
-    <t>218704918</t>
-  </si>
-  <si>
-    <t>214072161</t>
-  </si>
-  <si>
-    <t>213829462</t>
-  </si>
-  <si>
-    <t>204835346</t>
-  </si>
-  <si>
-    <t>193376351</t>
-  </si>
-  <si>
-    <t>200666935</t>
-  </si>
-  <si>
-    <t>198185567</t>
-  </si>
-  <si>
-    <t>197162880</t>
-  </si>
-  <si>
-    <t>951549744</t>
-  </si>
-  <si>
-    <t>957506854</t>
-  </si>
-  <si>
-    <t>955212356</t>
-  </si>
-  <si>
-    <t>948363506</t>
-  </si>
-  <si>
-    <t>942008404</t>
-  </si>
-  <si>
-    <t>932909512</t>
-  </si>
-  <si>
-    <t>931044386</t>
-  </si>
-  <si>
-    <t>928684798</t>
-  </si>
-  <si>
-    <t>849762095</t>
-  </si>
-  <si>
-    <t>827548607</t>
-  </si>
-  <si>
-    <t>819764196</t>
-  </si>
-  <si>
-    <t>826148219</t>
-  </si>
-  <si>
-    <t>826140828</t>
-  </si>
-  <si>
-    <t>823435080</t>
-  </si>
-  <si>
-    <t>803731151</t>
-  </si>
-  <si>
-    <t>275860660</t>
-  </si>
-  <si>
-    <t>274282486</t>
-  </si>
-  <si>
-    <t>273741706</t>
-  </si>
-  <si>
-    <t>273486096</t>
-  </si>
-  <si>
-    <t>273366876</t>
-  </si>
-  <si>
-    <t>272992797</t>
-  </si>
-  <si>
-    <t>270903721</t>
-  </si>
-  <si>
-    <t>270502101</t>
-  </si>
-  <si>
-    <t>267066649</t>
-  </si>
-  <si>
-    <t>266479033</t>
-  </si>
-  <si>
-    <t>827590369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
-  </si>
-  <si>
-    <t>179707942</t>
-  </si>
-  <si>
-    <t>238209245</t>
-  </si>
-  <si>
-    <t>179708361</t>
-  </si>
-  <si>
-    <t>904152810</t>
-  </si>
-  <si>
-    <t>849850528</t>
-  </si>
-  <si>
-    <t>266494321</t>
-  </si>
-  <si>
-    <t>924970670</t>
-  </si>
-  <si>
-    <t>911168122</t>
-  </si>
-  <si>
-    <t>903217564</t>
-  </si>
-  <si>
-    <t>844684898</t>
-  </si>
-  <si>
-    <t>898721471</t>
-  </si>
-  <si>
-    <t>931976686</t>
-  </si>
-  <si>
-    <t>910543473</t>
-  </si>
-  <si>
-    <t>963059427</t>
-  </si>
-  <si>
-    <t>210222794</t>
-  </si>
-  <si>
-    <t>867912788</t>
-  </si>
-  <si>
-    <t>186347302</t>
-  </si>
-  <si>
-    <t>217894983</t>
-  </si>
-  <si>
-    <t>232632053</t>
-  </si>
-  <si>
-    <t>193447079</t>
-  </si>
-  <si>
-    <t>266482466</t>
-  </si>
-  <si>
-    <t>244497685</t>
-  </si>
-  <si>
-    <t>262995222</t>
-  </si>
-  <si>
-    <t>264232889</t>
-  </si>
-  <si>
-    <t>205065232</t>
-  </si>
-  <si>
-    <t>960570889</t>
-  </si>
-  <si>
-    <t>869889141</t>
-  </si>
-  <si>
-    <t>913430454</t>
-  </si>
-  <si>
-    <t>252948363</t>
-  </si>
-  <si>
-    <t>253506533</t>
+    <t>277034991</t>
+  </si>
+  <si>
+    <t>803437247</t>
+  </si>
+  <si>
+    <t>872854371</t>
+  </si>
+  <si>
+    <t>820021370</t>
+  </si>
+  <si>
+    <t>976036263</t>
+  </si>
+  <si>
+    <t>969642705</t>
+  </si>
+  <si>
+    <t>967659149</t>
+  </si>
+  <si>
+    <t>964303972</t>
+  </si>
+  <si>
+    <t>953593252</t>
+  </si>
+  <si>
+    <t>952844870</t>
+  </si>
+  <si>
+    <t>951024177</t>
+  </si>
+  <si>
+    <t>948425636</t>
+  </si>
+  <si>
+    <t>944771017</t>
+  </si>
+  <si>
+    <t>943659510</t>
+  </si>
+  <si>
+    <t>943057194</t>
+  </si>
+  <si>
+    <t>926961750</t>
+  </si>
+  <si>
+    <t>909622668</t>
+  </si>
+  <si>
+    <t>238578987</t>
+  </si>
+  <si>
+    <t>254337797</t>
+  </si>
+  <si>
+    <t>254132297</t>
+  </si>
+  <si>
+    <t>194597567</t>
+  </si>
+  <si>
+    <t>811235930</t>
+  </si>
+  <si>
+    <t>267052771</t>
+  </si>
+  <si>
+    <t>273715007</t>
+  </si>
+  <si>
+    <t>270791795</t>
+  </si>
+  <si>
+    <t>269923953</t>
+  </si>
+  <si>
+    <t>269452714</t>
+  </si>
+  <si>
+    <t>268748617</t>
+  </si>
+  <si>
+    <t>268450164</t>
+  </si>
+  <si>
+    <t>268440702</t>
+  </si>
+  <si>
+    <t>263364097</t>
+  </si>
+  <si>
+    <t>264026307</t>
+  </si>
+  <si>
+    <t>265177489</t>
+  </si>
+  <si>
+    <t>253107498</t>
+  </si>
+  <si>
+    <t>246770691</t>
+  </si>
+  <si>
+    <t>238321149</t>
+  </si>
+  <si>
+    <t>245175827</t>
+  </si>
+  <si>
+    <t>245522929</t>
+  </si>
+  <si>
+    <t>202065730</t>
+  </si>
+  <si>
+    <t>229823715</t>
+  </si>
+  <si>
+    <t>227507989</t>
+  </si>
+  <si>
+    <t>226917312</t>
+  </si>
+  <si>
+    <t>205865615</t>
+  </si>
+  <si>
+    <t>208639157</t>
+  </si>
+  <si>
+    <t>194992859</t>
+  </si>
+  <si>
+    <t>902130206</t>
+  </si>
+  <si>
+    <t>877106553</t>
+  </si>
+  <si>
+    <t>899204550</t>
+  </si>
+  <si>
+    <t>899126431</t>
+  </si>
+  <si>
+    <t>877785695</t>
+  </si>
+  <si>
+    <t>861999856</t>
+  </si>
+  <si>
+    <t>856454131</t>
+  </si>
+  <si>
+    <t>973270360</t>
+  </si>
+  <si>
+    <t>963154897</t>
+  </si>
+  <si>
+    <t>959814751</t>
+  </si>
+  <si>
+    <t>926991443</t>
+  </si>
+  <si>
+    <t>936706633</t>
+  </si>
+  <si>
+    <t>187242262</t>
+  </si>
+  <si>
+    <t>186412734</t>
+  </si>
+  <si>
+    <t>180002663</t>
+  </si>
+  <si>
+    <t>268248774</t>
+  </si>
+  <si>
+    <t>827417969</t>
+  </si>
+  <si>
+    <t>843304993</t>
+  </si>
+  <si>
+    <t>839979063</t>
+  </si>
+  <si>
+    <t>834626099</t>
+  </si>
+  <si>
+    <t>276945163</t>
+  </si>
+  <si>
+    <t>276939810</t>
+  </si>
+  <si>
+    <t>276629684</t>
+  </si>
+  <si>
+    <t>276138595</t>
+  </si>
+  <si>
+    <t>276108259</t>
+  </si>
+  <si>
+    <t>275426835</t>
   </si>
   <si>
     <t>275422164</t>
   </si>
   <si>
-    <t>275741944</t>
-  </si>
-  <si>
-    <t>275606956</t>
+    <t>275286627</t>
+  </si>
+  <si>
+    <t>274331127</t>
+  </si>
+  <si>
+    <t>269188409</t>
+  </si>
+  <si>
+    <t>269881391</t>
+  </si>
+  <si>
+    <t>274112501</t>
+  </si>
+  <si>
+    <t>272863964</t>
+  </si>
+  <si>
+    <t>272133137</t>
+  </si>
+  <si>
+    <t>269601997</t>
+  </si>
+  <si>
+    <t>268162793</t>
+  </si>
+  <si>
+    <t>267271090</t>
+  </si>
+  <si>
+    <t>267602658</t>
+  </si>
+  <si>
+    <t>267331191</t>
+  </si>
+  <si>
+    <t>267005084</t>
+  </si>
+  <si>
+    <t>266745086</t>
+  </si>
+  <si>
+    <t>266272859</t>
+  </si>
+  <si>
+    <t>259493124</t>
+  </si>
+  <si>
+    <t>256073077</t>
+  </si>
+  <si>
+    <t>256009626</t>
+  </si>
+  <si>
+    <t>259399529</t>
+  </si>
+  <si>
+    <t>262468352</t>
+  </si>
+  <si>
+    <t>962537019</t>
+  </si>
+  <si>
+    <t>964753945</t>
+  </si>
+  <si>
+    <t>936805716</t>
+  </si>
+  <si>
+    <t>903133712</t>
+  </si>
+  <si>
+    <t>904778275</t>
+  </si>
+  <si>
+    <t>854766999</t>
+  </si>
+  <si>
+    <t>901681209</t>
+  </si>
+  <si>
+    <t>885778468</t>
+  </si>
+  <si>
+    <t>880138544</t>
+  </si>
+  <si>
+    <t>930966332</t>
+  </si>
+  <si>
+    <t>237428291</t>
+  </si>
+  <si>
+    <t>253001345</t>
+  </si>
+  <si>
+    <t>253330215</t>
+  </si>
+  <si>
+    <t>196053866</t>
+  </si>
+  <si>
+    <t>226636961</t>
+  </si>
+  <si>
+    <t>222389425</t>
+  </si>
+  <si>
+    <t>213527033</t>
+  </si>
+  <si>
+    <t>212486058</t>
+  </si>
+  <si>
+    <t>195713569</t>
+  </si>
+  <si>
+    <t>267358772</t>
+  </si>
+  <si>
+    <t>829932452</t>
+  </si>
+  <si>
+    <t>829597685</t>
+  </si>
+  <si>
+    <t>824522225</t>
+  </si>
+  <si>
+    <t>269404590</t>
+  </si>
+  <si>
+    <t>268748450</t>
+  </si>
+  <si>
+    <t>268682691</t>
+  </si>
+  <si>
+    <t>267496556</t>
+  </si>
+  <si>
+    <t>247308772</t>
+  </si>
+  <si>
+    <t>829343833</t>
+  </si>
+  <si>
+    <t>921703371</t>
+  </si>
+  <si>
+    <t>856548452</t>
+  </si>
+  <si>
+    <t>937771115</t>
+  </si>
+  <si>
+    <t>920256488</t>
+  </si>
+  <si>
+    <t>225002785</t>
+  </si>
+  <si>
+    <t>228983346</t>
+  </si>
+  <si>
+    <t>247944097</t>
+  </si>
+  <si>
+    <t>907926624</t>
+  </si>
+  <si>
+    <t>900960067</t>
+  </si>
+  <si>
+    <t>975277371</t>
+  </si>
+  <si>
+    <t>192930109</t>
+  </si>
+  <si>
+    <t>268617069</t>
+  </si>
+  <si>
+    <t>209386253</t>
+  </si>
+  <si>
+    <t>188568574</t>
+  </si>
+  <si>
+    <t>974399945</t>
+  </si>
+  <si>
+    <t>954333666</t>
+  </si>
+  <si>
+    <t>894628969</t>
+  </si>
+  <si>
+    <t>246565919</t>
+  </si>
+  <si>
+    <t>224192884</t>
+  </si>
+  <si>
+    <t>184336190</t>
+  </si>
+  <si>
+    <t>269405654</t>
+  </si>
+  <si>
+    <t>267939456</t>
+  </si>
+  <si>
+    <t>267885774</t>
+  </si>
+  <si>
+    <t>972874675</t>
+  </si>
+  <si>
+    <t>946822578</t>
+  </si>
+  <si>
+    <t>262122389</t>
+  </si>
+  <si>
+    <t>266855125</t>
+  </si>
+  <si>
+    <t>964137347</t>
+  </si>
+  <si>
+    <t>863463109</t>
+  </si>
+  <si>
+    <t>220397081</t>
+  </si>
+  <si>
+    <t>196572196</t>
+  </si>
+  <si>
+    <t>267908006</t>
+  </si>
+  <si>
+    <t>267305526</t>
+  </si>
+  <si>
+    <t>266767502</t>
+  </si>
+  <si>
+    <t>230298246</t>
+  </si>
+  <si>
+    <t>266708456</t>
+  </si>
+  <si>
+    <t>277019893</t>
+  </si>
+  <si>
+    <t>277494260</t>
   </si>
 </sst>
 </file>
@@ -793,7 +1030,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D93"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -870,7 +1107,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -954,7 +1191,7 @@
         <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -963,10 +1200,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>20</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -975,10 +1212,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -987,10 +1224,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -999,10 +1236,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1011,10 +1248,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1023,10 +1260,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1035,10 +1272,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1047,10 +1284,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1059,10 +1296,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1071,10 +1308,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1083,10 +1320,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1095,10 +1332,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1107,10 +1344,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1119,10 +1356,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1131,10 +1368,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1143,10 +1380,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1155,10 +1392,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1167,10 +1404,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1179,10 +1416,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1191,10 +1428,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1203,10 +1440,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1215,10 +1452,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1227,10 +1464,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1239,10 +1476,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1251,10 +1488,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1263,10 +1500,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1275,10 +1512,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1287,10 +1524,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1299,10 +1536,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1311,10 +1548,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1323,10 +1560,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1335,10 +1572,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1347,10 +1584,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1359,10 +1596,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1371,10 +1608,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1383,10 +1620,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1395,10 +1632,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1407,10 +1644,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1419,10 +1656,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1431,10 +1668,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1443,10 +1680,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1455,10 +1692,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1467,10 +1704,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1479,10 +1716,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1491,10 +1728,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1503,10 +1740,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1515,10 +1752,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1530,7 +1767,7 @@
         <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1542,7 +1779,7 @@
         <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1554,7 +1791,7 @@
         <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1566,7 +1803,7 @@
         <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1578,7 +1815,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1590,7 +1827,7 @@
         <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1602,7 +1839,7 @@
         <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1668,7 +1905,7 @@
         <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1679,7 +1916,7 @@
         <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1690,7 +1927,7 @@
         <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1701,7 +1938,7 @@
         <v>83</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1723,7 +1960,7 @@
         <v>85</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1734,7 +1971,7 @@
         <v>86</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1745,7 +1982,7 @@
         <v>87</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1756,7 +1993,7 @@
         <v>88</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1767,7 +2004,7 @@
         <v>89</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1778,7 +2015,7 @@
         <v>90</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1789,7 +2026,7 @@
         <v>91</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1800,7 +2037,7 @@
         <v>92</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1844,7 +2081,7 @@
         <v>96</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -1855,7 +2092,7 @@
         <v>97</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -1866,7 +2103,7 @@
         <v>98</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -1877,7 +2114,7 @@
         <v>99</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -1888,9 +2125,878 @@
         <v>100</v>
       </c>
       <c r="B93" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C93" s="6" t="s">
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C165" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C166" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C169" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C170" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43A5448B-23C9-43D1-8F6D-D318AA808AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB548D67-82FF-4766-AB95-A503D0A9B8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="83">
   <si>
     <t>Status</t>
   </si>
@@ -48,298 +48,238 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>972633725</t>
+    <t>905838714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">????????                                               </t>
+  </si>
+  <si>
+    <t>889456731</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>969939283</t>
-  </si>
-  <si>
-    <t>957135720</t>
-  </si>
-  <si>
-    <t>949751741</t>
-  </si>
-  <si>
-    <t>936878077</t>
-  </si>
-  <si>
-    <t>936878069</t>
-  </si>
-  <si>
-    <t>924056421</t>
-  </si>
-  <si>
-    <t>916957404</t>
-  </si>
-  <si>
-    <t>259190480</t>
-  </si>
-  <si>
-    <t>257693360</t>
-  </si>
-  <si>
-    <t>256198817</t>
-  </si>
-  <si>
-    <t>256015227</t>
-  </si>
-  <si>
-    <t>254279874</t>
-  </si>
-  <si>
-    <t>207905708</t>
-  </si>
-  <si>
-    <t>182268536</t>
-  </si>
-  <si>
-    <t>182268528</t>
-  </si>
-  <si>
-    <t>865449643</t>
-  </si>
-  <si>
-    <t>267158594</t>
-  </si>
-  <si>
-    <t>830730432</t>
-  </si>
-  <si>
-    <t>825829884</t>
-  </si>
-  <si>
-    <t>819144936</t>
-  </si>
-  <si>
-    <t>807007848</t>
-  </si>
-  <si>
-    <t>971462704</t>
-  </si>
-  <si>
-    <t>968056881</t>
+    <t>174248462</t>
+  </si>
+  <si>
+    <t>259342180</t>
+  </si>
+  <si>
+    <t>256703947</t>
+  </si>
+  <si>
+    <t>244966838</t>
+  </si>
+  <si>
+    <t>203979178</t>
+  </si>
+  <si>
+    <t>203615988</t>
+  </si>
+  <si>
+    <t>200216269</t>
+  </si>
+  <si>
+    <t>186350603</t>
+  </si>
+  <si>
+    <t>182736656</t>
+  </si>
+  <si>
+    <t>889456723</t>
+  </si>
+  <si>
+    <t>883542734</t>
+  </si>
+  <si>
+    <t>883190963</t>
+  </si>
+  <si>
+    <t>821880162</t>
+  </si>
+  <si>
+    <t>278624998</t>
+  </si>
+  <si>
+    <t>278624980</t>
+  </si>
+  <si>
+    <t>278624972</t>
+  </si>
+  <si>
+    <t>278624964</t>
+  </si>
+  <si>
+    <t>278624956</t>
+  </si>
+  <si>
+    <t>278624949</t>
+  </si>
+  <si>
+    <t>272995626</t>
+  </si>
+  <si>
+    <t>965305117</t>
+  </si>
+  <si>
+    <t>961556374</t>
+  </si>
+  <si>
+    <t>957741535</t>
+  </si>
+  <si>
+    <t>976232441</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>251297887</t>
-  </si>
-  <si>
-    <t>261785855</t>
-  </si>
-  <si>
-    <t>266397201</t>
-  </si>
-  <si>
-    <t>265691802</t>
-  </si>
-  <si>
-    <t>262548450</t>
-  </si>
-  <si>
-    <t>234559973</t>
-  </si>
-  <si>
-    <t>230814638</t>
-  </si>
-  <si>
-    <t>225874399</t>
-  </si>
-  <si>
-    <t>224870786</t>
-  </si>
-  <si>
-    <t>221447885</t>
-  </si>
-  <si>
-    <t>209281769</t>
-  </si>
-  <si>
-    <t>188797934</t>
-  </si>
-  <si>
-    <t>814710913</t>
-  </si>
-  <si>
-    <t>934971965</t>
-  </si>
-  <si>
-    <t>942952411</t>
-  </si>
-  <si>
-    <t>958062915</t>
-  </si>
-  <si>
-    <t>960032328</t>
-  </si>
-  <si>
-    <t>958437166</t>
-  </si>
-  <si>
-    <t>957589140</t>
-  </si>
-  <si>
-    <t>934568308</t>
-  </si>
-  <si>
-    <t>927805410</t>
-  </si>
-  <si>
-    <t>905836064</t>
-  </si>
-  <si>
-    <t>903453847</t>
-  </si>
-  <si>
-    <t>879975419</t>
-  </si>
-  <si>
-    <t>879600306</t>
-  </si>
-  <si>
-    <t>877170013</t>
-  </si>
-  <si>
-    <t>852209323</t>
-  </si>
-  <si>
-    <t>850984463</t>
-  </si>
-  <si>
-    <t>849232891</t>
-  </si>
-  <si>
-    <t>786531776</t>
-  </si>
-  <si>
-    <t>786531768</t>
-  </si>
-  <si>
-    <t>276913799</t>
-  </si>
-  <si>
-    <t>276544008</t>
-  </si>
-  <si>
-    <t>275677825</t>
-  </si>
-  <si>
-    <t>275673758</t>
-  </si>
-  <si>
-    <t>275511677</t>
-  </si>
-  <si>
-    <t>274105760</t>
-  </si>
-  <si>
-    <t>274012206</t>
-  </si>
-  <si>
-    <t>274012198</t>
-  </si>
-  <si>
-    <t>269707935</t>
-  </si>
-  <si>
-    <t>268123084</t>
-  </si>
-  <si>
-    <t>267885105</t>
-  </si>
-  <si>
-    <t>975555412</t>
-  </si>
-  <si>
-    <t>965513751</t>
+    <t>276748831</t>
+  </si>
+  <si>
+    <t>277895391</t>
+  </si>
+  <si>
+    <t>271139978</t>
+  </si>
+  <si>
+    <t>271043535</t>
+  </si>
+  <si>
+    <t>268571472</t>
+  </si>
+  <si>
+    <t>206451472</t>
+  </si>
+  <si>
+    <t>259277550</t>
+  </si>
+  <si>
+    <t>266237704</t>
+  </si>
+  <si>
+    <t>260618214</t>
+  </si>
+  <si>
+    <t>260256320</t>
+  </si>
+  <si>
+    <t>233061195</t>
+  </si>
+  <si>
+    <t>195467836</t>
+  </si>
+  <si>
+    <t>199271861</t>
+  </si>
+  <si>
+    <t>197831823</t>
+  </si>
+  <si>
+    <t>194875476</t>
+  </si>
+  <si>
+    <t>194723551</t>
+  </si>
+  <si>
+    <t>880847284</t>
+  </si>
+  <si>
+    <t>888062092</t>
+  </si>
+  <si>
+    <t>922243856</t>
+  </si>
+  <si>
+    <t>880566025</t>
+  </si>
+  <si>
+    <t>868841051</t>
+  </si>
+  <si>
+    <t>862341611</t>
+  </si>
+  <si>
+    <t>855440719</t>
+  </si>
+  <si>
+    <t>830102293</t>
+  </si>
+  <si>
+    <t>279022911</t>
+  </si>
+  <si>
+    <t>278868272</t>
+  </si>
+  <si>
+    <t>809116894</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>234771636</t>
-  </si>
-  <si>
-    <t>262971629</t>
-  </si>
-  <si>
-    <t>264696810</t>
-  </si>
-  <si>
-    <t>193841024</t>
-  </si>
-  <si>
-    <t>193584996</t>
-  </si>
-  <si>
-    <t>269231449</t>
-  </si>
-  <si>
-    <t>932984218</t>
-  </si>
-  <si>
-    <t>962936179</t>
-  </si>
-  <si>
-    <t>948088384</t>
-  </si>
-  <si>
-    <t>270431186</t>
-  </si>
-  <si>
-    <t>973371903</t>
-  </si>
-  <si>
-    <t>849203074</t>
-  </si>
-  <si>
-    <t>269926857</t>
-  </si>
-  <si>
-    <t>265142954</t>
-  </si>
-  <si>
-    <t>176789638</t>
-  </si>
-  <si>
-    <t>269244236</t>
-  </si>
-  <si>
-    <t>269555607</t>
-  </si>
-  <si>
-    <t>231454699</t>
-  </si>
-  <si>
-    <t>270173424</t>
-  </si>
-  <si>
-    <t>946733536</t>
-  </si>
-  <si>
-    <t>264268420</t>
-  </si>
-  <si>
-    <t>264688866</t>
-  </si>
-  <si>
-    <t>267634321</t>
-  </si>
-  <si>
-    <t>256469812</t>
-  </si>
-  <si>
-    <t>277606061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>271754693</t>
+    <t>268532961</t>
+  </si>
+  <si>
+    <t>196278380</t>
+  </si>
+  <si>
+    <t>252072412</t>
+  </si>
+  <si>
+    <t>226507071</t>
+  </si>
+  <si>
+    <t>223695713</t>
+  </si>
+  <si>
+    <t>200823064</t>
+  </si>
+  <si>
+    <t>199885702</t>
+  </si>
+  <si>
+    <t>937916595</t>
+  </si>
+  <si>
+    <t>853448326</t>
+  </si>
+  <si>
+    <t>252313790</t>
+  </si>
+  <si>
+    <t>270501566</t>
+  </si>
+  <si>
+    <t>855943068</t>
+  </si>
+  <si>
+    <t>191741291</t>
+  </si>
+  <si>
+    <t>267057994</t>
+  </si>
+  <si>
+    <t>270235686</t>
+  </si>
+  <si>
+    <t>266770217</t>
+  </si>
+  <si>
+    <t>898823780</t>
+  </si>
+  <si>
+    <t>278787720</t>
+  </si>
+  <si>
+    <t>279557965</t>
+  </si>
+  <si>
+    <t>279382133</t>
+  </si>
+  <si>
+    <t>279373934</t>
   </si>
 </sst>
 </file>
@@ -799,7 +739,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -840,7 +780,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -849,10 +789,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -861,10 +801,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -873,10 +813,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -885,10 +825,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -897,10 +837,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -909,10 +849,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -921,10 +861,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -933,10 +873,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -945,10 +885,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -957,10 +897,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -969,10 +909,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -981,10 +921,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -993,10 +933,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1005,10 +945,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1017,10 +957,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1029,10 +969,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1041,10 +981,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1053,10 +993,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1065,10 +1005,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1077,10 +1017,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1089,10 +1029,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1101,10 +1041,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1116,7 +1056,7 @@
         <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1128,7 +1068,7 @@
         <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1137,10 +1077,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1149,10 +1089,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1101,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1173,10 +1113,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1185,10 +1125,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1197,10 +1137,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1209,10 +1149,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1221,10 +1161,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1233,10 +1173,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1245,10 +1185,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1257,10 +1197,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1269,10 +1209,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1281,10 +1221,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1293,10 +1233,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1305,10 +1245,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1317,10 +1257,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1329,10 +1269,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1341,10 +1281,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1353,10 +1293,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1365,10 +1305,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1377,10 +1317,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1389,10 +1329,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1401,10 +1341,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1413,10 +1353,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1425,10 +1365,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1437,10 +1377,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1449,10 +1389,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1461,10 +1401,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1473,10 +1413,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="B56" s="5" t="s">
-        <v>30</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1485,10 +1425,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1497,10 +1437,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1509,10 +1449,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1521,10 +1461,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1533,10 +1473,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1545,10 +1485,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1557,10 +1497,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>30</v>
+        <v>61</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1569,10 +1509,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1581,10 +1521,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1593,10 +1533,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1605,10 +1545,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1616,10 +1556,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1627,10 +1567,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1638,10 +1578,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1649,10 +1589,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>75</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1660,10 +1600,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1671,10 +1611,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1682,10 +1622,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1693,232 +1633,12 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A76" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A77" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A78" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A79" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A80" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB548D67-82FF-4766-AB95-A503D0A9B8D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B45EC7-24E3-4BE0-9AA9-EB1A00CBB18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="147">
   <si>
     <t>Status</t>
   </si>
@@ -48,238 +48,430 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>905838714</t>
+    <t>806043885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
+  </si>
+  <si>
+    <t>266791031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
+  </si>
+  <si>
+    <t>268744996</t>
+  </si>
+  <si>
+    <t>961560293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
+  </si>
+  <si>
+    <t>879454076</t>
+  </si>
+  <si>
+    <t>247937596</t>
+  </si>
+  <si>
+    <t>238426765</t>
+  </si>
+  <si>
+    <t>217976392</t>
+  </si>
+  <si>
+    <t>186696500</t>
+  </si>
+  <si>
+    <t>196133734</t>
   </si>
   <si>
     <t xml:space="preserve">????????                                               </t>
   </si>
   <si>
-    <t>889456731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
-  </si>
-  <si>
-    <t>174248462</t>
-  </si>
-  <si>
-    <t>259342180</t>
-  </si>
-  <si>
-    <t>256703947</t>
-  </si>
-  <si>
-    <t>244966838</t>
-  </si>
-  <si>
-    <t>203979178</t>
-  </si>
-  <si>
-    <t>203615988</t>
-  </si>
-  <si>
-    <t>200216269</t>
-  </si>
-  <si>
-    <t>186350603</t>
-  </si>
-  <si>
-    <t>182736656</t>
-  </si>
-  <si>
-    <t>889456723</t>
-  </si>
-  <si>
-    <t>883542734</t>
-  </si>
-  <si>
-    <t>883190963</t>
-  </si>
-  <si>
-    <t>821880162</t>
-  </si>
-  <si>
-    <t>278624998</t>
-  </si>
-  <si>
-    <t>278624980</t>
-  </si>
-  <si>
-    <t>278624972</t>
-  </si>
-  <si>
-    <t>278624964</t>
-  </si>
-  <si>
-    <t>278624956</t>
-  </si>
-  <si>
-    <t>278624949</t>
-  </si>
-  <si>
-    <t>272995626</t>
-  </si>
-  <si>
-    <t>965305117</t>
-  </si>
-  <si>
-    <t>961556374</t>
-  </si>
-  <si>
-    <t>957741535</t>
-  </si>
-  <si>
-    <t>976232441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
-  </si>
-  <si>
-    <t>276748831</t>
-  </si>
-  <si>
-    <t>277895391</t>
-  </si>
-  <si>
-    <t>271139978</t>
-  </si>
-  <si>
-    <t>271043535</t>
-  </si>
-  <si>
-    <t>268571472</t>
-  </si>
-  <si>
-    <t>206451472</t>
-  </si>
-  <si>
-    <t>259277550</t>
-  </si>
-  <si>
-    <t>266237704</t>
-  </si>
-  <si>
-    <t>260618214</t>
-  </si>
-  <si>
-    <t>260256320</t>
-  </si>
-  <si>
-    <t>233061195</t>
-  </si>
-  <si>
-    <t>195467836</t>
-  </si>
-  <si>
-    <t>199271861</t>
-  </si>
-  <si>
-    <t>197831823</t>
-  </si>
-  <si>
-    <t>194875476</t>
-  </si>
-  <si>
-    <t>194723551</t>
-  </si>
-  <si>
-    <t>880847284</t>
-  </si>
-  <si>
-    <t>888062092</t>
-  </si>
-  <si>
-    <t>922243856</t>
-  </si>
-  <si>
-    <t>880566025</t>
-  </si>
-  <si>
-    <t>868841051</t>
-  </si>
-  <si>
-    <t>862341611</t>
-  </si>
-  <si>
-    <t>855440719</t>
-  </si>
-  <si>
-    <t>830102293</t>
-  </si>
-  <si>
-    <t>279022911</t>
-  </si>
-  <si>
-    <t>278868272</t>
-  </si>
-  <si>
-    <t>809116894</t>
+    <t>198923991</t>
+  </si>
+  <si>
+    <t>227572314</t>
+  </si>
+  <si>
+    <t>241410574</t>
+  </si>
+  <si>
+    <t>254344660</t>
+  </si>
+  <si>
+    <t>207326731</t>
+  </si>
+  <si>
+    <t>878909641</t>
+  </si>
+  <si>
+    <t>977128739</t>
+  </si>
+  <si>
+    <t>176930455</t>
+  </si>
+  <si>
+    <t>960438996</t>
+  </si>
+  <si>
+    <t>942743364</t>
+  </si>
+  <si>
+    <t>924642303</t>
+  </si>
+  <si>
+    <t>891128591</t>
+  </si>
+  <si>
+    <t>870323809</t>
+  </si>
+  <si>
+    <t>819040969</t>
+  </si>
+  <si>
+    <t>773072065</t>
+  </si>
+  <si>
+    <t>277459743</t>
+  </si>
+  <si>
+    <t>276045519</t>
+  </si>
+  <si>
+    <t>262117967</t>
+  </si>
+  <si>
+    <t>260175041</t>
+  </si>
+  <si>
+    <t>870323791</t>
+  </si>
+  <si>
+    <t>865050532</t>
+  </si>
+  <si>
+    <t>853508962</t>
+  </si>
+  <si>
+    <t>200608861</t>
+  </si>
+  <si>
+    <t>217691629</t>
+  </si>
+  <si>
+    <t>197520319</t>
+  </si>
+  <si>
+    <t>194804252</t>
+  </si>
+  <si>
+    <t>194412114</t>
+  </si>
+  <si>
+    <t>852754336</t>
+  </si>
+  <si>
+    <t>280660873</t>
+  </si>
+  <si>
+    <t>280465141</t>
+  </si>
+  <si>
+    <t>265349310</t>
+  </si>
+  <si>
+    <t>271330544</t>
+  </si>
+  <si>
+    <t>279314235</t>
+  </si>
+  <si>
+    <t>280444203</t>
+  </si>
+  <si>
+    <t>280363510</t>
+  </si>
+  <si>
+    <t>280242664</t>
+  </si>
+  <si>
+    <t>279957058</t>
+  </si>
+  <si>
+    <t>277056127</t>
+  </si>
+  <si>
+    <t>276906660</t>
+  </si>
+  <si>
+    <t>270892353</t>
+  </si>
+  <si>
+    <t>270815081</t>
+  </si>
+  <si>
+    <t>270589272</t>
+  </si>
+  <si>
+    <t>268468497</t>
+  </si>
+  <si>
+    <t>267496929</t>
+  </si>
+  <si>
+    <t>264243753</t>
+  </si>
+  <si>
+    <t>256598545</t>
+  </si>
+  <si>
+    <t>253132348</t>
+  </si>
+  <si>
+    <t>239534542</t>
+  </si>
+  <si>
+    <t>248942827</t>
+  </si>
+  <si>
+    <t>223697891</t>
+  </si>
+  <si>
+    <t>238288454</t>
+  </si>
+  <si>
+    <t>229809086</t>
+  </si>
+  <si>
+    <t>259556557</t>
+  </si>
+  <si>
+    <t>895078685</t>
+  </si>
+  <si>
+    <t>938400201</t>
+  </si>
+  <si>
+    <t>937913808</t>
+  </si>
+  <si>
+    <t>932484938</t>
+  </si>
+  <si>
+    <t>924426038</t>
+  </si>
+  <si>
+    <t>906792399</t>
+  </si>
+  <si>
+    <t>922107341</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>268532961</t>
-  </si>
-  <si>
-    <t>196278380</t>
-  </si>
-  <si>
-    <t>252072412</t>
-  </si>
-  <si>
-    <t>226507071</t>
-  </si>
-  <si>
-    <t>223695713</t>
-  </si>
-  <si>
-    <t>200823064</t>
-  </si>
-  <si>
-    <t>199885702</t>
-  </si>
-  <si>
-    <t>937916595</t>
-  </si>
-  <si>
-    <t>853448326</t>
-  </si>
-  <si>
-    <t>252313790</t>
-  </si>
-  <si>
-    <t>270501566</t>
-  </si>
-  <si>
-    <t>855943068</t>
-  </si>
-  <si>
-    <t>191741291</t>
-  </si>
-  <si>
-    <t>267057994</t>
-  </si>
-  <si>
-    <t>270235686</t>
-  </si>
-  <si>
-    <t>266770217</t>
-  </si>
-  <si>
-    <t>898823780</t>
-  </si>
-  <si>
-    <t>278787720</t>
-  </si>
-  <si>
-    <t>279557965</t>
-  </si>
-  <si>
-    <t>279382133</t>
-  </si>
-  <si>
-    <t>279373934</t>
+    <t>250129404</t>
+  </si>
+  <si>
+    <t>247069283</t>
+  </si>
+  <si>
+    <t>225869894</t>
+  </si>
+  <si>
+    <t>197351715</t>
+  </si>
+  <si>
+    <t>200784548</t>
+  </si>
+  <si>
+    <t>201380684</t>
+  </si>
+  <si>
+    <t>209675036</t>
+  </si>
+  <si>
+    <t>265671697</t>
+  </si>
+  <si>
+    <t>280750492</t>
+  </si>
+  <si>
+    <t>854170176</t>
+  </si>
+  <si>
+    <t>840969277</t>
+  </si>
+  <si>
+    <t>830405779</t>
+  </si>
+  <si>
+    <t>831820349</t>
+  </si>
+  <si>
+    <t>271291365</t>
+  </si>
+  <si>
+    <t>938798927</t>
+  </si>
+  <si>
+    <t>969235278</t>
+  </si>
+  <si>
+    <t>964292084</t>
+  </si>
+  <si>
+    <t>876432364</t>
+  </si>
+  <si>
+    <t>883305074</t>
+  </si>
+  <si>
+    <t>851749790</t>
+  </si>
+  <si>
+    <t>213772183</t>
+  </si>
+  <si>
+    <t>214746509</t>
+  </si>
+  <si>
+    <t>234433963</t>
+  </si>
+  <si>
+    <t>851475107</t>
+  </si>
+  <si>
+    <t>905085019</t>
+  </si>
+  <si>
+    <t>186491381</t>
+  </si>
+  <si>
+    <t>178551127</t>
+  </si>
+  <si>
+    <t>270615044</t>
+  </si>
+  <si>
+    <t>840118651</t>
+  </si>
+  <si>
+    <t>212993855</t>
+  </si>
+  <si>
+    <t>200851800</t>
+  </si>
+  <si>
+    <t>210712745</t>
+  </si>
+  <si>
+    <t>927830418</t>
+  </si>
+  <si>
+    <t>961228107</t>
+  </si>
+  <si>
+    <t>227966011</t>
+  </si>
+  <si>
+    <t>961220708</t>
+  </si>
+  <si>
+    <t>208910160</t>
+  </si>
+  <si>
+    <t>271260394</t>
+  </si>
+  <si>
+    <t>270891959</t>
+  </si>
+  <si>
+    <t>830395434</t>
+  </si>
+  <si>
+    <t>818210456</t>
+  </si>
+  <si>
+    <t>227893652</t>
+  </si>
+  <si>
+    <t>253510139</t>
+  </si>
+  <si>
+    <t>270852779</t>
+  </si>
+  <si>
+    <t>260147990</t>
+  </si>
+  <si>
+    <t>270816808</t>
+  </si>
+  <si>
+    <t>280467972</t>
+  </si>
+  <si>
+    <t>279860302</t>
+  </si>
+  <si>
+    <t>279754042</t>
+  </si>
+  <si>
+    <t>908622032</t>
+  </si>
+  <si>
+    <t>889982793</t>
+  </si>
+  <si>
+    <t>907128890</t>
+  </si>
+  <si>
+    <t>971530781</t>
+  </si>
+  <si>
+    <t>933345013</t>
+  </si>
+  <si>
+    <t>933345005</t>
+  </si>
+  <si>
+    <t>929560435</t>
+  </si>
+  <si>
+    <t>281840797</t>
+  </si>
+  <si>
+    <t>267143794</t>
+  </si>
+  <si>
+    <t>262693108</t>
+  </si>
+  <si>
+    <t>247086436</t>
+  </si>
+  <si>
+    <t>241818735</t>
+  </si>
+  <si>
+    <t>224555213</t>
+  </si>
+  <si>
+    <t>200088981</t>
+  </si>
+  <si>
+    <t>199006648</t>
+  </si>
+  <si>
+    <t>853379232</t>
+  </si>
+  <si>
+    <t>282169824</t>
+  </si>
+  <si>
+    <t>276384355</t>
   </si>
 </sst>
 </file>
@@ -739,7 +931,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -804,7 +996,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -813,7 +1005,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>8</v>
@@ -825,7 +1017,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>8</v>
@@ -837,7 +1029,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>8</v>
@@ -849,7 +1041,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>8</v>
@@ -861,7 +1053,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>8</v>
@@ -873,10 +1065,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -885,10 +1077,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -897,10 +1089,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -909,10 +1101,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -921,10 +1113,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -933,10 +1125,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -945,10 +1137,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -957,10 +1149,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -969,10 +1161,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -981,10 +1173,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -993,10 +1185,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1005,10 +1197,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1017,10 +1209,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1029,10 +1221,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1041,10 +1233,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1053,10 +1245,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1065,10 +1257,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1077,10 +1269,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1089,10 +1281,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1101,10 +1293,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1113,10 +1305,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1125,10 +1317,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1137,10 +1329,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1149,10 +1341,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1161,10 +1353,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1173,10 +1365,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1185,10 +1377,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1197,10 +1389,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1209,10 +1401,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1221,10 +1413,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1233,10 +1425,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1245,10 +1437,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1257,10 +1449,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1269,10 +1461,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1281,10 +1473,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1293,10 +1485,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1305,10 +1497,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1317,10 +1509,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1329,10 +1521,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1341,10 +1533,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1353,10 +1545,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1365,10 +1557,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1377,10 +1569,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1389,10 +1581,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1404,7 +1596,7 @@
         <v>62</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1416,7 +1608,7 @@
         <v>63</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1428,7 +1620,7 @@
         <v>64</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1440,7 +1632,7 @@
         <v>65</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1452,7 +1644,7 @@
         <v>66</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1464,7 +1656,7 @@
         <v>67</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1476,7 +1668,7 @@
         <v>68</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1488,7 +1680,7 @@
         <v>69</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1500,7 +1692,7 @@
         <v>70</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1524,7 +1716,7 @@
         <v>72</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1536,7 +1728,7 @@
         <v>73</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1559,7 +1751,7 @@
         <v>75</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1570,7 +1762,7 @@
         <v>76</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1581,7 +1773,7 @@
         <v>77</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1592,7 +1784,7 @@
         <v>78</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1600,10 +1792,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>6</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1611,10 +1803,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1622,10 +1814,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1633,12 +1825,705 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="C75" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C138" s="6" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Treinamento/GestaoCreditoDescarteincidencias.xlsx
+++ b/Treinamento/GestaoCreditoDescarteincidencias.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Treinamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B45EC7-24E3-4BE0-9AA9-EB1A00CBB18B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71DC590-8186-41DF-9968-19DA3543D668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="79">
   <si>
     <t>Status</t>
   </si>
@@ -48,430 +48,226 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>806043885</t>
+    <t>177931981</t>
   </si>
   <si>
     <t xml:space="preserve">CANCELADO - ANALISAR SE DEVE SER DEVOLVIDO             </t>
   </si>
   <si>
-    <t>266791031</t>
+    <t>975657416</t>
+  </si>
+  <si>
+    <t>941059325</t>
+  </si>
+  <si>
+    <t>824744746</t>
+  </si>
+  <si>
+    <t>818042107</t>
+  </si>
+  <si>
+    <t>279423754</t>
+  </si>
+  <si>
+    <t>270973906</t>
+  </si>
+  <si>
+    <t>263666657</t>
+  </si>
+  <si>
+    <t>260592435</t>
+  </si>
+  <si>
+    <t>265835813</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - ANALISAR SE DEVE SER DEVOLVIDO           </t>
   </si>
   <si>
-    <t>268744996</t>
-  </si>
-  <si>
-    <t>961560293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAGO A MAIOR NÃO BAIXADO - BAIXAR MANUALMENTE          </t>
-  </si>
-  <si>
-    <t>879454076</t>
-  </si>
-  <si>
-    <t>247937596</t>
-  </si>
-  <si>
-    <t>238426765</t>
-  </si>
-  <si>
-    <t>217976392</t>
-  </si>
-  <si>
-    <t>186696500</t>
-  </si>
-  <si>
-    <t>196133734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">????????                                               </t>
-  </si>
-  <si>
-    <t>198923991</t>
-  </si>
-  <si>
-    <t>227572314</t>
-  </si>
-  <si>
-    <t>241410574</t>
-  </si>
-  <si>
-    <t>254344660</t>
-  </si>
-  <si>
-    <t>207326731</t>
-  </si>
-  <si>
-    <t>878909641</t>
-  </si>
-  <si>
-    <t>977128739</t>
-  </si>
-  <si>
-    <t>176930455</t>
-  </si>
-  <si>
-    <t>960438996</t>
-  </si>
-  <si>
-    <t>942743364</t>
-  </si>
-  <si>
-    <t>924642303</t>
-  </si>
-  <si>
-    <t>891128591</t>
-  </si>
-  <si>
-    <t>870323809</t>
-  </si>
-  <si>
-    <t>819040969</t>
-  </si>
-  <si>
-    <t>773072065</t>
-  </si>
-  <si>
-    <t>277459743</t>
-  </si>
-  <si>
-    <t>276045519</t>
-  </si>
-  <si>
-    <t>262117967</t>
-  </si>
-  <si>
-    <t>260175041</t>
-  </si>
-  <si>
-    <t>870323791</t>
-  </si>
-  <si>
-    <t>865050532</t>
-  </si>
-  <si>
-    <t>853508962</t>
-  </si>
-  <si>
-    <t>200608861</t>
-  </si>
-  <si>
-    <t>217691629</t>
-  </si>
-  <si>
-    <t>197520319</t>
-  </si>
-  <si>
-    <t>194804252</t>
-  </si>
-  <si>
-    <t>194412114</t>
-  </si>
-  <si>
-    <t>852754336</t>
-  </si>
-  <si>
-    <t>280660873</t>
-  </si>
-  <si>
-    <t>280465141</t>
-  </si>
-  <si>
-    <t>265349310</t>
-  </si>
-  <si>
-    <t>271330544</t>
-  </si>
-  <si>
-    <t>279314235</t>
-  </si>
-  <si>
-    <t>280444203</t>
-  </si>
-  <si>
-    <t>280363510</t>
-  </si>
-  <si>
-    <t>280242664</t>
-  </si>
-  <si>
-    <t>279957058</t>
-  </si>
-  <si>
-    <t>277056127</t>
-  </si>
-  <si>
-    <t>276906660</t>
-  </si>
-  <si>
-    <t>270892353</t>
-  </si>
-  <si>
-    <t>270815081</t>
-  </si>
-  <si>
-    <t>270589272</t>
-  </si>
-  <si>
-    <t>268468497</t>
-  </si>
-  <si>
-    <t>267496929</t>
-  </si>
-  <si>
-    <t>264243753</t>
-  </si>
-  <si>
-    <t>256598545</t>
-  </si>
-  <si>
-    <t>253132348</t>
-  </si>
-  <si>
-    <t>239534542</t>
-  </si>
-  <si>
-    <t>248942827</t>
-  </si>
-  <si>
-    <t>223697891</t>
-  </si>
-  <si>
-    <t>238288454</t>
-  </si>
-  <si>
-    <t>229809086</t>
-  </si>
-  <si>
-    <t>259556557</t>
-  </si>
-  <si>
-    <t>895078685</t>
-  </si>
-  <si>
-    <t>938400201</t>
-  </si>
-  <si>
-    <t>937913808</t>
-  </si>
-  <si>
-    <t>932484938</t>
-  </si>
-  <si>
-    <t>924426038</t>
-  </si>
-  <si>
-    <t>906792399</t>
-  </si>
-  <si>
-    <t>922107341</t>
+    <t>269381749</t>
+  </si>
+  <si>
+    <t>269053223</t>
+  </si>
+  <si>
+    <t>245924737</t>
+  </si>
+  <si>
+    <t>244713883</t>
+  </si>
+  <si>
+    <t>239854593</t>
+  </si>
+  <si>
+    <t>229234129</t>
+  </si>
+  <si>
+    <t>222152104</t>
+  </si>
+  <si>
+    <t>203469121</t>
+  </si>
+  <si>
+    <t>831124486</t>
+  </si>
+  <si>
+    <t>976787634</t>
+  </si>
+  <si>
+    <t>968509327</t>
+  </si>
+  <si>
+    <t>965321486</t>
+  </si>
+  <si>
+    <t>961949652</t>
+  </si>
+  <si>
+    <t>937648628</t>
+  </si>
+  <si>
+    <t>958840328</t>
+  </si>
+  <si>
+    <t>951024003</t>
+  </si>
+  <si>
+    <t>933853982</t>
+  </si>
+  <si>
+    <t>921776856</t>
+  </si>
+  <si>
+    <t>916881158</t>
+  </si>
+  <si>
+    <t>911537896</t>
+  </si>
+  <si>
+    <t>910620636</t>
+  </si>
+  <si>
+    <t>197895638</t>
+  </si>
+  <si>
+    <t>195250992</t>
+  </si>
+  <si>
+    <t>188142701</t>
+  </si>
+  <si>
+    <t>886374747</t>
+  </si>
+  <si>
+    <t>856370196</t>
+  </si>
+  <si>
+    <t>842253324</t>
+  </si>
+  <si>
+    <t>833247145</t>
+  </si>
+  <si>
+    <t>830556308</t>
+  </si>
+  <si>
+    <t>794047237</t>
+  </si>
+  <si>
+    <t>281784417</t>
+  </si>
+  <si>
+    <t>281649271</t>
+  </si>
+  <si>
+    <t>281003446</t>
+  </si>
+  <si>
+    <t>272392550</t>
+  </si>
+  <si>
+    <t>280591482</t>
+  </si>
+  <si>
+    <t>279945798</t>
+  </si>
+  <si>
+    <t>272390158</t>
+  </si>
+  <si>
+    <t>272135165</t>
+  </si>
+  <si>
+    <t>271790614</t>
+  </si>
+  <si>
+    <t>227697434</t>
   </si>
   <si>
     <t xml:space="preserve">DUPLICIDADE - CRÉDITO RECEBIDO EM D/C E BOLETO         </t>
   </si>
   <si>
-    <t>250129404</t>
-  </si>
-  <si>
-    <t>247069283</t>
-  </si>
-  <si>
-    <t>225869894</t>
-  </si>
-  <si>
-    <t>197351715</t>
-  </si>
-  <si>
-    <t>200784548</t>
-  </si>
-  <si>
-    <t>201380684</t>
-  </si>
-  <si>
-    <t>209675036</t>
-  </si>
-  <si>
-    <t>265671697</t>
-  </si>
-  <si>
-    <t>280750492</t>
-  </si>
-  <si>
-    <t>854170176</t>
-  </si>
-  <si>
-    <t>840969277</t>
-  </si>
-  <si>
-    <t>830405779</t>
-  </si>
-  <si>
-    <t>831820349</t>
-  </si>
-  <si>
-    <t>271291365</t>
-  </si>
-  <si>
-    <t>938798927</t>
-  </si>
-  <si>
-    <t>969235278</t>
-  </si>
-  <si>
-    <t>964292084</t>
-  </si>
-  <si>
-    <t>876432364</t>
-  </si>
-  <si>
-    <t>883305074</t>
-  </si>
-  <si>
-    <t>851749790</t>
-  </si>
-  <si>
-    <t>213772183</t>
-  </si>
-  <si>
-    <t>214746509</t>
-  </si>
-  <si>
-    <t>234433963</t>
-  </si>
-  <si>
-    <t>851475107</t>
-  </si>
-  <si>
-    <t>905085019</t>
-  </si>
-  <si>
-    <t>186491381</t>
-  </si>
-  <si>
-    <t>178551127</t>
-  </si>
-  <si>
-    <t>270615044</t>
-  </si>
-  <si>
-    <t>840118651</t>
-  </si>
-  <si>
-    <t>212993855</t>
-  </si>
-  <si>
-    <t>200851800</t>
-  </si>
-  <si>
-    <t>210712745</t>
-  </si>
-  <si>
-    <t>927830418</t>
-  </si>
-  <si>
-    <t>961228107</t>
-  </si>
-  <si>
-    <t>227966011</t>
-  </si>
-  <si>
-    <t>961220708</t>
-  </si>
-  <si>
-    <t>208910160</t>
-  </si>
-  <si>
-    <t>271260394</t>
-  </si>
-  <si>
-    <t>270891959</t>
-  </si>
-  <si>
-    <t>830395434</t>
-  </si>
-  <si>
-    <t>818210456</t>
-  </si>
-  <si>
-    <t>227893652</t>
-  </si>
-  <si>
-    <t>253510139</t>
-  </si>
-  <si>
-    <t>270852779</t>
-  </si>
-  <si>
-    <t>260147990</t>
-  </si>
-  <si>
-    <t>270816808</t>
-  </si>
-  <si>
-    <t>280467972</t>
-  </si>
-  <si>
-    <t>279860302</t>
-  </si>
-  <si>
-    <t>279754042</t>
-  </si>
-  <si>
-    <t>908622032</t>
-  </si>
-  <si>
-    <t>889982793</t>
-  </si>
-  <si>
-    <t>907128890</t>
-  </si>
-  <si>
-    <t>971530781</t>
-  </si>
-  <si>
-    <t>933345013</t>
-  </si>
-  <si>
-    <t>933345005</t>
-  </si>
-  <si>
-    <t>929560435</t>
-  </si>
-  <si>
-    <t>281840797</t>
-  </si>
-  <si>
-    <t>267143794</t>
-  </si>
-  <si>
-    <t>262693108</t>
-  </si>
-  <si>
-    <t>247086436</t>
-  </si>
-  <si>
-    <t>241818735</t>
-  </si>
-  <si>
-    <t>224555213</t>
-  </si>
-  <si>
-    <t>200088981</t>
-  </si>
-  <si>
-    <t>199006648</t>
-  </si>
-  <si>
-    <t>853379232</t>
-  </si>
-  <si>
-    <t>282169824</t>
-  </si>
-  <si>
-    <t>276384355</t>
+    <t>257938039</t>
+  </si>
+  <si>
+    <t>261830511</t>
+  </si>
+  <si>
+    <t>832742906</t>
+  </si>
+  <si>
+    <t>949183820</t>
+  </si>
+  <si>
+    <t>858855525</t>
+  </si>
+  <si>
+    <t>254542537</t>
+  </si>
+  <si>
+    <t>259614463</t>
+  </si>
+  <si>
+    <t>272177159</t>
+  </si>
+  <si>
+    <t>271448619</t>
+  </si>
+  <si>
+    <t>271739637</t>
+  </si>
+  <si>
+    <t>849172014</t>
+  </si>
+  <si>
+    <t>271247912</t>
+  </si>
+  <si>
+    <t>270454667</t>
+  </si>
+  <si>
+    <t>269005900</t>
+  </si>
+  <si>
+    <t>247131646</t>
+  </si>
+  <si>
+    <t>909977617</t>
+  </si>
+  <si>
+    <t>192838963</t>
+  </si>
+  <si>
+    <t>240400279</t>
+  </si>
+  <si>
+    <t>905674689</t>
+  </si>
+  <si>
+    <t>281506083</t>
+  </si>
+  <si>
+    <t>281691711</t>
   </si>
 </sst>
 </file>
@@ -931,7 +727,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:D138"/>
+  <dimension ref="A1:D143"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" style="4" customWidth="1" collapsed="1"/>
@@ -972,7 +768,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>4</v>
@@ -981,10 +777,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>4</v>
@@ -993,10 +789,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>4</v>
@@ -1005,10 +801,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>4</v>
@@ -1017,10 +813,10 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>4</v>
@@ -1029,10 +825,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>4</v>
@@ -1041,10 +837,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>4</v>
@@ -1053,10 +849,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>4</v>
@@ -1065,10 +861,10 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>4</v>
@@ -1077,10 +873,10 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>4</v>
@@ -1089,10 +885,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>4</v>
@@ -1101,10 +897,10 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>4</v>
@@ -1113,10 +909,10 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>4</v>
@@ -1125,10 +921,10 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>4</v>
@@ -1137,10 +933,10 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>4</v>
@@ -1149,10 +945,10 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>4</v>
@@ -1161,10 +957,10 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>4</v>
@@ -1173,10 +969,10 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>4</v>
@@ -1185,10 +981,10 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>4</v>
@@ -1197,10 +993,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>4</v>
@@ -1209,10 +1005,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>4</v>
@@ -1221,10 +1017,10 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>4</v>
@@ -1233,10 +1029,10 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>4</v>
@@ -1245,10 +1041,10 @@
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>4</v>
@@ -1257,10 +1053,10 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>4</v>
@@ -1269,10 +1065,10 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>4</v>
@@ -1281,10 +1077,10 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>4</v>
@@ -1293,10 +1089,10 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>4</v>
@@ -1305,10 +1101,10 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>4</v>
@@ -1317,10 +1113,10 @@
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>4</v>
@@ -1329,10 +1125,10 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>4</v>
@@ -1341,10 +1137,10 @@
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>4</v>
@@ -1353,10 +1149,10 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>4</v>
@@ -1365,10 +1161,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>4</v>
@@ -1377,10 +1173,10 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>4</v>
@@ -1389,10 +1185,10 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>4</v>
@@ -1401,10 +1197,10 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>4</v>
@@ -1413,10 +1209,10 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>4</v>
@@ -1425,10 +1221,10 @@
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>4</v>
@@ -1437,10 +1233,10 @@
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>4</v>
@@ -1449,10 +1245,10 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>4</v>
@@ -1461,10 +1257,10 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>4</v>
@@ -1473,10 +1269,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>4</v>
@@ -1485,10 +1281,10 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>4</v>
@@ -1497,10 +1293,10 @@
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>4</v>
@@ -1509,10 +1305,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>4</v>
@@ -1521,10 +1317,10 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>4</v>
@@ -1533,10 +1329,10 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>4</v>
@@ -1545,10 +1341,10 @@
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>4</v>
@@ -1557,10 +1353,10 @@
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>4</v>
@@ -1569,10 +1365,10 @@
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>4</v>
@@ -1581,10 +1377,10 @@
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>4</v>
@@ -1593,10 +1389,10 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>4</v>
@@ -1605,10 +1401,10 @@
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>4</v>
@@ -1617,10 +1413,10 @@
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>4</v>
@@ -1629,10 +1425,10 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>4</v>
@@ -1641,10 +1437,10 @@
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>4</v>
@@ -1653,10 +1449,10 @@
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>4</v>
@@ -1665,10 +1461,10 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>4</v>
@@ -1677,10 +1473,10 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>4</v>
@@ -1689,10 +1485,10 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>4</v>
@@ -1701,10 +1497,10 @@
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>4</v>
@@ -1713,10 +1509,10 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>4</v>
@@ -1725,10 +1521,10 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>4</v>
@@ -1737,10 +1533,10 @@
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>4</v>
@@ -1748,10 +1544,10 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>4</v>
@@ -1759,10 +1555,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>4</v>
@@ -1770,10 +1566,10 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>4</v>
@@ -1781,10 +1577,10 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>4</v>
@@ -1792,10 +1588,10 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>4</v>
@@ -1803,10 +1599,10 @@
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>81</v>
+        <v>5</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>4</v>
@@ -1814,10 +1610,10 @@
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>82</v>
+        <v>7</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>4</v>
@@ -1825,10 +1621,10 @@
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>83</v>
+        <v>8</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>4</v>
@@ -1836,10 +1632,10 @@
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>4</v>
@@ -1847,10 +1643,10 @@
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>4</v>
@@ -1858,10 +1654,10 @@
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>86</v>
+        <v>11</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>4</v>
@@ -1869,10 +1665,10 @@
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>87</v>
+        <v>12</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>4</v>
@@ -1880,10 +1676,10 @@
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>4</v>
@@ -1891,10 +1687,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>79</v>
+        <v>6</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>4</v>
@@ -1902,10 +1698,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>4</v>
@@ -1913,10 +1709,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>91</v>
+        <v>17</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>4</v>
@@ -1924,10 +1720,10 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>4</v>
@@ -1935,10 +1731,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>93</v>
+        <v>19</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>4</v>
@@ -1946,10 +1742,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>4</v>
@@ -1957,10 +1753,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>95</v>
+        <v>21</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>4</v>
@@ -1968,10 +1764,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>4</v>
@@ -1979,10 +1775,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>97</v>
+        <v>23</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>4</v>
@@ -1990,10 +1786,10 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>4</v>
@@ -2001,10 +1797,10 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>99</v>
+        <v>25</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>4</v>
@@ -2012,10 +1808,10 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>100</v>
+        <v>26</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>4</v>
@@ -2023,10 +1819,10 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>4</v>
@@ -2034,10 +1830,10 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>102</v>
+        <v>28</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>4</v>
@@ -2045,10 +1841,10 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>103</v>
+        <v>29</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>4</v>
@@ -2056,10 +1852,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>4</v>
@@ -2067,10 +1863,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>4</v>
@@ -2078,10 +1874,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>106</v>
+        <v>32</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>4</v>
@@ -2089,10 +1885,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>4</v>
@@ -2100,10 +1896,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>108</v>
+        <v>34</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>4</v>
@@ -2111,10 +1907,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>4</v>
@@ -2122,10 +1918,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>110</v>
+        <v>36</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>4</v>
@@ -2133,10 +1929,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>111</v>
+        <v>37</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>4</v>
@@ -2144,10 +1940,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>112</v>
+        <v>38</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>4</v>
@@ -2155,10 +1951,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>4</v>
@@ -2166,10 +1962,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>4</v>
@@ -2177,10 +1973,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>115</v>
+        <v>41</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>4</v>
@@ -2188,10 +1984,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>4</v>
@@ -2199,10 +1995,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>4</v>
@@ -2210,10 +2006,10 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>4</v>
@@ -2221,10 +2017,10 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>4</v>
@@ -2232,10 +2028,10 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>4</v>
@@ -2243,10 +2039,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>121</v>
+        <v>47</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>4</v>
@@ -2254,10 +2050,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>122</v>
+        <v>48</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>4</v>
@@ -2265,10 +2061,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>4</v>
@@ -2276,10 +2072,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>4</v>
@@ -2287,10 +2083,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>125</v>
+        <v>51</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>79</v>
+        <v>16</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>4</v>
@@ -2298,10 +2094,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>4</v>
@@ -2309,10 +2105,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>4</v>
@@ -2320,10 +2116,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>4</v>
@@ -2331,10 +2127,10 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>129</v>
+        <v>55</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>4</v>
@@ -2342,10 +2138,10 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>130</v>
+        <v>56</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>4</v>
@@ -2353,10 +2149,10 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>131</v>
+        <v>58</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>4</v>
@@ -2364,10 +2160,10 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>132</v>
+        <v>59</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>4</v>
@@ -2375,10 +2171,10 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>133</v>
+        <v>60</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>4</v>
@@ -2386,10 +2182,10 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>134</v>
+        <v>61</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>4</v>
@@ -2397,10 +2193,10 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>135</v>
+        <v>62</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>8</v>
+        <v>57</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>4</v>
@@ -2408,10 +2204,10 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>4</v>
@@ -2419,10 +2215,10 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>137</v>
+        <v>64</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>4</v>
@@ -2430,10 +2226,10 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>138</v>
+        <v>65</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>4</v>
@@ -2441,10 +2237,10 @@
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>4</v>
@@ -2452,10 +2248,10 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>140</v>
+        <v>67</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>4</v>
@@ -2463,10 +2259,10 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>141</v>
+        <v>68</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>4</v>
@@ -2474,10 +2270,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>4</v>
@@ -2485,10 +2281,10 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>4</v>
@@ -2496,10 +2292,10 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>144</v>
+        <v>71</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>4</v>
@@ -2507,10 +2303,10 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>4</v>
@@ -2518,12 +2314,67 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>146</v>
+        <v>73</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C138" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2550,31 +2401,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxiZTU0OTU1PC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTgvMDUvMjAyMCAyMzo1NzoxMzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxOC8wNS8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97A0AEE1-2848-4A72-BCE5-B9583B575AC3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CAB945F2-A4F0-4F66-8E00-009883594EA4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>